--- a/OutputData.xlsx
+++ b/OutputData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="6516"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -336,567 +336,807 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>44.250164910686614</v>
+        <v>288.93163556688495</v>
       </c>
       <c r="B1">
-        <v>110.87714077288388</v>
+        <v>171.03901749008958</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>44.486164599580327</v>
+        <v>290.01327970778453</v>
       </c>
       <c r="B2">
-        <v>110.69672835450844</v>
+        <v>170.92382177807178</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>44.893226863637445</v>
+        <v>290.95573218800115</v>
       </c>
       <c r="B3">
-        <v>110.29106816182096</v>
+        <v>170.83050221416391</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>45.209372008665085</v>
+        <v>291.74503516901581</v>
       </c>
       <c r="B4">
-        <v>109.97303266647125</v>
+        <v>170.71025460760009</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>45.456015693338102</v>
+        <v>292.67906081127381</v>
       </c>
       <c r="B5">
-        <v>109.85924735777243</v>
+        <v>170.70457912204631</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>45.769881654251073</v>
+        <v>293.56958486132413</v>
       </c>
       <c r="B6">
-        <v>109.60707392989109</v>
+        <v>170.61318774297439</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>46.061933522631783</v>
+        <v>294.51028794602036</v>
       </c>
       <c r="B7">
-        <v>109.21080246167421</v>
+        <v>170.44167317347399</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>46.370520955500098</v>
+        <v>295.37288462512231</v>
       </c>
       <c r="B8">
-        <v>108.91096350647148</v>
+        <v>170.22906780868121</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>46.630151439551575</v>
+        <v>296.16010466841624</v>
       </c>
       <c r="B9">
-        <v>108.50698851301884</v>
+        <v>170.06137134179917</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>46.963949898953572</v>
+        <v>297.00172190894108</v>
       </c>
       <c r="B10">
-        <v>108.09233826329655</v>
+        <v>169.97828183504802</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>47.19930606024019</v>
+        <v>297.97272513899082</v>
       </c>
       <c r="B11">
-        <v>107.73357679293316</v>
+        <v>169.85698221185564</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>47.493508912481204</v>
+        <v>298.95740130089115</v>
       </c>
       <c r="B12">
-        <v>107.41152135264531</v>
+        <v>169.80842192498253</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>47.675406486428841</v>
+        <v>299.83066287569392</v>
       </c>
       <c r="B13">
-        <v>107.11223611916779</v>
+        <v>169.68350043869748</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>48.00054581782063</v>
+        <v>300.70254365730887</v>
       </c>
       <c r="B14">
-        <v>106.8479669118457</v>
+        <v>169.58164330927394</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>48.260590764844125</v>
+        <v>301.68841279021734</v>
       </c>
       <c r="B15">
-        <v>106.45522288846719</v>
+        <v>169.50678871758601</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>48.601827639599072</v>
+        <v>302.64214623966768</v>
       </c>
       <c r="B16">
-        <v>106.21210575835859</v>
+        <v>169.47056324956907</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>48.914392017208172</v>
+        <v>303.63800305684305</v>
       </c>
       <c r="B17">
-        <v>105.77442912336451</v>
+        <v>169.48544841238902</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>49.150791277824084</v>
+        <v>304.51820863672344</v>
       </c>
       <c r="B18">
-        <v>105.53316899935075</v>
+        <v>169.60045609118552</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>49.531336024104526</v>
+        <v>305.4589286989571</v>
       </c>
       <c r="B19">
-        <v>105.22108877585106</v>
+        <v>169.46453515319129</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>49.769951820504588</v>
+        <v>306.38439687708768</v>
       </c>
       <c r="B20">
-        <v>104.95780997997778</v>
+        <v>169.34589609465027</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>49.969659203484696</v>
+        <v>307.38078222240421</v>
       </c>
       <c r="B21">
-        <v>104.72476944233044</v>
+        <v>169.29299412448583</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>50.223367877562289</v>
+        <v>308.34223329940824</v>
       </c>
       <c r="B22">
-        <v>104.55184264865963</v>
+        <v>169.23174727376667</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>50.596309711931141</v>
+        <v>309.22061202710773</v>
       </c>
       <c r="B23">
-        <v>104.31791695035486</v>
+        <v>169.07485954817267</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>50.924523611783087</v>
+        <v>310.11184827777515</v>
       </c>
       <c r="B24">
-        <v>104.01318162426806</v>
+        <v>168.98153025624634</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>51.271691657519568</v>
+        <v>310.96882726215972</v>
       </c>
       <c r="B25">
-        <v>103.64076440030831</v>
+        <v>168.97400544839377</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>51.513576445428008</v>
+        <v>311.90847985465774</v>
       </c>
       <c r="B26">
-        <v>103.3655892834728</v>
+        <v>168.8448192768476</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>51.811020105127987</v>
+        <v>312.81237386038384</v>
       </c>
       <c r="B27">
-        <v>103.1737784884964</v>
+        <v>168.66335631447282</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>52.18936190779889</v>
+        <v>313.69096201437469</v>
       </c>
       <c r="B28">
-        <v>102.82551779774202</v>
+        <v>168.58422594251601</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>52.533141115237846</v>
+        <v>314.68384781745073</v>
       </c>
       <c r="B29">
-        <v>102.43895520552989</v>
+        <v>168.36499038230735</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>52.82806703663249</v>
+        <v>315.60151064479652</v>
       </c>
       <c r="B30">
-        <v>102.15004041483562</v>
+        <v>168.31333815641352</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>53.090455948707216</v>
+        <v>316.54406301768523</v>
       </c>
       <c r="B31">
-        <v>101.80750624453671</v>
+        <v>168.24345352360598</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>53.269300371808953</v>
+        <v>317.4190361305474</v>
       </c>
       <c r="B32">
-        <v>101.39115255214161</v>
+        <v>168.16652898127694</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>53.606763781828377</v>
+        <v>318.1989459807121</v>
       </c>
       <c r="B33">
-        <v>101.15170217454897</v>
+        <v>168.03956713316785</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>53.895485496588712</v>
+        <v>319.15310377465238</v>
       </c>
       <c r="B34">
-        <v>100.84857796224283</v>
+        <v>167.84942806860738</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>54.159869376270109</v>
+        <v>320.06822532325583</v>
       </c>
       <c r="B35">
-        <v>100.45712813388469</v>
+        <v>167.78019786349657</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>54.522786731145523</v>
+        <v>320.92620463622211</v>
       </c>
       <c r="B36">
-        <v>100.08172243356864</v>
+        <v>167.69104264413866</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>54.864510832369149</v>
+        <v>321.89472446852784</v>
       </c>
       <c r="B37">
-        <v>99.757091697191029</v>
+        <v>167.75145719143532</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>55.195402572657663</v>
+        <v>322.89717652120959</v>
       </c>
       <c r="B38">
-        <v>99.42113985675725</v>
+        <v>167.68261060635578</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>55.516392421298207</v>
+        <v>323.75883354964378</v>
       </c>
       <c r="B39">
-        <v>99.190721977120205</v>
+        <v>167.58795308322433</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>55.757809726852273</v>
+        <v>324.61235130704659</v>
       </c>
       <c r="B40">
-        <v>98.842069911940101</v>
+        <v>167.40778211667268</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>55.892139477355286</v>
+        <v>325.73509742123923</v>
       </c>
       <c r="B41">
-        <v>98.460257905626719</v>
+        <v>167.42257826888863</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>56.205042539025399</v>
+        <v>326.65368743753646</v>
       </c>
       <c r="B42">
-        <v>98.180576118256084</v>
+        <v>167.25307641118204</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>56.331014660420372</v>
+        <v>327.52367682210161</v>
       </c>
       <c r="B43">
-        <v>97.963945561495706</v>
+        <v>167.10646623681956</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>56.654973587943516</v>
+        <v>328.44126543738258</v>
       </c>
       <c r="B44">
-        <v>97.655074758976667</v>
+        <v>167.1355687755167</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>57.033373177426661</v>
+        <v>329.36175920416377</v>
       </c>
       <c r="B45">
-        <v>97.279209061366672</v>
+        <v>167.05066194128892</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>57.365813814225135</v>
+        <v>330.25290432501788</v>
       </c>
       <c r="B46">
-        <v>96.976693107029504</v>
+        <v>167.02556186108868</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>57.671985372367274</v>
+        <v>331.16024574679295</v>
       </c>
       <c r="B47">
-        <v>96.68839546408708</v>
+        <v>166.94729802095961</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>57.945064590833773</v>
+        <v>332.1046076906897</v>
       </c>
       <c r="B48">
-        <v>96.4053259145266</v>
+        <v>166.89526514275713</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>58.124331911898565</v>
+        <v>332.99369487830381</v>
       </c>
       <c r="B49">
-        <v>96.161184841401862</v>
+        <v>166.75102456401714</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>58.32439634731238</v>
+        <v>333.79530567885223</v>
       </c>
       <c r="B50">
-        <v>95.887457863633699</v>
+        <v>166.65850354482299</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>58.780569241903137</v>
+        <v>334.67098968490615</v>
       </c>
       <c r="B51">
-        <v>95.615049080157249</v>
+        <v>166.49122904639728</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>59.113267153872897</v>
+        <v>335.5603144188579</v>
       </c>
       <c r="B52">
-        <v>95.211970593564615</v>
+        <v>166.49410774513427</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>59.357466475154368</v>
+        <v>336.44601058220093</v>
       </c>
       <c r="B53">
-        <v>94.904495821170912</v>
+        <v>166.51892661417668</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>59.727711376041036</v>
+        <v>337.47315138804476</v>
       </c>
       <c r="B54">
-        <v>94.477781563836203</v>
+        <v>166.50715893511256</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>60.143628736160871</v>
+        <v>338.40664842868961</v>
       </c>
       <c r="B55">
-        <v>94.027421081629328</v>
+        <v>166.36432964735914</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>60.463641013346525</v>
+        <v>339.32545683648834</v>
       </c>
       <c r="B56">
-        <v>93.868302136548806</v>
+        <v>166.25005556642628</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>60.801989332556253</v>
+        <v>340.23941395034876</v>
       </c>
       <c r="B57">
-        <v>93.651229222685686</v>
+        <v>166.14407750742723</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>61.037622374306032</v>
+        <v>341.1532789769534</v>
       </c>
       <c r="B58">
-        <v>93.314173036075218</v>
+        <v>166.05455850944759</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>61.36836971708221</v>
+        <v>342.06794878712066</v>
       </c>
       <c r="B59">
-        <v>93.018422033296332</v>
+        <v>166.10272725619066</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>61.600321056318961</v>
+        <v>343.13558912153974</v>
       </c>
       <c r="B60">
-        <v>92.548016668251094</v>
+        <v>166.00565738734272</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>61.925102825381607</v>
+        <v>344.06153965779606</v>
       </c>
       <c r="B61">
-        <v>92.341446079391474</v>
+        <v>165.90503145602869</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>62.219572271133444</v>
+        <v>344.9796979550585</v>
       </c>
       <c r="B62">
-        <v>92.14023532202178</v>
+        <v>165.82230048585276</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>62.541902998554256</v>
+        <v>345.78102212968281</v>
       </c>
       <c r="B63">
-        <v>91.683484931641317</v>
+        <v>165.72073968933287</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>62.85127082333377</v>
+        <v>346.74403419194078</v>
       </c>
       <c r="B64">
-        <v>91.33841807281874</v>
+        <v>165.60461970851614</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>63.130002639303349</v>
+        <v>347.71335705426361</v>
       </c>
       <c r="B65">
-        <v>91.034736441808505</v>
+        <v>165.6293861494801</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>63.609552628787604</v>
+        <v>348.59807535739259</v>
       </c>
       <c r="B66">
-        <v>90.738446310135089</v>
+        <v>165.61824655471102</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>63.817162132701647</v>
+        <v>349.60421458743821</v>
       </c>
       <c r="B67">
-        <v>90.448941899700301</v>
+        <v>165.50143101541036</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>64.099288595582635</v>
+        <v>350.4718764127233</v>
       </c>
       <c r="B68">
-        <v>90.162892105956232</v>
+        <v>165.42566339112278</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>64.406674854477572</v>
+        <v>351.52983782160982</v>
       </c>
       <c r="B69">
-        <v>89.783220073321871</v>
+        <v>165.29131440860709</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>64.593890965929546</v>
+        <v>352.43113269267036</v>
       </c>
       <c r="B70">
-        <v>89.386298581391245</v>
+        <v>165.11996611048949</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>353.23954318074635</v>
+      </c>
+      <c r="B71">
+        <v>165.02232349406719</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>353.96358576522243</v>
+      </c>
+      <c r="B72">
+        <v>164.96298210062227</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>354.83322317259797</v>
+      </c>
+      <c r="B73">
+        <v>164.88597432842676</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>355.7565301237758</v>
+      </c>
+      <c r="B74">
+        <v>164.76462845840501</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>356.70360286711292</v>
+      </c>
+      <c r="B75">
+        <v>164.59988258865604</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>357.60329447952188</v>
+      </c>
+      <c r="B76">
+        <v>164.51900347409025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>358.5204000608943</v>
+      </c>
+      <c r="B77">
+        <v>164.34086878690255</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>359.36437955915346</v>
+      </c>
+      <c r="B78">
+        <v>164.32722507647256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>360.37093375524495</v>
+      </c>
+      <c r="B79">
+        <v>164.28907165490213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>361.21361786806477</v>
+      </c>
+      <c r="B80">
+        <v>164.24297329268225</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>362.20602482284943</v>
+      </c>
+      <c r="B81">
+        <v>164.15926322118827</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>363.13947911260919</v>
+      </c>
+      <c r="B82">
+        <v>164.07314991379391</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>363.94127026898559</v>
+      </c>
+      <c r="B83">
+        <v>163.80414609189049</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>364.89267379734656</v>
+      </c>
+      <c r="B84">
+        <v>163.58256434486276</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>365.76830321256222</v>
+      </c>
+      <c r="B85">
+        <v>163.39809088913242</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>366.6338065227406</v>
+      </c>
+      <c r="B86">
+        <v>163.32044010083249</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>367.60431384102549</v>
+      </c>
+      <c r="B87">
+        <v>163.07863793454462</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>368.53260434707926</v>
+      </c>
+      <c r="B88">
+        <v>163.00390288215527</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>369.45802139999279</v>
+      </c>
+      <c r="B89">
+        <v>162.84568554041269</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>370.40393134951455</v>
+      </c>
+      <c r="B90">
+        <v>162.69314312313784</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>371.25027953908591</v>
+      </c>
+      <c r="B91">
+        <v>162.65816578611827</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>372.12490565395808</v>
+      </c>
+      <c r="B92">
+        <v>162.61528468990772</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>372.95682879277342</v>
+      </c>
+      <c r="B93">
+        <v>162.48365457549076</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>373.84444136563525</v>
+      </c>
+      <c r="B94">
+        <v>162.28415063338315</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>374.68150829572375</v>
+      </c>
+      <c r="B95">
+        <v>162.20721378469494</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>375.77718292564788</v>
+      </c>
+      <c r="B96">
+        <v>162.26828909078446</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>376.63761050515603</v>
+      </c>
+      <c r="B97">
+        <v>162.00989603902252</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>377.57082966579276</v>
+      </c>
+      <c r="B98">
+        <v>161.81957020444349</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>378.4550823230847</v>
+      </c>
+      <c r="B99">
+        <v>161.69036560328448</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>379.26594872625617</v>
+      </c>
+      <c r="B100">
+        <v>161.7145615463798</v>
       </c>
     </row>
   </sheetData>

--- a/OutputData.xlsx
+++ b/OutputData.xlsx
@@ -341,802 +341,802 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>288.93163556688495</v>
+        <v>243.73692784263619</v>
       </c>
       <c r="B1">
-        <v>171.03901749008958</v>
+        <v>165.24877795818523</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>290.01327970778453</v>
+        <v>244.22414106906837</v>
       </c>
       <c r="B2">
-        <v>170.92382177807178</v>
+        <v>165.44152721206274</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>290.95573218800115</v>
+        <v>244.83097415031725</v>
       </c>
       <c r="B3">
-        <v>170.83050221416391</v>
+        <v>165.78890562745653</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>291.74503516901581</v>
+        <v>245.46866961289643</v>
       </c>
       <c r="B4">
-        <v>170.71025460760009</v>
+        <v>166.06545509207226</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>292.67906081127381</v>
+        <v>246.04474399698589</v>
       </c>
       <c r="B5">
-        <v>170.70457912204631</v>
+        <v>166.34511336624919</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>293.56958486132413</v>
+        <v>246.63985892707257</v>
       </c>
       <c r="B6">
-        <v>170.61318774297439</v>
+        <v>166.63699416454656</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>294.51028794602036</v>
+        <v>247.1380609017655</v>
       </c>
       <c r="B7">
-        <v>170.44167317347399</v>
+        <v>166.94580402212628</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>295.37288462512231</v>
+        <v>247.66932378148712</v>
       </c>
       <c r="B8">
-        <v>170.22906780868121</v>
+        <v>167.26707674086492</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>296.16010466841624</v>
+        <v>248.40406073449702</v>
       </c>
       <c r="B9">
-        <v>170.06137134179917</v>
+        <v>167.44496514450083</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>297.00172190894108</v>
+        <v>248.9941718377319</v>
       </c>
       <c r="B10">
-        <v>169.97828183504802</v>
+        <v>167.64288539709455</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>297.97272513899082</v>
+        <v>249.6401708214525</v>
       </c>
       <c r="B11">
-        <v>169.85698221185564</v>
+        <v>167.94722957776548</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>298.95740130089115</v>
+        <v>250.29029446647138</v>
       </c>
       <c r="B12">
-        <v>169.80842192498253</v>
+        <v>168.20344743180274</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>299.83066287569392</v>
+        <v>251.01861998096572</v>
       </c>
       <c r="B13">
-        <v>169.68350043869748</v>
+        <v>168.42140644283077</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>300.70254365730887</v>
+        <v>251.55600984795402</v>
       </c>
       <c r="B14">
-        <v>169.58164330927394</v>
+        <v>168.67949483557754</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>301.68841279021734</v>
+        <v>252.20122264051449</v>
       </c>
       <c r="B15">
-        <v>169.50678871758601</v>
+        <v>168.93927143504007</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>302.64214623966768</v>
+        <v>252.69444733995005</v>
       </c>
       <c r="B16">
-        <v>169.47056324956907</v>
+        <v>169.36292350120078</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>303.63800305684305</v>
+        <v>253.32717985217664</v>
       </c>
       <c r="B17">
-        <v>169.48544841238902</v>
+        <v>169.59260612617274</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>304.51820863672344</v>
+        <v>253.84914273897471</v>
       </c>
       <c r="B18">
-        <v>169.60045609118552</v>
+        <v>169.76957686837807</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>305.4589286989571</v>
+        <v>254.27139183666895</v>
       </c>
       <c r="B19">
-        <v>169.46453515319129</v>
+        <v>170.14375737670437</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>306.38439687708768</v>
+        <v>254.85109717950175</v>
       </c>
       <c r="B20">
-        <v>169.34589609465027</v>
+        <v>170.43277795436694</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>307.38078222240421</v>
+        <v>255.41959559332071</v>
       </c>
       <c r="B21">
-        <v>169.29299412448583</v>
+        <v>170.71454437382232</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>308.34223329940824</v>
+        <v>255.92041929958509</v>
       </c>
       <c r="B22">
-        <v>169.23174727376667</v>
+        <v>171.11096203813949</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>309.22061202710773</v>
+        <v>256.48177307171045</v>
       </c>
       <c r="B23">
-        <v>169.07485954817267</v>
+        <v>171.38454970079599</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>310.11184827777515</v>
+        <v>257.09459195580183</v>
       </c>
       <c r="B24">
-        <v>168.98153025624634</v>
+        <v>171.60481191377841</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>310.96882726215972</v>
+        <v>257.6033680629418</v>
       </c>
       <c r="B25">
-        <v>168.97400544839377</v>
+        <v>171.96992401046157</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>311.90847985465774</v>
+        <v>258.22861887181824</v>
       </c>
       <c r="B26">
-        <v>168.8448192768476</v>
+        <v>172.2985210066681</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>312.81237386038384</v>
+        <v>258.72006115316395</v>
       </c>
       <c r="B27">
-        <v>168.66335631447282</v>
+        <v>172.58479852368436</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>313.69096201437469</v>
+        <v>259.24868160643359</v>
       </c>
       <c r="B28">
-        <v>168.58422594251601</v>
+        <v>172.92290027251445</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>314.68384781745073</v>
+        <v>259.84029129868719</v>
       </c>
       <c r="B29">
-        <v>168.36499038230735</v>
+        <v>173.28885794682481</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>315.60151064479652</v>
+        <v>260.50454946086808</v>
       </c>
       <c r="B30">
-        <v>168.31333815641352</v>
+        <v>173.63364926562681</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>316.54406301768523</v>
+        <v>261.1081569737247</v>
       </c>
       <c r="B31">
-        <v>168.24345352360598</v>
+        <v>174.03826568306965</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>317.4190361305474</v>
+        <v>261.72408721478263</v>
       </c>
       <c r="B32">
-        <v>168.16652898127694</v>
+        <v>174.38806682585394</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>318.1989459807121</v>
+        <v>262.21230595497718</v>
       </c>
       <c r="B33">
-        <v>168.03956713316785</v>
+        <v>174.78580695406941</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>319.15310377465238</v>
+        <v>262.76949428745934</v>
       </c>
       <c r="B34">
-        <v>167.84942806860738</v>
+        <v>175.12282052802846</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>320.06822532325583</v>
+        <v>263.45603257955099</v>
       </c>
       <c r="B35">
-        <v>167.78019786349657</v>
+        <v>175.34529622448056</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>320.92620463622211</v>
+        <v>264.09010631497449</v>
       </c>
       <c r="B36">
-        <v>167.69104264413866</v>
+        <v>175.74825787469794</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>321.89472446852784</v>
+        <v>264.64828792197886</v>
       </c>
       <c r="B37">
-        <v>167.75145719143532</v>
+        <v>175.95374537447077</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>322.89717652120959</v>
+        <v>265.31209422161976</v>
       </c>
       <c r="B38">
-        <v>167.68261060635578</v>
+        <v>176.42197145694828</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>323.75883354964378</v>
+        <v>265.86773318136665</v>
       </c>
       <c r="B39">
-        <v>167.58795308322433</v>
+        <v>176.69962933281911</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>324.61235130704659</v>
+        <v>266.4147217979185</v>
       </c>
       <c r="B40">
-        <v>167.40778211667268</v>
+        <v>177.04790306879883</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>325.73509742123923</v>
+        <v>266.791235081335</v>
       </c>
       <c r="B41">
-        <v>167.42257826888863</v>
+        <v>177.43008606063708</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>326.65368743753646</v>
+        <v>267.34629272481044</v>
       </c>
       <c r="B42">
-        <v>167.25307641118204</v>
+        <v>177.76246279351372</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>327.52367682210161</v>
+        <v>268.00244518190522</v>
       </c>
       <c r="B43">
-        <v>167.10646623681956</v>
+        <v>177.97605653852438</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>328.44126543738258</v>
+        <v>268.55150394832765</v>
       </c>
       <c r="B44">
-        <v>167.1355687755167</v>
+        <v>178.2942715731713</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>329.36175920416377</v>
+        <v>269.10218978789993</v>
       </c>
       <c r="B45">
-        <v>167.05066194128892</v>
+        <v>178.63515821437869</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>330.25290432501788</v>
+        <v>269.69183722139428</v>
       </c>
       <c r="B46">
-        <v>167.02556186108868</v>
+        <v>179.02729288485037</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>331.16024574679295</v>
+        <v>270.29131528407959</v>
       </c>
       <c r="B47">
-        <v>166.94729802095961</v>
+        <v>179.44983398307193</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>332.1046076906897</v>
+        <v>270.95398638344443</v>
       </c>
       <c r="B48">
-        <v>166.89526514275713</v>
+        <v>179.79583892110759</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>332.99369487830381</v>
+        <v>271.56668171111579</v>
       </c>
       <c r="B49">
-        <v>166.75102456401714</v>
+        <v>180.00714105757848</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>333.79530567885223</v>
+        <v>272.16941261905885</v>
       </c>
       <c r="B50">
-        <v>166.65850354482299</v>
+        <v>180.44605881421899</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>334.67098968490615</v>
+        <v>272.76988575187801</v>
       </c>
       <c r="B51">
-        <v>166.49122904639728</v>
+        <v>180.77067370404936</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>335.5603144188579</v>
+        <v>273.35059372951497</v>
       </c>
       <c r="B52">
-        <v>166.49410774513427</v>
+        <v>181.13418358829341</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>336.44601058220093</v>
+        <v>273.99738295369781</v>
       </c>
       <c r="B53">
-        <v>166.51892661417668</v>
+        <v>181.50165351732153</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>337.47315138804476</v>
+        <v>274.71053293707041</v>
       </c>
       <c r="B54">
-        <v>166.50715893511256</v>
+        <v>181.7473997163132</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>338.40664842868961</v>
+        <v>275.3842947910565</v>
       </c>
       <c r="B55">
-        <v>166.36432964735914</v>
+        <v>182.10673233077824</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>339.32545683648834</v>
+        <v>276.00044556745064</v>
       </c>
       <c r="B56">
-        <v>166.25005556642628</v>
+        <v>182.39787593995575</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>340.23941395034876</v>
+        <v>276.45140908675899</v>
       </c>
       <c r="B57">
-        <v>166.14407750742723</v>
+        <v>182.61725723045757</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>341.1532789769534</v>
+        <v>276.97638303387191</v>
       </c>
       <c r="B58">
-        <v>166.05455850944759</v>
+        <v>182.90818084228815</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>342.06794878712066</v>
+        <v>277.53671330650855</v>
       </c>
       <c r="B59">
-        <v>166.10272725619066</v>
+        <v>183.16702506170796</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>343.13558912153974</v>
+        <v>278.12784648325754</v>
       </c>
       <c r="B60">
-        <v>166.00565738734272</v>
+        <v>183.62396234780249</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>344.06153965779606</v>
+        <v>278.81534855379277</v>
       </c>
       <c r="B61">
-        <v>165.90503145602869</v>
+        <v>183.92561681031404</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>344.9796979550585</v>
+        <v>279.42978841430107</v>
       </c>
       <c r="B62">
-        <v>165.82230048585276</v>
+        <v>184.2249042811867</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>345.78102212968281</v>
+        <v>280.12754531015702</v>
       </c>
       <c r="B63">
-        <v>165.72073968933287</v>
+        <v>184.48984612521565</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>346.74403419194078</v>
+        <v>280.70573252293997</v>
       </c>
       <c r="B64">
-        <v>165.60461970851614</v>
+        <v>184.74032682429373</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>347.71335705426361</v>
+        <v>281.39734538540893</v>
       </c>
       <c r="B65">
-        <v>165.6293861494801</v>
+        <v>185.21611024672629</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>348.59807535739259</v>
+        <v>281.98770888380096</v>
       </c>
       <c r="B66">
-        <v>165.61824655471102</v>
+        <v>185.60150790222576</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>349.60421458743821</v>
+        <v>282.5971229882133</v>
       </c>
       <c r="B67">
-        <v>165.50143101541036</v>
+        <v>185.88935441518527</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>350.4718764127233</v>
+        <v>283.2195909384576</v>
       </c>
       <c r="B68">
-        <v>165.42566339112278</v>
+        <v>186.20342296614396</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>351.52983782160982</v>
+        <v>283.74022465361895</v>
       </c>
       <c r="B69">
-        <v>165.29131440860709</v>
+        <v>186.48668145407851</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>352.43113269267036</v>
+        <v>284.29323078480502</v>
       </c>
       <c r="B70">
-        <v>165.11996611048949</v>
+        <v>186.69000878920616</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>353.23954318074635</v>
+        <v>284.82173482266751</v>
       </c>
       <c r="B71">
-        <v>165.02232349406719</v>
+        <v>186.91642520351624</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>353.96358576522243</v>
+        <v>285.54884017956158</v>
       </c>
       <c r="B72">
-        <v>164.96298210062227</v>
+        <v>187.24599519675806</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>354.83322317259797</v>
+        <v>286.14765106651964</v>
       </c>
       <c r="B73">
-        <v>164.88597432842676</v>
+        <v>187.31103464928455</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>355.7565301237758</v>
+        <v>286.7285845535207</v>
       </c>
       <c r="B74">
-        <v>164.76462845840501</v>
+        <v>187.55280213173933</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>356.70360286711292</v>
+        <v>287.27422114943124</v>
       </c>
       <c r="B75">
-        <v>164.59988258865604</v>
+        <v>187.94755021152389</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>357.60329447952188</v>
+        <v>287.85616674609889</v>
       </c>
       <c r="B76">
-        <v>164.51900347409025</v>
+        <v>188.3294690145496</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>358.5204000608943</v>
+        <v>288.48574875679918</v>
       </c>
       <c r="B77">
-        <v>164.34086878690255</v>
+        <v>188.58574947583918</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>359.36437955915346</v>
+        <v>289.19303700239959</v>
       </c>
       <c r="B78">
-        <v>164.32722507647256</v>
+        <v>189.01440315294752</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>360.37093375524495</v>
+        <v>289.83473366524657</v>
       </c>
       <c r="B79">
-        <v>164.28907165490213</v>
+        <v>189.39930544086852</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>361.21361786806477</v>
+        <v>290.45450289390635</v>
       </c>
       <c r="B80">
-        <v>164.24297329268225</v>
+        <v>189.65466200047666</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>362.20602482284943</v>
+        <v>291.07994856478678</v>
       </c>
       <c r="B81">
-        <v>164.15926322118827</v>
+        <v>189.96275460786188</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>363.13947911260919</v>
+        <v>291.62533595619925</v>
       </c>
       <c r="B82">
-        <v>164.07314991379391</v>
+        <v>190.20276972459644</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>363.94127026898559</v>
+        <v>292.17373168393402</v>
       </c>
       <c r="B83">
-        <v>163.80414609189049</v>
+        <v>190.39253043833307</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>364.89267379734656</v>
+        <v>292.89652119119597</v>
       </c>
       <c r="B84">
-        <v>163.58256434486276</v>
+        <v>190.70051097266162</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>365.76830321256222</v>
+        <v>293.53327554235142</v>
       </c>
       <c r="B85">
-        <v>163.39809088913242</v>
+        <v>190.95070608345006</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>366.6338065227406</v>
+        <v>294.06185004011564</v>
       </c>
       <c r="B86">
-        <v>163.32044010083249</v>
+        <v>191.20686028931178</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>367.60431384102549</v>
+        <v>294.66123247112887</v>
       </c>
       <c r="B87">
-        <v>163.07863793454462</v>
+        <v>191.51235992840756</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>368.53260434707926</v>
+        <v>295.29570913309419</v>
       </c>
       <c r="B88">
-        <v>163.00390288215527</v>
+        <v>191.86381719075817</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>369.45802139999279</v>
+        <v>296.00763643566893</v>
       </c>
       <c r="B89">
-        <v>162.84568554041269</v>
+        <v>192.09303734007503</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>370.40393134951455</v>
+        <v>296.60386238996006</v>
       </c>
       <c r="B90">
-        <v>162.69314312313784</v>
+        <v>192.38704867394375</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>371.25027953908591</v>
+        <v>297.31664846984756</v>
       </c>
       <c r="B91">
-        <v>162.65816578611827</v>
+        <v>192.70538177224867</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>372.12490565395808</v>
+        <v>297.95163529002519</v>
       </c>
       <c r="B92">
-        <v>162.61528468990772</v>
+        <v>193.07621184069086</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>372.95682879277342</v>
+        <v>298.54099476129875</v>
       </c>
       <c r="B93">
-        <v>162.48365457549076</v>
+        <v>193.32165168657295</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>373.84444136563525</v>
+        <v>299.07456819119136</v>
       </c>
       <c r="B94">
-        <v>162.28415063338315</v>
+        <v>193.67511773478927</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>374.68150829572375</v>
+        <v>299.74495489707596</v>
       </c>
       <c r="B95">
-        <v>162.20721378469494</v>
+        <v>194.05385508769106</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>375.77718292564788</v>
+        <v>300.20511554534045</v>
       </c>
       <c r="B96">
-        <v>162.26828909078446</v>
+        <v>194.38347513111842</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>376.63761050515603</v>
+        <v>300.83090900404039</v>
       </c>
       <c r="B97">
-        <v>162.00989603902252</v>
+        <v>194.6547017776119</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>377.57082966579276</v>
+        <v>301.47011301756947</v>
       </c>
       <c r="B98">
-        <v>161.81957020444349</v>
+        <v>194.94310459426003</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>378.4550823230847</v>
+        <v>302.14489474671109</v>
       </c>
       <c r="B99">
-        <v>161.69036560328448</v>
+        <v>195.2763541113533</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>379.26594872625617</v>
+        <v>302.71027163389209</v>
       </c>
       <c r="B100">
-        <v>161.7145615463798</v>
+        <v>195.57692608225923</v>
       </c>
     </row>
   </sheetData>

--- a/OutputData.xlsx
+++ b/OutputData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TUF\Desktop\particle filter 8\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Paper Codes\Particle Filter code\Matlab\particle filter 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -336,807 +336,8007 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>243.73692784263619</v>
+        <v>347.69371667915914</v>
       </c>
       <c r="B1">
-        <v>165.24877795818523</v>
+        <v>51.804913555152652</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>244.22414106906837</v>
+        <v>348.39813212560404</v>
       </c>
       <c r="B2">
-        <v>165.44152721206274</v>
+        <v>51.60267687001452</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>244.83097415031725</v>
+        <v>349.19288584430325</v>
       </c>
       <c r="B3">
-        <v>165.78890562745653</v>
+        <v>51.455924340806888</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>245.46866961289643</v>
+        <v>349.94609099021216</v>
       </c>
       <c r="B4">
-        <v>166.06545509207226</v>
+        <v>51.396083835653172</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>246.04474399698589</v>
+        <v>350.61873137218782</v>
       </c>
       <c r="B5">
-        <v>166.34511336624919</v>
+        <v>51.299521527741568</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>246.63985892707257</v>
+        <v>351.21552645335208</v>
       </c>
       <c r="B6">
-        <v>166.63699416454656</v>
+        <v>51.213259603809163</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>247.1380609017655</v>
+        <v>351.75102422839973</v>
       </c>
       <c r="B7">
-        <v>166.94580402212628</v>
+        <v>51.127115696642235</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>247.66932378148712</v>
+        <v>352.29975684038084</v>
       </c>
       <c r="B8">
-        <v>167.26707674086492</v>
+        <v>51.129448056087604</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>248.40406073449702</v>
+        <v>352.71858913890105</v>
       </c>
       <c r="B9">
-        <v>167.44496514450083</v>
+        <v>51.081284234489551</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>248.9941718377319</v>
+        <v>353.11497058635547</v>
       </c>
       <c r="B10">
-        <v>167.64288539709455</v>
+        <v>50.99938064321109</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>249.6401708214525</v>
+        <v>353.40763735606919</v>
       </c>
       <c r="B11">
-        <v>167.94722957776548</v>
+        <v>50.891975861585806</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>250.29029446647138</v>
+        <v>353.73812270804024</v>
       </c>
       <c r="B12">
-        <v>168.20344743180274</v>
+        <v>50.867866212171236</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>251.01861998096572</v>
+        <v>354.0160734812589</v>
       </c>
       <c r="B13">
-        <v>168.42140644283077</v>
+        <v>50.859255057438695</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>251.55600984795402</v>
+        <v>354.38753112180353</v>
       </c>
       <c r="B14">
-        <v>168.67949483557754</v>
+        <v>50.830001168804841</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>252.20122264051449</v>
+        <v>354.68915319913884</v>
       </c>
       <c r="B15">
-        <v>168.93927143504007</v>
+        <v>50.812173666085165</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>252.69444733995005</v>
+        <v>354.9784823681228</v>
       </c>
       <c r="B16">
-        <v>169.36292350120078</v>
+        <v>50.814013299417674</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>253.32717985217664</v>
+        <v>355.29188457342701</v>
       </c>
       <c r="B17">
-        <v>169.59260612617274</v>
+        <v>50.872581805666272</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>253.84914273897471</v>
+        <v>355.51534507118146</v>
       </c>
       <c r="B18">
-        <v>169.76957686837807</v>
+        <v>50.944569053325175</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>254.27139183666895</v>
+        <v>355.71811879709838</v>
       </c>
       <c r="B19">
-        <v>170.14375737670437</v>
+        <v>51.01173935346295</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>254.85109717950175</v>
+        <v>355.94160965260562</v>
       </c>
       <c r="B20">
-        <v>170.43277795436694</v>
+        <v>51.04993410966204</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>255.41959559332071</v>
+        <v>356.16364819348746</v>
       </c>
       <c r="B21">
-        <v>170.71454437382232</v>
+        <v>51.127581883884389</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>255.92041929958509</v>
+        <v>356.4664231646633</v>
       </c>
       <c r="B22">
-        <v>171.11096203813949</v>
+        <v>51.094156026575227</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>256.48177307171045</v>
+        <v>356.75898607337007</v>
       </c>
       <c r="B23">
-        <v>171.38454970079599</v>
+        <v>51.170130221046399</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>257.09459195580183</v>
+        <v>357.13545415543791</v>
       </c>
       <c r="B24">
-        <v>171.60481191377841</v>
+        <v>51.154543679955026</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>257.6033680629418</v>
+        <v>357.46955233519037</v>
       </c>
       <c r="B25">
-        <v>171.96992401046157</v>
+        <v>51.188017930293093</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>258.22861887181824</v>
+        <v>357.77223736379466</v>
       </c>
       <c r="B26">
-        <v>172.2985210066681</v>
+        <v>51.218624746412317</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>258.72006115316395</v>
+        <v>358.0381491267658</v>
       </c>
       <c r="B27">
-        <v>172.58479852368436</v>
+        <v>51.205778728395387</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>259.24868160643359</v>
+        <v>358.21840798332016</v>
       </c>
       <c r="B28">
-        <v>172.92290027251445</v>
+        <v>51.148840690492442</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>259.84029129868719</v>
+        <v>358.44356550944235</v>
       </c>
       <c r="B29">
-        <v>173.28885794682481</v>
+        <v>51.03805702684253</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>260.50454946086808</v>
+        <v>358.64606235354466</v>
       </c>
       <c r="B30">
-        <v>173.63364926562681</v>
+        <v>50.870071818062861</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>261.1081569737247</v>
+        <v>358.89739473367297</v>
       </c>
       <c r="B31">
-        <v>174.03826568306965</v>
+        <v>50.721496713981509</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>261.72408721478263</v>
+        <v>359.07193807580637</v>
       </c>
       <c r="B32">
-        <v>174.38806682585394</v>
+        <v>50.586999945299361</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>262.21230595497718</v>
+        <v>359.29616496760082</v>
       </c>
       <c r="B33">
-        <v>174.78580695406941</v>
+        <v>50.388911020673255</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>262.76949428745934</v>
+        <v>359.48783054305312</v>
       </c>
       <c r="B34">
-        <v>175.12282052802846</v>
+        <v>50.198230886415473</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>263.45603257955099</v>
+        <v>359.64179234029308</v>
       </c>
       <c r="B35">
-        <v>175.34529622448056</v>
+        <v>49.970686279891268</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>264.09010631497449</v>
+        <v>359.78804969731937</v>
       </c>
       <c r="B36">
-        <v>175.74825787469794</v>
+        <v>49.659125533721507</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>264.64828792197886</v>
+        <v>359.97536426050482</v>
       </c>
       <c r="B37">
-        <v>175.95374537447077</v>
+        <v>49.496696212387477</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>265.31209422161976</v>
+        <v>360.19109300044011</v>
       </c>
       <c r="B38">
-        <v>176.42197145694828</v>
+        <v>49.385858793574926</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>265.86773318136665</v>
+        <v>360.40979901432519</v>
       </c>
       <c r="B39">
-        <v>176.69962933281911</v>
+        <v>49.189128524841045</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>266.4147217979185</v>
+        <v>360.6005601278199</v>
       </c>
       <c r="B40">
-        <v>177.04790306879883</v>
+        <v>48.962537695774039</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>266.791235081335</v>
+        <v>360.77101671468159</v>
       </c>
       <c r="B41">
-        <v>177.43008606063708</v>
+        <v>48.758735480334416</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>267.34629272481044</v>
+        <v>360.96516115894798</v>
       </c>
       <c r="B42">
-        <v>177.76246279351372</v>
+        <v>48.536057323974212</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>268.00244518190522</v>
+        <v>361.21471020240369</v>
       </c>
       <c r="B43">
-        <v>177.97605653852438</v>
+        <v>48.269701757578979</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>268.55150394832765</v>
+        <v>361.40787954773378</v>
       </c>
       <c r="B44">
-        <v>178.2942715731713</v>
+        <v>48.033133942022054</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>269.10218978789993</v>
+        <v>361.6023960222235</v>
       </c>
       <c r="B45">
-        <v>178.63515821437869</v>
+        <v>47.711254820903832</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>269.69183722139428</v>
+        <v>361.83885860000493</v>
       </c>
       <c r="B46">
-        <v>179.02729288485037</v>
+        <v>47.348252184616911</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>270.29131528407959</v>
+        <v>361.99128340004484</v>
       </c>
       <c r="B47">
-        <v>179.44983398307193</v>
+        <v>47.000097290554692</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>270.95398638344443</v>
+        <v>362.22331415985826</v>
       </c>
       <c r="B48">
-        <v>179.79583892110759</v>
+        <v>46.607068365908837</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>271.56668171111579</v>
+        <v>362.51373601527013</v>
       </c>
       <c r="B49">
-        <v>180.00714105757848</v>
+        <v>46.093565263325189</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>272.16941261905885</v>
+        <v>362.78645449009514</v>
       </c>
       <c r="B50">
-        <v>180.44605881421899</v>
+        <v>45.585623750614403</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>272.76988575187801</v>
+        <v>363.05151420427495</v>
       </c>
       <c r="B51">
-        <v>180.77067370404936</v>
+        <v>45.133812561251517</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>273.35059372951497</v>
+        <v>363.25339503175763</v>
       </c>
       <c r="B52">
-        <v>181.13418358829341</v>
+        <v>44.736162617171544</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>273.99738295369781</v>
+        <v>363.42756387466363</v>
       </c>
       <c r="B53">
-        <v>181.50165351732153</v>
+        <v>44.272532341324919</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>274.71053293707041</v>
+        <v>363.62170711267737</v>
       </c>
       <c r="B54">
-        <v>181.7473997163132</v>
+        <v>43.802764349118441</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>275.3842947910565</v>
+        <v>363.88000630922892</v>
       </c>
       <c r="B55">
-        <v>182.10673233077824</v>
+        <v>43.286257429455084</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>276.00044556745064</v>
+        <v>364.14973529650263</v>
       </c>
       <c r="B56">
-        <v>182.39787593995575</v>
+        <v>42.776190003816929</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>276.45140908675899</v>
+        <v>364.31545492884504</v>
       </c>
       <c r="B57">
-        <v>182.61725723045757</v>
+        <v>42.204404291070873</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>276.97638303387191</v>
+        <v>364.6017621507591</v>
       </c>
       <c r="B58">
-        <v>182.90818084228815</v>
+        <v>41.688492275942941</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>277.53671330650855</v>
+        <v>364.95266335897702</v>
       </c>
       <c r="B59">
-        <v>183.16702506170796</v>
+        <v>41.18433556380127</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>278.12784648325754</v>
+        <v>365.34035137371882</v>
       </c>
       <c r="B60">
-        <v>183.62396234780249</v>
+        <v>40.683441712873261</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>278.81534855379277</v>
+        <v>365.69323228190751</v>
       </c>
       <c r="B61">
-        <v>183.92561681031404</v>
+        <v>40.118222769086444</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>279.42978841430107</v>
+        <v>366.09330441921054</v>
       </c>
       <c r="B62">
-        <v>184.2249042811867</v>
+        <v>39.578850584119074</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>280.12754531015702</v>
+        <v>366.44580817779604</v>
       </c>
       <c r="B63">
-        <v>184.48984612521565</v>
+        <v>38.997018563339893</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>280.70573252293997</v>
+        <v>366.72034145611917</v>
       </c>
       <c r="B64">
-        <v>184.74032682429373</v>
+        <v>38.435137385749066</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>281.39734538540893</v>
+        <v>366.91149809603257</v>
       </c>
       <c r="B65">
-        <v>185.21611024672629</v>
+        <v>37.837853560342737</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>281.98770888380096</v>
+        <v>367.19829949208287</v>
       </c>
       <c r="B66">
-        <v>185.60150790222576</v>
+        <v>37.139552275625306</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>282.5971229882133</v>
+        <v>367.38648595979487</v>
       </c>
       <c r="B67">
-        <v>185.88935441518527</v>
+        <v>36.467555526069823</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>283.2195909384576</v>
+        <v>367.63337547629004</v>
       </c>
       <c r="B68">
-        <v>186.20342296614396</v>
+        <v>35.935353808013346</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>283.74022465361895</v>
+        <v>367.93294460735603</v>
       </c>
       <c r="B69">
-        <v>186.48668145407851</v>
+        <v>35.336325759748931</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>284.29323078480502</v>
+        <v>368.25428288236719</v>
       </c>
       <c r="B70">
-        <v>186.69000878920616</v>
+        <v>34.790259838468579</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>284.82173482266751</v>
+        <v>368.58075695660176</v>
       </c>
       <c r="B71">
-        <v>186.91642520351624</v>
+        <v>34.263886566974627</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>285.54884017956158</v>
+        <v>368.9603924201316</v>
       </c>
       <c r="B72">
-        <v>187.24599519675806</v>
+        <v>33.704018136079355</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>286.14765106651964</v>
+        <v>369.33488067002753</v>
       </c>
       <c r="B73">
-        <v>187.31103464928455</v>
+        <v>33.164680942141885</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>286.7285845535207</v>
+        <v>369.74373630868695</v>
       </c>
       <c r="B74">
-        <v>187.55280213173933</v>
+        <v>32.499354879349731</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>287.27422114943124</v>
+        <v>370.23180677367702</v>
       </c>
       <c r="B75">
-        <v>187.94755021152389</v>
+        <v>31.773395756804376</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>287.85616674609889</v>
+        <v>370.71150069683591</v>
       </c>
       <c r="B76">
-        <v>188.3294690145496</v>
+        <v>31.129412934668235</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>288.48574875679918</v>
+        <v>371.17366466327104</v>
       </c>
       <c r="B77">
-        <v>188.58574947583918</v>
+        <v>30.454912355379943</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>289.19303700239959</v>
+        <v>371.63019582032626</v>
       </c>
       <c r="B78">
-        <v>189.01440315294752</v>
+        <v>29.80212506851489</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>289.83473366524657</v>
+        <v>372.02637949430931</v>
       </c>
       <c r="B79">
-        <v>189.39930544086852</v>
+        <v>29.164845070502945</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>290.45450289390635</v>
+        <v>372.42649559451274</v>
       </c>
       <c r="B80">
-        <v>189.65466200047666</v>
+        <v>28.537100288866675</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>291.07994856478678</v>
+        <v>372.73333043199102</v>
       </c>
       <c r="B81">
-        <v>189.96275460786188</v>
+        <v>27.982442923024717</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>291.62533595619925</v>
+        <v>372.99301190116296</v>
       </c>
       <c r="B82">
-        <v>190.20276972459644</v>
+        <v>27.460221729406221</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>292.17373168393402</v>
+        <v>373.17356240730726</v>
       </c>
       <c r="B83">
-        <v>190.39253043833307</v>
+        <v>26.913534699091738</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>292.89652119119597</v>
+        <v>373.43993170907947</v>
       </c>
       <c r="B84">
-        <v>190.70051097266162</v>
+        <v>26.300581647157578</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>293.53327554235142</v>
+        <v>373.63517309128366</v>
       </c>
       <c r="B85">
-        <v>190.95070608345006</v>
+        <v>25.735795380679221</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>294.06185004011564</v>
+        <v>373.82987860549639</v>
       </c>
       <c r="B86">
-        <v>191.20686028931178</v>
+        <v>25.1399684887954</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>294.66123247112887</v>
+        <v>374.07413437383735</v>
       </c>
       <c r="B87">
-        <v>191.51235992840756</v>
+        <v>24.477889982716125</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>295.29570913309419</v>
+        <v>374.34600772715413</v>
       </c>
       <c r="B88">
-        <v>191.86381719075817</v>
+        <v>23.779368835186474</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>296.00763643566893</v>
+        <v>374.59547403667517</v>
       </c>
       <c r="B89">
-        <v>192.09303734007503</v>
+        <v>22.992737337299527</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>296.60386238996006</v>
+        <v>374.85028300433117</v>
       </c>
       <c r="B90">
-        <v>192.38704867394375</v>
+        <v>22.323053400027124</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>297.31664846984756</v>
+        <v>375.14764442751385</v>
       </c>
       <c r="B91">
-        <v>192.70538177224867</v>
+        <v>21.696753013859674</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>297.95163529002519</v>
+        <v>375.39690395835345</v>
       </c>
       <c r="B92">
-        <v>193.07621184069086</v>
+        <v>21.037102035764313</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>298.54099476129875</v>
+        <v>375.61812443386515</v>
       </c>
       <c r="B93">
-        <v>193.32165168657295</v>
+        <v>20.333589293182332</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>299.07456819119136</v>
+        <v>375.78686190433223</v>
       </c>
       <c r="B94">
-        <v>193.67511773478927</v>
+        <v>19.632206693771479</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>299.74495489707596</v>
+        <v>375.88177592438291</v>
       </c>
       <c r="B95">
-        <v>194.05385508769106</v>
+        <v>19.090070652315404</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>300.20511554534045</v>
+        <v>375.9872048955458</v>
       </c>
       <c r="B96">
-        <v>194.38347513111842</v>
+        <v>18.439910404162841</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>300.83090900404039</v>
+        <v>376.01604664496875</v>
       </c>
       <c r="B97">
-        <v>194.6547017776119</v>
+        <v>17.766013561853857</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>301.47011301756947</v>
+        <v>376.03804933042261</v>
       </c>
       <c r="B98">
-        <v>194.94310459426003</v>
+        <v>17.097861367949669</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>302.14489474671109</v>
+        <v>376.02202424191188</v>
       </c>
       <c r="B99">
-        <v>195.2763541113533</v>
+        <v>16.392544663529122</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>302.71027163389209</v>
+        <v>375.99343462924895</v>
       </c>
       <c r="B100">
-        <v>195.57692608225923</v>
+        <v>15.64146259189007</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>375.98971828740054</v>
+      </c>
+      <c r="B101">
+        <v>14.957317948046072</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>375.98665083251518</v>
+      </c>
+      <c r="B102">
+        <v>14.227042492334773</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>375.98826910485536</v>
+      </c>
+      <c r="B103">
+        <v>13.52390233574318</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>375.90508898083948</v>
+      </c>
+      <c r="B104">
+        <v>12.773639119684702</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>375.89298091100522</v>
+      </c>
+      <c r="B105">
+        <v>12.016615128096777</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>375.9335261128814</v>
+      </c>
+      <c r="B106">
+        <v>11.270558486564974</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>375.90180670667741</v>
+      </c>
+      <c r="B107">
+        <v>10.548974403486854</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>375.938548126255</v>
+      </c>
+      <c r="B108">
+        <v>9.785772026008841</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>375.97850331744212</v>
+      </c>
+      <c r="B109">
+        <v>8.9372365157054308</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>376.13936709418584</v>
+      </c>
+      <c r="B110">
+        <v>8.0396410655876078</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>376.24081217325312</v>
+      </c>
+      <c r="B111">
+        <v>7.1542247114774957</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>376.41062252272155</v>
+      </c>
+      <c r="B112">
+        <v>6.3074301987710939</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>376.65011018573375</v>
+      </c>
+      <c r="B113">
+        <v>5.4921223910803914</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>376.90750322444012</v>
+      </c>
+      <c r="B114">
+        <v>4.7099775634888488</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>377.26017595088103</v>
+      </c>
+      <c r="B115">
+        <v>3.9229783206904139</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>377.61401530383904</v>
+      </c>
+      <c r="B116">
+        <v>3.152111082191329</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>377.92655050682322</v>
+      </c>
+      <c r="B117">
+        <v>2.5002681939827056</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>378.27179814186223</v>
+      </c>
+      <c r="B118">
+        <v>1.8748227928279335</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>378.5762757038292</v>
+      </c>
+      <c r="B119">
+        <v>1.2975912908452052</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>378.88207755593209</v>
+      </c>
+      <c r="B120">
+        <v>0.74390208010177949</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>379.26914982689158</v>
+      </c>
+      <c r="B121">
+        <v>0.25706158651326338</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>379.71122267567728</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>380.10106127718205</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>380.5773902860065</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>381.05703779688542</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>381.55864138950949</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>381.96444489500607</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>382.29806404167482</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>382.71476495515333</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>383.04035126646812</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>383.38503949325269</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>383.71809117080926</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>384.0207157139215</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>384.3402873959916</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>384.71188110819054</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>385.10050520792697</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>385.46541499757438</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>385.72633982311669</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>386.02928547533855</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>386.29572523921547</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>386.63743794101327</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>386.91520873242263</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>387.29178180708476</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>387.66404219190389</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>388.10429931189486</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>388.4837459318428</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>388.96504212424617</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>389.50081303764989</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>390.10518605251639</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>390.63706574517124</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>391.29077910354056</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>391.99439993617602</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>392.72879759668308</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>393.51112206033741</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>394.36145905147225</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>395.21950781477676</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>396.10950059812336</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>397.06823231741743</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>398.07866757065619</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>399.10931474534334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>400.09920254419706</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>401.16434514789387</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>402.22134108971528</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>403.30989783753057</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>404.36017127944115</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>405.38780129531443</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>406.53860000039077</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>407.64259856454265</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>408.69123421236492</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>409.76701247738555</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>410.78800593674646</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>411.91036929721918</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>412.96634624660572</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>414.04089986856587</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>415.10602870692384</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>416.15913742735398</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>417.21653693904341</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>418.38851017528833</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>419.59931252803921</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>420.8660051520622</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>422.16929195633298</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>423.4776427867331</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>424.84312983231075</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>426.21510622557787</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>427.51707002478463</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>428.8081882896941</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>430.11818051380334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>431.41596397391521</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>432.75950162681062</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>434.06446950352506</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>435.33022871541874</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>436.56989233411878</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>437.85022597010936</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>439.07648136378702</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>440.31043752731995</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>441.47174995078552</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>442.5778494284778</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>443.7956186769552</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>445.08923054270377</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>446.30214101702649</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>447.42288165438032</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>448.60411093544485</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>449.8304052823965</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>451.06484024210147</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>452.28109924383898</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>453.37424525081121</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>454.475162444749</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>455.59678833839502</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>456.74676333026179</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>457.88653919458108</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>459.02026475082783</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>460.26820257166497</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>461.41886796702397</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>462.50930819770946</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>463.59653397035544</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>464.71774201477047</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>465.87718563579256</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>467.07819540838409</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>468.24643740404082</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>469.41206756861874</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>470.56990226822279</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>471.6771543812979</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>472.90839125081681</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>474.14476545731509</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>475.46031726007669</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>476.77582156773417</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>478.04813683292201</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>479.38476429110557</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>480.71816934369099</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>482.04788984728356</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>483.30605316808271</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>484.63121245969478</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>486.02938113303537</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>487.36421119115164</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>488.77750707691439</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>490.09343185982834</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>491.45416276912368</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>492.80747157424707</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>494.23510481821046</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>495.67117304359311</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>497.07890361395198</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>498.5331382256042</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>499.94642728648006</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>500</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>500</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>500</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>500</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>500</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>500</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>500</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>500</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>500</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>500</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>500</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>500</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>500</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>500</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>500</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>500</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>500</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>500</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>500</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>500</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>500</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>500</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>500</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>500</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>500</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>500</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>500</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>500</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>500</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>500</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>500</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>500</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>500</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>500</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>500</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>500</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>500</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>500</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>500</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>500</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>500</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>500</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>500</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>500</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>500</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>500</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>500</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>500</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>500</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>500</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>500</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>500</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>500</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>500</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>500</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>500</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>500</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>500</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>500</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>500</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>500</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>500</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>500</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>500</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>500</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>500</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>500</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>500</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>500</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>500</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>500</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>500</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>500</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>500</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <v>500</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <v>500</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <v>500</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <v>500</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <v>500</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323">
+        <v>500</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <v>500</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <v>500</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <v>500</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <v>500</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <v>500</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <v>500</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <v>500</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <v>500</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <v>500</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <v>500</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <v>500</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335">
+        <v>500</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336">
+        <v>500</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337">
+        <v>500</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338">
+        <v>500</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339">
+        <v>500</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340">
+        <v>500</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341">
+        <v>500</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342">
+        <v>500</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343">
+        <v>500</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344">
+        <v>500</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345">
+        <v>500</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346">
+        <v>500</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <v>500</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348">
+        <v>500</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349">
+        <v>500</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350">
+        <v>500</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351">
+        <v>500</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352">
+        <v>500</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353">
+        <v>500</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354">
+        <v>500</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355">
+        <v>500</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356">
+        <v>500</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357">
+        <v>500</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358">
+        <v>500</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359">
+        <v>500</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360">
+        <v>500</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361">
+        <v>500</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362">
+        <v>500</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363">
+        <v>500</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364">
+        <v>500</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365">
+        <v>500</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366">
+        <v>500</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367">
+        <v>500</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368">
+        <v>500</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369">
+        <v>500</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370">
+        <v>500</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371">
+        <v>500</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372">
+        <v>500</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373">
+        <v>500</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374">
+        <v>500</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375">
+        <v>500</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376">
+        <v>500</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377">
+        <v>500</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378">
+        <v>500</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379">
+        <v>500</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380">
+        <v>500</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381">
+        <v>500</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382">
+        <v>500</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383">
+        <v>500</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384">
+        <v>500</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385">
+        <v>500</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386">
+        <v>500</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387">
+        <v>500</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388">
+        <v>500</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389">
+        <v>500</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390">
+        <v>500</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391">
+        <v>500</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392">
+        <v>500</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393">
+        <v>500</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394">
+        <v>500</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395">
+        <v>500</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396">
+        <v>500</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397">
+        <v>500</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398">
+        <v>500</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399">
+        <v>500</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400">
+        <v>500</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401">
+        <v>500</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402">
+        <v>500</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403">
+        <v>500</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404">
+        <v>500</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405">
+        <v>500</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406">
+        <v>500</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407">
+        <v>500</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408">
+        <v>500</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409">
+        <v>500</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410">
+        <v>500</v>
+      </c>
+      <c r="B410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411">
+        <v>500</v>
+      </c>
+      <c r="B411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412">
+        <v>500</v>
+      </c>
+      <c r="B412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413">
+        <v>500</v>
+      </c>
+      <c r="B413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414">
+        <v>500</v>
+      </c>
+      <c r="B414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415">
+        <v>500</v>
+      </c>
+      <c r="B415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416">
+        <v>500</v>
+      </c>
+      <c r="B416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417">
+        <v>500</v>
+      </c>
+      <c r="B417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418">
+        <v>500</v>
+      </c>
+      <c r="B418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419">
+        <v>500</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420">
+        <v>500</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421">
+        <v>500</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422">
+        <v>500</v>
+      </c>
+      <c r="B422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423">
+        <v>500</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424">
+        <v>500</v>
+      </c>
+      <c r="B424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425">
+        <v>500</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426">
+        <v>500</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427">
+        <v>500</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428">
+        <v>500</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429">
+        <v>500</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430">
+        <v>500</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431">
+        <v>500</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432">
+        <v>500</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433">
+        <v>500</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434">
+        <v>500</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435">
+        <v>500</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436">
+        <v>500</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A437">
+        <v>500</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A438">
+        <v>500</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A439">
+        <v>500</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A440">
+        <v>500</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A441">
+        <v>500</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A442">
+        <v>500</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A443">
+        <v>500</v>
+      </c>
+      <c r="B443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A444">
+        <v>500</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A445">
+        <v>500</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A446">
+        <v>500</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A447">
+        <v>500</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A448">
+        <v>500</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A449">
+        <v>500</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A450">
+        <v>500</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A451">
+        <v>500</v>
+      </c>
+      <c r="B451">
+        <v>2.71956016904224E-2</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A452">
+        <v>500</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A453">
+        <v>500</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A454">
+        <v>500</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A455">
+        <v>500</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A456">
+        <v>500</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A457">
+        <v>500</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A458">
+        <v>500</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A459">
+        <v>500</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A460">
+        <v>500</v>
+      </c>
+      <c r="B460">
+        <v>3.4272417007049194E-2</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A461">
+        <v>500</v>
+      </c>
+      <c r="B461">
+        <v>6.7854865295109285E-3</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A462">
+        <v>500</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A463">
+        <v>500</v>
+      </c>
+      <c r="B463">
+        <v>2.5676935890744171E-3</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A464">
+        <v>500</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A465">
+        <v>500</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A466">
+        <v>500</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A467">
+        <v>500</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A468">
+        <v>500</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A469">
+        <v>500</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A470">
+        <v>500</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A471">
+        <v>500</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A472">
+        <v>500</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A473">
+        <v>500</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A474">
+        <v>500</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A475">
+        <v>500</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A476">
+        <v>500</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A477">
+        <v>500</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A478">
+        <v>500</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A479">
+        <v>500</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A480">
+        <v>500</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A481">
+        <v>500</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A482">
+        <v>500</v>
+      </c>
+      <c r="B482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A483">
+        <v>500</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A484">
+        <v>500</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A485">
+        <v>500</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A486">
+        <v>500</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A487">
+        <v>500</v>
+      </c>
+      <c r="B487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A488">
+        <v>500</v>
+      </c>
+      <c r="B488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A489">
+        <v>500</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A490">
+        <v>500</v>
+      </c>
+      <c r="B490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A491">
+        <v>500</v>
+      </c>
+      <c r="B491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A492">
+        <v>500</v>
+      </c>
+      <c r="B492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A493">
+        <v>500</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A494">
+        <v>500</v>
+      </c>
+      <c r="B494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A495">
+        <v>500</v>
+      </c>
+      <c r="B495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A496">
+        <v>500</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A497">
+        <v>500</v>
+      </c>
+      <c r="B497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A498">
+        <v>500</v>
+      </c>
+      <c r="B498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A499">
+        <v>500</v>
+      </c>
+      <c r="B499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A500">
+        <v>500</v>
+      </c>
+      <c r="B500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A501">
+        <v>500</v>
+      </c>
+      <c r="B501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A503">
+        <v>500</v>
+      </c>
+      <c r="B503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A504">
+        <v>500</v>
+      </c>
+      <c r="B504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A505">
+        <v>500</v>
+      </c>
+      <c r="B505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A506">
+        <v>500</v>
+      </c>
+      <c r="B506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A507">
+        <v>500</v>
+      </c>
+      <c r="B507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A508">
+        <v>500</v>
+      </c>
+      <c r="B508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A509">
+        <v>500</v>
+      </c>
+      <c r="B509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A510">
+        <v>500</v>
+      </c>
+      <c r="B510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A511">
+        <v>500</v>
+      </c>
+      <c r="B511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A512">
+        <v>500</v>
+      </c>
+      <c r="B512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A513">
+        <v>500</v>
+      </c>
+      <c r="B513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A514">
+        <v>500</v>
+      </c>
+      <c r="B514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A515">
+        <v>500</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A516">
+        <v>500</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A517">
+        <v>500</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A518">
+        <v>500</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A519">
+        <v>500</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A520">
+        <v>500</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A521">
+        <v>500</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A522">
+        <v>500</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A523">
+        <v>500</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A524">
+        <v>500</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A525">
+        <v>500</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A526">
+        <v>500</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A527">
+        <v>500</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A528">
+        <v>500</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A529">
+        <v>500</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A530">
+        <v>500</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A531">
+        <v>500</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A532">
+        <v>500</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A533">
+        <v>500</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A534">
+        <v>500</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A535">
+        <v>500</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A536">
+        <v>500</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A537">
+        <v>500</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A538">
+        <v>500</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A539">
+        <v>500</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A540">
+        <v>500</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A541">
+        <v>500</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A542">
+        <v>500</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A543">
+        <v>500</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A544">
+        <v>500</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A545">
+        <v>500</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A546">
+        <v>500</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A547">
+        <v>500</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A548">
+        <v>500</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A549">
+        <v>500</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A550">
+        <v>500</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A551">
+        <v>500</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A552">
+        <v>500</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A553">
+        <v>500</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A554">
+        <v>500</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A555">
+        <v>500</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A556">
+        <v>500</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A557">
+        <v>500</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A558">
+        <v>500</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A559">
+        <v>500</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A560">
+        <v>500</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A561">
+        <v>500</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A562">
+        <v>500</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A563">
+        <v>500</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A564">
+        <v>500</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A565">
+        <v>500</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A566">
+        <v>500</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A567">
+        <v>500</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A568">
+        <v>500</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A569">
+        <v>500</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A570">
+        <v>500</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A571">
+        <v>500</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A572">
+        <v>500</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A573">
+        <v>500</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A574">
+        <v>500</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A575">
+        <v>500</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A576">
+        <v>500</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A577">
+        <v>500</v>
+      </c>
+      <c r="B577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A578">
+        <v>500</v>
+      </c>
+      <c r="B578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A579">
+        <v>500</v>
+      </c>
+      <c r="B579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A580">
+        <v>500</v>
+      </c>
+      <c r="B580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A581">
+        <v>500</v>
+      </c>
+      <c r="B581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A582">
+        <v>500</v>
+      </c>
+      <c r="B582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A583">
+        <v>500</v>
+      </c>
+      <c r="B583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A584">
+        <v>500</v>
+      </c>
+      <c r="B584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A585">
+        <v>500</v>
+      </c>
+      <c r="B585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A586">
+        <v>500</v>
+      </c>
+      <c r="B586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A587">
+        <v>500</v>
+      </c>
+      <c r="B587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A588">
+        <v>500</v>
+      </c>
+      <c r="B588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A589">
+        <v>500</v>
+      </c>
+      <c r="B589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A590">
+        <v>500</v>
+      </c>
+      <c r="B590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A591">
+        <v>500</v>
+      </c>
+      <c r="B591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A592">
+        <v>500</v>
+      </c>
+      <c r="B592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A593">
+        <v>500</v>
+      </c>
+      <c r="B593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A594">
+        <v>500</v>
+      </c>
+      <c r="B594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A595">
+        <v>500</v>
+      </c>
+      <c r="B595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A596">
+        <v>500</v>
+      </c>
+      <c r="B596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A597">
+        <v>500</v>
+      </c>
+      <c r="B597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A598">
+        <v>500</v>
+      </c>
+      <c r="B598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A599">
+        <v>500</v>
+      </c>
+      <c r="B599">
+        <v>8.6276570474647943E-2</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A600">
+        <v>500</v>
+      </c>
+      <c r="B600">
+        <v>0.16557113743843904</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A601">
+        <v>500</v>
+      </c>
+      <c r="B601">
+        <v>0.18326671260924812</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A602">
+        <v>500</v>
+      </c>
+      <c r="B602">
+        <v>0.22560068070164935</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A603">
+        <v>500</v>
+      </c>
+      <c r="B603">
+        <v>0.23466908641872625</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A604">
+        <v>500</v>
+      </c>
+      <c r="B604">
+        <v>0.30749760480651317</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A605">
+        <v>500</v>
+      </c>
+      <c r="B605">
+        <v>0.30347392639155091</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A606">
+        <v>500</v>
+      </c>
+      <c r="B606">
+        <v>0.2770407061919325</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A607">
+        <v>500</v>
+      </c>
+      <c r="B607">
+        <v>0.24454813931173919</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A608">
+        <v>500</v>
+      </c>
+      <c r="B608">
+        <v>5.8735165434175451E-2</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A609">
+        <v>500</v>
+      </c>
+      <c r="B609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A610">
+        <v>500</v>
+      </c>
+      <c r="B610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A611">
+        <v>500</v>
+      </c>
+      <c r="B611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A612">
+        <v>500</v>
+      </c>
+      <c r="B612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A613">
+        <v>500</v>
+      </c>
+      <c r="B613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A614">
+        <v>500</v>
+      </c>
+      <c r="B614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A615">
+        <v>500</v>
+      </c>
+      <c r="B615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A616">
+        <v>500</v>
+      </c>
+      <c r="B616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A617">
+        <v>500</v>
+      </c>
+      <c r="B617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A618">
+        <v>500</v>
+      </c>
+      <c r="B618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A619">
+        <v>500</v>
+      </c>
+      <c r="B619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A620">
+        <v>500</v>
+      </c>
+      <c r="B620">
+        <v>3.3124417997310002E-2</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A621">
+        <v>500</v>
+      </c>
+      <c r="B621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A622">
+        <v>500</v>
+      </c>
+      <c r="B622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A623">
+        <v>500</v>
+      </c>
+      <c r="B623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A624">
+        <v>500</v>
+      </c>
+      <c r="B624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A625">
+        <v>500</v>
+      </c>
+      <c r="B625">
+        <v>7.488281956886559E-3</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A626">
+        <v>500</v>
+      </c>
+      <c r="B626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A627">
+        <v>500</v>
+      </c>
+      <c r="B627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A628">
+        <v>500</v>
+      </c>
+      <c r="B628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A629">
+        <v>500</v>
+      </c>
+      <c r="B629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A630">
+        <v>500</v>
+      </c>
+      <c r="B630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A631">
+        <v>500</v>
+      </c>
+      <c r="B631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A632">
+        <v>500</v>
+      </c>
+      <c r="B632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A633">
+        <v>500</v>
+      </c>
+      <c r="B633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A634">
+        <v>500</v>
+      </c>
+      <c r="B634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A635">
+        <v>500</v>
+      </c>
+      <c r="B635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A636">
+        <v>500</v>
+      </c>
+      <c r="B636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A637">
+        <v>500</v>
+      </c>
+      <c r="B637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A638">
+        <v>500</v>
+      </c>
+      <c r="B638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A639">
+        <v>500</v>
+      </c>
+      <c r="B639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A640">
+        <v>500</v>
+      </c>
+      <c r="B640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A641">
+        <v>500</v>
+      </c>
+      <c r="B641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A642">
+        <v>500</v>
+      </c>
+      <c r="B642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A643">
+        <v>500</v>
+      </c>
+      <c r="B643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A644">
+        <v>500</v>
+      </c>
+      <c r="B644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A645">
+        <v>500</v>
+      </c>
+      <c r="B645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A646">
+        <v>500</v>
+      </c>
+      <c r="B646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A647">
+        <v>500</v>
+      </c>
+      <c r="B647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A648">
+        <v>500</v>
+      </c>
+      <c r="B648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A649">
+        <v>500</v>
+      </c>
+      <c r="B649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A650">
+        <v>500</v>
+      </c>
+      <c r="B650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A651">
+        <v>500</v>
+      </c>
+      <c r="B651">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A652">
+        <v>500</v>
+      </c>
+      <c r="B652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A653">
+        <v>500</v>
+      </c>
+      <c r="B653">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A654">
+        <v>500</v>
+      </c>
+      <c r="B654">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A655">
+        <v>500</v>
+      </c>
+      <c r="B655">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A656">
+        <v>500</v>
+      </c>
+      <c r="B656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A657">
+        <v>500</v>
+      </c>
+      <c r="B657">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A658">
+        <v>500</v>
+      </c>
+      <c r="B658">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A659">
+        <v>500</v>
+      </c>
+      <c r="B659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A660">
+        <v>500</v>
+      </c>
+      <c r="B660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A661">
+        <v>500</v>
+      </c>
+      <c r="B661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A662">
+        <v>500</v>
+      </c>
+      <c r="B662">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A663">
+        <v>500</v>
+      </c>
+      <c r="B663">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A664">
+        <v>500</v>
+      </c>
+      <c r="B664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A665">
+        <v>500</v>
+      </c>
+      <c r="B665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A666">
+        <v>500</v>
+      </c>
+      <c r="B666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A667">
+        <v>500</v>
+      </c>
+      <c r="B667">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A668">
+        <v>500</v>
+      </c>
+      <c r="B668">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A669">
+        <v>500</v>
+      </c>
+      <c r="B669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A670">
+        <v>500</v>
+      </c>
+      <c r="B670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A671">
+        <v>500</v>
+      </c>
+      <c r="B671">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A672">
+        <v>500</v>
+      </c>
+      <c r="B672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A673">
+        <v>500</v>
+      </c>
+      <c r="B673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A674">
+        <v>500</v>
+      </c>
+      <c r="B674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A675">
+        <v>500</v>
+      </c>
+      <c r="B675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A676">
+        <v>500</v>
+      </c>
+      <c r="B676">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A677">
+        <v>500</v>
+      </c>
+      <c r="B677">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A678">
+        <v>500</v>
+      </c>
+      <c r="B678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A679">
+        <v>500</v>
+      </c>
+      <c r="B679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A680">
+        <v>500</v>
+      </c>
+      <c r="B680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A681">
+        <v>500</v>
+      </c>
+      <c r="B681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A682">
+        <v>500</v>
+      </c>
+      <c r="B682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A683">
+        <v>500</v>
+      </c>
+      <c r="B683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A684">
+        <v>500</v>
+      </c>
+      <c r="B684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A685">
+        <v>500</v>
+      </c>
+      <c r="B685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A686">
+        <v>500</v>
+      </c>
+      <c r="B686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A687">
+        <v>500</v>
+      </c>
+      <c r="B687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A688">
+        <v>500</v>
+      </c>
+      <c r="B688">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A689">
+        <v>500</v>
+      </c>
+      <c r="B689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A690">
+        <v>500</v>
+      </c>
+      <c r="B690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A691">
+        <v>500</v>
+      </c>
+      <c r="B691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A692">
+        <v>500</v>
+      </c>
+      <c r="B692">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A693">
+        <v>500</v>
+      </c>
+      <c r="B693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A694">
+        <v>500</v>
+      </c>
+      <c r="B694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A695">
+        <v>500</v>
+      </c>
+      <c r="B695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A696">
+        <v>500</v>
+      </c>
+      <c r="B696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A697">
+        <v>500</v>
+      </c>
+      <c r="B697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A698">
+        <v>500</v>
+      </c>
+      <c r="B698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A699">
+        <v>500</v>
+      </c>
+      <c r="B699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A700">
+        <v>500</v>
+      </c>
+      <c r="B700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A701">
+        <v>500</v>
+      </c>
+      <c r="B701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A702">
+        <v>500</v>
+      </c>
+      <c r="B702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A703">
+        <v>500</v>
+      </c>
+      <c r="B703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A704">
+        <v>500</v>
+      </c>
+      <c r="B704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A705">
+        <v>500</v>
+      </c>
+      <c r="B705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A706">
+        <v>500</v>
+      </c>
+      <c r="B706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A707">
+        <v>500</v>
+      </c>
+      <c r="B707">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A708">
+        <v>500</v>
+      </c>
+      <c r="B708">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A709">
+        <v>500</v>
+      </c>
+      <c r="B709">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A710">
+        <v>500</v>
+      </c>
+      <c r="B710">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A711">
+        <v>500</v>
+      </c>
+      <c r="B711">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A712">
+        <v>500</v>
+      </c>
+      <c r="B712">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A713">
+        <v>500</v>
+      </c>
+      <c r="B713">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A714">
+        <v>500</v>
+      </c>
+      <c r="B714">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A715">
+        <v>500</v>
+      </c>
+      <c r="B715">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A716">
+        <v>500</v>
+      </c>
+      <c r="B716">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A717">
+        <v>500</v>
+      </c>
+      <c r="B717">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A718">
+        <v>500</v>
+      </c>
+      <c r="B718">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A719">
+        <v>500</v>
+      </c>
+      <c r="B719">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A720">
+        <v>500</v>
+      </c>
+      <c r="B720">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A721">
+        <v>500</v>
+      </c>
+      <c r="B721">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A722">
+        <v>500</v>
+      </c>
+      <c r="B722">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A723">
+        <v>500</v>
+      </c>
+      <c r="B723">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A724">
+        <v>500</v>
+      </c>
+      <c r="B724">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A725">
+        <v>500</v>
+      </c>
+      <c r="B725">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A726">
+        <v>500</v>
+      </c>
+      <c r="B726">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A727">
+        <v>500</v>
+      </c>
+      <c r="B727">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A728">
+        <v>500</v>
+      </c>
+      <c r="B728">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A729">
+        <v>500</v>
+      </c>
+      <c r="B729">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A730">
+        <v>500</v>
+      </c>
+      <c r="B730">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A731">
+        <v>500</v>
+      </c>
+      <c r="B731">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A732">
+        <v>500</v>
+      </c>
+      <c r="B732">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A733">
+        <v>500</v>
+      </c>
+      <c r="B733">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A734">
+        <v>500</v>
+      </c>
+      <c r="B734">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A735">
+        <v>500</v>
+      </c>
+      <c r="B735">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A736">
+        <v>500</v>
+      </c>
+      <c r="B736">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A737">
+        <v>500</v>
+      </c>
+      <c r="B737">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A738">
+        <v>500</v>
+      </c>
+      <c r="B738">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A739">
+        <v>500</v>
+      </c>
+      <c r="B739">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A740">
+        <v>500</v>
+      </c>
+      <c r="B740">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A741">
+        <v>500</v>
+      </c>
+      <c r="B741">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A742">
+        <v>500</v>
+      </c>
+      <c r="B742">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A743">
+        <v>500</v>
+      </c>
+      <c r="B743">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A744">
+        <v>500</v>
+      </c>
+      <c r="B744">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A745">
+        <v>500</v>
+      </c>
+      <c r="B745">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A746">
+        <v>500</v>
+      </c>
+      <c r="B746">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A747">
+        <v>500</v>
+      </c>
+      <c r="B747">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A748">
+        <v>500</v>
+      </c>
+      <c r="B748">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A749">
+        <v>500</v>
+      </c>
+      <c r="B749">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A750">
+        <v>500</v>
+      </c>
+      <c r="B750">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A751">
+        <v>500</v>
+      </c>
+      <c r="B751">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A752">
+        <v>500</v>
+      </c>
+      <c r="B752">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A753">
+        <v>500</v>
+      </c>
+      <c r="B753">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A754">
+        <v>500</v>
+      </c>
+      <c r="B754">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A755">
+        <v>500</v>
+      </c>
+      <c r="B755">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A756">
+        <v>500</v>
+      </c>
+      <c r="B756">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A757">
+        <v>500</v>
+      </c>
+      <c r="B757">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A758">
+        <v>500</v>
+      </c>
+      <c r="B758">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A759">
+        <v>500</v>
+      </c>
+      <c r="B759">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A760">
+        <v>500</v>
+      </c>
+      <c r="B760">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A761">
+        <v>500</v>
+      </c>
+      <c r="B761">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A762">
+        <v>500</v>
+      </c>
+      <c r="B762">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A763">
+        <v>500</v>
+      </c>
+      <c r="B763">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A764">
+        <v>500</v>
+      </c>
+      <c r="B764">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A765">
+        <v>500</v>
+      </c>
+      <c r="B765">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A766">
+        <v>500</v>
+      </c>
+      <c r="B766">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A767">
+        <v>500</v>
+      </c>
+      <c r="B767">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A768">
+        <v>500</v>
+      </c>
+      <c r="B768">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A769">
+        <v>500</v>
+      </c>
+      <c r="B769">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A770">
+        <v>500</v>
+      </c>
+      <c r="B770">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A771">
+        <v>500</v>
+      </c>
+      <c r="B771">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A772">
+        <v>500</v>
+      </c>
+      <c r="B772">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A773">
+        <v>500</v>
+      </c>
+      <c r="B773">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A774">
+        <v>500</v>
+      </c>
+      <c r="B774">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A775">
+        <v>500</v>
+      </c>
+      <c r="B775">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A776">
+        <v>500</v>
+      </c>
+      <c r="B776">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A777">
+        <v>500</v>
+      </c>
+      <c r="B777">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A778">
+        <v>500</v>
+      </c>
+      <c r="B778">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A779">
+        <v>500</v>
+      </c>
+      <c r="B779">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A780">
+        <v>500</v>
+      </c>
+      <c r="B780">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A781">
+        <v>500</v>
+      </c>
+      <c r="B781">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A782">
+        <v>500</v>
+      </c>
+      <c r="B782">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A783">
+        <v>500</v>
+      </c>
+      <c r="B783">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A784">
+        <v>500</v>
+      </c>
+      <c r="B784">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A785">
+        <v>500</v>
+      </c>
+      <c r="B785">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A786">
+        <v>500</v>
+      </c>
+      <c r="B786">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A787">
+        <v>500</v>
+      </c>
+      <c r="B787">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A788">
+        <v>500</v>
+      </c>
+      <c r="B788">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A789">
+        <v>500</v>
+      </c>
+      <c r="B789">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A790">
+        <v>500</v>
+      </c>
+      <c r="B790">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A791">
+        <v>500</v>
+      </c>
+      <c r="B791">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A792">
+        <v>500</v>
+      </c>
+      <c r="B792">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A793">
+        <v>500</v>
+      </c>
+      <c r="B793">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A794">
+        <v>500</v>
+      </c>
+      <c r="B794">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A795">
+        <v>500</v>
+      </c>
+      <c r="B795">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A796">
+        <v>500</v>
+      </c>
+      <c r="B796">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A797">
+        <v>500</v>
+      </c>
+      <c r="B797">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A798">
+        <v>500</v>
+      </c>
+      <c r="B798">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A799">
+        <v>500</v>
+      </c>
+      <c r="B799">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A800">
+        <v>500</v>
+      </c>
+      <c r="B800">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A801">
+        <v>500</v>
+      </c>
+      <c r="B801">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A802">
+        <v>500</v>
+      </c>
+      <c r="B802">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A803">
+        <v>500</v>
+      </c>
+      <c r="B803">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A804">
+        <v>500</v>
+      </c>
+      <c r="B804">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A805">
+        <v>500</v>
+      </c>
+      <c r="B805">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A806">
+        <v>500</v>
+      </c>
+      <c r="B806">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A807">
+        <v>500</v>
+      </c>
+      <c r="B807">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A808">
+        <v>500</v>
+      </c>
+      <c r="B808">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A809">
+        <v>500</v>
+      </c>
+      <c r="B809">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A810">
+        <v>500</v>
+      </c>
+      <c r="B810">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A811">
+        <v>500</v>
+      </c>
+      <c r="B811">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A812">
+        <v>500</v>
+      </c>
+      <c r="B812">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A813">
+        <v>500</v>
+      </c>
+      <c r="B813">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A814">
+        <v>500</v>
+      </c>
+      <c r="B814">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A815">
+        <v>500</v>
+      </c>
+      <c r="B815">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A816">
+        <v>500</v>
+      </c>
+      <c r="B816">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A817">
+        <v>500</v>
+      </c>
+      <c r="B817">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A818">
+        <v>500</v>
+      </c>
+      <c r="B818">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A819">
+        <v>500</v>
+      </c>
+      <c r="B819">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A820">
+        <v>500</v>
+      </c>
+      <c r="B820">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A821">
+        <v>500</v>
+      </c>
+      <c r="B821">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A822">
+        <v>500</v>
+      </c>
+      <c r="B822">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A823">
+        <v>500</v>
+      </c>
+      <c r="B823">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A824">
+        <v>500</v>
+      </c>
+      <c r="B824">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A825">
+        <v>500</v>
+      </c>
+      <c r="B825">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A826">
+        <v>500</v>
+      </c>
+      <c r="B826">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A827">
+        <v>500</v>
+      </c>
+      <c r="B827">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A828">
+        <v>500</v>
+      </c>
+      <c r="B828">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A829">
+        <v>500</v>
+      </c>
+      <c r="B829">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A830">
+        <v>500</v>
+      </c>
+      <c r="B830">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A831">
+        <v>500</v>
+      </c>
+      <c r="B831">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A832">
+        <v>500</v>
+      </c>
+      <c r="B832">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A833">
+        <v>500</v>
+      </c>
+      <c r="B833">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A834">
+        <v>500</v>
+      </c>
+      <c r="B834">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A835">
+        <v>500</v>
+      </c>
+      <c r="B835">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A836">
+        <v>500</v>
+      </c>
+      <c r="B836">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A837">
+        <v>500</v>
+      </c>
+      <c r="B837">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A838">
+        <v>500</v>
+      </c>
+      <c r="B838">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A839">
+        <v>500</v>
+      </c>
+      <c r="B839">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A840">
+        <v>500</v>
+      </c>
+      <c r="B840">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A841">
+        <v>500</v>
+      </c>
+      <c r="B841">
+        <v>5.2861731260154185E-3</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A842">
+        <v>500</v>
+      </c>
+      <c r="B842">
+        <v>5.9919479177296731E-2</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A843">
+        <v>500</v>
+      </c>
+      <c r="B843">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A844">
+        <v>500</v>
+      </c>
+      <c r="B844">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A845">
+        <v>500</v>
+      </c>
+      <c r="B845">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A846">
+        <v>500</v>
+      </c>
+      <c r="B846">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A847">
+        <v>500</v>
+      </c>
+      <c r="B847">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A848">
+        <v>500</v>
+      </c>
+      <c r="B848">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A849">
+        <v>500</v>
+      </c>
+      <c r="B849">
+        <v>4.2321595436561499E-2</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A850">
+        <v>500</v>
+      </c>
+      <c r="B850">
+        <v>5.3116375025546517E-2</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A851">
+        <v>500</v>
+      </c>
+      <c r="B851">
+        <v>3.9274592878331793E-2</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A852">
+        <v>500</v>
+      </c>
+      <c r="B852">
+        <v>3.7388187008557658E-2</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A853">
+        <v>500</v>
+      </c>
+      <c r="B853">
+        <v>5.2576870702312373E-2</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A854">
+        <v>500</v>
+      </c>
+      <c r="B854">
+        <v>7.2746033135538707E-2</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A855">
+        <v>500</v>
+      </c>
+      <c r="B855">
+        <v>8.7187645880053635E-2</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A856">
+        <v>500</v>
+      </c>
+      <c r="B856">
+        <v>3.4523239280967524E-2</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A857">
+        <v>500</v>
+      </c>
+      <c r="B857">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A858">
+        <v>500</v>
+      </c>
+      <c r="B858">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A859">
+        <v>500</v>
+      </c>
+      <c r="B859">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A860">
+        <v>500</v>
+      </c>
+      <c r="B860">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A861">
+        <v>500</v>
+      </c>
+      <c r="B861">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A862">
+        <v>500</v>
+      </c>
+      <c r="B862">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A863">
+        <v>500</v>
+      </c>
+      <c r="B863">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A864">
+        <v>500</v>
+      </c>
+      <c r="B864">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A865">
+        <v>500</v>
+      </c>
+      <c r="B865">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A866">
+        <v>500</v>
+      </c>
+      <c r="B866">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A867">
+        <v>500</v>
+      </c>
+      <c r="B867">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A868">
+        <v>500</v>
+      </c>
+      <c r="B868">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A869">
+        <v>500</v>
+      </c>
+      <c r="B869">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A870">
+        <v>500</v>
+      </c>
+      <c r="B870">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A871">
+        <v>500</v>
+      </c>
+      <c r="B871">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A872">
+        <v>500</v>
+      </c>
+      <c r="B872">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A873">
+        <v>500</v>
+      </c>
+      <c r="B873">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A874">
+        <v>500</v>
+      </c>
+      <c r="B874">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A875">
+        <v>500</v>
+      </c>
+      <c r="B875">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A876">
+        <v>500</v>
+      </c>
+      <c r="B876">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A877">
+        <v>500</v>
+      </c>
+      <c r="B877">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A878">
+        <v>500</v>
+      </c>
+      <c r="B878">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A879">
+        <v>500</v>
+      </c>
+      <c r="B879">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A880">
+        <v>500</v>
+      </c>
+      <c r="B880">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A881">
+        <v>500</v>
+      </c>
+      <c r="B881">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A882">
+        <v>500</v>
+      </c>
+      <c r="B882">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A883">
+        <v>500</v>
+      </c>
+      <c r="B883">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A884">
+        <v>500</v>
+      </c>
+      <c r="B884">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A885">
+        <v>500</v>
+      </c>
+      <c r="B885">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A886">
+        <v>500</v>
+      </c>
+      <c r="B886">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A887">
+        <v>500</v>
+      </c>
+      <c r="B887">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A888">
+        <v>500</v>
+      </c>
+      <c r="B888">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A889">
+        <v>500</v>
+      </c>
+      <c r="B889">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A890">
+        <v>500</v>
+      </c>
+      <c r="B890">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A891">
+        <v>500</v>
+      </c>
+      <c r="B891">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A892">
+        <v>500</v>
+      </c>
+      <c r="B892">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A893">
+        <v>500</v>
+      </c>
+      <c r="B893">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A894">
+        <v>500</v>
+      </c>
+      <c r="B894">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A895">
+        <v>500</v>
+      </c>
+      <c r="B895">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A896">
+        <v>500</v>
+      </c>
+      <c r="B896">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A897">
+        <v>500</v>
+      </c>
+      <c r="B897">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A898">
+        <v>500</v>
+      </c>
+      <c r="B898">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A899">
+        <v>500</v>
+      </c>
+      <c r="B899">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A900">
+        <v>500</v>
+      </c>
+      <c r="B900">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A901">
+        <v>500</v>
+      </c>
+      <c r="B901">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A902">
+        <v>500</v>
+      </c>
+      <c r="B902">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A903">
+        <v>500</v>
+      </c>
+      <c r="B903">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A904">
+        <v>500</v>
+      </c>
+      <c r="B904">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A905">
+        <v>500</v>
+      </c>
+      <c r="B905">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A906">
+        <v>500</v>
+      </c>
+      <c r="B906">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A907">
+        <v>500</v>
+      </c>
+      <c r="B907">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A908">
+        <v>500</v>
+      </c>
+      <c r="B908">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A909">
+        <v>500</v>
+      </c>
+      <c r="B909">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A910">
+        <v>500</v>
+      </c>
+      <c r="B910">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A911">
+        <v>500</v>
+      </c>
+      <c r="B911">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A912">
+        <v>500</v>
+      </c>
+      <c r="B912">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A913">
+        <v>500</v>
+      </c>
+      <c r="B913">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A914">
+        <v>500</v>
+      </c>
+      <c r="B914">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A915">
+        <v>500</v>
+      </c>
+      <c r="B915">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A916">
+        <v>500</v>
+      </c>
+      <c r="B916">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A917">
+        <v>500</v>
+      </c>
+      <c r="B917">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A918">
+        <v>500</v>
+      </c>
+      <c r="B918">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A919">
+        <v>500</v>
+      </c>
+      <c r="B919">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A920">
+        <v>500</v>
+      </c>
+      <c r="B920">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A921">
+        <v>500</v>
+      </c>
+      <c r="B921">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A922">
+        <v>500</v>
+      </c>
+      <c r="B922">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A923">
+        <v>500</v>
+      </c>
+      <c r="B923">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A924">
+        <v>500</v>
+      </c>
+      <c r="B924">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A925">
+        <v>500</v>
+      </c>
+      <c r="B925">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A926">
+        <v>500</v>
+      </c>
+      <c r="B926">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A927">
+        <v>500</v>
+      </c>
+      <c r="B927">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A928">
+        <v>500</v>
+      </c>
+      <c r="B928">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A929">
+        <v>500</v>
+      </c>
+      <c r="B929">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A930">
+        <v>500</v>
+      </c>
+      <c r="B930">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A931">
+        <v>500</v>
+      </c>
+      <c r="B931">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A932">
+        <v>500</v>
+      </c>
+      <c r="B932">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A933">
+        <v>500</v>
+      </c>
+      <c r="B933">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A934">
+        <v>500</v>
+      </c>
+      <c r="B934">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A935">
+        <v>500</v>
+      </c>
+      <c r="B935">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A936">
+        <v>500</v>
+      </c>
+      <c r="B936">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A937">
+        <v>500</v>
+      </c>
+      <c r="B937">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A938">
+        <v>500</v>
+      </c>
+      <c r="B938">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A939">
+        <v>500</v>
+      </c>
+      <c r="B939">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A940">
+        <v>500</v>
+      </c>
+      <c r="B940">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A941">
+        <v>500</v>
+      </c>
+      <c r="B941">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A942">
+        <v>500</v>
+      </c>
+      <c r="B942">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A943">
+        <v>500</v>
+      </c>
+      <c r="B943">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A944">
+        <v>500</v>
+      </c>
+      <c r="B944">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A945">
+        <v>500</v>
+      </c>
+      <c r="B945">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A946">
+        <v>500</v>
+      </c>
+      <c r="B946">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A947">
+        <v>500</v>
+      </c>
+      <c r="B947">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A948">
+        <v>500</v>
+      </c>
+      <c r="B948">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A949">
+        <v>500</v>
+      </c>
+      <c r="B949">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A950">
+        <v>500</v>
+      </c>
+      <c r="B950">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A951">
+        <v>500</v>
+      </c>
+      <c r="B951">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A952">
+        <v>500</v>
+      </c>
+      <c r="B952">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A953">
+        <v>500</v>
+      </c>
+      <c r="B953">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A954">
+        <v>500</v>
+      </c>
+      <c r="B954">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A955">
+        <v>500</v>
+      </c>
+      <c r="B955">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A956">
+        <v>500</v>
+      </c>
+      <c r="B956">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A957">
+        <v>500</v>
+      </c>
+      <c r="B957">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A958">
+        <v>500</v>
+      </c>
+      <c r="B958">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A959">
+        <v>500</v>
+      </c>
+      <c r="B959">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A960">
+        <v>500</v>
+      </c>
+      <c r="B960">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A961">
+        <v>500</v>
+      </c>
+      <c r="B961">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A962">
+        <v>500</v>
+      </c>
+      <c r="B962">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A963">
+        <v>500</v>
+      </c>
+      <c r="B963">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A964">
+        <v>500</v>
+      </c>
+      <c r="B964">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A965">
+        <v>500</v>
+      </c>
+      <c r="B965">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A966">
+        <v>500</v>
+      </c>
+      <c r="B966">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A967">
+        <v>500</v>
+      </c>
+      <c r="B967">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A968">
+        <v>500</v>
+      </c>
+      <c r="B968">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A969">
+        <v>500</v>
+      </c>
+      <c r="B969">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A970">
+        <v>500</v>
+      </c>
+      <c r="B970">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A971">
+        <v>500</v>
+      </c>
+      <c r="B971">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A972">
+        <v>500</v>
+      </c>
+      <c r="B972">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A973">
+        <v>500</v>
+      </c>
+      <c r="B973">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A974">
+        <v>500</v>
+      </c>
+      <c r="B974">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A975">
+        <v>500</v>
+      </c>
+      <c r="B975">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="976" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A976">
+        <v>500</v>
+      </c>
+      <c r="B976">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="977" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A977">
+        <v>500</v>
+      </c>
+      <c r="B977">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="978" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A978">
+        <v>500</v>
+      </c>
+      <c r="B978">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A979">
+        <v>500</v>
+      </c>
+      <c r="B979">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="980" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A980">
+        <v>500</v>
+      </c>
+      <c r="B980">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="981" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A981">
+        <v>500</v>
+      </c>
+      <c r="B981">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A982">
+        <v>500</v>
+      </c>
+      <c r="B982">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="983" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A983">
+        <v>500</v>
+      </c>
+      <c r="B983">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A984">
+        <v>500</v>
+      </c>
+      <c r="B984">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A985">
+        <v>500</v>
+      </c>
+      <c r="B985">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A986">
+        <v>500</v>
+      </c>
+      <c r="B986">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A987">
+        <v>500</v>
+      </c>
+      <c r="B987">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A988">
+        <v>500</v>
+      </c>
+      <c r="B988">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="989" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A989">
+        <v>500</v>
+      </c>
+      <c r="B989">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A990">
+        <v>500</v>
+      </c>
+      <c r="B990">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A991">
+        <v>500</v>
+      </c>
+      <c r="B991">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="992" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A992">
+        <v>500</v>
+      </c>
+      <c r="B992">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A993">
+        <v>500</v>
+      </c>
+      <c r="B993">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A994">
+        <v>500</v>
+      </c>
+      <c r="B994">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="995" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A995">
+        <v>500</v>
+      </c>
+      <c r="B995">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A996">
+        <v>500</v>
+      </c>
+      <c r="B996">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A997">
+        <v>500</v>
+      </c>
+      <c r="B997">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A998">
+        <v>500</v>
+      </c>
+      <c r="B998">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A999">
+        <v>500</v>
+      </c>
+      <c r="B999">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1000">
+        <v>500</v>
+      </c>
+      <c r="B1000">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/OutputData.xlsx
+++ b/OutputData.xlsx
@@ -338,6693 +338,6697 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>347.69371667915914</v>
+        <v>436.87432808551569</v>
       </c>
       <c r="B1">
-        <v>51.804913555152652</v>
+        <v>441.02294506972117</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>348.39813212560404</v>
+        <v>436.68176493183682</v>
       </c>
       <c r="B2">
-        <v>51.60267687001452</v>
+        <v>442.11029558904585</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>349.19288584430325</v>
+        <v>436.50709782305927</v>
       </c>
       <c r="B3">
-        <v>51.455924340806888</v>
+        <v>443.18564163185005</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>349.94609099021216</v>
+        <v>436.29221393453258</v>
       </c>
       <c r="B4">
-        <v>51.396083835653172</v>
+        <v>444.29290537032011</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>350.61873137218782</v>
+        <v>436.21187170013604</v>
       </c>
       <c r="B5">
-        <v>51.299521527741568</v>
+        <v>445.45281261764802</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>351.21552645335208</v>
+        <v>436.15765659599344</v>
       </c>
       <c r="B6">
-        <v>51.213259603809163</v>
+        <v>446.64044385771808</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>351.75102422839973</v>
+        <v>436.08929218785113</v>
       </c>
       <c r="B7">
-        <v>51.127115696642235</v>
+        <v>447.80749481224535</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>352.29975684038084</v>
+        <v>435.86695397719541</v>
       </c>
       <c r="B8">
-        <v>51.129448056087604</v>
+        <v>449.09012661219117</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>352.71858913890105</v>
+        <v>435.5125895283249</v>
       </c>
       <c r="B9">
-        <v>51.081284234489551</v>
+        <v>450.4867710438985</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>353.11497058635547</v>
+        <v>435.13450401365321</v>
       </c>
       <c r="B10">
-        <v>50.99938064321109</v>
+        <v>451.90204127614953</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>353.40763735606919</v>
+        <v>434.82948702568302</v>
       </c>
       <c r="B11">
-        <v>50.891975861585806</v>
+        <v>453.3460894008025</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>353.73812270804024</v>
+        <v>434.64863283754414</v>
       </c>
       <c r="B12">
-        <v>50.867866212171236</v>
+        <v>454.81102908601719</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>354.0160734812589</v>
+        <v>434.47736071560729</v>
       </c>
       <c r="B13">
-        <v>50.859255057438695</v>
+        <v>456.26124342668788</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>354.38753112180353</v>
+        <v>434.35021086242256</v>
       </c>
       <c r="B14">
-        <v>50.830001168804841</v>
+        <v>457.73163350817538</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>354.68915319913884</v>
+        <v>434.18788370556803</v>
       </c>
       <c r="B15">
-        <v>50.812173666085165</v>
+        <v>459.32631442712682</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>354.9784823681228</v>
+        <v>433.88033926830195</v>
       </c>
       <c r="B16">
-        <v>50.814013299417674</v>
+        <v>460.87192260189283</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>355.29188457342701</v>
+        <v>433.74644418761352</v>
       </c>
       <c r="B17">
-        <v>50.872581805666272</v>
+        <v>462.27576457237228</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>355.51534507118146</v>
+        <v>433.6797655805205</v>
       </c>
       <c r="B18">
-        <v>50.944569053325175</v>
+        <v>463.63977698166678</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>355.71811879709838</v>
+        <v>433.72678169710332</v>
       </c>
       <c r="B19">
-        <v>51.01173935346295</v>
+        <v>464.95166971856906</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>355.94160965260562</v>
+        <v>433.83337003748835</v>
       </c>
       <c r="B20">
-        <v>51.04993410966204</v>
+        <v>466.18184165607022</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>356.16364819348746</v>
+        <v>433.95163679043895</v>
       </c>
       <c r="B21">
-        <v>51.127581883884389</v>
+        <v>467.4436780911953</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>356.4664231646633</v>
+        <v>433.95070906193695</v>
       </c>
       <c r="B22">
-        <v>51.094156026575227</v>
+        <v>468.65987217083006</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>356.75898607337007</v>
+        <v>433.94729405323829</v>
       </c>
       <c r="B23">
-        <v>51.170130221046399</v>
+        <v>469.89239990340286</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>357.13545415543791</v>
+        <v>434.02805525024559</v>
       </c>
       <c r="B24">
-        <v>51.154543679955026</v>
+        <v>471.09596939523749</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>357.46955233519037</v>
+        <v>434.19189069398641</v>
       </c>
       <c r="B25">
-        <v>51.188017930293093</v>
+        <v>472.28031450214411</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>357.77223736379466</v>
+        <v>434.32976843972</v>
       </c>
       <c r="B26">
-        <v>51.218624746412317</v>
+        <v>473.47255901527757</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>358.0381491267658</v>
+        <v>434.43905131804377</v>
       </c>
       <c r="B27">
-        <v>51.205778728395387</v>
+        <v>474.7643534746299</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>358.21840798332016</v>
+        <v>434.62358750687179</v>
       </c>
       <c r="B28">
-        <v>51.148840690492442</v>
+        <v>476.0991308869651</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>358.44356550944235</v>
+        <v>434.68374457486505</v>
       </c>
       <c r="B29">
-        <v>51.03805702684253</v>
+        <v>477.4701867973165</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>358.64606235354466</v>
+        <v>434.56659246731567</v>
       </c>
       <c r="B30">
-        <v>50.870071818062861</v>
+        <v>478.8622037345836</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>358.89739473367297</v>
+        <v>434.39157417256217</v>
       </c>
       <c r="B31">
-        <v>50.721496713981509</v>
+        <v>480.30637862170084</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>359.07193807580637</v>
+        <v>434.2222153207984</v>
       </c>
       <c r="B32">
-        <v>50.586999945299361</v>
+        <v>481.87009474096084</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>359.29616496760082</v>
+        <v>434.04271811658379</v>
       </c>
       <c r="B33">
-        <v>50.388911020673255</v>
+        <v>483.44026666174818</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>359.48783054305312</v>
+        <v>433.92081169883909</v>
       </c>
       <c r="B34">
-        <v>50.198230886415473</v>
+        <v>484.99319103075737</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>359.64179234029308</v>
+        <v>433.82213086908428</v>
       </c>
       <c r="B35">
-        <v>49.970686279891268</v>
+        <v>486.5528332691074</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>359.78804969731937</v>
+        <v>433.72172868512121</v>
       </c>
       <c r="B36">
-        <v>49.659125533721507</v>
+        <v>488.18991748889965</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>359.97536426050482</v>
+        <v>433.70222074417535</v>
       </c>
       <c r="B37">
-        <v>49.496696212387477</v>
+        <v>489.83321924237708</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>360.19109300044011</v>
+        <v>433.6624075684453</v>
       </c>
       <c r="B38">
-        <v>49.385858793574926</v>
+        <v>491.51486110431625</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>360.40979901432519</v>
+        <v>433.67080703957907</v>
       </c>
       <c r="B39">
-        <v>49.189128524841045</v>
+        <v>493.17606451774998</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>360.6005601278199</v>
+        <v>433.62589285182094</v>
       </c>
       <c r="B40">
-        <v>48.962537695774039</v>
+        <v>494.84562099275126</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>360.77101671468159</v>
+        <v>433.47324846161877</v>
       </c>
       <c r="B41">
-        <v>48.758735480334416</v>
+        <v>496.55973169290309</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>360.96516115894798</v>
+        <v>433.22073435009332</v>
       </c>
       <c r="B42">
-        <v>48.536057323974212</v>
+        <v>498.2927294427717</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>361.21471020240369</v>
+        <v>432.99320164532634</v>
       </c>
       <c r="B43">
-        <v>48.269701757578979</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>361.40787954773378</v>
+        <v>432.82489480421611</v>
       </c>
       <c r="B44">
-        <v>48.033133942022054</v>
+        <v>500</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>361.6023960222235</v>
+        <v>432.53887327355824</v>
       </c>
       <c r="B45">
-        <v>47.711254820903832</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>361.83885860000493</v>
+        <v>432.27168900302672</v>
       </c>
       <c r="B46">
-        <v>47.348252184616911</v>
+        <v>500</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>361.99128340004484</v>
+        <v>432.04510652069979</v>
       </c>
       <c r="B47">
-        <v>47.000097290554692</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>362.22331415985826</v>
+        <v>431.75808934549019</v>
       </c>
       <c r="B48">
-        <v>46.607068365908837</v>
+        <v>500</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>362.51373601527013</v>
+        <v>431.41619477134913</v>
       </c>
       <c r="B49">
-        <v>46.093565263325189</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>362.78645449009514</v>
+        <v>431.02954005657404</v>
       </c>
       <c r="B50">
-        <v>45.585623750614403</v>
+        <v>500</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>363.05151420427495</v>
+        <v>430.74481270480669</v>
       </c>
       <c r="B51">
-        <v>45.133812561251517</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>363.25339503175763</v>
+        <v>430.37017235589173</v>
       </c>
       <c r="B52">
-        <v>44.736162617171544</v>
+        <v>500</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>363.42756387466363</v>
+        <v>429.96449626459952</v>
       </c>
       <c r="B53">
-        <v>44.272532341324919</v>
+        <v>500</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>363.62170711267737</v>
+        <v>429.41552040643398</v>
       </c>
       <c r="B54">
-        <v>43.802764349118441</v>
+        <v>500</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>363.88000630922892</v>
+        <v>428.84165430066906</v>
       </c>
       <c r="B55">
-        <v>43.286257429455084</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>364.14973529650263</v>
+        <v>428.28142012676619</v>
       </c>
       <c r="B56">
-        <v>42.776190003816929</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>364.31545492884504</v>
+        <v>427.73489911648659</v>
       </c>
       <c r="B57">
-        <v>42.204404291070873</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>364.6017621507591</v>
+        <v>427.16771473512256</v>
       </c>
       <c r="B58">
-        <v>41.688492275942941</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>364.95266335897702</v>
+        <v>426.61183904797628</v>
       </c>
       <c r="B59">
-        <v>41.18433556380127</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>365.34035137371882</v>
+        <v>426.10196710324061</v>
       </c>
       <c r="B60">
-        <v>40.683441712873261</v>
+        <v>500</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>365.69323228190751</v>
+        <v>425.50404011246019</v>
       </c>
       <c r="B61">
-        <v>40.118222769086444</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>366.09330441921054</v>
+        <v>424.88868669150605</v>
       </c>
       <c r="B62">
-        <v>39.578850584119074</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>366.44580817779604</v>
+        <v>424.25483453303275</v>
       </c>
       <c r="B63">
-        <v>38.997018563339893</v>
+        <v>500</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>366.72034145611917</v>
+        <v>423.43859756108736</v>
       </c>
       <c r="B64">
-        <v>38.435137385749066</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>366.91149809603257</v>
+        <v>422.42010499557006</v>
       </c>
       <c r="B65">
-        <v>37.837853560342737</v>
+        <v>500</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>367.19829949208287</v>
+        <v>421.28604197594512</v>
       </c>
       <c r="B66">
-        <v>37.139552275625306</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>367.38648595979487</v>
+        <v>420.09248687361395</v>
       </c>
       <c r="B67">
-        <v>36.467555526069823</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>367.63337547629004</v>
+        <v>418.89583979224597</v>
       </c>
       <c r="B68">
-        <v>35.935353808013346</v>
+        <v>500</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>367.93294460735603</v>
+        <v>417.80760226828454</v>
       </c>
       <c r="B69">
-        <v>35.336325759748931</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>368.25428288236719</v>
+        <v>416.79773205669778</v>
       </c>
       <c r="B70">
-        <v>34.790259838468579</v>
+        <v>500</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>368.58075695660176</v>
+        <v>415.93223793176111</v>
       </c>
       <c r="B71">
-        <v>34.263886566974627</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>368.9603924201316</v>
+        <v>415.19737579413572</v>
       </c>
       <c r="B72">
-        <v>33.704018136079355</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>369.33488067002753</v>
+        <v>414.40151039664499</v>
       </c>
       <c r="B73">
-        <v>33.164680942141885</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>369.74373630868695</v>
+        <v>413.60021808309097</v>
       </c>
       <c r="B74">
-        <v>32.499354879349731</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>370.23180677367702</v>
+        <v>412.916359068529</v>
       </c>
       <c r="B75">
-        <v>31.773395756804376</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>370.71150069683591</v>
+        <v>412.26078940168327</v>
       </c>
       <c r="B76">
-        <v>31.129412934668235</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>371.17366466327104</v>
+        <v>411.63205812640098</v>
       </c>
       <c r="B77">
-        <v>30.454912355379943</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>371.63019582032626</v>
+        <v>410.99199401058161</v>
       </c>
       <c r="B78">
-        <v>29.80212506851489</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>372.02637949430931</v>
+        <v>410.46018722414425</v>
       </c>
       <c r="B79">
-        <v>29.164845070502945</v>
+        <v>500</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>372.42649559451274</v>
+        <v>409.835723871298</v>
       </c>
       <c r="B80">
-        <v>28.537100288866675</v>
+        <v>500</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>372.73333043199102</v>
+        <v>409.11568341278212</v>
       </c>
       <c r="B81">
-        <v>27.982442923024717</v>
+        <v>500</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>372.99301190116296</v>
+        <v>408.40422370108871</v>
       </c>
       <c r="B82">
-        <v>27.460221729406221</v>
+        <v>500</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>373.17356240730726</v>
+        <v>407.63954235851935</v>
       </c>
       <c r="B83">
-        <v>26.913534699091738</v>
+        <v>500</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>373.43993170907947</v>
+        <v>406.9131576751069</v>
       </c>
       <c r="B84">
-        <v>26.300581647157578</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>373.63517309128366</v>
+        <v>406.22449994170182</v>
       </c>
       <c r="B85">
-        <v>25.735795380679221</v>
+        <v>500</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>373.82987860549639</v>
+        <v>405.51284581207705</v>
       </c>
       <c r="B86">
-        <v>25.1399684887954</v>
+        <v>500</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>374.07413437383735</v>
+        <v>404.74258093038975</v>
       </c>
       <c r="B87">
-        <v>24.477889982716125</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>374.34600772715413</v>
+        <v>403.91748589986162</v>
       </c>
       <c r="B88">
-        <v>23.779368835186474</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>374.59547403667517</v>
+        <v>403.08681789705565</v>
       </c>
       <c r="B89">
-        <v>22.992737337299527</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>374.85028300433117</v>
+        <v>402.31464979888716</v>
       </c>
       <c r="B90">
-        <v>22.323053400027124</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>375.14764442751385</v>
+        <v>401.55021247286248</v>
       </c>
       <c r="B91">
-        <v>21.696753013859674</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>375.39690395835345</v>
+        <v>400.76551023454078</v>
       </c>
       <c r="B92">
-        <v>21.037102035764313</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>375.61812443386515</v>
+        <v>399.99101676461851</v>
       </c>
       <c r="B93">
-        <v>20.333589293182332</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>375.78686190433223</v>
+        <v>399.2380245655001</v>
       </c>
       <c r="B94">
-        <v>19.632206693771479</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>375.88177592438291</v>
+        <v>398.45877071543106</v>
       </c>
       <c r="B95">
-        <v>19.090070652315404</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>375.9872048955458</v>
+        <v>397.62315047877109</v>
       </c>
       <c r="B96">
-        <v>18.439910404162841</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>376.01604664496875</v>
+        <v>396.75794288506148</v>
       </c>
       <c r="B97">
-        <v>17.766013561853857</v>
+        <v>500</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>376.03804933042261</v>
+        <v>396.03344941954231</v>
       </c>
       <c r="B98">
-        <v>17.097861367949669</v>
+        <v>500</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>376.02202424191188</v>
+        <v>395.22955521632667</v>
       </c>
       <c r="B99">
-        <v>16.392544663529122</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>375.99343462924895</v>
+        <v>394.33421255274692</v>
       </c>
       <c r="B100">
-        <v>15.64146259189007</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>375.98971828740054</v>
+        <v>393.42773353206894</v>
       </c>
       <c r="B101">
-        <v>14.957317948046072</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>375.98665083251518</v>
+        <v>392.53198011984398</v>
       </c>
       <c r="B102">
-        <v>14.227042492334773</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>375.98826910485536</v>
+        <v>391.58893829905617</v>
       </c>
       <c r="B103">
-        <v>13.52390233574318</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>375.90508898083948</v>
+        <v>390.48460383544995</v>
       </c>
       <c r="B104">
-        <v>12.773639119684702</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>375.89298091100522</v>
+        <v>389.27129400579918</v>
       </c>
       <c r="B105">
-        <v>12.016615128096777</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>375.9335261128814</v>
+        <v>388.1113157530134</v>
       </c>
       <c r="B106">
-        <v>11.270558486564974</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>375.90180670667741</v>
+        <v>386.95735690364216</v>
       </c>
       <c r="B107">
-        <v>10.548974403486854</v>
+        <v>500</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>375.938548126255</v>
+        <v>385.79909457856672</v>
       </c>
       <c r="B108">
-        <v>9.785772026008841</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>375.97850331744212</v>
+        <v>384.65573204267037</v>
       </c>
       <c r="B109">
-        <v>8.9372365157054308</v>
+        <v>500</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>376.13936709418584</v>
+        <v>383.35997849199759</v>
       </c>
       <c r="B110">
-        <v>8.0396410655876078</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>376.24081217325312</v>
+        <v>381.90683084519344</v>
       </c>
       <c r="B111">
-        <v>7.1542247114774957</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>376.41062252272155</v>
+        <v>380.34302436334252</v>
       </c>
       <c r="B112">
-        <v>6.3074301987710939</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>376.65011018573375</v>
+        <v>378.97137898850968</v>
       </c>
       <c r="B113">
-        <v>5.4921223910803914</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>376.90750322444012</v>
+        <v>377.7720662259519</v>
       </c>
       <c r="B114">
-        <v>4.7099775634888488</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>377.26017595088103</v>
+        <v>376.74911849014967</v>
       </c>
       <c r="B115">
-        <v>3.9229783206904139</v>
+        <v>500</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>377.61401530383904</v>
+        <v>375.80460831566495</v>
       </c>
       <c r="B116">
-        <v>3.152111082191329</v>
+        <v>500</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>377.92655050682322</v>
+        <v>374.75198444451212</v>
       </c>
       <c r="B117">
-        <v>2.5002681939827056</v>
+        <v>500</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>378.27179814186223</v>
+        <v>373.66911312135977</v>
       </c>
       <c r="B118">
-        <v>1.8748227928279335</v>
+        <v>500</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>378.5762757038292</v>
+        <v>372.7459423967133</v>
       </c>
       <c r="B119">
-        <v>1.2975912908452052</v>
+        <v>500</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>378.88207755593209</v>
+        <v>371.73544631291895</v>
       </c>
       <c r="B120">
-        <v>0.74390208010177949</v>
+        <v>500</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>379.26914982689158</v>
+        <v>370.6511145502464</v>
       </c>
       <c r="B121">
-        <v>0.25706158651326338</v>
+        <v>500</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>379.71122267567728</v>
+        <v>369.48214423216308</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>380.10106127718205</v>
+        <v>368.18984335665846</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>380.5773902860065</v>
+        <v>366.85830938979939</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>381.05703779688542</v>
+        <v>365.56416219939496</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>381.55864138950949</v>
+        <v>364.30189543736896</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>381.96444489500607</v>
+        <v>363.07428631522123</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>382.29806404167482</v>
+        <v>361.96644507612928</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>382.71476495515333</v>
+        <v>360.92041156875553</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>383.04035126646812</v>
+        <v>359.93475626468637</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>383.38503949325269</v>
+        <v>358.8902072722513</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>383.71809117080926</v>
+        <v>357.83948933741272</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>384.0207157139215</v>
+        <v>356.83069165850759</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>384.3402873959916</v>
+        <v>355.90304808414731</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>384.71188110819054</v>
+        <v>355.10460155231942</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>385.10050520792697</v>
+        <v>354.36491179911775</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>385.46541499757438</v>
+        <v>353.66111845821587</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>385.72633982311669</v>
+        <v>352.86747532251849</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>386.02928547533855</v>
+        <v>352.15278338674102</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>386.29572523921547</v>
+        <v>351.44377775816048</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>386.63743794101327</v>
+        <v>350.74589524406917</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>386.91520873242263</v>
+        <v>350.04620131053179</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>387.29178180708476</v>
+        <v>349.34263482445022</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>387.66404219190389</v>
+        <v>348.64577543370018</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>388.10429931189486</v>
+        <v>348.06461539161342</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>388.4837459318428</v>
+        <v>347.5191326436958</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>388.96504212424617</v>
+        <v>346.91957822006532</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>389.50081303764989</v>
+        <v>346.41052020032475</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>390.10518605251639</v>
+        <v>345.81572948612967</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>390.63706574517124</v>
+        <v>345.18078325185411</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>391.29077910354056</v>
+        <v>344.61201769475656</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>391.99439993617602</v>
+        <v>344.06724895860168</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>392.72879759668308</v>
+        <v>343.55030633849179</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>393.51112206033741</v>
+        <v>343.15904964491671</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>394.36145905147225</v>
+        <v>342.81830679399809</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>395.21950781477676</v>
+        <v>342.39329365305804</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>396.10950059812336</v>
+        <v>342.00117312648422</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>397.06823231741743</v>
+        <v>341.56413915441652</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>398.07866757065619</v>
+        <v>341.19552766089436</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>399.10931474534334</v>
+        <v>340.9215932246849</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>400.09920254419706</v>
+        <v>340.6192036677362</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>401.16434514789387</v>
+        <v>340.18977471401433</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>402.22134108971528</v>
+        <v>339.82602900723413</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>403.30989783753057</v>
+        <v>339.50114929941986</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>404.36017127944115</v>
+        <v>339.2808980881415</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>405.38780129531443</v>
+        <v>339.02478748390649</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>406.53860000039077</v>
+        <v>338.69865644346538</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>407.64259856454265</v>
+        <v>338.41945639056524</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>408.69123421236492</v>
+        <v>338.08115044005189</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>409.76701247738555</v>
+        <v>337.75625102168965</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>410.78800593674646</v>
+        <v>337.4827646378925</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>411.91036929721918</v>
+        <v>337.30169474659687</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>412.96634624660572</v>
+        <v>337.11683549313869</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>414.04089986856587</v>
+        <v>336.95765327352291</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>415.10602870692384</v>
+        <v>336.86952103847693</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>416.15913742735398</v>
+        <v>336.86706752455291</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>417.21653693904341</v>
+        <v>336.82221743060751</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>418.38851017528833</v>
+        <v>336.84998996735891</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>419.59931252803921</v>
+        <v>336.83516783011163</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>420.8660051520622</v>
+        <v>336.79477763920244</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>422.16929195633298</v>
+        <v>336.71547692150688</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>423.4776427867331</v>
+        <v>336.71316846768877</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>424.84312983231075</v>
+        <v>336.7906436095102</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>426.21510622557787</v>
+        <v>336.7108453696116</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>427.51707002478463</v>
+        <v>336.52233756152583</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>428.8081882896941</v>
+        <v>336.34021032619381</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>430.11818051380334</v>
+        <v>336.14728772425769</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>431.41596397391521</v>
+        <v>335.79725961225751</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>432.75950162681062</v>
+        <v>335.43678563422037</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>434.06446950352506</v>
+        <v>334.95142977088659</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>435.33022871541874</v>
+        <v>334.38890239082872</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>436.56989233411878</v>
+        <v>333.78269075237068</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>437.85022597010936</v>
+        <v>333.35820492023413</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>439.07648136378702</v>
+        <v>332.99069980145845</v>
       </c>
       <c r="B194">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>440.31043752731995</v>
+        <v>332.58760445451827</v>
       </c>
       <c r="B195">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>441.47174995078552</v>
+        <v>332.20699236384252</v>
       </c>
       <c r="B196">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>442.5778494284778</v>
+        <v>331.86928325146374</v>
       </c>
       <c r="B197">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>443.7956186769552</v>
+        <v>331.52366199979105</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>445.08923054270377</v>
+        <v>331.23024750496415</v>
       </c>
       <c r="B199">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>446.30214101702649</v>
+        <v>330.97330049276445</v>
       </c>
       <c r="B200">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>447.42288165438032</v>
+        <v>330.67602214144119</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>448.60411093544485</v>
+        <v>330.41557884885071</v>
       </c>
       <c r="B202">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>449.8304052823965</v>
+        <v>330.17591822174103</v>
       </c>
       <c r="B203">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>451.06484024210147</v>
+        <v>329.93293221912427</v>
       </c>
       <c r="B204">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>452.28109924383898</v>
+        <v>329.53563842099811</v>
       </c>
       <c r="B205">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>453.37424525081121</v>
+        <v>329.06291225774629</v>
       </c>
       <c r="B206">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>454.475162444749</v>
+        <v>328.55612281847704</v>
       </c>
       <c r="B207">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>455.59678833839502</v>
+        <v>328.07322424453412</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>456.74676333026179</v>
+        <v>327.61937084443775</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>457.88653919458108</v>
+        <v>327.27717572881426</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>459.02026475082783</v>
+        <v>326.94275757059376</v>
       </c>
       <c r="B211">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>460.26820257166497</v>
+        <v>326.63564581440261</v>
       </c>
       <c r="B212">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>461.41886796702397</v>
+        <v>326.30735082788539</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>462.50930819770946</v>
+        <v>325.87799149083185</v>
       </c>
       <c r="B214">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>463.59653397035544</v>
+        <v>325.47467941679798</v>
       </c>
       <c r="B215">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>464.71774201477047</v>
+        <v>325.03647696069174</v>
       </c>
       <c r="B216">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217">
-        <v>465.87718563579256</v>
+        <v>324.62255763181366</v>
       </c>
       <c r="B217">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218">
-        <v>467.07819540838409</v>
+        <v>324.19992848804839</v>
       </c>
       <c r="B218">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>468.24643740404082</v>
+        <v>324.03461697710168</v>
       </c>
       <c r="B219">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220">
-        <v>469.41206756861874</v>
+        <v>323.8240880701664</v>
       </c>
       <c r="B220">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221">
-        <v>470.56990226822279</v>
+        <v>323.58885578241558</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222">
-        <v>471.6771543812979</v>
+        <v>323.51282181511453</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223">
-        <v>472.90839125081681</v>
+        <v>323.36293911305404</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224">
-        <v>474.14476545731509</v>
+        <v>323.17672468881773</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225">
-        <v>475.46031726007669</v>
+        <v>323.04240597220354</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>476.77582156773417</v>
+        <v>322.91812626278073</v>
       </c>
       <c r="B226">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>478.04813683292201</v>
+        <v>322.83633837167486</v>
       </c>
       <c r="B227">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228">
-        <v>479.38476429110557</v>
+        <v>322.8080079519176</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229">
-        <v>480.71816934369099</v>
+        <v>322.71747743158824</v>
       </c>
       <c r="B229">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230">
-        <v>482.04788984728356</v>
+        <v>322.63428446013171</v>
       </c>
       <c r="B230">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231">
-        <v>483.30605316808271</v>
+        <v>322.53824561159797</v>
       </c>
       <c r="B231">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232">
-        <v>484.63121245969478</v>
+        <v>322.50634308761965</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233">
-        <v>486.02938113303537</v>
+        <v>322.3859237639561</v>
       </c>
       <c r="B233">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234">
-        <v>487.36421119115164</v>
+        <v>322.29938403566359</v>
       </c>
       <c r="B234">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235">
-        <v>488.77750707691439</v>
+        <v>322.15785603640677</v>
       </c>
       <c r="B235">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236">
-        <v>490.09343185982834</v>
+        <v>322.01000363596495</v>
       </c>
       <c r="B236">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237">
-        <v>491.45416276912368</v>
+        <v>321.83565844690258</v>
       </c>
       <c r="B237">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238">
-        <v>492.80747157424707</v>
+        <v>321.54522836159367</v>
       </c>
       <c r="B238">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239">
-        <v>494.23510481821046</v>
+        <v>321.3034192171969</v>
       </c>
       <c r="B239">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240">
-        <v>495.67117304359311</v>
+        <v>320.9487497185973</v>
       </c>
       <c r="B240">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241">
-        <v>497.07890361395198</v>
+        <v>320.65023474140378</v>
       </c>
       <c r="B241">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242">
-        <v>498.5331382256042</v>
+        <v>320.4677494764029</v>
       </c>
       <c r="B242">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243">
-        <v>499.94642728648006</v>
+        <v>320.21193434404074</v>
       </c>
       <c r="B243">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244">
-        <v>500</v>
+        <v>319.87344455178874</v>
       </c>
       <c r="B244">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245">
-        <v>500</v>
+        <v>319.47437338336943</v>
       </c>
       <c r="B245">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246">
-        <v>500</v>
+        <v>319.0738281403427</v>
       </c>
       <c r="B246">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247">
-        <v>500</v>
+        <v>318.7133667875442</v>
       </c>
       <c r="B247">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248">
-        <v>500</v>
+        <v>318.56648894596259</v>
       </c>
       <c r="B248">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249">
-        <v>500</v>
+        <v>318.45869461019663</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250">
-        <v>500</v>
+        <v>318.27647191175384</v>
       </c>
       <c r="B250">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251">
-        <v>500</v>
+        <v>318.10848220329376</v>
       </c>
       <c r="B251">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252">
-        <v>500</v>
+        <v>317.9588229014883</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253">
-        <v>500</v>
+        <v>317.83881110157569</v>
       </c>
       <c r="B253">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254">
-        <v>500</v>
+        <v>317.70030119114568</v>
       </c>
       <c r="B254">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255">
-        <v>500</v>
+        <v>317.36849919327034</v>
       </c>
       <c r="B255">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256">
-        <v>500</v>
+        <v>317.04007221454822</v>
       </c>
       <c r="B256">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257">
-        <v>500</v>
+        <v>316.65443391865534</v>
       </c>
       <c r="B257">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258">
-        <v>500</v>
+        <v>316.38007512712767</v>
       </c>
       <c r="B258">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259">
-        <v>500</v>
+        <v>316.17513150627906</v>
       </c>
       <c r="B259">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260">
-        <v>500</v>
+        <v>316.01271275990007</v>
       </c>
       <c r="B260">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261">
-        <v>500</v>
+        <v>315.79210839133628</v>
       </c>
       <c r="B261">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262">
-        <v>500</v>
+        <v>315.56535985708024</v>
       </c>
       <c r="B262">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263">
-        <v>500</v>
+        <v>315.36057232810231</v>
       </c>
       <c r="B263">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264">
-        <v>500</v>
+        <v>315.27578494602972</v>
       </c>
       <c r="B264">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265">
-        <v>500</v>
+        <v>315.25583995240265</v>
       </c>
       <c r="B265">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266">
-        <v>500</v>
+        <v>315.21269152869331</v>
       </c>
       <c r="B266">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267">
-        <v>500</v>
+        <v>315.20369818288924</v>
       </c>
       <c r="B267">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268">
-        <v>500</v>
+        <v>315.08829535366425</v>
       </c>
       <c r="B268">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269">
-        <v>500</v>
+        <v>314.96820021459706</v>
       </c>
       <c r="B269">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270">
-        <v>500</v>
+        <v>314.82274273235925</v>
       </c>
       <c r="B270">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271">
-        <v>500</v>
+        <v>314.70190423272771</v>
       </c>
       <c r="B271">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272">
-        <v>500</v>
+        <v>314.626759880328</v>
       </c>
       <c r="B272">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273">
-        <v>500</v>
+        <v>314.56799164955072</v>
       </c>
       <c r="B273">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274">
-        <v>500</v>
+        <v>314.56532919385882</v>
       </c>
       <c r="B274">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275">
-        <v>500</v>
+        <v>314.64303367321571</v>
       </c>
       <c r="B275">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276">
-        <v>500</v>
+        <v>314.70671523680511</v>
       </c>
       <c r="B276">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277">
-        <v>500</v>
+        <v>314.74343796686725</v>
       </c>
       <c r="B277">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278">
-        <v>500</v>
+        <v>314.68457373623073</v>
       </c>
       <c r="B278">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279">
-        <v>500</v>
+        <v>314.57299199967025</v>
       </c>
       <c r="B279">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280">
-        <v>500</v>
+        <v>314.43050086661412</v>
       </c>
       <c r="B280">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281">
-        <v>500</v>
+        <v>314.27168666216113</v>
       </c>
       <c r="B281">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282">
-        <v>500</v>
+        <v>314.05805575951962</v>
       </c>
       <c r="B282">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283">
-        <v>500</v>
+        <v>313.87847113389967</v>
       </c>
       <c r="B283">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284">
-        <v>500</v>
+        <v>313.64886574498689</v>
       </c>
       <c r="B284">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285">
-        <v>500</v>
+        <v>313.29960730377832</v>
       </c>
       <c r="B285">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286">
-        <v>500</v>
+        <v>312.93918051630396</v>
       </c>
       <c r="B286">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287">
-        <v>500</v>
+        <v>312.67929392892682</v>
       </c>
       <c r="B287">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288">
-        <v>500</v>
+        <v>312.38856275163658</v>
       </c>
       <c r="B288">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289">
-        <v>500</v>
+        <v>312.18197327505595</v>
       </c>
       <c r="B289">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290">
-        <v>500</v>
+        <v>311.91923663146486</v>
       </c>
       <c r="B290">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291">
-        <v>500</v>
+        <v>311.67371136503044</v>
       </c>
       <c r="B291">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292">
-        <v>500</v>
+        <v>311.54263008713548</v>
       </c>
       <c r="B292">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293">
-        <v>500</v>
+        <v>311.49145455305359</v>
       </c>
       <c r="B293">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294">
-        <v>500</v>
+        <v>311.5787587018466</v>
       </c>
       <c r="B294">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295">
-        <v>500</v>
+        <v>311.72496817227602</v>
       </c>
       <c r="B295">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296">
-        <v>500</v>
+        <v>311.8040004284922</v>
       </c>
       <c r="B296">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297">
-        <v>500</v>
+        <v>311.8124236411648</v>
       </c>
       <c r="B297">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298">
-        <v>500</v>
+        <v>311.84790298650671</v>
       </c>
       <c r="B298">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299">
-        <v>500</v>
+        <v>311.7105574655854</v>
       </c>
       <c r="B299">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300">
-        <v>500</v>
+        <v>311.6727416375731</v>
       </c>
       <c r="B300">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301">
-        <v>500</v>
+        <v>311.77265901169221</v>
       </c>
       <c r="B301">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302">
-        <v>500</v>
+        <v>311.87395239234883</v>
       </c>
       <c r="B302">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303">
-        <v>500</v>
+        <v>311.82826892550037</v>
       </c>
       <c r="B303">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304">
-        <v>500</v>
+        <v>311.75765296983406</v>
       </c>
       <c r="B304">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305">
-        <v>500</v>
+        <v>311.75352832706955</v>
       </c>
       <c r="B305">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306">
-        <v>500</v>
+        <v>311.74990104368771</v>
       </c>
       <c r="B306">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307">
-        <v>500</v>
+        <v>311.63609744506607</v>
       </c>
       <c r="B307">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308">
-        <v>500</v>
+        <v>311.56418794845194</v>
       </c>
       <c r="B308">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309">
-        <v>500</v>
+        <v>311.40694925379097</v>
       </c>
       <c r="B309">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310">
-        <v>500</v>
+        <v>311.23196713330367</v>
       </c>
       <c r="B310">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311">
-        <v>500</v>
+        <v>311.13090290095084</v>
       </c>
       <c r="B311">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312">
-        <v>500</v>
+        <v>311.17065044794492</v>
       </c>
       <c r="B312">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313">
-        <v>500</v>
+        <v>311.15149046781931</v>
       </c>
       <c r="B313">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314">
-        <v>500</v>
+        <v>311.11307868318437</v>
       </c>
       <c r="B314">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315">
-        <v>500</v>
+        <v>311.08581865850641</v>
       </c>
       <c r="B315">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316">
-        <v>500</v>
+        <v>311.03283478687291</v>
       </c>
       <c r="B316">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317">
-        <v>500</v>
+        <v>311.02075374545427</v>
       </c>
       <c r="B317">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318">
-        <v>500</v>
+        <v>310.96358597869374</v>
       </c>
       <c r="B318">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319">
-        <v>500</v>
+        <v>310.94965389082398</v>
       </c>
       <c r="B319">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320">
-        <v>500</v>
+        <v>311.01485363864583</v>
       </c>
       <c r="B320">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321">
-        <v>500</v>
+        <v>311.22938757576719</v>
       </c>
       <c r="B321">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322">
-        <v>500</v>
+        <v>311.62844365949042</v>
       </c>
       <c r="B322">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323">
-        <v>500</v>
+        <v>312.01101908501795</v>
       </c>
       <c r="B323">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324">
-        <v>500</v>
+        <v>312.2830095944546</v>
       </c>
       <c r="B324">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325">
-        <v>500</v>
+        <v>312.38422908873167</v>
       </c>
       <c r="B325">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326">
-        <v>500</v>
+        <v>312.41254719292783</v>
       </c>
       <c r="B326">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327">
-        <v>500</v>
+        <v>312.4127892147946</v>
       </c>
       <c r="B327">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328">
-        <v>500</v>
+        <v>312.37727344368551</v>
       </c>
       <c r="B328">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329">
-        <v>500</v>
+        <v>312.13544633785517</v>
       </c>
       <c r="B329">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330">
-        <v>500</v>
+        <v>312.04742111629503</v>
       </c>
       <c r="B330">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331">
-        <v>500</v>
+        <v>312.01132243447302</v>
       </c>
       <c r="B331">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332">
-        <v>500</v>
+        <v>311.94416107184361</v>
       </c>
       <c r="B332">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333">
-        <v>500</v>
+        <v>311.86684345160489</v>
       </c>
       <c r="B333">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334">
-        <v>500</v>
+        <v>311.89238368846048</v>
       </c>
       <c r="B334">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335">
-        <v>500</v>
+        <v>311.9019502664309</v>
       </c>
       <c r="B335">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336">
-        <v>500</v>
+        <v>311.94780171406472</v>
       </c>
       <c r="B336">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337">
-        <v>500</v>
+        <v>311.8507630801941</v>
       </c>
       <c r="B337">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338">
-        <v>500</v>
+        <v>311.6883744019143</v>
       </c>
       <c r="B338">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339">
-        <v>500</v>
+        <v>311.55027142646048</v>
       </c>
       <c r="B339">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340">
-        <v>500</v>
+        <v>311.4966161433735</v>
       </c>
       <c r="B340">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341">
-        <v>500</v>
+        <v>311.40056221859544</v>
       </c>
       <c r="B341">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342">
-        <v>500</v>
+        <v>311.25140802797125</v>
       </c>
       <c r="B342">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343">
-        <v>500</v>
+        <v>311.13766755764215</v>
       </c>
       <c r="B343">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344">
-        <v>500</v>
+        <v>311.12071991974005</v>
       </c>
       <c r="B344">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345">
-        <v>500</v>
+        <v>311.19094009594454</v>
       </c>
       <c r="B345">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346">
-        <v>500</v>
+        <v>311.33903117064091</v>
       </c>
       <c r="B346">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347">
-        <v>500</v>
+        <v>311.51681817474923</v>
       </c>
       <c r="B347">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348">
-        <v>500</v>
+        <v>311.61792494504112</v>
       </c>
       <c r="B348">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349">
-        <v>500</v>
+        <v>311.73363030917068</v>
       </c>
       <c r="B349">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350">
-        <v>500</v>
+        <v>311.81606057997664</v>
       </c>
       <c r="B350">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351">
-        <v>500</v>
+        <v>311.89308114742397</v>
       </c>
       <c r="B351">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352">
-        <v>500</v>
+        <v>311.85288972101142</v>
       </c>
       <c r="B352">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353">
-        <v>500</v>
+        <v>311.70387675972825</v>
       </c>
       <c r="B353">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354">
-        <v>500</v>
+        <v>311.42352314160433</v>
       </c>
       <c r="B354">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355">
-        <v>500</v>
+        <v>311.19561631073464</v>
       </c>
       <c r="B355">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356">
-        <v>500</v>
+        <v>310.97793990636939</v>
       </c>
       <c r="B356">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357">
-        <v>500</v>
+        <v>310.72678862123803</v>
       </c>
       <c r="B357">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358">
-        <v>500</v>
+        <v>310.48588194370194</v>
       </c>
       <c r="B358">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359">
-        <v>500</v>
+        <v>310.18729643867033</v>
       </c>
       <c r="B359">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360">
-        <v>500</v>
+        <v>309.79187856992911</v>
       </c>
       <c r="B360">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361">
-        <v>500</v>
+        <v>309.33913675408621</v>
       </c>
       <c r="B361">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362">
-        <v>500</v>
+        <v>308.98745172957234</v>
       </c>
       <c r="B362">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363">
-        <v>500</v>
+        <v>308.64426354789697</v>
       </c>
       <c r="B363">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364">
-        <v>500</v>
+        <v>308.35989569931871</v>
       </c>
       <c r="B364">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365">
-        <v>500</v>
+        <v>308.04819436393444</v>
       </c>
       <c r="B365">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366">
-        <v>500</v>
+        <v>307.80778684568588</v>
       </c>
       <c r="B366">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367">
-        <v>500</v>
+        <v>307.62657173176791</v>
       </c>
       <c r="B367">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368">
-        <v>500</v>
+        <v>307.39996950766857</v>
       </c>
       <c r="B368">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369">
-        <v>500</v>
+        <v>306.97337157664691</v>
       </c>
       <c r="B369">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370">
-        <v>500</v>
+        <v>306.54301732989217</v>
       </c>
       <c r="B370">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371">
-        <v>500</v>
+        <v>306.0375886404226</v>
       </c>
       <c r="B371">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372">
-        <v>500</v>
+        <v>305.50319152451783</v>
       </c>
       <c r="B372">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373">
-        <v>500</v>
+        <v>305.03438310959041</v>
       </c>
       <c r="B373">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374">
-        <v>500</v>
+        <v>304.56807678739858</v>
       </c>
       <c r="B374">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375">
-        <v>500</v>
+        <v>304.06458262423001</v>
       </c>
       <c r="B375">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376">
-        <v>500</v>
+        <v>303.52851932927797</v>
       </c>
       <c r="B376">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377">
-        <v>500</v>
+        <v>302.99633514952279</v>
       </c>
       <c r="B377">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378">
-        <v>500</v>
+        <v>302.59589918937462</v>
       </c>
       <c r="B378">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379">
-        <v>500</v>
+        <v>302.27288067964446</v>
       </c>
       <c r="B379">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380">
-        <v>500</v>
+        <v>301.9389659757133</v>
       </c>
       <c r="B380">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381">
-        <v>500</v>
+        <v>301.59958087286282</v>
       </c>
       <c r="B381">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382">
-        <v>500</v>
+        <v>301.33821390387055</v>
       </c>
       <c r="B382">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383">
-        <v>500</v>
+        <v>301.06352865655504</v>
       </c>
       <c r="B383">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384">
-        <v>500</v>
+        <v>300.82084905465177</v>
       </c>
       <c r="B384">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385">
-        <v>500</v>
+        <v>300.63573206260673</v>
       </c>
       <c r="B385">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386">
-        <v>500</v>
+        <v>300.45590553116267</v>
       </c>
       <c r="B386">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387">
-        <v>500</v>
+        <v>300.3283860295482</v>
       </c>
       <c r="B387">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388">
-        <v>500</v>
+        <v>300.31976384110857</v>
       </c>
       <c r="B388">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389">
-        <v>500</v>
+        <v>300.43894877918433</v>
       </c>
       <c r="B389">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390">
-        <v>500</v>
+        <v>300.4258714291243</v>
       </c>
       <c r="B390">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391">
-        <v>500</v>
+        <v>300.37541112604578</v>
       </c>
       <c r="B391">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392">
-        <v>500</v>
+        <v>300.33302517917383</v>
       </c>
       <c r="B392">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393">
-        <v>500</v>
+        <v>300.42570952147662</v>
       </c>
       <c r="B393">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394">
-        <v>500</v>
+        <v>300.57299985162757</v>
       </c>
       <c r="B394">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395">
-        <v>500</v>
+        <v>300.64856002187014</v>
       </c>
       <c r="B395">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396">
-        <v>500</v>
+        <v>300.71196245433578</v>
       </c>
       <c r="B396">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397">
-        <v>500</v>
+        <v>300.81062987615309</v>
       </c>
       <c r="B397">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398">
-        <v>500</v>
+        <v>300.68843876172224</v>
       </c>
       <c r="B398">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399">
-        <v>500</v>
+        <v>300.4405697342695</v>
       </c>
       <c r="B399">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400">
-        <v>500</v>
+        <v>300.20704994475904</v>
       </c>
       <c r="B400">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401">
-        <v>500</v>
+        <v>300.01961568516253</v>
       </c>
       <c r="B401">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402">
-        <v>500</v>
+        <v>299.79834312275642</v>
       </c>
       <c r="B402">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403">
-        <v>500</v>
+        <v>299.66947112772374</v>
       </c>
       <c r="B403">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404">
-        <v>500</v>
+        <v>299.53387242415641</v>
       </c>
       <c r="B404">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405">
-        <v>500</v>
+        <v>299.32277927427833</v>
       </c>
       <c r="B405">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406">
-        <v>500</v>
+        <v>299.10473058718634</v>
       </c>
       <c r="B406">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407">
-        <v>500</v>
+        <v>298.88224355596338</v>
       </c>
       <c r="B407">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408">
-        <v>500</v>
+        <v>298.69624236839661</v>
       </c>
       <c r="B408">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409">
-        <v>500</v>
+        <v>298.41590724272106</v>
       </c>
       <c r="B409">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410">
-        <v>500</v>
+        <v>298.03501353868592</v>
       </c>
       <c r="B410">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411">
-        <v>500</v>
+        <v>297.79481196528769</v>
       </c>
       <c r="B411">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412">
-        <v>500</v>
+        <v>297.57590758713815</v>
       </c>
       <c r="B412">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413">
-        <v>500</v>
+        <v>297.41538941477438</v>
       </c>
       <c r="B413">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414">
-        <v>500</v>
+        <v>297.30074459131527</v>
       </c>
       <c r="B414">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415">
-        <v>500</v>
+        <v>297.0996066513494</v>
       </c>
       <c r="B415">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416">
-        <v>500</v>
+        <v>296.93672226788237</v>
       </c>
       <c r="B416">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417">
-        <v>500</v>
+        <v>296.74386773337693</v>
       </c>
       <c r="B417">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418">
-        <v>500</v>
+        <v>296.50109621216546</v>
       </c>
       <c r="B418">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419">
-        <v>500</v>
+        <v>296.10791494237412</v>
       </c>
       <c r="B419">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420">
-        <v>500</v>
+        <v>295.73629118877847</v>
       </c>
       <c r="B420">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421">
-        <v>500</v>
+        <v>295.49866658691195</v>
       </c>
       <c r="B421">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422">
-        <v>500</v>
+        <v>295.37451775072958</v>
       </c>
       <c r="B422">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423">
-        <v>500</v>
+        <v>295.34219759513871</v>
       </c>
       <c r="B423">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424">
-        <v>500</v>
+        <v>295.26384762516841</v>
       </c>
       <c r="B424">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425">
-        <v>500</v>
+        <v>295.20322911060509</v>
       </c>
       <c r="B425">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426">
-        <v>500</v>
+        <v>295.12098084709015</v>
       </c>
       <c r="B426">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427">
-        <v>500</v>
+        <v>295.18638847758012</v>
       </c>
       <c r="B427">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428">
-        <v>500</v>
+        <v>295.32190331388261</v>
       </c>
       <c r="B428">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429">
-        <v>500</v>
+        <v>295.48274322259266</v>
       </c>
       <c r="B429">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430">
-        <v>500</v>
+        <v>295.664061982362</v>
       </c>
       <c r="B430">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431">
-        <v>500</v>
+        <v>295.86242613662995</v>
       </c>
       <c r="B431">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432">
-        <v>500</v>
+        <v>296.23195514330121</v>
       </c>
       <c r="B432">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433">
-        <v>500</v>
+        <v>296.61350382899883</v>
       </c>
       <c r="B433">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434">
-        <v>500</v>
+        <v>296.92317404704909</v>
       </c>
       <c r="B434">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435">
-        <v>500</v>
+        <v>297.23831150190802</v>
       </c>
       <c r="B435">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436">
-        <v>500</v>
+        <v>297.73338308634271</v>
       </c>
       <c r="B436">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437">
-        <v>500</v>
+        <v>298.31682376763308</v>
       </c>
       <c r="B437">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438">
-        <v>500</v>
+        <v>298.89837042066063</v>
       </c>
       <c r="B438">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439">
-        <v>500</v>
+        <v>299.46101107152083</v>
       </c>
       <c r="B439">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440">
-        <v>500</v>
+        <v>299.92290269214709</v>
       </c>
       <c r="B440">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441">
-        <v>500</v>
+        <v>300.56970895251936</v>
       </c>
       <c r="B441">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442">
-        <v>500</v>
+        <v>301.26219211494447</v>
       </c>
       <c r="B442">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443">
-        <v>500</v>
+        <v>301.9062003126387</v>
       </c>
       <c r="B443">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444">
-        <v>500</v>
+        <v>302.48067707538269</v>
       </c>
       <c r="B444">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445">
-        <v>500</v>
+        <v>303.03831574909321</v>
       </c>
       <c r="B445">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446">
-        <v>500</v>
+        <v>303.5143944503676</v>
       </c>
       <c r="B446">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447">
-        <v>500</v>
+        <v>304.09876155340487</v>
       </c>
       <c r="B447">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448">
-        <v>500</v>
+        <v>304.72193693846481</v>
       </c>
       <c r="B448">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449">
-        <v>500</v>
+        <v>305.3497999571797</v>
       </c>
       <c r="B449">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450">
-        <v>500</v>
+        <v>305.99965413465526</v>
       </c>
       <c r="B450">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451">
-        <v>500</v>
+        <v>306.74305650001799</v>
       </c>
       <c r="B451">
-        <v>2.71956016904224E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452">
-        <v>500</v>
+        <v>307.56056602718576</v>
       </c>
       <c r="B452">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453">
-        <v>500</v>
+        <v>308.37779907088031</v>
       </c>
       <c r="B453">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454">
-        <v>500</v>
+        <v>309.08445999861675</v>
       </c>
       <c r="B454">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455">
-        <v>500</v>
+        <v>309.7066365282007</v>
       </c>
       <c r="B455">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456">
-        <v>500</v>
+        <v>310.30577563255173</v>
       </c>
       <c r="B456">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457">
-        <v>500</v>
+        <v>310.89150277752265</v>
       </c>
       <c r="B457">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458">
-        <v>500</v>
+        <v>311.45744250429243</v>
       </c>
       <c r="B458">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459">
-        <v>500</v>
+        <v>312.01168767659857</v>
       </c>
       <c r="B459">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460">
-        <v>500</v>
+        <v>312.58585439014695</v>
       </c>
       <c r="B460">
-        <v>3.4272417007049194E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461">
-        <v>500</v>
+        <v>313.24113529842111</v>
       </c>
       <c r="B461">
-        <v>6.7854865295109285E-3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462">
-        <v>500</v>
+        <v>313.86258270168827</v>
       </c>
       <c r="B462">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463">
-        <v>500</v>
+        <v>314.48599175014027</v>
       </c>
       <c r="B463">
-        <v>2.5676935890744171E-3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464">
-        <v>500</v>
+        <v>315.03390113775504</v>
       </c>
       <c r="B464">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465">
-        <v>500</v>
+        <v>315.56925911200176</v>
       </c>
       <c r="B465">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466">
-        <v>500</v>
+        <v>316.07176049404296</v>
       </c>
       <c r="B466">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467">
-        <v>500</v>
+        <v>316.49794768885431</v>
       </c>
       <c r="B467">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468">
-        <v>500</v>
+        <v>316.90085671291769</v>
       </c>
       <c r="B468">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469">
-        <v>500</v>
+        <v>317.29693080053391</v>
       </c>
       <c r="B469">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470">
-        <v>500</v>
+        <v>317.7694155565477</v>
       </c>
       <c r="B470">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471">
-        <v>500</v>
+        <v>318.18198971502909</v>
       </c>
       <c r="B471">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472">
-        <v>500</v>
+        <v>318.51768034953085</v>
       </c>
       <c r="B472">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473">
-        <v>500</v>
+        <v>318.76789107147783</v>
       </c>
       <c r="B473">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474">
-        <v>500</v>
+        <v>318.99787970334773</v>
       </c>
       <c r="B474">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475">
-        <v>500</v>
+        <v>319.33829433073993</v>
       </c>
       <c r="B475">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476">
-        <v>500</v>
+        <v>319.83090483064314</v>
       </c>
       <c r="B476">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477">
-        <v>500</v>
+        <v>320.43288723634896</v>
       </c>
       <c r="B477">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478">
-        <v>500</v>
+        <v>321.13999857398551</v>
       </c>
       <c r="B478">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479">
-        <v>500</v>
+        <v>321.90415022163171</v>
       </c>
       <c r="B479">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480">
-        <v>500</v>
+        <v>322.73517133108885</v>
       </c>
       <c r="B480">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481">
-        <v>500</v>
+        <v>323.49809064838144</v>
       </c>
       <c r="B481">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482">
-        <v>500</v>
+        <v>324.36693807984</v>
       </c>
       <c r="B482">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483">
-        <v>500</v>
+        <v>325.26247226792646</v>
       </c>
       <c r="B483">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484">
-        <v>500</v>
+        <v>326.11304542712162</v>
       </c>
       <c r="B484">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485">
-        <v>500</v>
+        <v>326.90497026245549</v>
       </c>
       <c r="B485">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486">
-        <v>500</v>
+        <v>327.72457940313183</v>
       </c>
       <c r="B486">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487">
-        <v>500</v>
+        <v>328.69244947643114</v>
       </c>
       <c r="B487">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488">
-        <v>500</v>
+        <v>329.63685854764151</v>
       </c>
       <c r="B488">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489">
-        <v>500</v>
+        <v>330.6765554909498</v>
       </c>
       <c r="B489">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490">
-        <v>500</v>
+        <v>331.59030844424706</v>
       </c>
       <c r="B490">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491">
-        <v>500</v>
+        <v>332.368093685313</v>
       </c>
       <c r="B491">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492">
-        <v>500</v>
+        <v>333.22441567145592</v>
       </c>
       <c r="B492">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493">
-        <v>500</v>
+        <v>333.98162903150836</v>
       </c>
       <c r="B493">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494">
-        <v>500</v>
+        <v>334.77841273302056</v>
       </c>
       <c r="B494">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495">
-        <v>500</v>
+        <v>335.52295404934995</v>
       </c>
       <c r="B495">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496">
-        <v>500</v>
+        <v>336.0761497188505</v>
       </c>
       <c r="B496">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497">
-        <v>500</v>
+        <v>336.44841417328286</v>
       </c>
       <c r="B497">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498">
-        <v>500</v>
+        <v>336.89190864598481</v>
       </c>
       <c r="B498">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499">
-        <v>500</v>
+        <v>337.30562625140936</v>
       </c>
       <c r="B499">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500">
-        <v>500</v>
+        <v>337.82107255062459</v>
       </c>
       <c r="B500">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501">
-        <v>500</v>
+        <v>338.3562109541582</v>
       </c>
       <c r="B501">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502">
-        <v>500</v>
+        <v>338.96571976552838</v>
       </c>
       <c r="B502">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503">
-        <v>500</v>
+        <v>339.64951070993339</v>
       </c>
       <c r="B503">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504">
-        <v>500</v>
+        <v>340.22636762755229</v>
       </c>
       <c r="B504">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505">
-        <v>500</v>
+        <v>340.82113654375536</v>
       </c>
       <c r="B505">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506">
-        <v>500</v>
+        <v>341.41814628652497</v>
       </c>
       <c r="B506">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507">
-        <v>500</v>
+        <v>342.02932971234623</v>
       </c>
       <c r="B507">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508">
-        <v>500</v>
+        <v>342.65022771787716</v>
       </c>
       <c r="B508">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509">
-        <v>500</v>
+        <v>343.28046471017598</v>
       </c>
       <c r="B509">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510">
-        <v>500</v>
+        <v>343.97697923043478</v>
       </c>
       <c r="B510">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511">
-        <v>500</v>
+        <v>344.7431025984219</v>
       </c>
       <c r="B511">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512">
-        <v>500</v>
+        <v>345.58550869667209</v>
       </c>
       <c r="B512">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513">
-        <v>500</v>
+        <v>346.46480145859863</v>
       </c>
       <c r="B513">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514">
-        <v>500</v>
+        <v>347.40132544198457</v>
       </c>
       <c r="B514">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515">
-        <v>500</v>
+        <v>348.37650023388989</v>
       </c>
       <c r="B515">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516">
-        <v>500</v>
+        <v>349.41384288156615</v>
       </c>
       <c r="B516">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517">
-        <v>500</v>
+        <v>350.48046509527171</v>
       </c>
       <c r="B517">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518">
-        <v>500</v>
+        <v>351.58156641563284</v>
       </c>
       <c r="B518">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519">
-        <v>500</v>
+        <v>352.6990551606217</v>
       </c>
       <c r="B519">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520">
-        <v>500</v>
+        <v>353.76067289596602</v>
       </c>
       <c r="B520">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521">
-        <v>500</v>
+        <v>354.70679581215109</v>
       </c>
       <c r="B521">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522">
-        <v>500</v>
+        <v>355.67774025930038</v>
       </c>
       <c r="B522">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523">
-        <v>500</v>
+        <v>356.62011754595414</v>
       </c>
       <c r="B523">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524">
-        <v>500</v>
+        <v>357.47937996309275</v>
       </c>
       <c r="B524">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525">
-        <v>500</v>
+        <v>358.34268778738482</v>
       </c>
       <c r="B525">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526">
-        <v>500</v>
+        <v>359.25156068966544</v>
       </c>
       <c r="B526">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527">
-        <v>500</v>
+        <v>360.14953438927603</v>
       </c>
       <c r="B527">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528">
-        <v>500</v>
+        <v>361.06712964666212</v>
       </c>
       <c r="B528">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529">
-        <v>500</v>
+        <v>361.82909901754056</v>
       </c>
       <c r="B529">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530">
-        <v>500</v>
+        <v>362.64716760968776</v>
       </c>
       <c r="B530">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531">
-        <v>500</v>
+        <v>363.57607702803421</v>
       </c>
       <c r="B531">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532">
-        <v>500</v>
+        <v>364.53011862233723</v>
       </c>
       <c r="B532">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533">
-        <v>500</v>
+        <v>365.443016312054</v>
       </c>
       <c r="B533">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534">
-        <v>500</v>
+        <v>366.28298928129254</v>
       </c>
       <c r="B534">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535">
-        <v>500</v>
+        <v>367.12481710152315</v>
       </c>
       <c r="B535">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536">
-        <v>500</v>
+        <v>367.99043488004537</v>
       </c>
       <c r="B536">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537">
-        <v>500</v>
+        <v>368.77397840352182</v>
       </c>
       <c r="B537">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538">
-        <v>500</v>
+        <v>369.57163832192077</v>
       </c>
       <c r="B538">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539">
-        <v>500</v>
+        <v>370.38346019279567</v>
       </c>
       <c r="B539">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540">
-        <v>500</v>
+        <v>371.12425028739926</v>
       </c>
       <c r="B540">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541">
-        <v>500</v>
+        <v>372.00219404309911</v>
       </c>
       <c r="B541">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542">
-        <v>500</v>
+        <v>372.81254175450925</v>
       </c>
       <c r="B542">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543">
-        <v>500</v>
+        <v>373.57610854743683</v>
       </c>
       <c r="B543">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544">
-        <v>500</v>
+        <v>374.3251413084289</v>
       </c>
       <c r="B544">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545">
-        <v>500</v>
+        <v>375.11198451479794</v>
       </c>
       <c r="B545">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546">
-        <v>500</v>
+        <v>375.84573922237212</v>
       </c>
       <c r="B546">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A547">
-        <v>500</v>
+        <v>376.61301671793842</v>
       </c>
       <c r="B547">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548">
-        <v>500</v>
+        <v>377.4368748026983</v>
       </c>
       <c r="B548">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549">
-        <v>500</v>
+        <v>378.18572998097471</v>
       </c>
       <c r="B549">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550">
-        <v>500</v>
+        <v>378.78529107844491</v>
       </c>
       <c r="B550">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551">
-        <v>500</v>
+        <v>379.29495318019968</v>
       </c>
       <c r="B551">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552">
-        <v>500</v>
+        <v>379.76000278506871</v>
       </c>
       <c r="B552">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553">
-        <v>500</v>
+        <v>380.21845783133483</v>
       </c>
       <c r="B553">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554">
-        <v>500</v>
+        <v>380.66252321278796</v>
       </c>
       <c r="B554">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555">
-        <v>500</v>
+        <v>381.10944957059081</v>
       </c>
       <c r="B555">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556">
-        <v>500</v>
+        <v>381.57423413666868</v>
       </c>
       <c r="B556">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557">
-        <v>500</v>
+        <v>382.07639758000801</v>
       </c>
       <c r="B557">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558">
-        <v>500</v>
+        <v>382.57146304327034</v>
       </c>
       <c r="B558">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559">
-        <v>500</v>
+        <v>382.97294094021845</v>
       </c>
       <c r="B559">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560">
-        <v>500</v>
+        <v>383.41338903148761</v>
       </c>
       <c r="B560">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561">
-        <v>500</v>
+        <v>383.95761685833833</v>
       </c>
       <c r="B561">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562">
-        <v>500</v>
+        <v>384.63082655941963</v>
       </c>
       <c r="B562">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563">
-        <v>500</v>
+        <v>385.2009626791484</v>
       </c>
       <c r="B563">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564">
-        <v>500</v>
+        <v>385.77679883919433</v>
       </c>
       <c r="B564">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565">
-        <v>500</v>
+        <v>386.43776732087821</v>
       </c>
       <c r="B565">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566">
-        <v>500</v>
+        <v>387.2022249820015</v>
       </c>
       <c r="B566">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567">
-        <v>500</v>
+        <v>388.03137569053825</v>
       </c>
       <c r="B567">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568">
-        <v>500</v>
+        <v>388.84082652262333</v>
       </c>
       <c r="B568">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569">
-        <v>500</v>
+        <v>389.64016816817133</v>
       </c>
       <c r="B569">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570">
-        <v>500</v>
+        <v>390.42049338993348</v>
       </c>
       <c r="B570">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571">
-        <v>500</v>
+        <v>391.03919586597607</v>
       </c>
       <c r="B571">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572">
-        <v>500</v>
+        <v>391.56617546372962</v>
       </c>
       <c r="B572">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573">
-        <v>500</v>
+        <v>391.95373151126324</v>
       </c>
       <c r="B573">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574">
-        <v>500</v>
+        <v>392.38720068862074</v>
       </c>
       <c r="B574">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575">
-        <v>500</v>
+        <v>392.82811614494523</v>
       </c>
       <c r="B575">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576">
-        <v>500</v>
+        <v>393.22227889768817</v>
       </c>
       <c r="B576">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577">
-        <v>500</v>
+        <v>393.51598892580455</v>
       </c>
       <c r="B577">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578">
-        <v>500</v>
+        <v>393.83839121634531</v>
       </c>
       <c r="B578">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579">
-        <v>500</v>
+        <v>394.20490908682655</v>
       </c>
       <c r="B579">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580">
-        <v>500</v>
+        <v>394.70134711643487</v>
       </c>
       <c r="B580">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581">
-        <v>500</v>
+        <v>395.07433700437525</v>
       </c>
       <c r="B581">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582">
-        <v>500</v>
+        <v>395.35292741585334</v>
       </c>
       <c r="B582">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583">
-        <v>500</v>
+        <v>395.55587006872588</v>
       </c>
       <c r="B583">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584">
-        <v>500</v>
+        <v>395.78428916434888</v>
       </c>
       <c r="B584">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585">
-        <v>500</v>
+        <v>395.97667598075566</v>
       </c>
       <c r="B585">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586">
-        <v>500</v>
+        <v>396.15522788118949</v>
       </c>
       <c r="B586">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587">
-        <v>500</v>
+        <v>396.33891010514196</v>
       </c>
       <c r="B587">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588">
-        <v>500</v>
+        <v>396.65814983519937</v>
       </c>
       <c r="B588">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589">
-        <v>500</v>
+        <v>397.18388087807409</v>
       </c>
       <c r="B589">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590">
-        <v>500</v>
+        <v>397.70801927549627</v>
       </c>
       <c r="B590">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591">
-        <v>500</v>
+        <v>398.21567933924246</v>
       </c>
       <c r="B591">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592">
-        <v>500</v>
+        <v>398.75439715265594</v>
       </c>
       <c r="B592">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593">
-        <v>500</v>
+        <v>399.34592605207291</v>
       </c>
       <c r="B593">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594">
-        <v>500</v>
+        <v>399.9188916260087</v>
       </c>
       <c r="B594">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595">
-        <v>500</v>
+        <v>400.51979747327385</v>
       </c>
       <c r="B595">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596">
-        <v>500</v>
+        <v>401.1065633746727</v>
       </c>
       <c r="B596">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597">
-        <v>500</v>
+        <v>401.65142426622208</v>
       </c>
       <c r="B597">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598">
-        <v>500</v>
+        <v>402.22853993453612</v>
       </c>
       <c r="B598">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599">
-        <v>500</v>
+        <v>402.89391521955798</v>
       </c>
       <c r="B599">
-        <v>8.6276570474647943E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600">
-        <v>500</v>
+        <v>403.55924919597692</v>
       </c>
       <c r="B600">
-        <v>0.16557113743843904</v>
+        <v>500</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601">
-        <v>500</v>
+        <v>404.10053342193902</v>
       </c>
       <c r="B601">
-        <v>0.18326671260924812</v>
+        <v>500</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602">
-        <v>500</v>
+        <v>404.65017707983577</v>
       </c>
       <c r="B602">
-        <v>0.22560068070164935</v>
+        <v>500</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603">
-        <v>500</v>
+        <v>405.13607622127682</v>
       </c>
       <c r="B603">
-        <v>0.23466908641872625</v>
+        <v>500</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604">
-        <v>500</v>
+        <v>405.49296940252526</v>
       </c>
       <c r="B604">
-        <v>0.30749760480651317</v>
+        <v>500</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605">
-        <v>500</v>
+        <v>405.74101199418078</v>
       </c>
       <c r="B605">
-        <v>0.30347392639155091</v>
+        <v>500</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606">
-        <v>500</v>
+        <v>405.9436304772056</v>
       </c>
       <c r="B606">
-        <v>0.2770407061919325</v>
+        <v>500</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607">
-        <v>500</v>
+        <v>405.96124763752329</v>
       </c>
       <c r="B607">
-        <v>0.24454813931173919</v>
+        <v>500</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608">
-        <v>500</v>
+        <v>405.94007732958113</v>
       </c>
       <c r="B608">
-        <v>5.8735165434175451E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609">
-        <v>500</v>
+        <v>405.98386825540564</v>
       </c>
       <c r="B609">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610">
-        <v>500</v>
+        <v>405.94634673422132</v>
       </c>
       <c r="B610">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611">
-        <v>500</v>
+        <v>405.91720770862071</v>
       </c>
       <c r="B611">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612">
-        <v>500</v>
+        <v>405.97549608868655</v>
       </c>
       <c r="B612">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613">
-        <v>500</v>
+        <v>406.04836919390772</v>
       </c>
       <c r="B613">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614">
-        <v>500</v>
+        <v>406.25529861771724</v>
       </c>
       <c r="B614">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615">
-        <v>500</v>
+        <v>406.45688625018596</v>
       </c>
       <c r="B615">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616">
-        <v>500</v>
+        <v>406.76345468065813</v>
       </c>
       <c r="B616">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617">
-        <v>500</v>
+        <v>407.17084880174809</v>
       </c>
       <c r="B617">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618">
-        <v>500</v>
+        <v>407.63028920643558</v>
       </c>
       <c r="B618">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A619">
-        <v>500</v>
+        <v>408.15246728741067</v>
       </c>
       <c r="B619">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620">
-        <v>500</v>
+        <v>408.63937793413874</v>
       </c>
       <c r="B620">
-        <v>3.3124417997310002E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621">
-        <v>500</v>
+        <v>409.15599486162779</v>
       </c>
       <c r="B621">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A622">
-        <v>500</v>
+        <v>409.57539414573614</v>
       </c>
       <c r="B622">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623">
-        <v>500</v>
+        <v>410.00143181198757</v>
       </c>
       <c r="B623">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624">
-        <v>500</v>
+        <v>410.41369073664544</v>
       </c>
       <c r="B624">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625">
-        <v>500</v>
+        <v>410.65813154633372</v>
       </c>
       <c r="B625">
-        <v>7.488281956886559E-3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626">
-        <v>500</v>
+        <v>410.81872740056372</v>
       </c>
       <c r="B626">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627">
-        <v>500</v>
+        <v>411.07425118024531</v>
       </c>
       <c r="B627">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628">
-        <v>500</v>
+        <v>411.41902663813806</v>
       </c>
       <c r="B628">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629">
-        <v>500</v>
+        <v>411.88164171155012</v>
       </c>
       <c r="B629">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630">
-        <v>500</v>
+        <v>412.37263883985668</v>
       </c>
       <c r="B630">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631">
-        <v>500</v>
+        <v>412.90792389578365</v>
       </c>
       <c r="B631">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632">
-        <v>500</v>
+        <v>413.39869695311603</v>
       </c>
       <c r="B632">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633">
-        <v>500</v>
+        <v>413.9397569502529</v>
       </c>
       <c r="B633">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634">
-        <v>500</v>
+        <v>414.57729536295625</v>
       </c>
       <c r="B634">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635">
-        <v>500</v>
+        <v>415.23086638926515</v>
       </c>
       <c r="B635">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636">
-        <v>500</v>
+        <v>415.75358563639134</v>
       </c>
       <c r="B636">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637">
-        <v>500</v>
+        <v>416.25288654662552</v>
       </c>
       <c r="B637">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638">
-        <v>500</v>
+        <v>416.63966267045862</v>
       </c>
       <c r="B638">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639">
-        <v>500</v>
+        <v>417.00908145195757</v>
       </c>
       <c r="B639">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640">
-        <v>500</v>
+        <v>417.36375500572632</v>
       </c>
       <c r="B640">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641">
-        <v>500</v>
+        <v>417.65919526755982</v>
       </c>
       <c r="B641">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642">
-        <v>500</v>
+        <v>418.09502871840419</v>
       </c>
       <c r="B642">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643">
-        <v>500</v>
+        <v>418.47935004299688</v>
       </c>
       <c r="B643">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644">
-        <v>500</v>
+        <v>418.94318856629269</v>
       </c>
       <c r="B644">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645">
-        <v>500</v>
+        <v>419.36417615573964</v>
       </c>
       <c r="B645">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646">
-        <v>500</v>
+        <v>419.67575121953604</v>
       </c>
       <c r="B646">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647">
-        <v>500</v>
+        <v>419.97042143302309</v>
       </c>
       <c r="B647">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648">
-        <v>500</v>
+        <v>420.22784191115562</v>
       </c>
       <c r="B648">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649">
-        <v>500</v>
+        <v>420.40481300166095</v>
       </c>
       <c r="B649">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650">
-        <v>500</v>
+        <v>420.60501550477886</v>
       </c>
       <c r="B650">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651">
-        <v>500</v>
+        <v>420.79457631122528</v>
       </c>
       <c r="B651">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652">
-        <v>500</v>
+        <v>421.02752708442159</v>
       </c>
       <c r="B652">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653">
-        <v>500</v>
+        <v>421.22522032743683</v>
       </c>
       <c r="B653">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654">
-        <v>500</v>
+        <v>421.28830432450513</v>
       </c>
       <c r="B654">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655">
-        <v>500</v>
+        <v>421.46494075756635</v>
       </c>
       <c r="B655">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656">
-        <v>500</v>
+        <v>421.599885922201</v>
       </c>
       <c r="B656">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657">
-        <v>500</v>
+        <v>421.67249767312529</v>
       </c>
       <c r="B657">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658">
-        <v>500</v>
+        <v>421.88331214347903</v>
       </c>
       <c r="B658">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659">
-        <v>500</v>
+        <v>422.20443370254509</v>
       </c>
       <c r="B659">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660">
-        <v>500</v>
+        <v>422.5672937269228</v>
       </c>
       <c r="B660">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661">
-        <v>500</v>
+        <v>422.8401446625129</v>
       </c>
       <c r="B661">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662">
-        <v>500</v>
+        <v>423.13849409820244</v>
       </c>
       <c r="B662">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663">
-        <v>500</v>
+        <v>423.37732878301961</v>
       </c>
       <c r="B663">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664">
-        <v>500</v>
+        <v>423.53188544896739</v>
       </c>
       <c r="B664">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665">
-        <v>500</v>
+        <v>423.62236790647853</v>
       </c>
       <c r="B665">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666">
-        <v>500</v>
+        <v>423.5722178415707</v>
       </c>
       <c r="B666">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667">
-        <v>500</v>
+        <v>423.58076215772979</v>
       </c>
       <c r="B667">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668">
-        <v>500</v>
+        <v>423.58914705565451</v>
       </c>
       <c r="B668">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669">
-        <v>500</v>
+        <v>423.49205636361745</v>
       </c>
       <c r="B669">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670">
-        <v>500</v>
+        <v>423.27034366752792</v>
       </c>
       <c r="B670">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671">
-        <v>500</v>
+        <v>423.00772866640744</v>
       </c>
       <c r="B671">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672">
-        <v>500</v>
+        <v>422.73631756864256</v>
       </c>
       <c r="B672">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673">
-        <v>500</v>
+        <v>422.52580995231875</v>
       </c>
       <c r="B673">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674">
-        <v>500</v>
+        <v>422.33763960521463</v>
       </c>
       <c r="B674">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A675">
-        <v>500</v>
+        <v>422.12096453832402</v>
       </c>
       <c r="B675">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676">
-        <v>500</v>
+        <v>422.12719337461806</v>
       </c>
       <c r="B676">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677">
-        <v>500</v>
+        <v>422.2207102931439</v>
       </c>
       <c r="B677">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678">
-        <v>500</v>
+        <v>422.20220281113671</v>
       </c>
       <c r="B678">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679">
-        <v>500</v>
+        <v>422.26239963212328</v>
       </c>
       <c r="B679">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680">
-        <v>500</v>
+        <v>422.24214957446475</v>
       </c>
       <c r="B680">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681">
-        <v>500</v>
+        <v>422.10149365887253</v>
       </c>
       <c r="B681">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682">
-        <v>500</v>
+        <v>421.95216548306576</v>
       </c>
       <c r="B682">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683">
-        <v>500</v>
+        <v>421.87601613595297</v>
       </c>
       <c r="B683">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684">
-        <v>500</v>
+        <v>421.73695116968639</v>
       </c>
       <c r="B684">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685">
-        <v>500</v>
+        <v>421.76766199005823</v>
       </c>
       <c r="B685">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686">
-        <v>500</v>
+        <v>421.69152234290624</v>
       </c>
       <c r="B686">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687">
-        <v>500</v>
+        <v>421.54775646234674</v>
       </c>
       <c r="B687">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688">
-        <v>500</v>
+        <v>421.45492622751038</v>
       </c>
       <c r="B688">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689">
-        <v>500</v>
+        <v>421.32216373020361</v>
       </c>
       <c r="B689">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690">
-        <v>500</v>
+        <v>421.1614945813713</v>
       </c>
       <c r="B690">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691">
-        <v>500</v>
+        <v>421.01798792912615</v>
       </c>
       <c r="B691">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692">
-        <v>500</v>
+        <v>420.87292392900133</v>
       </c>
       <c r="B692">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693">
-        <v>500</v>
+        <v>420.83377451771105</v>
       </c>
       <c r="B693">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694">
-        <v>500</v>
+        <v>420.90616862018231</v>
       </c>
       <c r="B694">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695">
-        <v>500</v>
+        <v>420.97589299738831</v>
       </c>
       <c r="B695">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696">
-        <v>500</v>
+        <v>421.06460435891137</v>
       </c>
       <c r="B696">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697">
-        <v>500</v>
+        <v>421.17617088995348</v>
       </c>
       <c r="B697">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698">
-        <v>500</v>
+        <v>421.1369756981959</v>
       </c>
       <c r="B698">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699">
-        <v>500</v>
+        <v>421.0534924057485</v>
       </c>
       <c r="B699">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700">
-        <v>500</v>
+        <v>420.90744568377988</v>
       </c>
       <c r="B700">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701">
-        <v>500</v>
+        <v>420.76575569858215</v>
       </c>
       <c r="B701">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702">
-        <v>500</v>
+        <v>420.71549194297415</v>
       </c>
       <c r="B702">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703">
-        <v>500</v>
+        <v>420.78316795202693</v>
       </c>
       <c r="B703">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704">
-        <v>500</v>
+        <v>420.84477352108001</v>
       </c>
       <c r="B704">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705">
-        <v>500</v>
+        <v>421.05553308917843</v>
       </c>
       <c r="B705">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706">
-        <v>500</v>
+        <v>421.26580369855094</v>
       </c>
       <c r="B706">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707">
-        <v>500</v>
+        <v>421.43798853634263</v>
       </c>
       <c r="B707">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A708">
-        <v>500</v>
+        <v>421.71851096320711</v>
       </c>
       <c r="B708">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709">
-        <v>500</v>
+        <v>422.07821979174992</v>
       </c>
       <c r="B709">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710">
-        <v>500</v>
+        <v>422.39981466223645</v>
       </c>
       <c r="B710">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A711">
-        <v>500</v>
+        <v>422.8084068622174</v>
       </c>
       <c r="B711">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A712">
-        <v>500</v>
+        <v>423.28437577526239</v>
       </c>
       <c r="B712">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713">
-        <v>500</v>
+        <v>423.7668794037366</v>
       </c>
       <c r="B713">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714">
-        <v>500</v>
+        <v>424.2391473012413</v>
       </c>
       <c r="B714">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715">
-        <v>500</v>
+        <v>424.73128614124676</v>
       </c>
       <c r="B715">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716">
-        <v>500</v>
+        <v>425.3128350601994</v>
       </c>
       <c r="B716">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717">
-        <v>500</v>
+        <v>425.85405887933592</v>
       </c>
       <c r="B717">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718">
-        <v>500</v>
+        <v>426.4430423781987</v>
       </c>
       <c r="B718">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719">
-        <v>500</v>
+        <v>427.0018252287997</v>
       </c>
       <c r="B719">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720">
-        <v>500</v>
+        <v>427.64368437775136</v>
       </c>
       <c r="B720">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721">
-        <v>500</v>
+        <v>428.2366915671563</v>
       </c>
       <c r="B721">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722">
-        <v>500</v>
+        <v>428.80308046429201</v>
       </c>
       <c r="B722">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723">
-        <v>500</v>
+        <v>429.43128434017376</v>
       </c>
       <c r="B723">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A724">
-        <v>500</v>
+        <v>430.16891464505102</v>
       </c>
       <c r="B724">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725">
-        <v>500</v>
+        <v>430.92785201356168</v>
       </c>
       <c r="B725">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726">
-        <v>500</v>
+        <v>431.6320593937163</v>
       </c>
       <c r="B726">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727">
-        <v>500</v>
+        <v>432.21812150715823</v>
       </c>
       <c r="B727">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728">
-        <v>500</v>
+        <v>432.77521876987157</v>
       </c>
       <c r="B728">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729">
-        <v>500</v>
+        <v>433.38908539432936</v>
       </c>
       <c r="B729">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730">
-        <v>500</v>
+        <v>434.08465818154781</v>
       </c>
       <c r="B730">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731">
-        <v>500</v>
+        <v>434.8345260419166</v>
       </c>
       <c r="B731">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732">
-        <v>500</v>
+        <v>435.70635186467183</v>
       </c>
       <c r="B732">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733">
-        <v>500</v>
+        <v>436.62883841514918</v>
       </c>
       <c r="B733">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734">
-        <v>500</v>
+        <v>437.65041778614523</v>
       </c>
       <c r="B734">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A735">
-        <v>500</v>
+        <v>438.56816898061754</v>
       </c>
       <c r="B735">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736">
-        <v>500</v>
+        <v>439.43309179835177</v>
       </c>
       <c r="B736">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737">
-        <v>500</v>
+        <v>440.32219519205478</v>
       </c>
       <c r="B737">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738">
-        <v>500</v>
+        <v>441.13889247781219</v>
       </c>
       <c r="B738">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739">
-        <v>500</v>
+        <v>441.8919977970038</v>
       </c>
       <c r="B739">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740">
-        <v>500</v>
+        <v>442.65084539787995</v>
       </c>
       <c r="B740">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741">
-        <v>500</v>
+        <v>443.4077798281711</v>
       </c>
       <c r="B741">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742">
-        <v>500</v>
+        <v>444.00481469377314</v>
       </c>
       <c r="B742">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743">
-        <v>500</v>
+        <v>444.52376474995759</v>
       </c>
       <c r="B743">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744">
-        <v>500</v>
+        <v>445.10456289344063</v>
       </c>
       <c r="B744">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A745">
-        <v>500</v>
+        <v>445.66822432517284</v>
       </c>
       <c r="B745">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746">
-        <v>500</v>
+        <v>446.21715683628628</v>
       </c>
       <c r="B746">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747">
-        <v>500</v>
+        <v>446.82950449893445</v>
       </c>
       <c r="B747">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748">
-        <v>500</v>
+        <v>447.46306352677425</v>
       </c>
       <c r="B748">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749">
-        <v>500</v>
+        <v>448.0753363088217</v>
       </c>
       <c r="B749">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750">
-        <v>500</v>
+        <v>448.78554707283052</v>
       </c>
       <c r="B750">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751">
-        <v>500</v>
+        <v>449.49790094596949</v>
       </c>
       <c r="B751">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752">
-        <v>500</v>
+        <v>450.39115003369858</v>
       </c>
       <c r="B752">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753">
-        <v>500</v>
+        <v>451.43382845300857</v>
       </c>
       <c r="B753">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A754">
-        <v>500</v>
+        <v>452.5894845376269</v>
       </c>
       <c r="B754">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A755">
-        <v>500</v>
+        <v>453.65712044777393</v>
       </c>
       <c r="B755">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A756">
-        <v>500</v>
+        <v>454.84180509574219</v>
       </c>
       <c r="B756">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A757">
-        <v>500</v>
+        <v>456.0121221922937</v>
       </c>
       <c r="B757">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A758">
-        <v>500</v>
+        <v>457.19645332270954</v>
       </c>
       <c r="B758">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A759">
-        <v>500</v>
+        <v>458.36709834541495</v>
       </c>
       <c r="B759">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A760">
-        <v>500</v>
+        <v>459.42632776579285</v>
       </c>
       <c r="B760">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A761">
-        <v>500</v>
+        <v>460.38286101147844</v>
       </c>
       <c r="B761">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A762">
-        <v>500</v>
+        <v>461.33087462356076</v>
       </c>
       <c r="B762">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A763">
-        <v>500</v>
+        <v>462.22869646160996</v>
       </c>
       <c r="B763">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A764">
-        <v>500</v>
+        <v>463.26394932834205</v>
       </c>
       <c r="B764">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A765">
-        <v>500</v>
+        <v>464.28098271184263</v>
       </c>
       <c r="B765">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A766">
-        <v>500</v>
+        <v>465.31557162370774</v>
       </c>
       <c r="B766">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A767">
-        <v>500</v>
+        <v>466.28437351055129</v>
       </c>
       <c r="B767">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A768">
-        <v>500</v>
+        <v>467.28432510221143</v>
       </c>
       <c r="B768">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A769">
-        <v>500</v>
+        <v>468.25502341971685</v>
       </c>
       <c r="B769">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A770">
-        <v>500</v>
+        <v>469.18392852014659</v>
       </c>
       <c r="B770">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A771">
-        <v>500</v>
+        <v>470.23543964645529</v>
       </c>
       <c r="B771">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A772">
-        <v>500</v>
+        <v>471.26529117868665</v>
       </c>
       <c r="B772">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A773">
-        <v>500</v>
+        <v>472.24338948472581</v>
       </c>
       <c r="B773">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A774">
-        <v>500</v>
+        <v>473.25870572442682</v>
       </c>
       <c r="B774">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A775">
-        <v>500</v>
+        <v>474.25354316587431</v>
       </c>
       <c r="B775">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A776">
-        <v>500</v>
+        <v>475.2029968475959</v>
       </c>
       <c r="B776">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A777">
-        <v>500</v>
+        <v>476.1818972022283</v>
       </c>
       <c r="B777">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A778">
-        <v>500</v>
+        <v>477.07499552515497</v>
       </c>
       <c r="B778">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A779">
-        <v>500</v>
+        <v>477.92191048262316</v>
       </c>
       <c r="B779">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A780">
-        <v>500</v>
+        <v>478.744799643899</v>
       </c>
       <c r="B780">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A781">
-        <v>500</v>
+        <v>479.39351016640973</v>
       </c>
       <c r="B781">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A782">
-        <v>500</v>
+        <v>480.05870022926717</v>
       </c>
       <c r="B782">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A783">
-        <v>500</v>
+        <v>480.81104964823049</v>
       </c>
       <c r="B783">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A784">
-        <v>500</v>
+        <v>481.55552405079328</v>
       </c>
       <c r="B784">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A785">
-        <v>500</v>
+        <v>482.23277660384389</v>
       </c>
       <c r="B785">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A786">
-        <v>500</v>
+        <v>482.86856523996249</v>
       </c>
       <c r="B786">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A787">
-        <v>500</v>
+        <v>483.55285821212959</v>
       </c>
       <c r="B787">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A788">
-        <v>500</v>
+        <v>484.2025428430332</v>
       </c>
       <c r="B788">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A789">
-        <v>500</v>
+        <v>484.80235008712168</v>
       </c>
       <c r="B789">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A790">
-        <v>500</v>
+        <v>485.47639270535063</v>
       </c>
       <c r="B790">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A791">
-        <v>500</v>
+        <v>486.15699169506917</v>
       </c>
       <c r="B791">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A792">
-        <v>500</v>
+        <v>486.81661974146311</v>
       </c>
       <c r="B792">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A793">
-        <v>500</v>
+        <v>487.46093529098039</v>
       </c>
       <c r="B793">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A794">
-        <v>500</v>
+        <v>488.05201545336615</v>
       </c>
       <c r="B794">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A795">
-        <v>500</v>
+        <v>488.60525238571006</v>
       </c>
       <c r="B795">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A796">
-        <v>500</v>
+        <v>489.16071747774447</v>
       </c>
       <c r="B796">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A797">
-        <v>500</v>
+        <v>489.69076884377489</v>
       </c>
       <c r="B797">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A798">
-        <v>500</v>
+        <v>490.22582743539982</v>
       </c>
       <c r="B798">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A799">
-        <v>500</v>
+        <v>490.69777942436059</v>
       </c>
       <c r="B799">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A800">
-        <v>500</v>
+        <v>491.0683434320033</v>
       </c>
       <c r="B800">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A801">
-        <v>500</v>
+        <v>491.32260700639773</v>
       </c>
       <c r="B801">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A802">
-        <v>500</v>
+        <v>491.6195978327803</v>
       </c>
       <c r="B802">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A803">
-        <v>500</v>
+        <v>491.89105725673727</v>
       </c>
       <c r="B803">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A804">
-        <v>500</v>
+        <v>492.14832310123205</v>
       </c>
       <c r="B804">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A805">
-        <v>500</v>
+        <v>492.42599261348596</v>
       </c>
       <c r="B805">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A806">
-        <v>500</v>
+        <v>492.63579305530874</v>
       </c>
       <c r="B806">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A807">
-        <v>500</v>
+        <v>492.93012049349733</v>
       </c>
       <c r="B807">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A808">
-        <v>500</v>
+        <v>493.31212784696072</v>
       </c>
       <c r="B808">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A809">
-        <v>500</v>
+        <v>493.5443736545717</v>
       </c>
       <c r="B809">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A810">
-        <v>500</v>
+        <v>493.82959091232897</v>
       </c>
       <c r="B810">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A811">
-        <v>500</v>
+        <v>494.17849432898453</v>
       </c>
       <c r="B811">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A812">
-        <v>500</v>
+        <v>494.57854619358551</v>
       </c>
       <c r="B812">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A813">
-        <v>500</v>
+        <v>495.01999058818319</v>
       </c>
       <c r="B813">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A814">
-        <v>500</v>
+        <v>495.41039125411766</v>
       </c>
       <c r="B814">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A815">
-        <v>500</v>
+        <v>495.6479801105769</v>
       </c>
       <c r="B815">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A816">
-        <v>500</v>
+        <v>495.79821489673066</v>
       </c>
       <c r="B816">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A817">
-        <v>500</v>
+        <v>495.85981986974542</v>
       </c>
       <c r="B817">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A818">
-        <v>500</v>
+        <v>495.82362664170711</v>
       </c>
       <c r="B818">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A819">
-        <v>500</v>
+        <v>495.94445768031903</v>
       </c>
       <c r="B819">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A820">
-        <v>500</v>
+        <v>496.14849464369547</v>
       </c>
       <c r="B820">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A821">
-        <v>500</v>
+        <v>496.35291948337255</v>
       </c>
       <c r="B821">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A822">
-        <v>500</v>
+        <v>496.61249154895665</v>
       </c>
       <c r="B822">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A823">
-        <v>500</v>
+        <v>496.80700609779973</v>
       </c>
       <c r="B823">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A824">
-        <v>500</v>
+        <v>496.98857766761103</v>
       </c>
       <c r="B824">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A825">
-        <v>500</v>
+        <v>497.16393884434495</v>
       </c>
       <c r="B825">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A826">
-        <v>500</v>
+        <v>497.33488795587516</v>
       </c>
       <c r="B826">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A827">
-        <v>500</v>
+        <v>497.42482527577454</v>
       </c>
       <c r="B827">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A828">
-        <v>500</v>
+        <v>497.51501877932458</v>
       </c>
       <c r="B828">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A829">
-        <v>500</v>
+        <v>497.71339616687897</v>
       </c>
       <c r="B829">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A830">
-        <v>500</v>
+        <v>498.02392094107364</v>
       </c>
       <c r="B830">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A831">
-        <v>500</v>
+        <v>498.38505561679921</v>
       </c>
       <c r="B831">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A832">
-        <v>500</v>
+        <v>498.76101202729473</v>
       </c>
       <c r="B832">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A833">
-        <v>500</v>
+        <v>499.09393353154735</v>
       </c>
       <c r="B833">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A834">
-        <v>500</v>
+        <v>499.36275933377431</v>
       </c>
       <c r="B834">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A835">
-        <v>500</v>
+        <v>499.66772289382186</v>
       </c>
       <c r="B835">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A836">
-        <v>500</v>
+        <v>499.96046742296852</v>
       </c>
       <c r="B836">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.3">
@@ -7032,7 +7036,7 @@
         <v>500</v>
       </c>
       <c r="B837">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.3">
@@ -7040,7 +7044,7 @@
         <v>500</v>
       </c>
       <c r="B838">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.3">
@@ -7048,7 +7052,7 @@
         <v>500</v>
       </c>
       <c r="B839">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.3">
@@ -7056,7 +7060,7 @@
         <v>500</v>
       </c>
       <c r="B840">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.3">
@@ -7064,7 +7068,7 @@
         <v>500</v>
       </c>
       <c r="B841">
-        <v>5.2861731260154185E-3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.3">
@@ -7072,7 +7076,7 @@
         <v>500</v>
       </c>
       <c r="B842">
-        <v>5.9919479177296731E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.3">
@@ -7080,7 +7084,7 @@
         <v>500</v>
       </c>
       <c r="B843">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.3">
@@ -7088,7 +7092,7 @@
         <v>500</v>
       </c>
       <c r="B844">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.3">
@@ -7096,7 +7100,7 @@
         <v>500</v>
       </c>
       <c r="B845">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.3">
@@ -7104,7 +7108,7 @@
         <v>500</v>
       </c>
       <c r="B846">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.3">
@@ -7112,7 +7116,7 @@
         <v>500</v>
       </c>
       <c r="B847">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.3">
@@ -7120,7 +7124,7 @@
         <v>500</v>
       </c>
       <c r="B848">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.3">
@@ -7128,7 +7132,7 @@
         <v>500</v>
       </c>
       <c r="B849">
-        <v>4.2321595436561499E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.3">
@@ -7136,7 +7140,7 @@
         <v>500</v>
       </c>
       <c r="B850">
-        <v>5.3116375025546517E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.3">
@@ -7144,7 +7148,7 @@
         <v>500</v>
       </c>
       <c r="B851">
-        <v>3.9274592878331793E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.3">
@@ -7152,7 +7156,7 @@
         <v>500</v>
       </c>
       <c r="B852">
-        <v>3.7388187008557658E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.3">
@@ -7160,7 +7164,7 @@
         <v>500</v>
       </c>
       <c r="B853">
-        <v>5.2576870702312373E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.3">
@@ -7168,7 +7172,7 @@
         <v>500</v>
       </c>
       <c r="B854">
-        <v>7.2746033135538707E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.3">
@@ -7176,7 +7180,7 @@
         <v>500</v>
       </c>
       <c r="B855">
-        <v>8.7187645880053635E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.3">
@@ -7184,7 +7188,7 @@
         <v>500</v>
       </c>
       <c r="B856">
-        <v>3.4523239280967524E-2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.3">
@@ -7192,7 +7196,7 @@
         <v>500</v>
       </c>
       <c r="B857">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.3">
@@ -7200,7 +7204,7 @@
         <v>500</v>
       </c>
       <c r="B858">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.3">
@@ -7208,7 +7212,7 @@
         <v>500</v>
       </c>
       <c r="B859">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.3">
@@ -7216,7 +7220,7 @@
         <v>500</v>
       </c>
       <c r="B860">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.3">
@@ -7224,7 +7228,7 @@
         <v>500</v>
       </c>
       <c r="B861">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.3">
@@ -7232,7 +7236,7 @@
         <v>500</v>
       </c>
       <c r="B862">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.3">
@@ -7240,7 +7244,7 @@
         <v>500</v>
       </c>
       <c r="B863">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.3">
@@ -7248,7 +7252,7 @@
         <v>500</v>
       </c>
       <c r="B864">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.3">
@@ -7256,7 +7260,7 @@
         <v>500</v>
       </c>
       <c r="B865">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.3">
@@ -7264,7 +7268,7 @@
         <v>500</v>
       </c>
       <c r="B866">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.3">
@@ -7272,7 +7276,7 @@
         <v>500</v>
       </c>
       <c r="B867">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.3">
@@ -7280,7 +7284,7 @@
         <v>500</v>
       </c>
       <c r="B868">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.3">
@@ -7288,7 +7292,7 @@
         <v>500</v>
       </c>
       <c r="B869">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.3">
@@ -7296,7 +7300,7 @@
         <v>500</v>
       </c>
       <c r="B870">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.3">
@@ -7304,7 +7308,7 @@
         <v>500</v>
       </c>
       <c r="B871">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.3">
@@ -7312,7 +7316,7 @@
         <v>500</v>
       </c>
       <c r="B872">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.3">
@@ -7320,7 +7324,7 @@
         <v>500</v>
       </c>
       <c r="B873">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.3">
@@ -7328,7 +7332,7 @@
         <v>500</v>
       </c>
       <c r="B874">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.3">
@@ -7336,7 +7340,7 @@
         <v>500</v>
       </c>
       <c r="B875">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.3">
@@ -7344,7 +7348,7 @@
         <v>500</v>
       </c>
       <c r="B876">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.3">
@@ -7352,7 +7356,7 @@
         <v>500</v>
       </c>
       <c r="B877">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.3">
@@ -7360,7 +7364,7 @@
         <v>500</v>
       </c>
       <c r="B878">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.3">
@@ -7368,7 +7372,7 @@
         <v>500</v>
       </c>
       <c r="B879">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.3">
@@ -7376,7 +7380,7 @@
         <v>500</v>
       </c>
       <c r="B880">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.3">
@@ -7384,7 +7388,7 @@
         <v>500</v>
       </c>
       <c r="B881">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.3">
@@ -7392,7 +7396,7 @@
         <v>500</v>
       </c>
       <c r="B882">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.3">
@@ -7400,7 +7404,7 @@
         <v>500</v>
       </c>
       <c r="B883">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.3">
@@ -7408,7 +7412,7 @@
         <v>500</v>
       </c>
       <c r="B884">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.3">
@@ -7416,7 +7420,7 @@
         <v>500</v>
       </c>
       <c r="B885">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.3">
@@ -7424,7 +7428,7 @@
         <v>500</v>
       </c>
       <c r="B886">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.3">
@@ -7432,7 +7436,7 @@
         <v>500</v>
       </c>
       <c r="B887">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.3">
@@ -7440,7 +7444,7 @@
         <v>500</v>
       </c>
       <c r="B888">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.3">
@@ -7448,7 +7452,7 @@
         <v>500</v>
       </c>
       <c r="B889">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.3">
@@ -7456,7 +7460,7 @@
         <v>500</v>
       </c>
       <c r="B890">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.3">
@@ -7464,7 +7468,7 @@
         <v>500</v>
       </c>
       <c r="B891">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.3">
@@ -7472,7 +7476,7 @@
         <v>500</v>
       </c>
       <c r="B892">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.3">
@@ -7480,7 +7484,7 @@
         <v>500</v>
       </c>
       <c r="B893">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.3">
@@ -7488,7 +7492,7 @@
         <v>500</v>
       </c>
       <c r="B894">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.3">
@@ -7496,7 +7500,7 @@
         <v>500</v>
       </c>
       <c r="B895">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.3">
@@ -7504,7 +7508,7 @@
         <v>500</v>
       </c>
       <c r="B896">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.3">
@@ -7512,7 +7516,7 @@
         <v>500</v>
       </c>
       <c r="B897">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.3">
@@ -7520,7 +7524,7 @@
         <v>500</v>
       </c>
       <c r="B898">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.3">
@@ -7528,7 +7532,7 @@
         <v>500</v>
       </c>
       <c r="B899">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.3">
@@ -7536,7 +7540,7 @@
         <v>500</v>
       </c>
       <c r="B900">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.3">
@@ -7544,7 +7548,7 @@
         <v>500</v>
       </c>
       <c r="B901">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.3">
@@ -7552,7 +7556,7 @@
         <v>500</v>
       </c>
       <c r="B902">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.3">
@@ -7560,7 +7564,7 @@
         <v>500</v>
       </c>
       <c r="B903">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.3">
@@ -7568,7 +7572,7 @@
         <v>500</v>
       </c>
       <c r="B904">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.3">
@@ -7576,7 +7580,7 @@
         <v>500</v>
       </c>
       <c r="B905">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.3">
@@ -7584,7 +7588,7 @@
         <v>500</v>
       </c>
       <c r="B906">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.3">
@@ -7592,7 +7596,7 @@
         <v>500</v>
       </c>
       <c r="B907">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.3">
@@ -7600,7 +7604,7 @@
         <v>500</v>
       </c>
       <c r="B908">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.3">
@@ -7608,7 +7612,7 @@
         <v>500</v>
       </c>
       <c r="B909">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.3">
@@ -7616,7 +7620,7 @@
         <v>500</v>
       </c>
       <c r="B910">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.3">
@@ -7624,7 +7628,7 @@
         <v>500</v>
       </c>
       <c r="B911">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.3">
@@ -7632,7 +7636,7 @@
         <v>500</v>
       </c>
       <c r="B912">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.3">
@@ -7640,7 +7644,7 @@
         <v>500</v>
       </c>
       <c r="B913">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.3">
@@ -7648,7 +7652,7 @@
         <v>500</v>
       </c>
       <c r="B914">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.3">
@@ -7656,7 +7660,7 @@
         <v>500</v>
       </c>
       <c r="B915">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.3">
@@ -7664,7 +7668,7 @@
         <v>500</v>
       </c>
       <c r="B916">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.3">
@@ -7672,7 +7676,7 @@
         <v>500</v>
       </c>
       <c r="B917">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.3">
@@ -7680,7 +7684,7 @@
         <v>500</v>
       </c>
       <c r="B918">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.3">
@@ -7688,7 +7692,7 @@
         <v>500</v>
       </c>
       <c r="B919">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.3">
@@ -7696,7 +7700,7 @@
         <v>500</v>
       </c>
       <c r="B920">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.3">
@@ -7704,7 +7708,7 @@
         <v>500</v>
       </c>
       <c r="B921">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.3">
@@ -7712,7 +7716,7 @@
         <v>500</v>
       </c>
       <c r="B922">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.3">
@@ -7720,7 +7724,7 @@
         <v>500</v>
       </c>
       <c r="B923">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.3">
@@ -7728,7 +7732,7 @@
         <v>500</v>
       </c>
       <c r="B924">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.3">
@@ -7736,7 +7740,7 @@
         <v>500</v>
       </c>
       <c r="B925">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.3">
@@ -7744,7 +7748,7 @@
         <v>500</v>
       </c>
       <c r="B926">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.3">
@@ -7752,7 +7756,7 @@
         <v>500</v>
       </c>
       <c r="B927">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.3">
@@ -7760,7 +7764,7 @@
         <v>500</v>
       </c>
       <c r="B928">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.3">
@@ -7768,7 +7772,7 @@
         <v>500</v>
       </c>
       <c r="B929">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.3">
@@ -7776,7 +7780,7 @@
         <v>500</v>
       </c>
       <c r="B930">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.3">
@@ -7784,7 +7788,7 @@
         <v>500</v>
       </c>
       <c r="B931">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.3">
@@ -7792,7 +7796,7 @@
         <v>500</v>
       </c>
       <c r="B932">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.3">
@@ -7800,7 +7804,7 @@
         <v>500</v>
       </c>
       <c r="B933">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.3">
@@ -7808,7 +7812,7 @@
         <v>500</v>
       </c>
       <c r="B934">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.3">
@@ -7816,7 +7820,7 @@
         <v>500</v>
       </c>
       <c r="B935">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.3">
@@ -7824,7 +7828,7 @@
         <v>500</v>
       </c>
       <c r="B936">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.3">
@@ -7832,7 +7836,7 @@
         <v>500</v>
       </c>
       <c r="B937">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.3">
@@ -7840,7 +7844,7 @@
         <v>500</v>
       </c>
       <c r="B938">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.3">
@@ -7848,7 +7852,7 @@
         <v>500</v>
       </c>
       <c r="B939">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.3">
@@ -7856,7 +7860,7 @@
         <v>500</v>
       </c>
       <c r="B940">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.3">
@@ -7864,7 +7868,7 @@
         <v>500</v>
       </c>
       <c r="B941">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.3">
@@ -7872,7 +7876,7 @@
         <v>500</v>
       </c>
       <c r="B942">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.3">
@@ -7880,7 +7884,7 @@
         <v>500</v>
       </c>
       <c r="B943">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.3">
@@ -7888,7 +7892,7 @@
         <v>500</v>
       </c>
       <c r="B944">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.3">
@@ -7896,7 +7900,7 @@
         <v>500</v>
       </c>
       <c r="B945">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.3">
@@ -7904,7 +7908,7 @@
         <v>500</v>
       </c>
       <c r="B946">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.3">
@@ -7912,7 +7916,7 @@
         <v>500</v>
       </c>
       <c r="B947">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.3">
@@ -7920,7 +7924,7 @@
         <v>500</v>
       </c>
       <c r="B948">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.3">
@@ -7928,7 +7932,7 @@
         <v>500</v>
       </c>
       <c r="B949">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.3">
@@ -7936,7 +7940,7 @@
         <v>500</v>
       </c>
       <c r="B950">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.3">
@@ -7944,7 +7948,7 @@
         <v>500</v>
       </c>
       <c r="B951">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.3">
@@ -7952,7 +7956,7 @@
         <v>500</v>
       </c>
       <c r="B952">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.3">
@@ -7960,7 +7964,7 @@
         <v>500</v>
       </c>
       <c r="B953">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.3">
@@ -7968,7 +7972,7 @@
         <v>500</v>
       </c>
       <c r="B954">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.3">
@@ -7976,7 +7980,7 @@
         <v>500</v>
       </c>
       <c r="B955">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.3">
@@ -7984,7 +7988,7 @@
         <v>500</v>
       </c>
       <c r="B956">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.3">
@@ -7992,7 +7996,7 @@
         <v>500</v>
       </c>
       <c r="B957">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.3">
@@ -8000,7 +8004,7 @@
         <v>500</v>
       </c>
       <c r="B958">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.3">
@@ -8008,7 +8012,7 @@
         <v>500</v>
       </c>
       <c r="B959">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.3">
@@ -8016,7 +8020,7 @@
         <v>500</v>
       </c>
       <c r="B960">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.3">
@@ -8024,7 +8028,7 @@
         <v>500</v>
       </c>
       <c r="B961">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.3">
@@ -8032,7 +8036,7 @@
         <v>500</v>
       </c>
       <c r="B962">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.3">
@@ -8040,7 +8044,7 @@
         <v>500</v>
       </c>
       <c r="B963">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.3">
@@ -8048,7 +8052,7 @@
         <v>500</v>
       </c>
       <c r="B964">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.3">
@@ -8056,7 +8060,7 @@
         <v>500</v>
       </c>
       <c r="B965">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.3">
@@ -8064,7 +8068,7 @@
         <v>500</v>
       </c>
       <c r="B966">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.3">
@@ -8072,7 +8076,7 @@
         <v>500</v>
       </c>
       <c r="B967">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.3">
@@ -8080,7 +8084,7 @@
         <v>500</v>
       </c>
       <c r="B968">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.3">
@@ -8088,7 +8092,7 @@
         <v>500</v>
       </c>
       <c r="B969">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.3">
@@ -8096,7 +8100,7 @@
         <v>500</v>
       </c>
       <c r="B970">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.3">
@@ -8104,7 +8108,7 @@
         <v>500</v>
       </c>
       <c r="B971">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.3">
@@ -8112,7 +8116,7 @@
         <v>500</v>
       </c>
       <c r="B972">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.3">
@@ -8120,7 +8124,7 @@
         <v>500</v>
       </c>
       <c r="B973">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.3">
@@ -8128,7 +8132,7 @@
         <v>500</v>
       </c>
       <c r="B974">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.3">
@@ -8136,7 +8140,7 @@
         <v>500</v>
       </c>
       <c r="B975">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.3">
@@ -8144,7 +8148,7 @@
         <v>500</v>
       </c>
       <c r="B976">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.3">
@@ -8152,7 +8156,7 @@
         <v>500</v>
       </c>
       <c r="B977">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.3">
@@ -8160,7 +8164,7 @@
         <v>500</v>
       </c>
       <c r="B978">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.3">
@@ -8168,7 +8172,7 @@
         <v>500</v>
       </c>
       <c r="B979">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.3">
@@ -8176,7 +8180,7 @@
         <v>500</v>
       </c>
       <c r="B980">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.3">
@@ -8184,7 +8188,7 @@
         <v>500</v>
       </c>
       <c r="B981">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.3">
@@ -8192,7 +8196,7 @@
         <v>500</v>
       </c>
       <c r="B982">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.3">
@@ -8200,7 +8204,7 @@
         <v>500</v>
       </c>
       <c r="B983">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.3">
@@ -8208,7 +8212,7 @@
         <v>500</v>
       </c>
       <c r="B984">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.3">
@@ -8216,7 +8220,7 @@
         <v>500</v>
       </c>
       <c r="B985">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.3">
@@ -8224,7 +8228,7 @@
         <v>500</v>
       </c>
       <c r="B986">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.3">
@@ -8232,7 +8236,7 @@
         <v>500</v>
       </c>
       <c r="B987">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.3">
@@ -8240,7 +8244,7 @@
         <v>500</v>
       </c>
       <c r="B988">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.3">
@@ -8248,7 +8252,7 @@
         <v>500</v>
       </c>
       <c r="B989">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.3">
@@ -8256,7 +8260,7 @@
         <v>500</v>
       </c>
       <c r="B990">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="991" spans="1:2" x14ac:dyDescent="0.3">
@@ -8264,7 +8268,7 @@
         <v>500</v>
       </c>
       <c r="B991">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="992" spans="1:2" x14ac:dyDescent="0.3">
@@ -8272,7 +8276,7 @@
         <v>500</v>
       </c>
       <c r="B992">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="993" spans="1:2" x14ac:dyDescent="0.3">
@@ -8280,7 +8284,7 @@
         <v>500</v>
       </c>
       <c r="B993">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.3">
@@ -8288,7 +8292,7 @@
         <v>500</v>
       </c>
       <c r="B994">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="995" spans="1:2" x14ac:dyDescent="0.3">
@@ -8296,7 +8300,7 @@
         <v>500</v>
       </c>
       <c r="B995">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.3">
@@ -8304,7 +8308,7 @@
         <v>500</v>
       </c>
       <c r="B996">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="997" spans="1:2" x14ac:dyDescent="0.3">
@@ -8312,7 +8316,7 @@
         <v>500</v>
       </c>
       <c r="B997">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.3">
@@ -8320,7 +8324,7 @@
         <v>500</v>
       </c>
       <c r="B998">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.3">
@@ -8328,7 +8332,7 @@
         <v>500</v>
       </c>
       <c r="B999">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1000" spans="1:2" x14ac:dyDescent="0.3">
@@ -8336,7 +8340,7 @@
         <v>500</v>
       </c>
       <c r="B1000">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/OutputData.xlsx
+++ b/OutputData.xlsx
@@ -345,2447 +345,2447 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>436.87432808551569</v>
+        <v>347.66433646777023</v>
       </c>
       <c r="B1">
-        <v>441.02294506972117</v>
+        <v>51.855510439113523</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>436.68176493183682</v>
+        <v>348.46707194756931</v>
       </c>
       <c r="B2">
-        <v>442.11029558904585</v>
+        <v>51.818574682422131</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>436.50709782305927</v>
+        <v>349.31380952501496</v>
       </c>
       <c r="B3">
-        <v>443.18564163185005</v>
+        <v>51.876477116954632</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>436.29221393453258</v>
+        <v>350.14245887815605</v>
       </c>
       <c r="B4">
-        <v>444.29290537032011</v>
+        <v>51.903895297499204</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>436.21187170013604</v>
+        <v>350.94063904382722</v>
       </c>
       <c r="B5">
-        <v>445.45281261764802</v>
+        <v>51.913401654302433</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>436.15765659599344</v>
+        <v>351.67120204619442</v>
       </c>
       <c r="B6">
-        <v>446.64044385771808</v>
+        <v>51.908127291279612</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>436.08929218785113</v>
+        <v>352.4113946059345</v>
       </c>
       <c r="B7">
-        <v>447.80749481224535</v>
+        <v>51.908734635803313</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>435.86695397719541</v>
+        <v>353.19374950081402</v>
       </c>
       <c r="B8">
-        <v>449.09012661219117</v>
+        <v>51.92303735319382</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>435.5125895283249</v>
+        <v>354.00777390184851</v>
       </c>
       <c r="B9">
-        <v>450.4867710438985</v>
+        <v>51.934302746939856</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>435.13450401365321</v>
+        <v>354.83159496963776</v>
       </c>
       <c r="B10">
-        <v>451.90204127614953</v>
+        <v>51.986026736494395</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>434.82948702568302</v>
+        <v>355.71302550143946</v>
       </c>
       <c r="B11">
-        <v>453.3460894008025</v>
+        <v>52.048425456301459</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>434.64863283754414</v>
+        <v>356.63186560067288</v>
       </c>
       <c r="B12">
-        <v>454.81102908601719</v>
+        <v>52.079880553034499</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>434.47736071560729</v>
+        <v>357.71289244853892</v>
       </c>
       <c r="B13">
-        <v>456.26124342668788</v>
+        <v>52.096372466983347</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>434.35021086242256</v>
+        <v>358.81277820609455</v>
       </c>
       <c r="B14">
-        <v>457.73163350817538</v>
+        <v>52.181924911723691</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>434.18788370556803</v>
+        <v>359.94868716005664</v>
       </c>
       <c r="B15">
-        <v>459.32631442712682</v>
+        <v>52.346189667421442</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>433.88033926830195</v>
+        <v>360.961148963315</v>
       </c>
       <c r="B16">
-        <v>460.87192260189283</v>
+        <v>52.567404268177881</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>433.74644418761352</v>
+        <v>361.94570332696793</v>
       </c>
       <c r="B17">
-        <v>462.27576457237228</v>
+        <v>52.80215657565288</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>433.6797655805205</v>
+        <v>362.94850971561499</v>
       </c>
       <c r="B18">
-        <v>463.63977698166678</v>
+        <v>52.987941630929967</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>433.72678169710332</v>
+        <v>363.89954791505113</v>
       </c>
       <c r="B19">
-        <v>464.95166971856906</v>
+        <v>53.308242225306564</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>433.83337003748835</v>
+        <v>364.88719629554976</v>
       </c>
       <c r="B20">
-        <v>466.18184165607022</v>
+        <v>53.770682860003092</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>433.95163679043895</v>
+        <v>365.83713724678285</v>
       </c>
       <c r="B21">
-        <v>467.4436780911953</v>
+        <v>54.205311423694731</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>433.95070906193695</v>
+        <v>366.90010792238769</v>
       </c>
       <c r="B22">
-        <v>468.65987217083006</v>
+        <v>54.494188379207159</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>433.94729405323829</v>
+        <v>368.11170989689663</v>
       </c>
       <c r="B23">
-        <v>469.89239990340286</v>
+        <v>54.738809780838331</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>434.02805525024559</v>
+        <v>369.41823781129517</v>
       </c>
       <c r="B24">
-        <v>471.09596939523749</v>
+        <v>54.888587387055544</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>434.19189069398641</v>
+        <v>370.74314747552603</v>
       </c>
       <c r="B25">
-        <v>472.28031450214411</v>
+        <v>54.955769660697349</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>434.32976843972</v>
+        <v>371.96789703466396</v>
       </c>
       <c r="B26">
-        <v>473.47255901527757</v>
+        <v>55.084445844107108</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>434.43905131804377</v>
+        <v>373.20055346169102</v>
       </c>
       <c r="B27">
-        <v>474.7643534746299</v>
+        <v>55.261329398560562</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>434.62358750687179</v>
+        <v>374.35151098181274</v>
       </c>
       <c r="B28">
-        <v>476.0991308869651</v>
+        <v>55.415898532251582</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>434.68374457486505</v>
+        <v>375.54685206035367</v>
       </c>
       <c r="B29">
-        <v>477.4701867973165</v>
+        <v>55.458193322474152</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>434.56659246731567</v>
+        <v>376.74899391961014</v>
       </c>
       <c r="B30">
-        <v>478.8622037345836</v>
+        <v>55.511528218141734</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>434.39157417256217</v>
+        <v>377.88945238606209</v>
       </c>
       <c r="B31">
-        <v>480.30637862170084</v>
+        <v>55.707181675663421</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>434.2222153207984</v>
+        <v>379.06751452090924</v>
       </c>
       <c r="B32">
-        <v>481.87009474096084</v>
+        <v>55.926926142231309</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>434.04271811658379</v>
+        <v>380.21603770804631</v>
       </c>
       <c r="B33">
-        <v>483.44026666174818</v>
+        <v>56.173702920074277</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>433.92081169883909</v>
+        <v>381.30590985673786</v>
       </c>
       <c r="B34">
-        <v>484.99319103075737</v>
+        <v>56.451992931644909</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>433.82213086908428</v>
+        <v>382.31454581779565</v>
       </c>
       <c r="B35">
-        <v>486.5528332691074</v>
+        <v>56.79558201774757</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>433.72172868512121</v>
+        <v>383.3999420925137</v>
       </c>
       <c r="B36">
-        <v>488.18991748889965</v>
+        <v>57.165783368182957</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>433.70222074417535</v>
+        <v>384.39446287310636</v>
       </c>
       <c r="B37">
-        <v>489.83321924237708</v>
+        <v>57.521976527023078</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>433.6624075684453</v>
+        <v>385.38943765036515</v>
       </c>
       <c r="B38">
-        <v>491.51486110431625</v>
+        <v>57.926784152712401</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>433.67080703957907</v>
+        <v>386.50363098070119</v>
       </c>
       <c r="B39">
-        <v>493.17606451774998</v>
+        <v>58.266440139777629</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>433.62589285182094</v>
+        <v>387.7837829140496</v>
       </c>
       <c r="B40">
-        <v>494.84562099275126</v>
+        <v>58.479234920857081</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>433.47324846161877</v>
+        <v>389.22723789807696</v>
       </c>
       <c r="B41">
-        <v>496.55973169290309</v>
+        <v>58.859357663047071</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>433.22073435009332</v>
+        <v>390.8111481220929</v>
       </c>
       <c r="B42">
-        <v>498.2927294427717</v>
+        <v>59.405531495733925</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>432.99320164532634</v>
+        <v>392.37827109543446</v>
       </c>
       <c r="B43">
-        <v>500</v>
+        <v>60.031361363223041</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>432.82489480421611</v>
+        <v>393.90149652132664</v>
       </c>
       <c r="B44">
-        <v>500</v>
+        <v>60.547907082343251</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>432.53887327355824</v>
+        <v>395.40707633304663</v>
       </c>
       <c r="B45">
-        <v>500</v>
+        <v>60.970800500265817</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>432.27168900302672</v>
+        <v>397.04213852382065</v>
       </c>
       <c r="B46">
-        <v>500</v>
+        <v>61.400339013115776</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>432.04510652069979</v>
+        <v>398.75666130013968</v>
       </c>
       <c r="B47">
-        <v>500</v>
+        <v>61.776146596802462</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>431.75808934549019</v>
+        <v>400.38749190250923</v>
       </c>
       <c r="B48">
-        <v>500</v>
+        <v>62.259765152821331</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>431.41619477134913</v>
+        <v>401.99500272704739</v>
       </c>
       <c r="B49">
-        <v>500</v>
+        <v>62.766441528765327</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>431.02954005657404</v>
+        <v>403.53755687300259</v>
       </c>
       <c r="B50">
-        <v>500</v>
+        <v>63.253630910501165</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>430.74481270480669</v>
+        <v>405.07646035897505</v>
       </c>
       <c r="B51">
-        <v>500</v>
+        <v>63.671232805085296</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>430.37017235589173</v>
+        <v>406.63593283343596</v>
       </c>
       <c r="B52">
-        <v>500</v>
+        <v>64.00480033311581</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>429.96449626459952</v>
+        <v>408.10417453814011</v>
       </c>
       <c r="B53">
-        <v>500</v>
+        <v>64.234394045504658</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>429.41552040643398</v>
+        <v>409.48577437057611</v>
       </c>
       <c r="B54">
-        <v>500</v>
+        <v>64.479281395187769</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>428.84165430066906</v>
+        <v>410.88544672394858</v>
       </c>
       <c r="B55">
-        <v>500</v>
+        <v>64.715070053697417</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>428.28142012676619</v>
+        <v>412.33978388419371</v>
       </c>
       <c r="B56">
-        <v>500</v>
+        <v>64.937441592865696</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>427.73489911648659</v>
+        <v>413.7910082467742</v>
       </c>
       <c r="B57">
-        <v>500</v>
+        <v>65.088760649634395</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>427.16771473512256</v>
+        <v>415.26372592255518</v>
       </c>
       <c r="B58">
-        <v>500</v>
+        <v>65.130114142442437</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>426.61183904797628</v>
+        <v>416.78816087953044</v>
       </c>
       <c r="B59">
-        <v>500</v>
+        <v>65.061018066610259</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>426.10196710324061</v>
+        <v>418.33595509166793</v>
       </c>
       <c r="B60">
-        <v>500</v>
+        <v>65.021691073251787</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>425.50404011246019</v>
+        <v>419.90664781663145</v>
       </c>
       <c r="B61">
-        <v>500</v>
+        <v>65.061473299122923</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>424.88868669150605</v>
+        <v>421.53715703089642</v>
       </c>
       <c r="B62">
-        <v>500</v>
+        <v>65.161491012845246</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>424.25483453303275</v>
+        <v>423.21212533022657</v>
       </c>
       <c r="B63">
-        <v>500</v>
+        <v>65.238812979260061</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>423.43859756108736</v>
+        <v>424.96520986475832</v>
       </c>
       <c r="B64">
-        <v>500</v>
+        <v>65.292341328307415</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>422.42010499557006</v>
+        <v>426.78918644466108</v>
       </c>
       <c r="B65">
-        <v>500</v>
+        <v>65.294839185497764</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>421.28604197594512</v>
+        <v>428.61315621399774</v>
       </c>
       <c r="B66">
-        <v>500</v>
+        <v>65.230706824395796</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>420.09248687361395</v>
+        <v>430.40642990107756</v>
       </c>
       <c r="B67">
-        <v>500</v>
+        <v>65.13015027570205</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>418.89583979224597</v>
+        <v>432.19823636270547</v>
       </c>
       <c r="B68">
-        <v>500</v>
+        <v>64.985443310448957</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>417.80760226828454</v>
+        <v>433.94393018542081</v>
       </c>
       <c r="B69">
-        <v>500</v>
+        <v>64.824028737221553</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>416.79773205669778</v>
+        <v>435.77465999340524</v>
       </c>
       <c r="B70">
-        <v>500</v>
+        <v>64.732057830575229</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>415.93223793176111</v>
+        <v>437.74907646574189</v>
       </c>
       <c r="B71">
-        <v>500</v>
+        <v>64.631377772660201</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>415.19737579413572</v>
+        <v>439.71390368900461</v>
       </c>
       <c r="B72">
-        <v>500</v>
+        <v>64.624978294330347</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>414.40151039664499</v>
+        <v>441.69431159486504</v>
       </c>
       <c r="B73">
-        <v>500</v>
+        <v>64.763837423442865</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>413.60021808309097</v>
+        <v>443.58758172694252</v>
       </c>
       <c r="B74">
-        <v>500</v>
+        <v>65.070813596302074</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>412.916359068529</v>
+        <v>445.53650322089544</v>
       </c>
       <c r="B75">
-        <v>500</v>
+        <v>65.38578261777333</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>412.26078940168327</v>
+        <v>447.56695545080265</v>
       </c>
       <c r="B76">
-        <v>500</v>
+        <v>65.606337434225836</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>411.63205812640098</v>
+        <v>449.6081102527894</v>
       </c>
       <c r="B77">
-        <v>500</v>
+        <v>65.975716470818611</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>410.99199401058161</v>
+        <v>451.63298752784112</v>
       </c>
       <c r="B78">
-        <v>500</v>
+        <v>66.285542185488794</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>410.46018722414425</v>
+        <v>453.62456768998697</v>
       </c>
       <c r="B79">
-        <v>500</v>
+        <v>66.553638345212846</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>409.835723871298</v>
+        <v>455.69636976023548</v>
       </c>
       <c r="B80">
-        <v>500</v>
+        <v>66.799754251968821</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>409.11568341278212</v>
+        <v>457.81209116059216</v>
       </c>
       <c r="B81">
-        <v>500</v>
+        <v>67.142013563820754</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>408.40422370108871</v>
+        <v>459.98805059129722</v>
       </c>
       <c r="B82">
-        <v>500</v>
+        <v>67.504513519657877</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>407.63954235851935</v>
+        <v>462.08895247356264</v>
       </c>
       <c r="B83">
-        <v>500</v>
+        <v>67.936848354673856</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>406.9131576751069</v>
+        <v>464.16005912392683</v>
       </c>
       <c r="B84">
-        <v>500</v>
+        <v>68.448454688182863</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>406.22449994170182</v>
+        <v>466.26825186302113</v>
       </c>
       <c r="B85">
-        <v>500</v>
+        <v>68.841429272718074</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>405.51284581207705</v>
+        <v>468.27028374183146</v>
       </c>
       <c r="B86">
-        <v>500</v>
+        <v>69.168692459992272</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>404.74258093038975</v>
+        <v>470.34713194287735</v>
       </c>
       <c r="B87">
-        <v>500</v>
+        <v>69.418660679565789</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>403.91748589986162</v>
+        <v>472.50648496862789</v>
       </c>
       <c r="B88">
-        <v>500</v>
+        <v>69.642961725148041</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>403.08681789705565</v>
+        <v>474.62276038280078</v>
       </c>
       <c r="B89">
-        <v>500</v>
+        <v>69.849052244133446</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>402.31464979888716</v>
+        <v>476.80818541605902</v>
       </c>
       <c r="B90">
-        <v>500</v>
+        <v>70.021780908958803</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>401.55021247286248</v>
+        <v>479.11558008297135</v>
       </c>
       <c r="B91">
-        <v>500</v>
+        <v>70.2935940612807</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>400.76551023454078</v>
+        <v>481.36287753442355</v>
       </c>
       <c r="B92">
-        <v>500</v>
+        <v>70.614423087409662</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>399.99101676461851</v>
+        <v>483.65420633938703</v>
       </c>
       <c r="B93">
-        <v>500</v>
+        <v>71.00566770715615</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>399.2380245655001</v>
+        <v>486.05191372844712</v>
       </c>
       <c r="B94">
-        <v>500</v>
+        <v>71.291122569183315</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>398.45877071543106</v>
+        <v>488.48133512702731</v>
       </c>
       <c r="B95">
-        <v>500</v>
+        <v>71.386739056183842</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>397.62315047877109</v>
+        <v>491.00370575591404</v>
       </c>
       <c r="B96">
-        <v>500</v>
+        <v>71.449303614368347</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>396.75794288506148</v>
+        <v>493.61249061990412</v>
       </c>
       <c r="B97">
-        <v>500</v>
+        <v>71.457298557417758</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>396.03344941954231</v>
+        <v>496.04785126549717</v>
       </c>
       <c r="B98">
-        <v>500</v>
+        <v>71.357675593215589</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>395.22955521632667</v>
+        <v>498.43945397843191</v>
       </c>
       <c r="B99">
-        <v>500</v>
+        <v>71.324270243853377</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>394.33421255274692</v>
+        <v>500</v>
       </c>
       <c r="B100">
-        <v>500</v>
+        <v>71.513025275375171</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>393.42773353206894</v>
+        <v>500</v>
       </c>
       <c r="B101">
-        <v>500</v>
+        <v>71.619016327279326</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>392.53198011984398</v>
+        <v>500</v>
       </c>
       <c r="B102">
-        <v>500</v>
+        <v>71.732596984043241</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>391.58893829905617</v>
+        <v>500</v>
       </c>
       <c r="B103">
-        <v>500</v>
+        <v>71.797043524544037</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>390.48460383544995</v>
+        <v>500</v>
       </c>
       <c r="B104">
-        <v>500</v>
+        <v>71.90834444895205</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>389.27129400579918</v>
+        <v>500</v>
       </c>
       <c r="B105">
-        <v>500</v>
+        <v>72.008341378712529</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>388.1113157530134</v>
+        <v>500</v>
       </c>
       <c r="B106">
-        <v>500</v>
+        <v>72.063605964848463</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>386.95735690364216</v>
+        <v>500</v>
       </c>
       <c r="B107">
-        <v>500</v>
+        <v>72.070644698177446</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>385.79909457856672</v>
+        <v>500</v>
       </c>
       <c r="B108">
-        <v>500</v>
+        <v>72.10683947523043</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>384.65573204267037</v>
+        <v>500</v>
       </c>
       <c r="B109">
-        <v>500</v>
+        <v>72.272602852707237</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>383.35997849199759</v>
+        <v>500</v>
       </c>
       <c r="B110">
-        <v>500</v>
+        <v>72.395331586389858</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>381.90683084519344</v>
+        <v>500</v>
       </c>
       <c r="B111">
-        <v>500</v>
+        <v>72.378936185469428</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>380.34302436334252</v>
+        <v>500</v>
       </c>
       <c r="B112">
-        <v>500</v>
+        <v>72.285255023431304</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>378.97137898850968</v>
+        <v>500</v>
       </c>
       <c r="B113">
-        <v>500</v>
+        <v>72.097256643836587</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>377.7720662259519</v>
+        <v>500</v>
       </c>
       <c r="B114">
-        <v>500</v>
+        <v>71.918211460948967</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>376.74911849014967</v>
+        <v>500</v>
       </c>
       <c r="B115">
-        <v>500</v>
+        <v>71.83773783351765</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>375.80460831566495</v>
+        <v>500</v>
       </c>
       <c r="B116">
-        <v>500</v>
+        <v>71.831208877266064</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>374.75198444451212</v>
+        <v>500</v>
       </c>
       <c r="B117">
-        <v>500</v>
+        <v>71.90990217023365</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>373.66911312135977</v>
+        <v>500</v>
       </c>
       <c r="B118">
-        <v>500</v>
+        <v>72.067099438297475</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>372.7459423967133</v>
+        <v>500</v>
       </c>
       <c r="B119">
-        <v>500</v>
+        <v>72.348453701875428</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>371.73544631291895</v>
+        <v>500</v>
       </c>
       <c r="B120">
-        <v>500</v>
+        <v>72.515811321186348</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>370.6511145502464</v>
+        <v>500</v>
       </c>
       <c r="B121">
-        <v>500</v>
+        <v>72.638342971088548</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>369.48214423216308</v>
+        <v>500</v>
       </c>
       <c r="B122">
-        <v>500</v>
+        <v>72.76989842917196</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>368.18984335665846</v>
+        <v>500</v>
       </c>
       <c r="B123">
-        <v>500</v>
+        <v>72.845376454300194</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>366.85830938979939</v>
+        <v>500</v>
       </c>
       <c r="B124">
-        <v>500</v>
+        <v>73.09205916664807</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>365.56416219939496</v>
+        <v>500</v>
       </c>
       <c r="B125">
-        <v>500</v>
+        <v>73.536343462270409</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>364.30189543736896</v>
+        <v>500</v>
       </c>
       <c r="B126">
-        <v>500</v>
+        <v>73.971439606392565</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>363.07428631522123</v>
+        <v>500</v>
       </c>
       <c r="B127">
-        <v>500</v>
+        <v>74.3676544817218</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>361.96644507612928</v>
+        <v>500</v>
       </c>
       <c r="B128">
-        <v>500</v>
+        <v>74.561881481076654</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>360.92041156875553</v>
+        <v>500</v>
       </c>
       <c r="B129">
-        <v>500</v>
+        <v>74.899310400132208</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>359.93475626468637</v>
+        <v>500</v>
       </c>
       <c r="B130">
-        <v>500</v>
+        <v>75.310138152503654</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>358.8902072722513</v>
+        <v>500</v>
       </c>
       <c r="B131">
-        <v>500</v>
+        <v>75.712591099112032</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>357.83948933741272</v>
+        <v>500</v>
       </c>
       <c r="B132">
-        <v>500</v>
+        <v>76.12422278172042</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>356.83069165850759</v>
+        <v>500</v>
       </c>
       <c r="B133">
-        <v>500</v>
+        <v>76.653382655130358</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>355.90304808414731</v>
+        <v>500</v>
       </c>
       <c r="B134">
-        <v>500</v>
+        <v>77.212736434012953</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>355.10460155231942</v>
+        <v>500</v>
       </c>
       <c r="B135">
-        <v>500</v>
+        <v>77.711320794930799</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>354.36491179911775</v>
+        <v>500</v>
       </c>
       <c r="B136">
-        <v>500</v>
+        <v>78.251123836145567</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>353.66111845821587</v>
+        <v>500</v>
       </c>
       <c r="B137">
-        <v>500</v>
+        <v>78.825729820005591</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>352.86747532251849</v>
+        <v>500</v>
       </c>
       <c r="B138">
-        <v>500</v>
+        <v>79.550892619744957</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>352.15278338674102</v>
+        <v>500</v>
       </c>
       <c r="B139">
-        <v>500</v>
+        <v>80.35763637246103</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>351.44377775816048</v>
+        <v>500</v>
       </c>
       <c r="B140">
-        <v>500</v>
+        <v>81.192207200500363</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>350.74589524406917</v>
+        <v>500</v>
       </c>
       <c r="B141">
-        <v>500</v>
+        <v>82.010917819033779</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>350.04620131053179</v>
+        <v>500</v>
       </c>
       <c r="B142">
-        <v>500</v>
+        <v>82.836666957292948</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>349.34263482445022</v>
+        <v>500</v>
       </c>
       <c r="B143">
-        <v>500</v>
+        <v>83.676571746067026</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>348.64577543370018</v>
+        <v>500</v>
       </c>
       <c r="B144">
-        <v>500</v>
+        <v>84.683641922280458</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>348.06461539161342</v>
+        <v>500</v>
       </c>
       <c r="B145">
-        <v>500</v>
+        <v>85.708690283336821</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>347.5191326436958</v>
+        <v>500</v>
       </c>
       <c r="B146">
-        <v>500</v>
+        <v>86.65307406662231</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>346.91957822006532</v>
+        <v>500</v>
       </c>
       <c r="B147">
-        <v>500</v>
+        <v>87.598888420849875</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>346.41052020032475</v>
+        <v>500</v>
       </c>
       <c r="B148">
-        <v>500</v>
+        <v>88.653477702607304</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>345.81572948612967</v>
+        <v>500</v>
       </c>
       <c r="B149">
-        <v>500</v>
+        <v>89.674076469184286</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>345.18078325185411</v>
+        <v>500</v>
       </c>
       <c r="B150">
-        <v>500</v>
+        <v>90.753054506190381</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>344.61201769475656</v>
+        <v>500</v>
       </c>
       <c r="B151">
-        <v>500</v>
+        <v>91.800420876248253</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>344.06724895860168</v>
+        <v>500</v>
       </c>
       <c r="B152">
-        <v>500</v>
+        <v>92.974228641293777</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>343.55030633849179</v>
+        <v>500</v>
       </c>
       <c r="B153">
-        <v>500</v>
+        <v>94.051538000085401</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>343.15904964491671</v>
+        <v>500</v>
       </c>
       <c r="B154">
-        <v>500</v>
+        <v>95.198146090384867</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>342.81830679399809</v>
+        <v>500</v>
       </c>
       <c r="B155">
-        <v>500</v>
+        <v>96.400436645559225</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>342.39329365305804</v>
+        <v>500</v>
       </c>
       <c r="B156">
-        <v>500</v>
+        <v>97.720025598604806</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>342.00117312648422</v>
+        <v>500</v>
       </c>
       <c r="B157">
-        <v>500</v>
+        <v>99.077464204659009</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>341.56413915441652</v>
+        <v>500</v>
       </c>
       <c r="B158">
-        <v>500</v>
+        <v>100.41652294020176</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>341.19552766089436</v>
+        <v>500</v>
       </c>
       <c r="B159">
-        <v>500</v>
+        <v>101.85000554502457</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>340.9215932246849</v>
+        <v>500</v>
       </c>
       <c r="B160">
-        <v>500</v>
+        <v>103.18619142738198</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>340.6192036677362</v>
+        <v>500</v>
       </c>
       <c r="B161">
-        <v>500</v>
+        <v>104.53482533083044</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>340.18977471401433</v>
+        <v>500</v>
       </c>
       <c r="B162">
-        <v>500</v>
+        <v>105.85748217210153</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>339.82602900723413</v>
+        <v>500</v>
       </c>
       <c r="B163">
-        <v>500</v>
+        <v>107.2287851266111</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>339.50114929941986</v>
+        <v>500</v>
       </c>
       <c r="B164">
-        <v>500</v>
+        <v>108.53404324489968</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>339.2808980881415</v>
+        <v>500</v>
       </c>
       <c r="B165">
-        <v>500</v>
+        <v>109.75513355579768</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>339.02478748390649</v>
+        <v>500</v>
       </c>
       <c r="B166">
-        <v>500</v>
+        <v>111.0867271075771</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>338.69865644346538</v>
+        <v>500</v>
       </c>
       <c r="B167">
-        <v>500</v>
+        <v>112.4329565593</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>338.41945639056524</v>
+        <v>500</v>
       </c>
       <c r="B168">
-        <v>500</v>
+        <v>113.89494201591278</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>338.08115044005189</v>
+        <v>500</v>
       </c>
       <c r="B169">
-        <v>500</v>
+        <v>115.46674616755035</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>337.75625102168965</v>
+        <v>500</v>
       </c>
       <c r="B170">
-        <v>500</v>
+        <v>117.23105395530368</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>337.4827646378925</v>
+        <v>500</v>
       </c>
       <c r="B171">
-        <v>500</v>
+        <v>119.12942338318976</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>337.30169474659687</v>
+        <v>500</v>
       </c>
       <c r="B172">
-        <v>500</v>
+        <v>121.09187819889229</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>337.11683549313869</v>
+        <v>500</v>
       </c>
       <c r="B173">
-        <v>500</v>
+        <v>122.98730291226747</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>336.95765327352291</v>
+        <v>500</v>
       </c>
       <c r="B174">
-        <v>500</v>
+        <v>124.83240877352029</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>336.86952103847693</v>
+        <v>500</v>
       </c>
       <c r="B175">
-        <v>500</v>
+        <v>126.68178936751424</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>336.86706752455291</v>
+        <v>500</v>
       </c>
       <c r="B176">
-        <v>500</v>
+        <v>128.40690425378872</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>336.82221743060751</v>
+        <v>500</v>
       </c>
       <c r="B177">
-        <v>500</v>
+        <v>130.06233433374095</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>336.84998996735891</v>
+        <v>500</v>
       </c>
       <c r="B178">
-        <v>500</v>
+        <v>131.7400701418577</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>336.83516783011163</v>
+        <v>500</v>
       </c>
       <c r="B179">
-        <v>500</v>
+        <v>133.6054167859555</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>336.79477763920244</v>
+        <v>500</v>
       </c>
       <c r="B180">
-        <v>500</v>
+        <v>135.5866488247992</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>336.71547692150688</v>
+        <v>500</v>
       </c>
       <c r="B181">
-        <v>500</v>
+        <v>137.73944415941116</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>336.71316846768877</v>
+        <v>500</v>
       </c>
       <c r="B182">
-        <v>500</v>
+        <v>139.88553420562474</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>336.7906436095102</v>
+        <v>500</v>
       </c>
       <c r="B183">
-        <v>500</v>
+        <v>142.01003074457137</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>336.7108453696116</v>
+        <v>500</v>
       </c>
       <c r="B184">
-        <v>500</v>
+        <v>144.15341483887849</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>336.52233756152583</v>
+        <v>500</v>
       </c>
       <c r="B185">
-        <v>500</v>
+        <v>146.2445185808636</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>336.34021032619381</v>
+        <v>500</v>
       </c>
       <c r="B186">
-        <v>500</v>
+        <v>148.27555852041544</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>336.14728772425769</v>
+        <v>500</v>
       </c>
       <c r="B187">
-        <v>500</v>
+        <v>150.29067524048344</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>335.79725961225751</v>
+        <v>500</v>
       </c>
       <c r="B188">
-        <v>500</v>
+        <v>152.40836276182563</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>335.43678563422037</v>
+        <v>500</v>
       </c>
       <c r="B189">
-        <v>500</v>
+        <v>154.52328018835587</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>334.95142977088659</v>
+        <v>500</v>
       </c>
       <c r="B190">
-        <v>500</v>
+        <v>156.7249618403512</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>334.38890239082872</v>
+        <v>500</v>
       </c>
       <c r="B191">
-        <v>500</v>
+        <v>158.89038982069945</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>333.78269075237068</v>
+        <v>500</v>
       </c>
       <c r="B192">
-        <v>500</v>
+        <v>161.14226800101679</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>333.35820492023413</v>
+        <v>500</v>
       </c>
       <c r="B193">
-        <v>500</v>
+        <v>163.38326601983391</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>332.99069980145845</v>
+        <v>500</v>
       </c>
       <c r="B194">
-        <v>500</v>
+        <v>165.48384095284891</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>332.58760445451827</v>
+        <v>500</v>
       </c>
       <c r="B195">
-        <v>500</v>
+        <v>167.68635577575506</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>332.20699236384252</v>
+        <v>500</v>
       </c>
       <c r="B196">
-        <v>500</v>
+        <v>170.1140011726778</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>331.86928325146374</v>
+        <v>500</v>
       </c>
       <c r="B197">
-        <v>500</v>
+        <v>172.5172533693036</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>331.52366199979105</v>
+        <v>500</v>
       </c>
       <c r="B198">
-        <v>500</v>
+        <v>174.86367039032078</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>331.23024750496415</v>
+        <v>500</v>
       </c>
       <c r="B199">
-        <v>500</v>
+        <v>177.22868574540868</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>330.97330049276445</v>
+        <v>500</v>
       </c>
       <c r="B200">
-        <v>500</v>
+        <v>179.61512736777166</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>330.67602214144119</v>
+        <v>500</v>
       </c>
       <c r="B201">
-        <v>500</v>
+        <v>182.08877181818869</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>330.41557884885071</v>
+        <v>500</v>
       </c>
       <c r="B202">
-        <v>500</v>
+        <v>184.61216660569031</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>330.17591822174103</v>
+        <v>500</v>
       </c>
       <c r="B203">
-        <v>500</v>
+        <v>187.13464006125403</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>329.93293221912427</v>
+        <v>500</v>
       </c>
       <c r="B204">
-        <v>500</v>
+        <v>189.60799770244662</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>329.53563842099811</v>
+        <v>500</v>
       </c>
       <c r="B205">
-        <v>500</v>
+        <v>192.13039649729942</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>329.06291225774629</v>
+        <v>500</v>
       </c>
       <c r="B206">
-        <v>500</v>
+        <v>194.69093977107011</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>328.55612281847704</v>
+        <v>500</v>
       </c>
       <c r="B207">
-        <v>500</v>
+        <v>197.18734126256098</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>328.07322424453412</v>
+        <v>500</v>
       </c>
       <c r="B208">
-        <v>500</v>
+        <v>199.60284034848229</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>327.61937084443775</v>
+        <v>500</v>
       </c>
       <c r="B209">
-        <v>500</v>
+        <v>201.92393143763664</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>327.27717572881426</v>
+        <v>500</v>
       </c>
       <c r="B210">
-        <v>500</v>
+        <v>204.24479934340548</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>326.94275757059376</v>
+        <v>500</v>
       </c>
       <c r="B211">
-        <v>500</v>
+        <v>206.55922452755939</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>326.63564581440261</v>
+        <v>500</v>
       </c>
       <c r="B212">
-        <v>500</v>
+        <v>208.9465336977126</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>326.30735082788539</v>
+        <v>500</v>
       </c>
       <c r="B213">
-        <v>500</v>
+        <v>211.31333594393078</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>325.87799149083185</v>
+        <v>500</v>
       </c>
       <c r="B214">
-        <v>500</v>
+        <v>213.76977226150535</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>325.47467941679798</v>
+        <v>500</v>
       </c>
       <c r="B215">
-        <v>500</v>
+        <v>216.19316296678173</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>325.03647696069174</v>
+        <v>500</v>
       </c>
       <c r="B216">
-        <v>500</v>
+        <v>218.33130787313888</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217">
-        <v>324.62255763181366</v>
+        <v>500</v>
       </c>
       <c r="B217">
-        <v>500</v>
+        <v>220.25850682418087</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218">
-        <v>324.19992848804839</v>
+        <v>500</v>
       </c>
       <c r="B218">
-        <v>500</v>
+        <v>222.20669904932279</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>324.03461697710168</v>
+        <v>500</v>
       </c>
       <c r="B219">
-        <v>500</v>
+        <v>224.06553619891437</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220">
-        <v>323.8240880701664</v>
+        <v>500</v>
       </c>
       <c r="B220">
-        <v>500</v>
+        <v>225.92744657874522</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221">
-        <v>323.58885578241558</v>
+        <v>500</v>
       </c>
       <c r="B221">
-        <v>500</v>
+        <v>227.81502727609799</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222">
-        <v>323.51282181511453</v>
+        <v>500</v>
       </c>
       <c r="B222">
-        <v>500</v>
+        <v>229.72435816562833</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223">
-        <v>323.36293911305404</v>
+        <v>500</v>
       </c>
       <c r="B223">
-        <v>500</v>
+        <v>231.62967227828261</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224">
-        <v>323.17672468881773</v>
+        <v>500</v>
       </c>
       <c r="B224">
-        <v>500</v>
+        <v>233.48960465813536</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225">
-        <v>323.04240597220354</v>
+        <v>500</v>
       </c>
       <c r="B225">
-        <v>500</v>
+        <v>235.46697744473457</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>322.91812626278073</v>
+        <v>500</v>
       </c>
       <c r="B226">
-        <v>500</v>
+        <v>237.53962583596095</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>322.83633837167486</v>
+        <v>500</v>
       </c>
       <c r="B227">
-        <v>500</v>
+        <v>239.63242060057104</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228">
-        <v>322.8080079519176</v>
+        <v>500</v>
       </c>
       <c r="B228">
-        <v>500</v>
+        <v>241.71436745447011</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229">
-        <v>322.71747743158824</v>
+        <v>500</v>
       </c>
       <c r="B229">
-        <v>500</v>
+        <v>243.87259839383088</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230">
-        <v>322.63428446013171</v>
+        <v>500</v>
       </c>
       <c r="B230">
-        <v>500</v>
+        <v>246.01139294833985</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231">
-        <v>322.53824561159797</v>
+        <v>500</v>
       </c>
       <c r="B231">
-        <v>500</v>
+        <v>248.04779978012434</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232">
-        <v>322.50634308761965</v>
+        <v>500</v>
       </c>
       <c r="B232">
-        <v>500</v>
+        <v>250.18047325780773</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233">
-        <v>322.3859237639561</v>
+        <v>500</v>
       </c>
       <c r="B233">
-        <v>500</v>
+        <v>252.29084269393468</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234">
-        <v>322.29938403566359</v>
+        <v>500</v>
       </c>
       <c r="B234">
-        <v>500</v>
+        <v>254.36325468447873</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235">
-        <v>322.15785603640677</v>
+        <v>500</v>
       </c>
       <c r="B235">
-        <v>500</v>
+        <v>256.43042560775069</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236">
-        <v>322.01000363596495</v>
+        <v>500</v>
       </c>
       <c r="B236">
-        <v>500</v>
+        <v>258.51025487077902</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237">
-        <v>321.83565844690258</v>
+        <v>500</v>
       </c>
       <c r="B237">
-        <v>500</v>
+        <v>260.63161964898745</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238">
-        <v>321.54522836159367</v>
+        <v>500</v>
       </c>
       <c r="B238">
-        <v>500</v>
+        <v>262.96578615174332</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239">
-        <v>321.3034192171969</v>
+        <v>500</v>
       </c>
       <c r="B239">
-        <v>500</v>
+        <v>265.30169890569698</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240">
-        <v>320.9487497185973</v>
+        <v>500</v>
       </c>
       <c r="B240">
-        <v>500</v>
+        <v>267.64708286788664</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241">
-        <v>320.65023474140378</v>
+        <v>500</v>
       </c>
       <c r="B241">
-        <v>500</v>
+        <v>270.03208823751885</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242">
-        <v>320.4677494764029</v>
+        <v>500</v>
       </c>
       <c r="B242">
-        <v>500</v>
+        <v>272.33930635042361</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243">
-        <v>320.21193434404074</v>
+        <v>500</v>
       </c>
       <c r="B243">
-        <v>500</v>
+        <v>274.83371118559296</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244">
-        <v>319.87344455178874</v>
+        <v>500</v>
       </c>
       <c r="B244">
-        <v>500</v>
+        <v>277.37669211815466</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245">
-        <v>319.47437338336943</v>
+        <v>500</v>
       </c>
       <c r="B245">
-        <v>500</v>
+        <v>279.86063796948332</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246">
-        <v>319.0738281403427</v>
+        <v>500</v>
       </c>
       <c r="B246">
-        <v>500</v>
+        <v>282.42425027496694</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247">
-        <v>318.7133667875442</v>
+        <v>500</v>
       </c>
       <c r="B247">
-        <v>500</v>
+        <v>284.96114766252487</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248">
-        <v>318.56648894596259</v>
+        <v>500</v>
       </c>
       <c r="B248">
-        <v>500</v>
+        <v>287.55264877626996</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249">
-        <v>318.45869461019663</v>
+        <v>500</v>
       </c>
       <c r="B249">
-        <v>500</v>
+        <v>290.27579812029745</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250">
-        <v>318.27647191175384</v>
+        <v>500</v>
       </c>
       <c r="B250">
-        <v>500</v>
+        <v>293.05828742262418</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251">
-        <v>318.10848220329376</v>
+        <v>500</v>
       </c>
       <c r="B251">
-        <v>500</v>
+        <v>295.9104443239716</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252">
-        <v>317.9588229014883</v>
+        <v>500</v>
       </c>
       <c r="B252">
-        <v>500</v>
+        <v>298.83463621566341</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253">
-        <v>317.83881110157569</v>
+        <v>500</v>
       </c>
       <c r="B253">
-        <v>500</v>
+        <v>301.79363340786364</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254">
-        <v>317.70030119114568</v>
+        <v>500</v>
       </c>
       <c r="B254">
-        <v>500</v>
+        <v>304.81056714533457</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255">
-        <v>317.36849919327034</v>
+        <v>500</v>
       </c>
       <c r="B255">
-        <v>500</v>
+        <v>307.99628138039884</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256">
-        <v>317.04007221454822</v>
+        <v>500</v>
       </c>
       <c r="B256">
-        <v>500</v>
+        <v>311.2641199174987</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257">
-        <v>316.65443391865534</v>
+        <v>500</v>
       </c>
       <c r="B257">
-        <v>500</v>
+        <v>314.44051771493469</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258">
-        <v>316.38007512712767</v>
+        <v>500</v>
       </c>
       <c r="B258">
-        <v>500</v>
+        <v>317.542500075389</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259">
-        <v>316.17513150627906</v>
+        <v>500</v>
       </c>
       <c r="B259">
-        <v>500</v>
+        <v>320.65360400808567</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260">
-        <v>316.01271275990007</v>
+        <v>500</v>
       </c>
       <c r="B260">
-        <v>500</v>
+        <v>323.77632816937103</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261">
-        <v>315.79210839133628</v>
+        <v>500</v>
       </c>
       <c r="B261">
-        <v>500</v>
+        <v>326.93910937392963</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262">
-        <v>315.56535985708024</v>
+        <v>500</v>
       </c>
       <c r="B262">
-        <v>500</v>
+        <v>330.14423285579096</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263">
-        <v>315.36057232810231</v>
+        <v>500</v>
       </c>
       <c r="B263">
-        <v>500</v>
+        <v>333.31357065469746</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264">
-        <v>315.27578494602972</v>
+        <v>500</v>
       </c>
       <c r="B264">
-        <v>500</v>
+        <v>336.47076109456589</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265">
-        <v>315.25583995240265</v>
+        <v>500</v>
       </c>
       <c r="B265">
-        <v>500</v>
+        <v>339.73143101318942</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266">
-        <v>315.21269152869331</v>
+        <v>500</v>
       </c>
       <c r="B266">
-        <v>500</v>
+        <v>342.98313162536942</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267">
-        <v>315.20369818288924</v>
+        <v>500</v>
       </c>
       <c r="B267">
-        <v>500</v>
+        <v>346.34001814872755</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268">
-        <v>315.08829535366425</v>
+        <v>500</v>
       </c>
       <c r="B268">
-        <v>500</v>
+        <v>349.79724749010643</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269">
-        <v>314.96820021459706</v>
+        <v>500</v>
       </c>
       <c r="B269">
-        <v>500</v>
+        <v>353.24041005112684</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270">
-        <v>314.82274273235925</v>
+        <v>500</v>
       </c>
       <c r="B270">
-        <v>500</v>
+        <v>356.64724863309345</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271">
-        <v>314.70190423272771</v>
+        <v>500</v>
       </c>
       <c r="B271">
-        <v>500</v>
+        <v>360.05137602466181</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272">
-        <v>314.626759880328</v>
+        <v>500</v>
       </c>
       <c r="B272">
-        <v>500</v>
+        <v>363.44549314752658</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273">
-        <v>314.56799164955072</v>
+        <v>500</v>
       </c>
       <c r="B273">
-        <v>500</v>
+        <v>366.9861147964383</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274">
-        <v>314.56532919385882</v>
+        <v>500</v>
       </c>
       <c r="B274">
-        <v>500</v>
+        <v>370.63187940143303</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275">
-        <v>314.64303367321571</v>
+        <v>500</v>
       </c>
       <c r="B275">
-        <v>500</v>
+        <v>374.23802161878473</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276">
-        <v>314.70671523680511</v>
+        <v>500</v>
       </c>
       <c r="B276">
-        <v>500</v>
+        <v>377.90388012724844</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277">
-        <v>314.74343796686725</v>
+        <v>500</v>
       </c>
       <c r="B277">
-        <v>500</v>
+        <v>381.66225345675048</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278">
-        <v>314.68457373623073</v>
+        <v>500</v>
       </c>
       <c r="B278">
-        <v>500</v>
+        <v>385.39228350662665</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279">
-        <v>314.57299199967025</v>
+        <v>500</v>
       </c>
       <c r="B279">
-        <v>500</v>
+        <v>389.25470088793401</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280">
-        <v>314.43050086661412</v>
+        <v>500</v>
       </c>
       <c r="B280">
-        <v>500</v>
+        <v>393.25509363541011</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281">
-        <v>314.27168666216113</v>
+        <v>500</v>
       </c>
       <c r="B281">
-        <v>500</v>
+        <v>397.22140912430893</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282">
-        <v>314.05805575951962</v>
+        <v>500</v>
       </c>
       <c r="B282">
-        <v>500</v>
+        <v>401.06875785644644</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283">
-        <v>313.87847113389967</v>
+        <v>500</v>
       </c>
       <c r="B283">
-        <v>500</v>
+        <v>404.94101125641618</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284">
-        <v>313.64886574498689</v>
+        <v>500</v>
       </c>
       <c r="B284">
-        <v>500</v>
+        <v>408.85829252028543</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285">
-        <v>313.29960730377832</v>
+        <v>500</v>
       </c>
       <c r="B285">
-        <v>500</v>
+        <v>412.82933956444094</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286">
-        <v>312.93918051630396</v>
+        <v>500</v>
       </c>
       <c r="B286">
-        <v>500</v>
+        <v>416.71893452712544</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287">
-        <v>312.67929392892682</v>
+        <v>500</v>
       </c>
       <c r="B287">
-        <v>500</v>
+        <v>420.65164575393538</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288">
-        <v>312.38856275163658</v>
+        <v>500</v>
       </c>
       <c r="B288">
-        <v>500</v>
+        <v>424.56095196248276</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289">
-        <v>312.18197327505595</v>
+        <v>500</v>
       </c>
       <c r="B289">
-        <v>500</v>
+        <v>428.47383684928769</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290">
-        <v>311.91923663146486</v>
+        <v>500</v>
       </c>
       <c r="B290">
-        <v>500</v>
+        <v>432.37266949483745</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291">
-        <v>311.67371136503044</v>
+        <v>500</v>
       </c>
       <c r="B291">
-        <v>500</v>
+        <v>436.35594152153368</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292">
-        <v>311.54263008713548</v>
+        <v>500</v>
       </c>
       <c r="B292">
-        <v>500</v>
+        <v>440.43396392862235</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293">
-        <v>311.49145455305359</v>
+        <v>500</v>
       </c>
       <c r="B293">
-        <v>500</v>
+        <v>444.52295410422204</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294">
-        <v>311.5787587018466</v>
+        <v>500</v>
       </c>
       <c r="B294">
-        <v>500</v>
+        <v>448.51544207287048</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295">
-        <v>311.72496817227602</v>
+        <v>500</v>
       </c>
       <c r="B295">
-        <v>500</v>
+        <v>452.67934431232402</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296">
-        <v>311.8040004284922</v>
+        <v>500</v>
       </c>
       <c r="B296">
-        <v>500</v>
+        <v>456.9885613775989</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297">
-        <v>311.8124236411648</v>
+        <v>500</v>
       </c>
       <c r="B297">
-        <v>500</v>
+        <v>461.40559569592693</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298">
-        <v>311.84790298650671</v>
+        <v>500</v>
       </c>
       <c r="B298">
-        <v>500</v>
+        <v>465.96218346521857</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299">
-        <v>311.7105574655854</v>
+        <v>500</v>
       </c>
       <c r="B299">
-        <v>500</v>
+        <v>470.60143997184332</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300">
-        <v>311.6727416375731</v>
+        <v>500</v>
       </c>
       <c r="B300">
-        <v>500</v>
+        <v>475.12167933477122</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301">
-        <v>311.77265901169221</v>
+        <v>500</v>
       </c>
       <c r="B301">
-        <v>500</v>
+        <v>479.54007227522675</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302">
-        <v>311.87395239234883</v>
+        <v>500</v>
       </c>
       <c r="B302">
-        <v>500</v>
+        <v>484.03665242493429</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303">
-        <v>311.82826892550037</v>
+        <v>500</v>
       </c>
       <c r="B303">
-        <v>500</v>
+        <v>488.55198212775684</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304">
-        <v>311.75765296983406</v>
+        <v>500</v>
       </c>
       <c r="B304">
-        <v>500</v>
+        <v>493.03885957136902</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305">
-        <v>311.75352832706955</v>
+        <v>500</v>
       </c>
       <c r="B305">
-        <v>500</v>
+        <v>497.53296059984996</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306">
-        <v>311.74990104368771</v>
+        <v>500</v>
       </c>
       <c r="B306">
         <v>500</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307">
-        <v>311.63609744506607</v>
+        <v>500</v>
       </c>
       <c r="B307">
         <v>500</v>
@@ -2801,7 +2801,7 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308">
-        <v>311.56418794845194</v>
+        <v>500</v>
       </c>
       <c r="B308">
         <v>500</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309">
-        <v>311.40694925379097</v>
+        <v>500</v>
       </c>
       <c r="B309">
         <v>500</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310">
-        <v>311.23196713330367</v>
+        <v>500</v>
       </c>
       <c r="B310">
         <v>500</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311">
-        <v>311.13090290095084</v>
+        <v>500</v>
       </c>
       <c r="B311">
         <v>500</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312">
-        <v>311.17065044794492</v>
+        <v>500</v>
       </c>
       <c r="B312">
         <v>500</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313">
-        <v>311.15149046781931</v>
+        <v>500</v>
       </c>
       <c r="B313">
         <v>500</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314">
-        <v>311.11307868318437</v>
+        <v>500</v>
       </c>
       <c r="B314">
         <v>500</v>
@@ -2857,7 +2857,7 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315">
-        <v>311.08581865850641</v>
+        <v>500</v>
       </c>
       <c r="B315">
         <v>500</v>
@@ -2865,7 +2865,7 @@
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316">
-        <v>311.03283478687291</v>
+        <v>500</v>
       </c>
       <c r="B316">
         <v>500</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317">
-        <v>311.02075374545427</v>
+        <v>500</v>
       </c>
       <c r="B317">
         <v>500</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318">
-        <v>310.96358597869374</v>
+        <v>500</v>
       </c>
       <c r="B318">
         <v>500</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319">
-        <v>310.94965389082398</v>
+        <v>500</v>
       </c>
       <c r="B319">
         <v>500</v>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320">
-        <v>311.01485363864583</v>
+        <v>500</v>
       </c>
       <c r="B320">
         <v>500</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321">
-        <v>311.22938757576719</v>
+        <v>500</v>
       </c>
       <c r="B321">
         <v>500</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322">
-        <v>311.62844365949042</v>
+        <v>500</v>
       </c>
       <c r="B322">
         <v>500</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323">
-        <v>312.01101908501795</v>
+        <v>500</v>
       </c>
       <c r="B323">
         <v>500</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324">
-        <v>312.2830095944546</v>
+        <v>500</v>
       </c>
       <c r="B324">
         <v>500</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325">
-        <v>312.38422908873167</v>
+        <v>500</v>
       </c>
       <c r="B325">
         <v>500</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326">
-        <v>312.41254719292783</v>
+        <v>500</v>
       </c>
       <c r="B326">
         <v>500</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327">
-        <v>312.4127892147946</v>
+        <v>500</v>
       </c>
       <c r="B327">
         <v>500</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328">
-        <v>312.37727344368551</v>
+        <v>500</v>
       </c>
       <c r="B328">
         <v>500</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329">
-        <v>312.13544633785517</v>
+        <v>500</v>
       </c>
       <c r="B329">
         <v>500</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330">
-        <v>312.04742111629503</v>
+        <v>500</v>
       </c>
       <c r="B330">
         <v>500</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331">
-        <v>312.01132243447302</v>
+        <v>500</v>
       </c>
       <c r="B331">
         <v>500</v>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332">
-        <v>311.94416107184361</v>
+        <v>500</v>
       </c>
       <c r="B332">
         <v>500</v>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333">
-        <v>311.86684345160489</v>
+        <v>500</v>
       </c>
       <c r="B333">
         <v>500</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334">
-        <v>311.89238368846048</v>
+        <v>500</v>
       </c>
       <c r="B334">
         <v>500</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335">
-        <v>311.9019502664309</v>
+        <v>500</v>
       </c>
       <c r="B335">
         <v>500</v>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336">
-        <v>311.94780171406472</v>
+        <v>500</v>
       </c>
       <c r="B336">
         <v>500</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337">
-        <v>311.8507630801941</v>
+        <v>500</v>
       </c>
       <c r="B337">
         <v>500</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338">
-        <v>311.6883744019143</v>
+        <v>500</v>
       </c>
       <c r="B338">
         <v>500</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339">
-        <v>311.55027142646048</v>
+        <v>500</v>
       </c>
       <c r="B339">
         <v>500</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340">
-        <v>311.4966161433735</v>
+        <v>500</v>
       </c>
       <c r="B340">
         <v>500</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341">
-        <v>311.40056221859544</v>
+        <v>500</v>
       </c>
       <c r="B341">
         <v>500</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342">
-        <v>311.25140802797125</v>
+        <v>500</v>
       </c>
       <c r="B342">
         <v>500</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343">
-        <v>311.13766755764215</v>
+        <v>500</v>
       </c>
       <c r="B343">
         <v>500</v>
@@ -3089,7 +3089,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344">
-        <v>311.12071991974005</v>
+        <v>500</v>
       </c>
       <c r="B344">
         <v>500</v>
@@ -3097,7 +3097,7 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345">
-        <v>311.19094009594454</v>
+        <v>500</v>
       </c>
       <c r="B345">
         <v>500</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346">
-        <v>311.33903117064091</v>
+        <v>500</v>
       </c>
       <c r="B346">
         <v>500</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347">
-        <v>311.51681817474923</v>
+        <v>500</v>
       </c>
       <c r="B347">
         <v>500</v>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348">
-        <v>311.61792494504112</v>
+        <v>500</v>
       </c>
       <c r="B348">
         <v>500</v>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349">
-        <v>311.73363030917068</v>
+        <v>500</v>
       </c>
       <c r="B349">
         <v>500</v>
@@ -3137,7 +3137,7 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350">
-        <v>311.81606057997664</v>
+        <v>500</v>
       </c>
       <c r="B350">
         <v>500</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351">
-        <v>311.89308114742397</v>
+        <v>500</v>
       </c>
       <c r="B351">
         <v>500</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352">
-        <v>311.85288972101142</v>
+        <v>500</v>
       </c>
       <c r="B352">
         <v>500</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353">
-        <v>311.70387675972825</v>
+        <v>500</v>
       </c>
       <c r="B353">
         <v>500</v>
@@ -3169,7 +3169,7 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354">
-        <v>311.42352314160433</v>
+        <v>500</v>
       </c>
       <c r="B354">
         <v>500</v>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355">
-        <v>311.19561631073464</v>
+        <v>500</v>
       </c>
       <c r="B355">
         <v>500</v>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356">
-        <v>310.97793990636939</v>
+        <v>500</v>
       </c>
       <c r="B356">
         <v>500</v>
@@ -3193,7 +3193,7 @@
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357">
-        <v>310.72678862123803</v>
+        <v>500</v>
       </c>
       <c r="B357">
         <v>500</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358">
-        <v>310.48588194370194</v>
+        <v>500</v>
       </c>
       <c r="B358">
         <v>500</v>
@@ -3209,7 +3209,7 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359">
-        <v>310.18729643867033</v>
+        <v>500</v>
       </c>
       <c r="B359">
         <v>500</v>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360">
-        <v>309.79187856992911</v>
+        <v>500</v>
       </c>
       <c r="B360">
         <v>500</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361">
-        <v>309.33913675408621</v>
+        <v>500</v>
       </c>
       <c r="B361">
         <v>500</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362">
-        <v>308.98745172957234</v>
+        <v>500</v>
       </c>
       <c r="B362">
         <v>500</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363">
-        <v>308.64426354789697</v>
+        <v>500</v>
       </c>
       <c r="B363">
         <v>500</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364">
-        <v>308.35989569931871</v>
+        <v>500</v>
       </c>
       <c r="B364">
         <v>500</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365">
-        <v>308.04819436393444</v>
+        <v>500</v>
       </c>
       <c r="B365">
         <v>500</v>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366">
-        <v>307.80778684568588</v>
+        <v>500</v>
       </c>
       <c r="B366">
         <v>500</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367">
-        <v>307.62657173176791</v>
+        <v>500</v>
       </c>
       <c r="B367">
         <v>500</v>
@@ -3281,7 +3281,7 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368">
-        <v>307.39996950766857</v>
+        <v>500</v>
       </c>
       <c r="B368">
         <v>500</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369">
-        <v>306.97337157664691</v>
+        <v>500</v>
       </c>
       <c r="B369">
         <v>500</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370">
-        <v>306.54301732989217</v>
+        <v>500</v>
       </c>
       <c r="B370">
         <v>500</v>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371">
-        <v>306.0375886404226</v>
+        <v>500</v>
       </c>
       <c r="B371">
         <v>500</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372">
-        <v>305.50319152451783</v>
+        <v>500</v>
       </c>
       <c r="B372">
         <v>500</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373">
-        <v>305.03438310959041</v>
+        <v>500</v>
       </c>
       <c r="B373">
         <v>500</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374">
-        <v>304.56807678739858</v>
+        <v>500</v>
       </c>
       <c r="B374">
         <v>500</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375">
-        <v>304.06458262423001</v>
+        <v>500</v>
       </c>
       <c r="B375">
         <v>500</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376">
-        <v>303.52851932927797</v>
+        <v>500</v>
       </c>
       <c r="B376">
         <v>500</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377">
-        <v>302.99633514952279</v>
+        <v>500</v>
       </c>
       <c r="B377">
         <v>500</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378">
-        <v>302.59589918937462</v>
+        <v>500</v>
       </c>
       <c r="B378">
         <v>500</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379">
-        <v>302.27288067964446</v>
+        <v>500</v>
       </c>
       <c r="B379">
         <v>500</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380">
-        <v>301.9389659757133</v>
+        <v>500</v>
       </c>
       <c r="B380">
         <v>500</v>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381">
-        <v>301.59958087286282</v>
+        <v>500</v>
       </c>
       <c r="B381">
         <v>500</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382">
-        <v>301.33821390387055</v>
+        <v>500</v>
       </c>
       <c r="B382">
         <v>500</v>
@@ -3401,7 +3401,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383">
-        <v>301.06352865655504</v>
+        <v>500</v>
       </c>
       <c r="B383">
         <v>500</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384">
-        <v>300.82084905465177</v>
+        <v>500</v>
       </c>
       <c r="B384">
         <v>500</v>
@@ -3417,7 +3417,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385">
-        <v>300.63573206260673</v>
+        <v>500</v>
       </c>
       <c r="B385">
         <v>500</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386">
-        <v>300.45590553116267</v>
+        <v>500</v>
       </c>
       <c r="B386">
         <v>500</v>
@@ -3433,7 +3433,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387">
-        <v>300.3283860295482</v>
+        <v>500</v>
       </c>
       <c r="B387">
         <v>500</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388">
-        <v>300.31976384110857</v>
+        <v>500</v>
       </c>
       <c r="B388">
         <v>500</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389">
-        <v>300.43894877918433</v>
+        <v>500</v>
       </c>
       <c r="B389">
         <v>500</v>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390">
-        <v>300.4258714291243</v>
+        <v>500</v>
       </c>
       <c r="B390">
         <v>500</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391">
-        <v>300.37541112604578</v>
+        <v>500</v>
       </c>
       <c r="B391">
         <v>500</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392">
-        <v>300.33302517917383</v>
+        <v>500</v>
       </c>
       <c r="B392">
         <v>500</v>
@@ -3481,7 +3481,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393">
-        <v>300.42570952147662</v>
+        <v>500</v>
       </c>
       <c r="B393">
         <v>500</v>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394">
-        <v>300.57299985162757</v>
+        <v>500</v>
       </c>
       <c r="B394">
         <v>500</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395">
-        <v>300.64856002187014</v>
+        <v>500</v>
       </c>
       <c r="B395">
         <v>500</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396">
-        <v>300.71196245433578</v>
+        <v>500</v>
       </c>
       <c r="B396">
         <v>500</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397">
-        <v>300.81062987615309</v>
+        <v>500</v>
       </c>
       <c r="B397">
         <v>500</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398">
-        <v>300.68843876172224</v>
+        <v>500</v>
       </c>
       <c r="B398">
         <v>500</v>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399">
-        <v>300.4405697342695</v>
+        <v>500</v>
       </c>
       <c r="B399">
         <v>500</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400">
-        <v>300.20704994475904</v>
+        <v>500</v>
       </c>
       <c r="B400">
         <v>500</v>
@@ -3545,7 +3545,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401">
-        <v>300.01961568516253</v>
+        <v>500</v>
       </c>
       <c r="B401">
         <v>500</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402">
-        <v>299.79834312275642</v>
+        <v>500</v>
       </c>
       <c r="B402">
         <v>500</v>
@@ -3561,7 +3561,7 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403">
-        <v>299.66947112772374</v>
+        <v>500</v>
       </c>
       <c r="B403">
         <v>500</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404">
-        <v>299.53387242415641</v>
+        <v>500</v>
       </c>
       <c r="B404">
         <v>500</v>
@@ -3577,7 +3577,7 @@
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405">
-        <v>299.32277927427833</v>
+        <v>500</v>
       </c>
       <c r="B405">
         <v>500</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406">
-        <v>299.10473058718634</v>
+        <v>500</v>
       </c>
       <c r="B406">
         <v>500</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407">
-        <v>298.88224355596338</v>
+        <v>500</v>
       </c>
       <c r="B407">
         <v>500</v>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408">
-        <v>298.69624236839661</v>
+        <v>500</v>
       </c>
       <c r="B408">
         <v>500</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409">
-        <v>298.41590724272106</v>
+        <v>500</v>
       </c>
       <c r="B409">
         <v>500</v>
@@ -3617,7 +3617,7 @@
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410">
-        <v>298.03501353868592</v>
+        <v>500</v>
       </c>
       <c r="B410">
         <v>500</v>
@@ -3625,7 +3625,7 @@
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411">
-        <v>297.79481196528769</v>
+        <v>500</v>
       </c>
       <c r="B411">
         <v>500</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412">
-        <v>297.57590758713815</v>
+        <v>500</v>
       </c>
       <c r="B412">
         <v>500</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413">
-        <v>297.41538941477438</v>
+        <v>500</v>
       </c>
       <c r="B413">
         <v>500</v>
@@ -3649,7 +3649,7 @@
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414">
-        <v>297.30074459131527</v>
+        <v>500</v>
       </c>
       <c r="B414">
         <v>500</v>
@@ -3657,7 +3657,7 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415">
-        <v>297.0996066513494</v>
+        <v>500</v>
       </c>
       <c r="B415">
         <v>500</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416">
-        <v>296.93672226788237</v>
+        <v>500</v>
       </c>
       <c r="B416">
         <v>500</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417">
-        <v>296.74386773337693</v>
+        <v>500</v>
       </c>
       <c r="B417">
         <v>500</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418">
-        <v>296.50109621216546</v>
+        <v>500</v>
       </c>
       <c r="B418">
         <v>500</v>
@@ -3689,7 +3689,7 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419">
-        <v>296.10791494237412</v>
+        <v>500</v>
       </c>
       <c r="B419">
         <v>500</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420">
-        <v>295.73629118877847</v>
+        <v>500</v>
       </c>
       <c r="B420">
         <v>500</v>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421">
-        <v>295.49866658691195</v>
+        <v>500</v>
       </c>
       <c r="B421">
         <v>500</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422">
-        <v>295.37451775072958</v>
+        <v>500</v>
       </c>
       <c r="B422">
         <v>500</v>
@@ -3721,7 +3721,7 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423">
-        <v>295.34219759513871</v>
+        <v>500</v>
       </c>
       <c r="B423">
         <v>500</v>
@@ -3729,7 +3729,7 @@
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424">
-        <v>295.26384762516841</v>
+        <v>500</v>
       </c>
       <c r="B424">
         <v>500</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425">
-        <v>295.20322911060509</v>
+        <v>500</v>
       </c>
       <c r="B425">
         <v>500</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426">
-        <v>295.12098084709015</v>
+        <v>500</v>
       </c>
       <c r="B426">
         <v>500</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427">
-        <v>295.18638847758012</v>
+        <v>500</v>
       </c>
       <c r="B427">
         <v>500</v>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428">
-        <v>295.32190331388261</v>
+        <v>500</v>
       </c>
       <c r="B428">
         <v>500</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429">
-        <v>295.48274322259266</v>
+        <v>500</v>
       </c>
       <c r="B429">
         <v>500</v>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430">
-        <v>295.664061982362</v>
+        <v>500</v>
       </c>
       <c r="B430">
         <v>500</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431">
-        <v>295.86242613662995</v>
+        <v>500</v>
       </c>
       <c r="B431">
         <v>500</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432">
-        <v>296.23195514330121</v>
+        <v>500</v>
       </c>
       <c r="B432">
         <v>500</v>
@@ -3801,7 +3801,7 @@
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433">
-        <v>296.61350382899883</v>
+        <v>500</v>
       </c>
       <c r="B433">
         <v>500</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434">
-        <v>296.92317404704909</v>
+        <v>500</v>
       </c>
       <c r="B434">
         <v>500</v>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435">
-        <v>297.23831150190802</v>
+        <v>500</v>
       </c>
       <c r="B435">
         <v>500</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436">
-        <v>297.73338308634271</v>
+        <v>500</v>
       </c>
       <c r="B436">
         <v>500</v>
@@ -3833,7 +3833,7 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437">
-        <v>298.31682376763308</v>
+        <v>500</v>
       </c>
       <c r="B437">
         <v>500</v>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438">
-        <v>298.89837042066063</v>
+        <v>500</v>
       </c>
       <c r="B438">
         <v>500</v>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439">
-        <v>299.46101107152083</v>
+        <v>500</v>
       </c>
       <c r="B439">
         <v>500</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440">
-        <v>299.92290269214709</v>
+        <v>500</v>
       </c>
       <c r="B440">
         <v>500</v>
@@ -3865,7 +3865,7 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441">
-        <v>300.56970895251936</v>
+        <v>500</v>
       </c>
       <c r="B441">
         <v>500</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442">
-        <v>301.26219211494447</v>
+        <v>500</v>
       </c>
       <c r="B442">
         <v>500</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443">
-        <v>301.9062003126387</v>
+        <v>500</v>
       </c>
       <c r="B443">
         <v>500</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444">
-        <v>302.48067707538269</v>
+        <v>500</v>
       </c>
       <c r="B444">
         <v>500</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445">
-        <v>303.03831574909321</v>
+        <v>500</v>
       </c>
       <c r="B445">
         <v>500</v>
@@ -3905,7 +3905,7 @@
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446">
-        <v>303.5143944503676</v>
+        <v>500</v>
       </c>
       <c r="B446">
         <v>500</v>
@@ -3913,7 +3913,7 @@
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447">
-        <v>304.09876155340487</v>
+        <v>500</v>
       </c>
       <c r="B447">
         <v>500</v>
@@ -3921,7 +3921,7 @@
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448">
-        <v>304.72193693846481</v>
+        <v>500</v>
       </c>
       <c r="B448">
         <v>500</v>
@@ -3929,7 +3929,7 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449">
-        <v>305.3497999571797</v>
+        <v>500</v>
       </c>
       <c r="B449">
         <v>500</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450">
-        <v>305.99965413465526</v>
+        <v>500</v>
       </c>
       <c r="B450">
         <v>500</v>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451">
-        <v>306.74305650001799</v>
+        <v>500</v>
       </c>
       <c r="B451">
         <v>500</v>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452">
-        <v>307.56056602718576</v>
+        <v>500</v>
       </c>
       <c r="B452">
         <v>500</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453">
-        <v>308.37779907088031</v>
+        <v>500</v>
       </c>
       <c r="B453">
         <v>500</v>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454">
-        <v>309.08445999861675</v>
+        <v>500</v>
       </c>
       <c r="B454">
         <v>500</v>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455">
-        <v>309.7066365282007</v>
+        <v>500</v>
       </c>
       <c r="B455">
         <v>500</v>
@@ -3985,7 +3985,7 @@
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456">
-        <v>310.30577563255173</v>
+        <v>500</v>
       </c>
       <c r="B456">
         <v>500</v>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457">
-        <v>310.89150277752265</v>
+        <v>500</v>
       </c>
       <c r="B457">
         <v>500</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458">
-        <v>311.45744250429243</v>
+        <v>500</v>
       </c>
       <c r="B458">
         <v>500</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459">
-        <v>312.01168767659857</v>
+        <v>500</v>
       </c>
       <c r="B459">
         <v>500</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460">
-        <v>312.58585439014695</v>
+        <v>500</v>
       </c>
       <c r="B460">
         <v>500</v>
@@ -4025,7 +4025,7 @@
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461">
-        <v>313.24113529842111</v>
+        <v>500</v>
       </c>
       <c r="B461">
         <v>500</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462">
-        <v>313.86258270168827</v>
+        <v>500</v>
       </c>
       <c r="B462">
         <v>500</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463">
-        <v>314.48599175014027</v>
+        <v>500</v>
       </c>
       <c r="B463">
         <v>500</v>
@@ -4049,7 +4049,7 @@
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464">
-        <v>315.03390113775504</v>
+        <v>500</v>
       </c>
       <c r="B464">
         <v>500</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465">
-        <v>315.56925911200176</v>
+        <v>500</v>
       </c>
       <c r="B465">
         <v>500</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466">
-        <v>316.07176049404296</v>
+        <v>500</v>
       </c>
       <c r="B466">
         <v>500</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467">
-        <v>316.49794768885431</v>
+        <v>500</v>
       </c>
       <c r="B467">
         <v>500</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468">
-        <v>316.90085671291769</v>
+        <v>500</v>
       </c>
       <c r="B468">
         <v>500</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469">
-        <v>317.29693080053391</v>
+        <v>500</v>
       </c>
       <c r="B469">
         <v>500</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470">
-        <v>317.7694155565477</v>
+        <v>500</v>
       </c>
       <c r="B470">
         <v>500</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471">
-        <v>318.18198971502909</v>
+        <v>500</v>
       </c>
       <c r="B471">
         <v>500</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472">
-        <v>318.51768034953085</v>
+        <v>500</v>
       </c>
       <c r="B472">
         <v>500</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473">
-        <v>318.76789107147783</v>
+        <v>500</v>
       </c>
       <c r="B473">
         <v>500</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474">
-        <v>318.99787970334773</v>
+        <v>500</v>
       </c>
       <c r="B474">
         <v>500</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475">
-        <v>319.33829433073993</v>
+        <v>500</v>
       </c>
       <c r="B475">
         <v>500</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476">
-        <v>319.83090483064314</v>
+        <v>500</v>
       </c>
       <c r="B476">
         <v>500</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477">
-        <v>320.43288723634896</v>
+        <v>500</v>
       </c>
       <c r="B477">
         <v>500</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478">
-        <v>321.13999857398551</v>
+        <v>500</v>
       </c>
       <c r="B478">
         <v>500</v>
@@ -4169,7 +4169,7 @@
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479">
-        <v>321.90415022163171</v>
+        <v>500</v>
       </c>
       <c r="B479">
         <v>500</v>
@@ -4177,7 +4177,7 @@
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480">
-        <v>322.73517133108885</v>
+        <v>500</v>
       </c>
       <c r="B480">
         <v>500</v>
@@ -4185,7 +4185,7 @@
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481">
-        <v>323.49809064838144</v>
+        <v>500</v>
       </c>
       <c r="B481">
         <v>500</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482">
-        <v>324.36693807984</v>
+        <v>500</v>
       </c>
       <c r="B482">
         <v>500</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483">
-        <v>325.26247226792646</v>
+        <v>500</v>
       </c>
       <c r="B483">
         <v>500</v>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484">
-        <v>326.11304542712162</v>
+        <v>500</v>
       </c>
       <c r="B484">
         <v>500</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485">
-        <v>326.90497026245549</v>
+        <v>500</v>
       </c>
       <c r="B485">
         <v>500</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486">
-        <v>327.72457940313183</v>
+        <v>500</v>
       </c>
       <c r="B486">
         <v>500</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487">
-        <v>328.69244947643114</v>
+        <v>500</v>
       </c>
       <c r="B487">
         <v>500</v>
@@ -4241,7 +4241,7 @@
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488">
-        <v>329.63685854764151</v>
+        <v>500</v>
       </c>
       <c r="B488">
         <v>500</v>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489">
-        <v>330.6765554909498</v>
+        <v>500</v>
       </c>
       <c r="B489">
         <v>500</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490">
-        <v>331.59030844424706</v>
+        <v>500</v>
       </c>
       <c r="B490">
         <v>500</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491">
-        <v>332.368093685313</v>
+        <v>500</v>
       </c>
       <c r="B491">
         <v>500</v>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492">
-        <v>333.22441567145592</v>
+        <v>500</v>
       </c>
       <c r="B492">
         <v>500</v>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493">
-        <v>333.98162903150836</v>
+        <v>500</v>
       </c>
       <c r="B493">
         <v>500</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494">
-        <v>334.77841273302056</v>
+        <v>500</v>
       </c>
       <c r="B494">
         <v>500</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495">
-        <v>335.52295404934995</v>
+        <v>500</v>
       </c>
       <c r="B495">
         <v>500</v>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496">
-        <v>336.0761497188505</v>
+        <v>500</v>
       </c>
       <c r="B496">
         <v>500</v>
@@ -4313,7 +4313,7 @@
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497">
-        <v>336.44841417328286</v>
+        <v>500</v>
       </c>
       <c r="B497">
         <v>500</v>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498">
-        <v>336.89190864598481</v>
+        <v>500</v>
       </c>
       <c r="B498">
         <v>500</v>
@@ -4329,7 +4329,7 @@
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499">
-        <v>337.30562625140936</v>
+        <v>500</v>
       </c>
       <c r="B499">
         <v>500</v>
@@ -4337,7 +4337,7 @@
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500">
-        <v>337.82107255062459</v>
+        <v>500</v>
       </c>
       <c r="B500">
         <v>500</v>
@@ -4345,7 +4345,7 @@
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501">
-        <v>338.3562109541582</v>
+        <v>500</v>
       </c>
       <c r="B501">
         <v>500</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502">
-        <v>338.96571976552838</v>
+        <v>500</v>
       </c>
       <c r="B502">
         <v>500</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503">
-        <v>339.64951070993339</v>
+        <v>500</v>
       </c>
       <c r="B503">
         <v>500</v>
@@ -4369,7 +4369,7 @@
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504">
-        <v>340.22636762755229</v>
+        <v>500</v>
       </c>
       <c r="B504">
         <v>500</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505">
-        <v>340.82113654375536</v>
+        <v>500</v>
       </c>
       <c r="B505">
         <v>500</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506">
-        <v>341.41814628652497</v>
+        <v>500</v>
       </c>
       <c r="B506">
         <v>500</v>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507">
-        <v>342.02932971234623</v>
+        <v>500</v>
       </c>
       <c r="B507">
         <v>500</v>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508">
-        <v>342.65022771787716</v>
+        <v>500</v>
       </c>
       <c r="B508">
         <v>500</v>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509">
-        <v>343.28046471017598</v>
+        <v>500</v>
       </c>
       <c r="B509">
         <v>500</v>
@@ -4417,7 +4417,7 @@
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510">
-        <v>343.97697923043478</v>
+        <v>500</v>
       </c>
       <c r="B510">
         <v>500</v>
@@ -4425,7 +4425,7 @@
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511">
-        <v>344.7431025984219</v>
+        <v>500</v>
       </c>
       <c r="B511">
         <v>500</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512">
-        <v>345.58550869667209</v>
+        <v>500</v>
       </c>
       <c r="B512">
         <v>500</v>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513">
-        <v>346.46480145859863</v>
+        <v>500</v>
       </c>
       <c r="B513">
         <v>500</v>
@@ -4449,7 +4449,7 @@
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514">
-        <v>347.40132544198457</v>
+        <v>500</v>
       </c>
       <c r="B514">
         <v>500</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515">
-        <v>348.37650023388989</v>
+        <v>500</v>
       </c>
       <c r="B515">
         <v>500</v>
@@ -4465,7 +4465,7 @@
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516">
-        <v>349.41384288156615</v>
+        <v>500</v>
       </c>
       <c r="B516">
         <v>500</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517">
-        <v>350.48046509527171</v>
+        <v>500</v>
       </c>
       <c r="B517">
         <v>500</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518">
-        <v>351.58156641563284</v>
+        <v>500</v>
       </c>
       <c r="B518">
         <v>500</v>
@@ -4489,7 +4489,7 @@
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519">
-        <v>352.6990551606217</v>
+        <v>500</v>
       </c>
       <c r="B519">
         <v>500</v>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520">
-        <v>353.76067289596602</v>
+        <v>500</v>
       </c>
       <c r="B520">
         <v>500</v>
@@ -4505,7 +4505,7 @@
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521">
-        <v>354.70679581215109</v>
+        <v>500</v>
       </c>
       <c r="B521">
         <v>500</v>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522">
-        <v>355.67774025930038</v>
+        <v>500</v>
       </c>
       <c r="B522">
         <v>500</v>
@@ -4521,7 +4521,7 @@
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523">
-        <v>356.62011754595414</v>
+        <v>500</v>
       </c>
       <c r="B523">
         <v>500</v>
@@ -4529,7 +4529,7 @@
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524">
-        <v>357.47937996309275</v>
+        <v>500</v>
       </c>
       <c r="B524">
         <v>500</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525">
-        <v>358.34268778738482</v>
+        <v>500</v>
       </c>
       <c r="B525">
         <v>500</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526">
-        <v>359.25156068966544</v>
+        <v>500</v>
       </c>
       <c r="B526">
         <v>500</v>
@@ -4553,7 +4553,7 @@
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527">
-        <v>360.14953438927603</v>
+        <v>500</v>
       </c>
       <c r="B527">
         <v>500</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528">
-        <v>361.06712964666212</v>
+        <v>500</v>
       </c>
       <c r="B528">
         <v>500</v>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529">
-        <v>361.82909901754056</v>
+        <v>500</v>
       </c>
       <c r="B529">
         <v>500</v>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530">
-        <v>362.64716760968776</v>
+        <v>500</v>
       </c>
       <c r="B530">
         <v>500</v>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531">
-        <v>363.57607702803421</v>
+        <v>500</v>
       </c>
       <c r="B531">
         <v>500</v>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532">
-        <v>364.53011862233723</v>
+        <v>500</v>
       </c>
       <c r="B532">
         <v>500</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533">
-        <v>365.443016312054</v>
+        <v>500</v>
       </c>
       <c r="B533">
         <v>500</v>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534">
-        <v>366.28298928129254</v>
+        <v>500</v>
       </c>
       <c r="B534">
         <v>500</v>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535">
-        <v>367.12481710152315</v>
+        <v>500</v>
       </c>
       <c r="B535">
         <v>500</v>
@@ -4625,7 +4625,7 @@
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536">
-        <v>367.99043488004537</v>
+        <v>500</v>
       </c>
       <c r="B536">
         <v>500</v>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537">
-        <v>368.77397840352182</v>
+        <v>500</v>
       </c>
       <c r="B537">
         <v>500</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538">
-        <v>369.57163832192077</v>
+        <v>500</v>
       </c>
       <c r="B538">
         <v>500</v>
@@ -4649,7 +4649,7 @@
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539">
-        <v>370.38346019279567</v>
+        <v>500</v>
       </c>
       <c r="B539">
         <v>500</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540">
-        <v>371.12425028739926</v>
+        <v>500</v>
       </c>
       <c r="B540">
         <v>500</v>
@@ -4665,7 +4665,7 @@
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541">
-        <v>372.00219404309911</v>
+        <v>500</v>
       </c>
       <c r="B541">
         <v>500</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542">
-        <v>372.81254175450925</v>
+        <v>500</v>
       </c>
       <c r="B542">
         <v>500</v>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543">
-        <v>373.57610854743683</v>
+        <v>500</v>
       </c>
       <c r="B543">
         <v>500</v>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544">
-        <v>374.3251413084289</v>
+        <v>500</v>
       </c>
       <c r="B544">
         <v>500</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545">
-        <v>375.11198451479794</v>
+        <v>500</v>
       </c>
       <c r="B545">
         <v>500</v>
@@ -4705,7 +4705,7 @@
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546">
-        <v>375.84573922237212</v>
+        <v>500</v>
       </c>
       <c r="B546">
         <v>500</v>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A547">
-        <v>376.61301671793842</v>
+        <v>500</v>
       </c>
       <c r="B547">
         <v>500</v>
@@ -4721,7 +4721,7 @@
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548">
-        <v>377.4368748026983</v>
+        <v>500</v>
       </c>
       <c r="B548">
         <v>500</v>
@@ -4729,7 +4729,7 @@
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549">
-        <v>378.18572998097471</v>
+        <v>500</v>
       </c>
       <c r="B549">
         <v>500</v>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550">
-        <v>378.78529107844491</v>
+        <v>500</v>
       </c>
       <c r="B550">
         <v>500</v>
@@ -4745,7 +4745,7 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551">
-        <v>379.29495318019968</v>
+        <v>500</v>
       </c>
       <c r="B551">
         <v>500</v>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552">
-        <v>379.76000278506871</v>
+        <v>500</v>
       </c>
       <c r="B552">
         <v>500</v>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553">
-        <v>380.21845783133483</v>
+        <v>500</v>
       </c>
       <c r="B553">
         <v>500</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554">
-        <v>380.66252321278796</v>
+        <v>500</v>
       </c>
       <c r="B554">
         <v>500</v>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555">
-        <v>381.10944957059081</v>
+        <v>500</v>
       </c>
       <c r="B555">
         <v>500</v>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556">
-        <v>381.57423413666868</v>
+        <v>500</v>
       </c>
       <c r="B556">
         <v>500</v>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557">
-        <v>382.07639758000801</v>
+        <v>500</v>
       </c>
       <c r="B557">
         <v>500</v>
@@ -4801,7 +4801,7 @@
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558">
-        <v>382.57146304327034</v>
+        <v>500</v>
       </c>
       <c r="B558">
         <v>500</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559">
-        <v>382.97294094021845</v>
+        <v>500</v>
       </c>
       <c r="B559">
         <v>500</v>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560">
-        <v>383.41338903148761</v>
+        <v>500</v>
       </c>
       <c r="B560">
         <v>500</v>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561">
-        <v>383.95761685833833</v>
+        <v>500</v>
       </c>
       <c r="B561">
         <v>500</v>
@@ -4833,7 +4833,7 @@
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562">
-        <v>384.63082655941963</v>
+        <v>500</v>
       </c>
       <c r="B562">
         <v>500</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563">
-        <v>385.2009626791484</v>
+        <v>500</v>
       </c>
       <c r="B563">
         <v>500</v>
@@ -4849,7 +4849,7 @@
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564">
-        <v>385.77679883919433</v>
+        <v>500</v>
       </c>
       <c r="B564">
         <v>500</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565">
-        <v>386.43776732087821</v>
+        <v>500</v>
       </c>
       <c r="B565">
         <v>500</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566">
-        <v>387.2022249820015</v>
+        <v>500</v>
       </c>
       <c r="B566">
         <v>500</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567">
-        <v>388.03137569053825</v>
+        <v>500</v>
       </c>
       <c r="B567">
         <v>500</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568">
-        <v>388.84082652262333</v>
+        <v>500</v>
       </c>
       <c r="B568">
         <v>500</v>
@@ -4889,7 +4889,7 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569">
-        <v>389.64016816817133</v>
+        <v>500</v>
       </c>
       <c r="B569">
         <v>500</v>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570">
-        <v>390.42049338993348</v>
+        <v>500</v>
       </c>
       <c r="B570">
         <v>500</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571">
-        <v>391.03919586597607</v>
+        <v>500</v>
       </c>
       <c r="B571">
         <v>500</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572">
-        <v>391.56617546372962</v>
+        <v>500</v>
       </c>
       <c r="B572">
         <v>500</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573">
-        <v>391.95373151126324</v>
+        <v>500</v>
       </c>
       <c r="B573">
         <v>500</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574">
-        <v>392.38720068862074</v>
+        <v>500</v>
       </c>
       <c r="B574">
         <v>500</v>
@@ -4937,7 +4937,7 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575">
-        <v>392.82811614494523</v>
+        <v>500</v>
       </c>
       <c r="B575">
         <v>500</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576">
-        <v>393.22227889768817</v>
+        <v>500</v>
       </c>
       <c r="B576">
         <v>500</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577">
-        <v>393.51598892580455</v>
+        <v>500</v>
       </c>
       <c r="B577">
         <v>500</v>
@@ -4961,7 +4961,7 @@
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578">
-        <v>393.83839121634531</v>
+        <v>500</v>
       </c>
       <c r="B578">
         <v>500</v>
@@ -4969,7 +4969,7 @@
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579">
-        <v>394.20490908682655</v>
+        <v>500</v>
       </c>
       <c r="B579">
         <v>500</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580">
-        <v>394.70134711643487</v>
+        <v>500</v>
       </c>
       <c r="B580">
         <v>500</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581">
-        <v>395.07433700437525</v>
+        <v>500</v>
       </c>
       <c r="B581">
         <v>500</v>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582">
-        <v>395.35292741585334</v>
+        <v>500</v>
       </c>
       <c r="B582">
         <v>500</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583">
-        <v>395.55587006872588</v>
+        <v>500</v>
       </c>
       <c r="B583">
         <v>500</v>
@@ -5009,7 +5009,7 @@
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584">
-        <v>395.78428916434888</v>
+        <v>500</v>
       </c>
       <c r="B584">
         <v>500</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585">
-        <v>395.97667598075566</v>
+        <v>500</v>
       </c>
       <c r="B585">
         <v>500</v>
@@ -5025,7 +5025,7 @@
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586">
-        <v>396.15522788118949</v>
+        <v>500</v>
       </c>
       <c r="B586">
         <v>500</v>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587">
-        <v>396.33891010514196</v>
+        <v>500</v>
       </c>
       <c r="B587">
         <v>500</v>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588">
-        <v>396.65814983519937</v>
+        <v>500</v>
       </c>
       <c r="B588">
         <v>500</v>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589">
-        <v>397.18388087807409</v>
+        <v>500</v>
       </c>
       <c r="B589">
         <v>500</v>
@@ -5057,7 +5057,7 @@
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590">
-        <v>397.70801927549627</v>
+        <v>500</v>
       </c>
       <c r="B590">
         <v>500</v>
@@ -5065,7 +5065,7 @@
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591">
-        <v>398.21567933924246</v>
+        <v>500</v>
       </c>
       <c r="B591">
         <v>500</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592">
-        <v>398.75439715265594</v>
+        <v>500</v>
       </c>
       <c r="B592">
         <v>500</v>
@@ -5081,7 +5081,7 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593">
-        <v>399.34592605207291</v>
+        <v>500</v>
       </c>
       <c r="B593">
         <v>500</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594">
-        <v>399.9188916260087</v>
+        <v>500</v>
       </c>
       <c r="B594">
         <v>500</v>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595">
-        <v>400.51979747327385</v>
+        <v>500</v>
       </c>
       <c r="B595">
         <v>500</v>
@@ -5105,7 +5105,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596">
-        <v>401.1065633746727</v>
+        <v>500</v>
       </c>
       <c r="B596">
         <v>500</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597">
-        <v>401.65142426622208</v>
+        <v>500</v>
       </c>
       <c r="B597">
         <v>500</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598">
-        <v>402.22853993453612</v>
+        <v>500</v>
       </c>
       <c r="B598">
         <v>500</v>
@@ -5129,7 +5129,7 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599">
-        <v>402.89391521955798</v>
+        <v>500</v>
       </c>
       <c r="B599">
         <v>500</v>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600">
-        <v>403.55924919597692</v>
+        <v>500</v>
       </c>
       <c r="B600">
         <v>500</v>
@@ -5145,7 +5145,7 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601">
-        <v>404.10053342193902</v>
+        <v>500</v>
       </c>
       <c r="B601">
         <v>500</v>
@@ -5153,7 +5153,7 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602">
-        <v>404.65017707983577</v>
+        <v>500</v>
       </c>
       <c r="B602">
         <v>500</v>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603">
-        <v>405.13607622127682</v>
+        <v>500</v>
       </c>
       <c r="B603">
         <v>500</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604">
-        <v>405.49296940252526</v>
+        <v>500</v>
       </c>
       <c r="B604">
         <v>500</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605">
-        <v>405.74101199418078</v>
+        <v>500</v>
       </c>
       <c r="B605">
         <v>500</v>
@@ -5185,7 +5185,7 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606">
-        <v>405.9436304772056</v>
+        <v>500</v>
       </c>
       <c r="B606">
         <v>500</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607">
-        <v>405.96124763752329</v>
+        <v>500</v>
       </c>
       <c r="B607">
         <v>500</v>
@@ -5201,7 +5201,7 @@
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608">
-        <v>405.94007732958113</v>
+        <v>500</v>
       </c>
       <c r="B608">
         <v>500</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609">
-        <v>405.98386825540564</v>
+        <v>500</v>
       </c>
       <c r="B609">
         <v>500</v>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610">
-        <v>405.94634673422132</v>
+        <v>500</v>
       </c>
       <c r="B610">
         <v>500</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611">
-        <v>405.91720770862071</v>
+        <v>500</v>
       </c>
       <c r="B611">
         <v>500</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612">
-        <v>405.97549608868655</v>
+        <v>500</v>
       </c>
       <c r="B612">
         <v>500</v>
@@ -5241,7 +5241,7 @@
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613">
-        <v>406.04836919390772</v>
+        <v>500</v>
       </c>
       <c r="B613">
         <v>500</v>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614">
-        <v>406.25529861771724</v>
+        <v>500</v>
       </c>
       <c r="B614">
         <v>500</v>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615">
-        <v>406.45688625018596</v>
+        <v>500</v>
       </c>
       <c r="B615">
         <v>500</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616">
-        <v>406.76345468065813</v>
+        <v>500</v>
       </c>
       <c r="B616">
         <v>500</v>
@@ -5273,7 +5273,7 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617">
-        <v>407.17084880174809</v>
+        <v>500</v>
       </c>
       <c r="B617">
         <v>500</v>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618">
-        <v>407.63028920643558</v>
+        <v>500</v>
       </c>
       <c r="B618">
         <v>500</v>
@@ -5289,7 +5289,7 @@
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A619">
-        <v>408.15246728741067</v>
+        <v>500</v>
       </c>
       <c r="B619">
         <v>500</v>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620">
-        <v>408.63937793413874</v>
+        <v>500</v>
       </c>
       <c r="B620">
         <v>500</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621">
-        <v>409.15599486162779</v>
+        <v>500</v>
       </c>
       <c r="B621">
         <v>500</v>
@@ -5313,7 +5313,7 @@
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A622">
-        <v>409.57539414573614</v>
+        <v>500</v>
       </c>
       <c r="B622">
         <v>500</v>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623">
-        <v>410.00143181198757</v>
+        <v>500</v>
       </c>
       <c r="B623">
         <v>500</v>
@@ -5329,7 +5329,7 @@
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624">
-        <v>410.41369073664544</v>
+        <v>500</v>
       </c>
       <c r="B624">
         <v>500</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625">
-        <v>410.65813154633372</v>
+        <v>500</v>
       </c>
       <c r="B625">
         <v>500</v>
@@ -5345,7 +5345,7 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626">
-        <v>410.81872740056372</v>
+        <v>500</v>
       </c>
       <c r="B626">
         <v>500</v>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627">
-        <v>411.07425118024531</v>
+        <v>500</v>
       </c>
       <c r="B627">
         <v>500</v>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628">
-        <v>411.41902663813806</v>
+        <v>500</v>
       </c>
       <c r="B628">
         <v>500</v>
@@ -5369,7 +5369,7 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629">
-        <v>411.88164171155012</v>
+        <v>500</v>
       </c>
       <c r="B629">
         <v>500</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630">
-        <v>412.37263883985668</v>
+        <v>500</v>
       </c>
       <c r="B630">
         <v>500</v>
@@ -5385,7 +5385,7 @@
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631">
-        <v>412.90792389578365</v>
+        <v>500</v>
       </c>
       <c r="B631">
         <v>500</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632">
-        <v>413.39869695311603</v>
+        <v>500</v>
       </c>
       <c r="B632">
         <v>500</v>
@@ -5401,7 +5401,7 @@
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633">
-        <v>413.9397569502529</v>
+        <v>500</v>
       </c>
       <c r="B633">
         <v>500</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634">
-        <v>414.57729536295625</v>
+        <v>500</v>
       </c>
       <c r="B634">
         <v>500</v>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635">
-        <v>415.23086638926515</v>
+        <v>500</v>
       </c>
       <c r="B635">
         <v>500</v>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636">
-        <v>415.75358563639134</v>
+        <v>500</v>
       </c>
       <c r="B636">
         <v>500</v>
@@ -5433,7 +5433,7 @@
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637">
-        <v>416.25288654662552</v>
+        <v>500</v>
       </c>
       <c r="B637">
         <v>500</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638">
-        <v>416.63966267045862</v>
+        <v>500</v>
       </c>
       <c r="B638">
         <v>500</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639">
-        <v>417.00908145195757</v>
+        <v>500</v>
       </c>
       <c r="B639">
         <v>500</v>
@@ -5457,7 +5457,7 @@
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640">
-        <v>417.36375500572632</v>
+        <v>500</v>
       </c>
       <c r="B640">
         <v>500</v>
@@ -5465,7 +5465,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641">
-        <v>417.65919526755982</v>
+        <v>500</v>
       </c>
       <c r="B641">
         <v>500</v>
@@ -5473,7 +5473,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642">
-        <v>418.09502871840419</v>
+        <v>500</v>
       </c>
       <c r="B642">
         <v>500</v>
@@ -5481,7 +5481,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643">
-        <v>418.47935004299688</v>
+        <v>500</v>
       </c>
       <c r="B643">
         <v>500</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644">
-        <v>418.94318856629269</v>
+        <v>500</v>
       </c>
       <c r="B644">
         <v>500</v>
@@ -5497,7 +5497,7 @@
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645">
-        <v>419.36417615573964</v>
+        <v>500</v>
       </c>
       <c r="B645">
         <v>500</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646">
-        <v>419.67575121953604</v>
+        <v>500</v>
       </c>
       <c r="B646">
         <v>500</v>
@@ -5513,7 +5513,7 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647">
-        <v>419.97042143302309</v>
+        <v>500</v>
       </c>
       <c r="B647">
         <v>500</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648">
-        <v>420.22784191115562</v>
+        <v>500</v>
       </c>
       <c r="B648">
         <v>500</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649">
-        <v>420.40481300166095</v>
+        <v>500</v>
       </c>
       <c r="B649">
         <v>500</v>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650">
-        <v>420.60501550477886</v>
+        <v>500</v>
       </c>
       <c r="B650">
         <v>500</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651">
-        <v>420.79457631122528</v>
+        <v>500</v>
       </c>
       <c r="B651">
         <v>500</v>
@@ -5553,7 +5553,7 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652">
-        <v>421.02752708442159</v>
+        <v>500</v>
       </c>
       <c r="B652">
         <v>500</v>
@@ -5561,7 +5561,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653">
-        <v>421.22522032743683</v>
+        <v>500</v>
       </c>
       <c r="B653">
         <v>500</v>
@@ -5569,7 +5569,7 @@
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654">
-        <v>421.28830432450513</v>
+        <v>500</v>
       </c>
       <c r="B654">
         <v>500</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655">
-        <v>421.46494075756635</v>
+        <v>500</v>
       </c>
       <c r="B655">
         <v>500</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656">
-        <v>421.599885922201</v>
+        <v>500</v>
       </c>
       <c r="B656">
         <v>500</v>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657">
-        <v>421.67249767312529</v>
+        <v>500</v>
       </c>
       <c r="B657">
         <v>500</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658">
-        <v>421.88331214347903</v>
+        <v>500</v>
       </c>
       <c r="B658">
         <v>500</v>
@@ -5609,7 +5609,7 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659">
-        <v>422.20443370254509</v>
+        <v>500</v>
       </c>
       <c r="B659">
         <v>500</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660">
-        <v>422.5672937269228</v>
+        <v>500</v>
       </c>
       <c r="B660">
         <v>500</v>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661">
-        <v>422.8401446625129</v>
+        <v>500</v>
       </c>
       <c r="B661">
         <v>500</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662">
-        <v>423.13849409820244</v>
+        <v>500</v>
       </c>
       <c r="B662">
         <v>500</v>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663">
-        <v>423.37732878301961</v>
+        <v>500</v>
       </c>
       <c r="B663">
         <v>500</v>
@@ -5649,7 +5649,7 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664">
-        <v>423.53188544896739</v>
+        <v>500</v>
       </c>
       <c r="B664">
         <v>500</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665">
-        <v>423.62236790647853</v>
+        <v>500</v>
       </c>
       <c r="B665">
         <v>500</v>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666">
-        <v>423.5722178415707</v>
+        <v>500</v>
       </c>
       <c r="B666">
         <v>500</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667">
-        <v>423.58076215772979</v>
+        <v>500</v>
       </c>
       <c r="B667">
         <v>500</v>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668">
-        <v>423.58914705565451</v>
+        <v>500</v>
       </c>
       <c r="B668">
         <v>500</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669">
-        <v>423.49205636361745</v>
+        <v>500</v>
       </c>
       <c r="B669">
         <v>500</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670">
-        <v>423.27034366752792</v>
+        <v>500</v>
       </c>
       <c r="B670">
         <v>500</v>
@@ -5705,7 +5705,7 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671">
-        <v>423.00772866640744</v>
+        <v>500</v>
       </c>
       <c r="B671">
         <v>500</v>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672">
-        <v>422.73631756864256</v>
+        <v>500</v>
       </c>
       <c r="B672">
         <v>500</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673">
-        <v>422.52580995231875</v>
+        <v>500</v>
       </c>
       <c r="B673">
         <v>500</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674">
-        <v>422.33763960521463</v>
+        <v>500</v>
       </c>
       <c r="B674">
         <v>500</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A675">
-        <v>422.12096453832402</v>
+        <v>500</v>
       </c>
       <c r="B675">
         <v>500</v>
@@ -5745,7 +5745,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676">
-        <v>422.12719337461806</v>
+        <v>500</v>
       </c>
       <c r="B676">
         <v>500</v>
@@ -5753,7 +5753,7 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677">
-        <v>422.2207102931439</v>
+        <v>500</v>
       </c>
       <c r="B677">
         <v>500</v>
@@ -5761,7 +5761,7 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678">
-        <v>422.20220281113671</v>
+        <v>500</v>
       </c>
       <c r="B678">
         <v>500</v>
@@ -5769,7 +5769,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679">
-        <v>422.26239963212328</v>
+        <v>500</v>
       </c>
       <c r="B679">
         <v>500</v>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680">
-        <v>422.24214957446475</v>
+        <v>500</v>
       </c>
       <c r="B680">
         <v>500</v>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681">
-        <v>422.10149365887253</v>
+        <v>500</v>
       </c>
       <c r="B681">
         <v>500</v>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682">
-        <v>421.95216548306576</v>
+        <v>500</v>
       </c>
       <c r="B682">
         <v>500</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683">
-        <v>421.87601613595297</v>
+        <v>500</v>
       </c>
       <c r="B683">
         <v>500</v>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684">
-        <v>421.73695116968639</v>
+        <v>500</v>
       </c>
       <c r="B684">
         <v>500</v>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685">
-        <v>421.76766199005823</v>
+        <v>500</v>
       </c>
       <c r="B685">
         <v>500</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686">
-        <v>421.69152234290624</v>
+        <v>500</v>
       </c>
       <c r="B686">
         <v>500</v>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687">
-        <v>421.54775646234674</v>
+        <v>500</v>
       </c>
       <c r="B687">
         <v>500</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688">
-        <v>421.45492622751038</v>
+        <v>500</v>
       </c>
       <c r="B688">
         <v>500</v>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689">
-        <v>421.32216373020361</v>
+        <v>500</v>
       </c>
       <c r="B689">
         <v>500</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690">
-        <v>421.1614945813713</v>
+        <v>500</v>
       </c>
       <c r="B690">
         <v>500</v>
@@ -5865,7 +5865,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691">
-        <v>421.01798792912615</v>
+        <v>500</v>
       </c>
       <c r="B691">
         <v>500</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692">
-        <v>420.87292392900133</v>
+        <v>500</v>
       </c>
       <c r="B692">
         <v>500</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693">
-        <v>420.83377451771105</v>
+        <v>500</v>
       </c>
       <c r="B693">
         <v>500</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694">
-        <v>420.90616862018231</v>
+        <v>500</v>
       </c>
       <c r="B694">
         <v>500</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695">
-        <v>420.97589299738831</v>
+        <v>500</v>
       </c>
       <c r="B695">
         <v>500</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696">
-        <v>421.06460435891137</v>
+        <v>500</v>
       </c>
       <c r="B696">
         <v>500</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697">
-        <v>421.17617088995348</v>
+        <v>500</v>
       </c>
       <c r="B697">
         <v>500</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698">
-        <v>421.1369756981959</v>
+        <v>500</v>
       </c>
       <c r="B698">
         <v>500</v>
@@ -5929,7 +5929,7 @@
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699">
-        <v>421.0534924057485</v>
+        <v>500</v>
       </c>
       <c r="B699">
         <v>500</v>
@@ -5937,7 +5937,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700">
-        <v>420.90744568377988</v>
+        <v>500</v>
       </c>
       <c r="B700">
         <v>500</v>
@@ -5945,7 +5945,7 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701">
-        <v>420.76575569858215</v>
+        <v>500</v>
       </c>
       <c r="B701">
         <v>500</v>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702">
-        <v>420.71549194297415</v>
+        <v>500</v>
       </c>
       <c r="B702">
         <v>500</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703">
-        <v>420.78316795202693</v>
+        <v>500</v>
       </c>
       <c r="B703">
         <v>500</v>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704">
-        <v>420.84477352108001</v>
+        <v>500</v>
       </c>
       <c r="B704">
         <v>500</v>
@@ -5977,7 +5977,7 @@
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705">
-        <v>421.05553308917843</v>
+        <v>500</v>
       </c>
       <c r="B705">
         <v>500</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706">
-        <v>421.26580369855094</v>
+        <v>500</v>
       </c>
       <c r="B706">
         <v>500</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707">
-        <v>421.43798853634263</v>
+        <v>500</v>
       </c>
       <c r="B707">
         <v>500</v>
@@ -6001,7 +6001,7 @@
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A708">
-        <v>421.71851096320711</v>
+        <v>500</v>
       </c>
       <c r="B708">
         <v>500</v>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709">
-        <v>422.07821979174992</v>
+        <v>500</v>
       </c>
       <c r="B709">
         <v>500</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710">
-        <v>422.39981466223645</v>
+        <v>500</v>
       </c>
       <c r="B710">
         <v>500</v>
@@ -6025,7 +6025,7 @@
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A711">
-        <v>422.8084068622174</v>
+        <v>500</v>
       </c>
       <c r="B711">
         <v>500</v>
@@ -6033,7 +6033,7 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A712">
-        <v>423.28437577526239</v>
+        <v>500</v>
       </c>
       <c r="B712">
         <v>500</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713">
-        <v>423.7668794037366</v>
+        <v>500</v>
       </c>
       <c r="B713">
         <v>500</v>
@@ -6049,7 +6049,7 @@
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714">
-        <v>424.2391473012413</v>
+        <v>500</v>
       </c>
       <c r="B714">
         <v>500</v>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715">
-        <v>424.73128614124676</v>
+        <v>500</v>
       </c>
       <c r="B715">
         <v>500</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716">
-        <v>425.3128350601994</v>
+        <v>500</v>
       </c>
       <c r="B716">
         <v>500</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717">
-        <v>425.85405887933592</v>
+        <v>500</v>
       </c>
       <c r="B717">
         <v>500</v>
@@ -6081,7 +6081,7 @@
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718">
-        <v>426.4430423781987</v>
+        <v>500</v>
       </c>
       <c r="B718">
         <v>500</v>
@@ -6089,7 +6089,7 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719">
-        <v>427.0018252287997</v>
+        <v>500</v>
       </c>
       <c r="B719">
         <v>500</v>
@@ -6097,7 +6097,7 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720">
-        <v>427.64368437775136</v>
+        <v>500</v>
       </c>
       <c r="B720">
         <v>500</v>
@@ -6105,7 +6105,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721">
-        <v>428.2366915671563</v>
+        <v>500</v>
       </c>
       <c r="B721">
         <v>500</v>
@@ -6113,7 +6113,7 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722">
-        <v>428.80308046429201</v>
+        <v>500</v>
       </c>
       <c r="B722">
         <v>500</v>
@@ -6121,7 +6121,7 @@
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723">
-        <v>429.43128434017376</v>
+        <v>500</v>
       </c>
       <c r="B723">
         <v>500</v>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A724">
-        <v>430.16891464505102</v>
+        <v>500</v>
       </c>
       <c r="B724">
         <v>500</v>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725">
-        <v>430.92785201356168</v>
+        <v>500</v>
       </c>
       <c r="B725">
         <v>500</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726">
-        <v>431.6320593937163</v>
+        <v>500</v>
       </c>
       <c r="B726">
         <v>500</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727">
-        <v>432.21812150715823</v>
+        <v>500</v>
       </c>
       <c r="B727">
         <v>500</v>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728">
-        <v>432.77521876987157</v>
+        <v>500</v>
       </c>
       <c r="B728">
         <v>500</v>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729">
-        <v>433.38908539432936</v>
+        <v>500</v>
       </c>
       <c r="B729">
         <v>500</v>
@@ -6177,7 +6177,7 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730">
-        <v>434.08465818154781</v>
+        <v>500</v>
       </c>
       <c r="B730">
         <v>500</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731">
-        <v>434.8345260419166</v>
+        <v>500</v>
       </c>
       <c r="B731">
         <v>500</v>
@@ -6193,7 +6193,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732">
-        <v>435.70635186467183</v>
+        <v>500</v>
       </c>
       <c r="B732">
         <v>500</v>
@@ -6201,7 +6201,7 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733">
-        <v>436.62883841514918</v>
+        <v>500</v>
       </c>
       <c r="B733">
         <v>500</v>
@@ -6209,7 +6209,7 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734">
-        <v>437.65041778614523</v>
+        <v>500</v>
       </c>
       <c r="B734">
         <v>500</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A735">
-        <v>438.56816898061754</v>
+        <v>500</v>
       </c>
       <c r="B735">
         <v>500</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736">
-        <v>439.43309179835177</v>
+        <v>500</v>
       </c>
       <c r="B736">
         <v>500</v>
@@ -6233,7 +6233,7 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737">
-        <v>440.32219519205478</v>
+        <v>500</v>
       </c>
       <c r="B737">
         <v>500</v>
@@ -6241,7 +6241,7 @@
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738">
-        <v>441.13889247781219</v>
+        <v>500</v>
       </c>
       <c r="B738">
         <v>500</v>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739">
-        <v>441.8919977970038</v>
+        <v>500</v>
       </c>
       <c r="B739">
         <v>500</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740">
-        <v>442.65084539787995</v>
+        <v>500</v>
       </c>
       <c r="B740">
         <v>500</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741">
-        <v>443.4077798281711</v>
+        <v>500</v>
       </c>
       <c r="B741">
         <v>500</v>
@@ -6273,7 +6273,7 @@
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742">
-        <v>444.00481469377314</v>
+        <v>500</v>
       </c>
       <c r="B742">
         <v>500</v>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743">
-        <v>444.52376474995759</v>
+        <v>500</v>
       </c>
       <c r="B743">
         <v>500</v>
@@ -6289,7 +6289,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744">
-        <v>445.10456289344063</v>
+        <v>500</v>
       </c>
       <c r="B744">
         <v>500</v>
@@ -6297,7 +6297,7 @@
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A745">
-        <v>445.66822432517284</v>
+        <v>500</v>
       </c>
       <c r="B745">
         <v>500</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746">
-        <v>446.21715683628628</v>
+        <v>500</v>
       </c>
       <c r="B746">
         <v>500</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747">
-        <v>446.82950449893445</v>
+        <v>500</v>
       </c>
       <c r="B747">
         <v>500</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748">
-        <v>447.46306352677425</v>
+        <v>500</v>
       </c>
       <c r="B748">
         <v>500</v>
@@ -6329,7 +6329,7 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749">
-        <v>448.0753363088217</v>
+        <v>500</v>
       </c>
       <c r="B749">
         <v>500</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750">
-        <v>448.78554707283052</v>
+        <v>500</v>
       </c>
       <c r="B750">
         <v>500</v>
@@ -6345,7 +6345,7 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751">
-        <v>449.49790094596949</v>
+        <v>500</v>
       </c>
       <c r="B751">
         <v>500</v>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752">
-        <v>450.39115003369858</v>
+        <v>500</v>
       </c>
       <c r="B752">
         <v>500</v>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753">
-        <v>451.43382845300857</v>
+        <v>500</v>
       </c>
       <c r="B753">
         <v>500</v>
@@ -6369,7 +6369,7 @@
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A754">
-        <v>452.5894845376269</v>
+        <v>500</v>
       </c>
       <c r="B754">
         <v>500</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A755">
-        <v>453.65712044777393</v>
+        <v>500</v>
       </c>
       <c r="B755">
         <v>500</v>
@@ -6385,7 +6385,7 @@
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A756">
-        <v>454.84180509574219</v>
+        <v>500</v>
       </c>
       <c r="B756">
         <v>500</v>
@@ -6393,7 +6393,7 @@
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A757">
-        <v>456.0121221922937</v>
+        <v>500</v>
       </c>
       <c r="B757">
         <v>500</v>
@@ -6401,7 +6401,7 @@
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A758">
-        <v>457.19645332270954</v>
+        <v>500</v>
       </c>
       <c r="B758">
         <v>500</v>
@@ -6409,7 +6409,7 @@
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A759">
-        <v>458.36709834541495</v>
+        <v>500</v>
       </c>
       <c r="B759">
         <v>500</v>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A760">
-        <v>459.42632776579285</v>
+        <v>500</v>
       </c>
       <c r="B760">
         <v>500</v>
@@ -6425,7 +6425,7 @@
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A761">
-        <v>460.38286101147844</v>
+        <v>500</v>
       </c>
       <c r="B761">
         <v>500</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A762">
-        <v>461.33087462356076</v>
+        <v>500</v>
       </c>
       <c r="B762">
         <v>500</v>
@@ -6441,7 +6441,7 @@
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A763">
-        <v>462.22869646160996</v>
+        <v>500</v>
       </c>
       <c r="B763">
         <v>500</v>
@@ -6449,7 +6449,7 @@
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A764">
-        <v>463.26394932834205</v>
+        <v>500</v>
       </c>
       <c r="B764">
         <v>500</v>
@@ -6457,7 +6457,7 @@
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A765">
-        <v>464.28098271184263</v>
+        <v>500</v>
       </c>
       <c r="B765">
         <v>500</v>
@@ -6465,7 +6465,7 @@
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A766">
-        <v>465.31557162370774</v>
+        <v>500</v>
       </c>
       <c r="B766">
         <v>500</v>
@@ -6473,7 +6473,7 @@
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A767">
-        <v>466.28437351055129</v>
+        <v>500</v>
       </c>
       <c r="B767">
         <v>500</v>
@@ -6481,7 +6481,7 @@
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A768">
-        <v>467.28432510221143</v>
+        <v>500</v>
       </c>
       <c r="B768">
         <v>500</v>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A769">
-        <v>468.25502341971685</v>
+        <v>500</v>
       </c>
       <c r="B769">
         <v>500</v>
@@ -6497,7 +6497,7 @@
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A770">
-        <v>469.18392852014659</v>
+        <v>500</v>
       </c>
       <c r="B770">
         <v>500</v>
@@ -6505,7 +6505,7 @@
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A771">
-        <v>470.23543964645529</v>
+        <v>500</v>
       </c>
       <c r="B771">
         <v>500</v>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A772">
-        <v>471.26529117868665</v>
+        <v>500</v>
       </c>
       <c r="B772">
         <v>500</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A773">
-        <v>472.24338948472581</v>
+        <v>500</v>
       </c>
       <c r="B773">
         <v>500</v>
@@ -6529,7 +6529,7 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A774">
-        <v>473.25870572442682</v>
+        <v>500</v>
       </c>
       <c r="B774">
         <v>500</v>
@@ -6537,7 +6537,7 @@
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A775">
-        <v>474.25354316587431</v>
+        <v>500</v>
       </c>
       <c r="B775">
         <v>500</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A776">
-        <v>475.2029968475959</v>
+        <v>500</v>
       </c>
       <c r="B776">
         <v>500</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A777">
-        <v>476.1818972022283</v>
+        <v>500</v>
       </c>
       <c r="B777">
         <v>500</v>
@@ -6561,7 +6561,7 @@
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A778">
-        <v>477.07499552515497</v>
+        <v>500</v>
       </c>
       <c r="B778">
         <v>500</v>
@@ -6569,7 +6569,7 @@
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A779">
-        <v>477.92191048262316</v>
+        <v>500</v>
       </c>
       <c r="B779">
         <v>500</v>
@@ -6577,7 +6577,7 @@
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A780">
-        <v>478.744799643899</v>
+        <v>500</v>
       </c>
       <c r="B780">
         <v>500</v>
@@ -6585,7 +6585,7 @@
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A781">
-        <v>479.39351016640973</v>
+        <v>500</v>
       </c>
       <c r="B781">
         <v>500</v>
@@ -6593,7 +6593,7 @@
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A782">
-        <v>480.05870022926717</v>
+        <v>500</v>
       </c>
       <c r="B782">
         <v>500</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A783">
-        <v>480.81104964823049</v>
+        <v>500</v>
       </c>
       <c r="B783">
         <v>500</v>
@@ -6609,7 +6609,7 @@
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A784">
-        <v>481.55552405079328</v>
+        <v>500</v>
       </c>
       <c r="B784">
         <v>500</v>
@@ -6617,7 +6617,7 @@
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A785">
-        <v>482.23277660384389</v>
+        <v>500</v>
       </c>
       <c r="B785">
         <v>500</v>
@@ -6625,7 +6625,7 @@
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A786">
-        <v>482.86856523996249</v>
+        <v>500</v>
       </c>
       <c r="B786">
         <v>500</v>
@@ -6633,7 +6633,7 @@
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A787">
-        <v>483.55285821212959</v>
+        <v>500</v>
       </c>
       <c r="B787">
         <v>500</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A788">
-        <v>484.2025428430332</v>
+        <v>500</v>
       </c>
       <c r="B788">
         <v>500</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A789">
-        <v>484.80235008712168</v>
+        <v>500</v>
       </c>
       <c r="B789">
         <v>500</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A790">
-        <v>485.47639270535063</v>
+        <v>500</v>
       </c>
       <c r="B790">
         <v>500</v>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A791">
-        <v>486.15699169506917</v>
+        <v>500</v>
       </c>
       <c r="B791">
         <v>500</v>
@@ -6673,7 +6673,7 @@
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A792">
-        <v>486.81661974146311</v>
+        <v>500</v>
       </c>
       <c r="B792">
         <v>500</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A793">
-        <v>487.46093529098039</v>
+        <v>500</v>
       </c>
       <c r="B793">
         <v>500</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A794">
-        <v>488.05201545336615</v>
+        <v>500</v>
       </c>
       <c r="B794">
         <v>500</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A795">
-        <v>488.60525238571006</v>
+        <v>500</v>
       </c>
       <c r="B795">
         <v>500</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A796">
-        <v>489.16071747774447</v>
+        <v>500</v>
       </c>
       <c r="B796">
         <v>500</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A797">
-        <v>489.69076884377489</v>
+        <v>500</v>
       </c>
       <c r="B797">
         <v>500</v>
@@ -6721,7 +6721,7 @@
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A798">
-        <v>490.22582743539982</v>
+        <v>500</v>
       </c>
       <c r="B798">
         <v>500</v>
@@ -6729,7 +6729,7 @@
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A799">
-        <v>490.69777942436059</v>
+        <v>500</v>
       </c>
       <c r="B799">
         <v>500</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A800">
-        <v>491.0683434320033</v>
+        <v>500</v>
       </c>
       <c r="B800">
         <v>500</v>
@@ -6745,7 +6745,7 @@
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A801">
-        <v>491.32260700639773</v>
+        <v>500</v>
       </c>
       <c r="B801">
         <v>500</v>
@@ -6753,7 +6753,7 @@
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A802">
-        <v>491.6195978327803</v>
+        <v>500</v>
       </c>
       <c r="B802">
         <v>500</v>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A803">
-        <v>491.89105725673727</v>
+        <v>500</v>
       </c>
       <c r="B803">
         <v>500</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A804">
-        <v>492.14832310123205</v>
+        <v>500</v>
       </c>
       <c r="B804">
         <v>500</v>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A805">
-        <v>492.42599261348596</v>
+        <v>500</v>
       </c>
       <c r="B805">
         <v>500</v>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A806">
-        <v>492.63579305530874</v>
+        <v>500</v>
       </c>
       <c r="B806">
         <v>500</v>
@@ -6793,7 +6793,7 @@
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A807">
-        <v>492.93012049349733</v>
+        <v>500</v>
       </c>
       <c r="B807">
         <v>500</v>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A808">
-        <v>493.31212784696072</v>
+        <v>500</v>
       </c>
       <c r="B808">
         <v>500</v>
@@ -6809,7 +6809,7 @@
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A809">
-        <v>493.5443736545717</v>
+        <v>500</v>
       </c>
       <c r="B809">
         <v>500</v>
@@ -6817,7 +6817,7 @@
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A810">
-        <v>493.82959091232897</v>
+        <v>500</v>
       </c>
       <c r="B810">
         <v>500</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A811">
-        <v>494.17849432898453</v>
+        <v>500</v>
       </c>
       <c r="B811">
         <v>500</v>
@@ -6833,7 +6833,7 @@
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A812">
-        <v>494.57854619358551</v>
+        <v>500</v>
       </c>
       <c r="B812">
         <v>500</v>
@@ -6841,7 +6841,7 @@
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A813">
-        <v>495.01999058818319</v>
+        <v>500</v>
       </c>
       <c r="B813">
         <v>500</v>
@@ -6849,7 +6849,7 @@
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A814">
-        <v>495.41039125411766</v>
+        <v>500</v>
       </c>
       <c r="B814">
         <v>500</v>
@@ -6857,7 +6857,7 @@
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A815">
-        <v>495.6479801105769</v>
+        <v>500</v>
       </c>
       <c r="B815">
         <v>500</v>
@@ -6865,7 +6865,7 @@
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A816">
-        <v>495.79821489673066</v>
+        <v>500</v>
       </c>
       <c r="B816">
         <v>500</v>
@@ -6873,7 +6873,7 @@
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A817">
-        <v>495.85981986974542</v>
+        <v>500</v>
       </c>
       <c r="B817">
         <v>500</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A818">
-        <v>495.82362664170711</v>
+        <v>500</v>
       </c>
       <c r="B818">
         <v>500</v>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A819">
-        <v>495.94445768031903</v>
+        <v>500</v>
       </c>
       <c r="B819">
         <v>500</v>
@@ -6897,7 +6897,7 @@
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A820">
-        <v>496.14849464369547</v>
+        <v>500</v>
       </c>
       <c r="B820">
         <v>500</v>
@@ -6905,7 +6905,7 @@
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A821">
-        <v>496.35291948337255</v>
+        <v>500</v>
       </c>
       <c r="B821">
         <v>500</v>
@@ -6913,7 +6913,7 @@
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A822">
-        <v>496.61249154895665</v>
+        <v>500</v>
       </c>
       <c r="B822">
         <v>500</v>
@@ -6921,7 +6921,7 @@
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A823">
-        <v>496.80700609779973</v>
+        <v>500</v>
       </c>
       <c r="B823">
         <v>500</v>
@@ -6929,7 +6929,7 @@
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A824">
-        <v>496.98857766761103</v>
+        <v>500</v>
       </c>
       <c r="B824">
         <v>500</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A825">
-        <v>497.16393884434495</v>
+        <v>500</v>
       </c>
       <c r="B825">
         <v>500</v>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A826">
-        <v>497.33488795587516</v>
+        <v>500</v>
       </c>
       <c r="B826">
         <v>500</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A827">
-        <v>497.42482527577454</v>
+        <v>500</v>
       </c>
       <c r="B827">
         <v>500</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A828">
-        <v>497.51501877932458</v>
+        <v>500</v>
       </c>
       <c r="B828">
         <v>500</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A829">
-        <v>497.71339616687897</v>
+        <v>500</v>
       </c>
       <c r="B829">
         <v>500</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A830">
-        <v>498.02392094107364</v>
+        <v>500</v>
       </c>
       <c r="B830">
         <v>500</v>
@@ -6985,7 +6985,7 @@
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A831">
-        <v>498.38505561679921</v>
+        <v>500</v>
       </c>
       <c r="B831">
         <v>500</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A832">
-        <v>498.76101202729473</v>
+        <v>500</v>
       </c>
       <c r="B832">
         <v>500</v>
@@ -7001,7 +7001,7 @@
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A833">
-        <v>499.09393353154735</v>
+        <v>500</v>
       </c>
       <c r="B833">
         <v>500</v>
@@ -7009,7 +7009,7 @@
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A834">
-        <v>499.36275933377431</v>
+        <v>500</v>
       </c>
       <c r="B834">
         <v>500</v>
@@ -7017,7 +7017,7 @@
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A835">
-        <v>499.66772289382186</v>
+        <v>500</v>
       </c>
       <c r="B835">
         <v>500</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A836">
-        <v>499.96046742296852</v>
+        <v>500</v>
       </c>
       <c r="B836">
         <v>500</v>
@@ -7393,7 +7393,7 @@
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A882">
-        <v>500</v>
+        <v>499.98511151192423</v>
       </c>
       <c r="B882">
         <v>500</v>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A883">
-        <v>500</v>
+        <v>499.88251689319378</v>
       </c>
       <c r="B883">
         <v>500</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A884">
-        <v>500</v>
+        <v>499.61883552984199</v>
       </c>
       <c r="B884">
         <v>500</v>
@@ -7417,7 +7417,7 @@
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A885">
-        <v>500</v>
+        <v>499.2937167985462</v>
       </c>
       <c r="B885">
         <v>500</v>
@@ -7425,7 +7425,7 @@
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A886">
-        <v>500</v>
+        <v>498.87747102486082</v>
       </c>
       <c r="B886">
         <v>500</v>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A887">
-        <v>500</v>
+        <v>498.41165961205951</v>
       </c>
       <c r="B887">
         <v>500</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A888">
-        <v>500</v>
+        <v>497.98292257491346</v>
       </c>
       <c r="B888">
         <v>500</v>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A889">
-        <v>500</v>
+        <v>497.51203890676845</v>
       </c>
       <c r="B889">
         <v>500</v>
@@ -7457,7 +7457,7 @@
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A890">
-        <v>500</v>
+        <v>497.20126165763367</v>
       </c>
       <c r="B890">
         <v>500</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A891">
-        <v>500</v>
+        <v>497.09944801874798</v>
       </c>
       <c r="B891">
         <v>500</v>
@@ -7473,7 +7473,7 @@
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A892">
-        <v>500</v>
+        <v>497.11554254460009</v>
       </c>
       <c r="B892">
         <v>500</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A893">
-        <v>500</v>
+        <v>497.09772604024954</v>
       </c>
       <c r="B893">
         <v>500</v>
@@ -7489,7 +7489,7 @@
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A894">
-        <v>500</v>
+        <v>497.02483112834545</v>
       </c>
       <c r="B894">
         <v>500</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A895">
-        <v>500</v>
+        <v>496.9279577905798</v>
       </c>
       <c r="B895">
         <v>500</v>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A896">
-        <v>500</v>
+        <v>496.85310744782055</v>
       </c>
       <c r="B896">
         <v>500</v>
@@ -7513,7 +7513,7 @@
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A897">
-        <v>500</v>
+        <v>496.63392096386519</v>
       </c>
       <c r="B897">
         <v>500</v>
@@ -7521,7 +7521,7 @@
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A898">
-        <v>500</v>
+        <v>496.34448078844349</v>
       </c>
       <c r="B898">
         <v>500</v>
@@ -7529,7 +7529,7 @@
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A899">
-        <v>500</v>
+        <v>495.88361229792679</v>
       </c>
       <c r="B899">
         <v>500</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A900">
-        <v>500</v>
+        <v>495.49350433069327</v>
       </c>
       <c r="B900">
         <v>500</v>
@@ -7545,7 +7545,7 @@
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A901">
-        <v>500</v>
+        <v>495.1412462418748</v>
       </c>
       <c r="B901">
         <v>500</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A902">
-        <v>500</v>
+        <v>494.72141364952205</v>
       </c>
       <c r="B902">
         <v>500</v>
@@ -7561,7 +7561,7 @@
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A903">
-        <v>500</v>
+        <v>494.24808532218941</v>
       </c>
       <c r="B903">
         <v>500</v>
@@ -7569,7 +7569,7 @@
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A904">
-        <v>500</v>
+        <v>493.86115315051211</v>
       </c>
       <c r="B904">
         <v>500</v>
@@ -7577,7 +7577,7 @@
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A905">
-        <v>500</v>
+        <v>493.35840057406665</v>
       </c>
       <c r="B905">
         <v>500</v>
@@ -7585,7 +7585,7 @@
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A906">
-        <v>500</v>
+        <v>492.81055947686576</v>
       </c>
       <c r="B906">
         <v>500</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A907">
-        <v>500</v>
+        <v>492.26887985519318</v>
       </c>
       <c r="B907">
         <v>500</v>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A908">
-        <v>500</v>
+        <v>491.64011324150357</v>
       </c>
       <c r="B908">
         <v>500</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A909">
-        <v>500</v>
+        <v>490.97306196537187</v>
       </c>
       <c r="B909">
         <v>500</v>
@@ -7617,7 +7617,7 @@
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A910">
-        <v>500</v>
+        <v>490.42660217005027</v>
       </c>
       <c r="B910">
         <v>500</v>
@@ -7625,7 +7625,7 @@
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A911">
-        <v>500</v>
+        <v>490.00953414470075</v>
       </c>
       <c r="B911">
         <v>500</v>
@@ -7633,7 +7633,7 @@
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A912">
-        <v>500</v>
+        <v>489.75854736759044</v>
       </c>
       <c r="B912">
         <v>500</v>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A913">
-        <v>500</v>
+        <v>489.59735304309226</v>
       </c>
       <c r="B913">
         <v>500</v>
@@ -7649,7 +7649,7 @@
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A914">
-        <v>500</v>
+        <v>489.41619634756552</v>
       </c>
       <c r="B914">
         <v>500</v>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A915">
-        <v>500</v>
+        <v>489.20821610263511</v>
       </c>
       <c r="B915">
         <v>500</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A916">
-        <v>500</v>
+        <v>488.90915162176884</v>
       </c>
       <c r="B916">
         <v>500</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A917">
-        <v>500</v>
+        <v>488.58199453749404</v>
       </c>
       <c r="B917">
         <v>500</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A918">
-        <v>500</v>
+        <v>488.3288734092452</v>
       </c>
       <c r="B918">
         <v>500</v>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A919">
-        <v>500</v>
+        <v>488.12442437526238</v>
       </c>
       <c r="B919">
         <v>500</v>
@@ -7697,7 +7697,7 @@
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A920">
-        <v>500</v>
+        <v>487.82988402228187</v>
       </c>
       <c r="B920">
         <v>500</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A921">
-        <v>500</v>
+        <v>487.67072620869266</v>
       </c>
       <c r="B921">
         <v>500</v>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A922">
-        <v>500</v>
+        <v>487.46991613247405</v>
       </c>
       <c r="B922">
         <v>500</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A923">
-        <v>500</v>
+        <v>487.15534645158596</v>
       </c>
       <c r="B923">
         <v>500</v>
@@ -7729,7 +7729,7 @@
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A924">
-        <v>500</v>
+        <v>486.78381025668807</v>
       </c>
       <c r="B924">
         <v>500</v>
@@ -7737,7 +7737,7 @@
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A925">
-        <v>500</v>
+        <v>486.27790858413886</v>
       </c>
       <c r="B925">
         <v>500</v>
@@ -7745,7 +7745,7 @@
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A926">
-        <v>500</v>
+        <v>485.72444105264896</v>
       </c>
       <c r="B926">
         <v>500</v>
@@ -7753,7 +7753,7 @@
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A927">
-        <v>500</v>
+        <v>485.20261574955538</v>
       </c>
       <c r="B927">
         <v>500</v>
@@ -7761,7 +7761,7 @@
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A928">
-        <v>500</v>
+        <v>484.73103952482904</v>
       </c>
       <c r="B928">
         <v>500</v>
@@ -7769,7 +7769,7 @@
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A929">
-        <v>500</v>
+        <v>484.17921340366502</v>
       </c>
       <c r="B929">
         <v>500</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A930">
-        <v>500</v>
+        <v>483.67250652555191</v>
       </c>
       <c r="B930">
         <v>500</v>
@@ -7785,7 +7785,7 @@
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A931">
-        <v>500</v>
+        <v>483.11609878551218</v>
       </c>
       <c r="B931">
         <v>500</v>
@@ -7793,7 +7793,7 @@
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A932">
-        <v>500</v>
+        <v>482.53410786251175</v>
       </c>
       <c r="B932">
         <v>500</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A933">
-        <v>500</v>
+        <v>481.92403110733289</v>
       </c>
       <c r="B933">
         <v>500</v>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A934">
-        <v>500</v>
+        <v>481.34192180159334</v>
       </c>
       <c r="B934">
         <v>500</v>
@@ -7817,7 +7817,7 @@
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A935">
-        <v>500</v>
+        <v>480.78930079760431</v>
       </c>
       <c r="B935">
         <v>500</v>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A936">
-        <v>500</v>
+        <v>480.27474376584195</v>
       </c>
       <c r="B936">
         <v>500</v>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A937">
-        <v>500</v>
+        <v>479.77359828708097</v>
       </c>
       <c r="B937">
         <v>500</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A938">
-        <v>500</v>
+        <v>479.39696342594084</v>
       </c>
       <c r="B938">
         <v>500</v>
@@ -7849,7 +7849,7 @@
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A939">
-        <v>500</v>
+        <v>478.97098909630319</v>
       </c>
       <c r="B939">
         <v>500</v>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A940">
-        <v>500</v>
+        <v>478.58681496333134</v>
       </c>
       <c r="B940">
         <v>500</v>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A941">
-        <v>500</v>
+        <v>478.24586030070708</v>
       </c>
       <c r="B941">
         <v>500</v>
@@ -7873,7 +7873,7 @@
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A942">
-        <v>500</v>
+        <v>477.92130385481892</v>
       </c>
       <c r="B942">
         <v>500</v>
@@ -7881,7 +7881,7 @@
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A943">
-        <v>500</v>
+        <v>477.51385913841722</v>
       </c>
       <c r="B943">
         <v>500</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A944">
-        <v>500</v>
+        <v>477.0463383906843</v>
       </c>
       <c r="B944">
         <v>500</v>
@@ -7897,7 +7897,7 @@
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A945">
-        <v>500</v>
+        <v>476.82450911666848</v>
       </c>
       <c r="B945">
         <v>500</v>
@@ -7905,7 +7905,7 @@
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A946">
-        <v>500</v>
+        <v>476.83607368221652</v>
       </c>
       <c r="B946">
         <v>500</v>
@@ -7913,7 +7913,7 @@
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A947">
-        <v>500</v>
+        <v>476.87627890537169</v>
       </c>
       <c r="B947">
         <v>500</v>
@@ -7921,7 +7921,7 @@
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A948">
-        <v>500</v>
+        <v>476.97773967462808</v>
       </c>
       <c r="B948">
         <v>500</v>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A949">
-        <v>500</v>
+        <v>477.1223262504011</v>
       </c>
       <c r="B949">
         <v>500</v>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A950">
-        <v>500</v>
+        <v>477.396956245502</v>
       </c>
       <c r="B950">
         <v>500</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A951">
-        <v>500</v>
+        <v>477.69570906471188</v>
       </c>
       <c r="B951">
         <v>500</v>
@@ -7953,7 +7953,7 @@
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A952">
-        <v>500</v>
+        <v>478.07391254774836</v>
       </c>
       <c r="B952">
         <v>500</v>
@@ -7961,7 +7961,7 @@
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A953">
-        <v>500</v>
+        <v>478.42052207377066</v>
       </c>
       <c r="B953">
         <v>500</v>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A954">
-        <v>500</v>
+        <v>478.61394626987823</v>
       </c>
       <c r="B954">
         <v>500</v>
@@ -7977,7 +7977,7 @@
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A955">
-        <v>500</v>
+        <v>478.89250444604448</v>
       </c>
       <c r="B955">
         <v>500</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A956">
-        <v>500</v>
+        <v>479.23420961349962</v>
       </c>
       <c r="B956">
         <v>500</v>
@@ -7993,7 +7993,7 @@
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A957">
-        <v>500</v>
+        <v>479.63296721322268</v>
       </c>
       <c r="B957">
         <v>500</v>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A958">
-        <v>500</v>
+        <v>480.00668277935381</v>
       </c>
       <c r="B958">
         <v>500</v>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A959">
-        <v>500</v>
+        <v>480.33307662898756</v>
       </c>
       <c r="B959">
         <v>500</v>
@@ -8017,7 +8017,7 @@
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A960">
-        <v>500</v>
+        <v>480.73620071265447</v>
       </c>
       <c r="B960">
         <v>500</v>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A961">
-        <v>500</v>
+        <v>481.23110388513811</v>
       </c>
       <c r="B961">
         <v>500</v>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A962">
-        <v>500</v>
+        <v>481.75921118273141</v>
       </c>
       <c r="B962">
         <v>500</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A963">
-        <v>500</v>
+        <v>482.36689977715167</v>
       </c>
       <c r="B963">
         <v>500</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A964">
-        <v>500</v>
+        <v>482.99845281446125</v>
       </c>
       <c r="B964">
         <v>500</v>
@@ -8057,7 +8057,7 @@
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A965">
-        <v>500</v>
+        <v>483.5485781922124</v>
       </c>
       <c r="B965">
         <v>500</v>
@@ -8065,7 +8065,7 @@
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A966">
-        <v>500</v>
+        <v>484.09967598152093</v>
       </c>
       <c r="B966">
         <v>500</v>
@@ -8073,7 +8073,7 @@
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A967">
-        <v>500</v>
+        <v>484.67825712855182</v>
       </c>
       <c r="B967">
         <v>500</v>
@@ -8081,7 +8081,7 @@
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A968">
-        <v>500</v>
+        <v>485.30572297605818</v>
       </c>
       <c r="B968">
         <v>500</v>
@@ -8089,7 +8089,7 @@
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A969">
-        <v>500</v>
+        <v>486.01210098079389</v>
       </c>
       <c r="B969">
         <v>500</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A970">
-        <v>500</v>
+        <v>486.82904567095483</v>
       </c>
       <c r="B970">
         <v>500</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A971">
-        <v>500</v>
+        <v>487.61710638353202</v>
       </c>
       <c r="B971">
         <v>500</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A972">
-        <v>500</v>
+        <v>488.43899347140547</v>
       </c>
       <c r="B972">
         <v>500</v>
@@ -8121,7 +8121,7 @@
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A973">
-        <v>500</v>
+        <v>489.25290437665353</v>
       </c>
       <c r="B973">
         <v>500</v>
@@ -8129,7 +8129,7 @@
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A974">
-        <v>500</v>
+        <v>490.17514101057498</v>
       </c>
       <c r="B974">
         <v>500</v>
@@ -8137,7 +8137,7 @@
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A975">
-        <v>500</v>
+        <v>490.96730217703811</v>
       </c>
       <c r="B975">
         <v>500</v>
@@ -8145,7 +8145,7 @@
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A976">
-        <v>500</v>
+        <v>491.84101247214329</v>
       </c>
       <c r="B976">
         <v>500</v>
@@ -8153,7 +8153,7 @@
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A977">
-        <v>500</v>
+        <v>492.835315577941</v>
       </c>
       <c r="B977">
         <v>500</v>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A978">
-        <v>500</v>
+        <v>493.79523246747397</v>
       </c>
       <c r="B978">
         <v>500</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A979">
-        <v>500</v>
+        <v>494.67401796004543</v>
       </c>
       <c r="B979">
         <v>500</v>
@@ -8177,7 +8177,7 @@
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A980">
-        <v>500</v>
+        <v>495.60241302562997</v>
       </c>
       <c r="B980">
         <v>500</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A981">
-        <v>500</v>
+        <v>496.58841485602193</v>
       </c>
       <c r="B981">
         <v>500</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A982">
-        <v>500</v>
+        <v>497.76741000695108</v>
       </c>
       <c r="B982">
         <v>500</v>
@@ -8201,7 +8201,7 @@
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A983">
-        <v>500</v>
+        <v>498.97014417165053</v>
       </c>
       <c r="B983">
         <v>500</v>

--- a/OutputData.xlsx
+++ b/OutputData.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Important\Paper Codes\Particle Filter code\Matlab\particle filter 8\"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -345,2447 +345,2447 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>347.66433646777023</v>
+        <v>406.90101660249184</v>
       </c>
       <c r="B1">
-        <v>51.855510439113523</v>
+        <v>452.63670793954697</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>348.46707194756931</v>
+        <v>406.79983586852734</v>
       </c>
       <c r="B2">
-        <v>51.818574682422131</v>
+        <v>453.37115643749877</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>349.31380952501496</v>
+        <v>406.62614214305484</v>
       </c>
       <c r="B3">
-        <v>51.876477116954632</v>
+        <v>454.12799624564184</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>350.14245887815605</v>
+        <v>406.42638727461747</v>
       </c>
       <c r="B4">
-        <v>51.903895297499204</v>
+        <v>454.8802135995943</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>350.94063904382722</v>
+        <v>406.1902323632778</v>
       </c>
       <c r="B5">
-        <v>51.913401654302433</v>
+        <v>455.69506636355453</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>351.67120204619442</v>
+        <v>405.79907710411396</v>
       </c>
       <c r="B6">
-        <v>51.908127291279612</v>
+        <v>456.38982949289607</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>352.4113946059345</v>
+        <v>405.3872657347639</v>
       </c>
       <c r="B7">
-        <v>51.908734635803313</v>
+        <v>457.18855736841425</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>353.19374950081402</v>
+        <v>405.00133181122476</v>
       </c>
       <c r="B8">
-        <v>51.92303735319382</v>
+        <v>458.11975887004922</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>354.00777390184851</v>
+        <v>404.76001242245457</v>
       </c>
       <c r="B9">
-        <v>51.934302746939856</v>
+        <v>459.126782622441</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>354.83159496963776</v>
+        <v>404.58898416425825</v>
       </c>
       <c r="B10">
-        <v>51.986026736494395</v>
+        <v>460.14022301169769</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>355.71302550143946</v>
+        <v>404.41998993601476</v>
       </c>
       <c r="B11">
-        <v>52.048425456301459</v>
+        <v>461.18441812981121</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>356.63186560067288</v>
+        <v>404.37514152220973</v>
       </c>
       <c r="B12">
-        <v>52.079880553034499</v>
+        <v>462.22360336759505</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>357.71289244853892</v>
+        <v>404.36097603994364</v>
       </c>
       <c r="B13">
-        <v>52.096372466983347</v>
+        <v>463.30639923128297</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>358.81277820609455</v>
+        <v>404.36165851577454</v>
       </c>
       <c r="B14">
-        <v>52.181924911723691</v>
+        <v>464.40386139448464</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>359.94868716005664</v>
+        <v>404.32374077623052</v>
       </c>
       <c r="B15">
-        <v>52.346189667421442</v>
+        <v>465.71474779766396</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>360.961148963315</v>
+        <v>404.31302990792193</v>
       </c>
       <c r="B16">
-        <v>52.567404268177881</v>
+        <v>467.01611941182762</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>361.94570332696793</v>
+        <v>404.35959328885514</v>
       </c>
       <c r="B17">
-        <v>52.80215657565288</v>
+        <v>468.26433010005746</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>362.94850971561499</v>
+        <v>404.39180124616183</v>
       </c>
       <c r="B18">
-        <v>52.987941630929967</v>
+        <v>469.50620753566693</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>363.89954791505113</v>
+        <v>404.47478610533608</v>
       </c>
       <c r="B19">
-        <v>53.308242225306564</v>
+        <v>470.71548669129908</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>364.88719629554976</v>
+        <v>404.51743321946378</v>
       </c>
       <c r="B20">
-        <v>53.770682860003092</v>
+        <v>471.99499495938232</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>365.83713724678285</v>
+        <v>404.66189308391984</v>
       </c>
       <c r="B21">
-        <v>54.205311423694731</v>
+        <v>473.2589351827225</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>366.90010792238769</v>
+        <v>404.77059923690001</v>
       </c>
       <c r="B22">
-        <v>54.494188379207159</v>
+        <v>474.47808363576638</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>368.11170989689663</v>
+        <v>405.04728751042541</v>
       </c>
       <c r="B23">
-        <v>54.738809780838331</v>
+        <v>475.70471373855349</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>369.41823781129517</v>
+        <v>405.4131107688678</v>
       </c>
       <c r="B24">
-        <v>54.888587387055544</v>
+        <v>476.84252002434249</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>370.74314747552603</v>
+        <v>405.69777476131384</v>
       </c>
       <c r="B25">
-        <v>54.955769660697349</v>
+        <v>478.13782934645297</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>371.96789703466396</v>
+        <v>405.86761971247961</v>
       </c>
       <c r="B26">
-        <v>55.084445844107108</v>
+        <v>479.55501044839383</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>373.20055346169102</v>
+        <v>406.09414907826368</v>
       </c>
       <c r="B27">
-        <v>55.261329398560562</v>
+        <v>481.04270670341384</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>374.35151098181274</v>
+        <v>406.36873088932748</v>
       </c>
       <c r="B28">
-        <v>55.415898532251582</v>
+        <v>482.5806376755346</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>375.54685206035367</v>
+        <v>406.59375017568942</v>
       </c>
       <c r="B29">
-        <v>55.458193322474152</v>
+        <v>484.01951910460457</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>376.74899391961014</v>
+        <v>406.7285353530537</v>
       </c>
       <c r="B30">
-        <v>55.511528218141734</v>
+        <v>485.39882622845317</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>377.88945238606209</v>
+        <v>406.81882779047822</v>
       </c>
       <c r="B31">
-        <v>55.707181675663421</v>
+        <v>486.6911388834547</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>379.06751452090924</v>
+        <v>406.78439026792688</v>
       </c>
       <c r="B32">
-        <v>55.926926142231309</v>
+        <v>488.02424779956095</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>380.21603770804631</v>
+        <v>406.80290124436522</v>
       </c>
       <c r="B33">
-        <v>56.173702920074277</v>
+        <v>489.40462141150368</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>381.30590985673786</v>
+        <v>406.90482313377834</v>
       </c>
       <c r="B34">
-        <v>56.451992931644909</v>
+        <v>490.91716128888834</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>382.31454581779565</v>
+        <v>407.08464306428004</v>
       </c>
       <c r="B35">
-        <v>56.79558201774757</v>
+        <v>492.35865078970625</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>383.3999420925137</v>
+        <v>407.16579920146341</v>
       </c>
       <c r="B36">
-        <v>57.165783368182957</v>
+        <v>493.6909976658647</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>384.39446287310636</v>
+        <v>407.14887735489503</v>
       </c>
       <c r="B37">
-        <v>57.521976527023078</v>
+        <v>495.06102799948394</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>385.38943765036515</v>
+        <v>407.16323410911826</v>
       </c>
       <c r="B38">
-        <v>57.926784152712401</v>
+        <v>496.44944394771238</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>386.50363098070119</v>
+        <v>407.30121304781318</v>
       </c>
       <c r="B39">
-        <v>58.266440139777629</v>
+        <v>497.80997022205656</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>387.7837829140496</v>
+        <v>407.40957467105392</v>
       </c>
       <c r="B40">
-        <v>58.479234920857081</v>
+        <v>499.0774800920521</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>389.22723789807696</v>
+        <v>407.45468130611488</v>
       </c>
       <c r="B41">
-        <v>58.859357663047071</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>390.8111481220929</v>
+        <v>407.70282457535842</v>
       </c>
       <c r="B42">
-        <v>59.405531495733925</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>392.37827109543446</v>
+        <v>408.10173956064216</v>
       </c>
       <c r="B43">
-        <v>60.031361363223041</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>393.90149652132664</v>
+        <v>408.55840508114233</v>
       </c>
       <c r="B44">
-        <v>60.547907082343251</v>
+        <v>500</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>395.40707633304663</v>
+        <v>408.99289093507633</v>
       </c>
       <c r="B45">
-        <v>60.970800500265817</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>397.04213852382065</v>
+        <v>409.41411243125259</v>
       </c>
       <c r="B46">
-        <v>61.400339013115776</v>
+        <v>500</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>398.75666130013968</v>
+        <v>409.67104577297857</v>
       </c>
       <c r="B47">
-        <v>61.776146596802462</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>400.38749190250923</v>
+        <v>409.9544342318149</v>
       </c>
       <c r="B48">
-        <v>62.259765152821331</v>
+        <v>500</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>401.99500272704739</v>
+        <v>410.33874588745357</v>
       </c>
       <c r="B49">
-        <v>62.766441528765327</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>403.53755687300259</v>
+        <v>410.8588493010061</v>
       </c>
       <c r="B50">
-        <v>63.253630910501165</v>
+        <v>500</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>405.07646035897505</v>
+        <v>411.36357988776444</v>
       </c>
       <c r="B51">
-        <v>63.671232805085296</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>406.63593283343596</v>
+        <v>411.79375677284412</v>
       </c>
       <c r="B52">
-        <v>64.00480033311581</v>
+        <v>500</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>408.10417453814011</v>
+        <v>412.21582383911715</v>
       </c>
       <c r="B53">
-        <v>64.234394045504658</v>
+        <v>500</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>409.48577437057611</v>
+        <v>412.61001268895649</v>
       </c>
       <c r="B54">
-        <v>64.479281395187769</v>
+        <v>500</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>410.88544672394858</v>
+        <v>413.04787440361406</v>
       </c>
       <c r="B55">
-        <v>64.715070053697417</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>412.33978388419371</v>
+        <v>413.55077092699116</v>
       </c>
       <c r="B56">
-        <v>64.937441592865696</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>413.7910082467742</v>
+        <v>413.96009623758289</v>
       </c>
       <c r="B57">
-        <v>65.088760649634395</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>415.26372592255518</v>
+        <v>414.33428254336786</v>
       </c>
       <c r="B58">
-        <v>65.130114142442437</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>416.78816087953044</v>
+        <v>414.69154065646882</v>
       </c>
       <c r="B59">
-        <v>65.061018066610259</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>418.33595509166793</v>
+        <v>415.0200303788294</v>
       </c>
       <c r="B60">
-        <v>65.021691073251787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>419.90664781663145</v>
+        <v>415.45021227123885</v>
       </c>
       <c r="B61">
-        <v>65.061473299122923</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>421.53715703089642</v>
+        <v>415.78679497570101</v>
       </c>
       <c r="B62">
-        <v>65.161491012845246</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>423.21212533022657</v>
+        <v>415.99765953508899</v>
       </c>
       <c r="B63">
-        <v>65.238812979260061</v>
+        <v>500</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>424.96520986475832</v>
+        <v>416.11996306124172</v>
       </c>
       <c r="B64">
-        <v>65.292341328307415</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>426.78918644466108</v>
+        <v>416.0063163751571</v>
       </c>
       <c r="B65">
-        <v>65.294839185497764</v>
+        <v>500</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>428.61315621399774</v>
+        <v>415.8795972733563</v>
       </c>
       <c r="B66">
-        <v>65.230706824395796</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>430.40642990107756</v>
+        <v>415.74451337610401</v>
       </c>
       <c r="B67">
-        <v>65.13015027570205</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>432.19823636270547</v>
+        <v>415.66964322559159</v>
       </c>
       <c r="B68">
-        <v>64.985443310448957</v>
+        <v>500</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>433.94393018542081</v>
+        <v>415.52511771958621</v>
       </c>
       <c r="B69">
-        <v>64.824028737221553</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>435.77465999340524</v>
+        <v>415.39990461326846</v>
       </c>
       <c r="B70">
-        <v>64.732057830575229</v>
+        <v>500</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>437.74907646574189</v>
+        <v>415.16609074431898</v>
       </c>
       <c r="B71">
-        <v>64.631377772660201</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>439.71390368900461</v>
+        <v>414.9049024011656</v>
       </c>
       <c r="B72">
-        <v>64.624978294330347</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>441.69431159486504</v>
+        <v>414.69586750784379</v>
       </c>
       <c r="B73">
-        <v>64.763837423442865</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>443.58758172694252</v>
+        <v>414.57493998253301</v>
       </c>
       <c r="B74">
-        <v>65.070813596302074</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>445.53650322089544</v>
+        <v>414.48532767608236</v>
       </c>
       <c r="B75">
-        <v>65.38578261777333</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>447.56695545080265</v>
+        <v>414.53215095074898</v>
       </c>
       <c r="B76">
-        <v>65.606337434225836</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>449.6081102527894</v>
+        <v>414.61832845596183</v>
       </c>
       <c r="B77">
-        <v>65.975716470818611</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>451.63298752784112</v>
+        <v>414.73429569727836</v>
       </c>
       <c r="B78">
-        <v>66.285542185488794</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>453.62456768998697</v>
+        <v>414.84123760010237</v>
       </c>
       <c r="B79">
-        <v>66.553638345212846</v>
+        <v>500</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>455.69636976023548</v>
+        <v>414.95652235471323</v>
       </c>
       <c r="B80">
-        <v>66.799754251968821</v>
+        <v>500</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>457.81209116059216</v>
+        <v>414.99731490103107</v>
       </c>
       <c r="B81">
-        <v>67.142013563820754</v>
+        <v>500</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>459.98805059129722</v>
+        <v>415.00060298673418</v>
       </c>
       <c r="B82">
-        <v>67.504513519657877</v>
+        <v>500</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>462.08895247356264</v>
+        <v>415.04311318773296</v>
       </c>
       <c r="B83">
-        <v>67.936848354673856</v>
+        <v>500</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>464.16005912392683</v>
+        <v>415.04439891159222</v>
       </c>
       <c r="B84">
-        <v>68.448454688182863</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>466.26825186302113</v>
+        <v>414.95606252212804</v>
       </c>
       <c r="B85">
-        <v>68.841429272718074</v>
+        <v>500</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>468.27028374183146</v>
+        <v>414.88197944615104</v>
       </c>
       <c r="B86">
-        <v>69.168692459992272</v>
+        <v>500</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>470.34713194287735</v>
+        <v>414.88367697116729</v>
       </c>
       <c r="B87">
-        <v>69.418660679565789</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>472.50648496862789</v>
+        <v>414.87196526667304</v>
       </c>
       <c r="B88">
-        <v>69.642961725148041</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>474.62276038280078</v>
+        <v>414.71245307114776</v>
       </c>
       <c r="B89">
-        <v>69.849052244133446</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>476.80818541605902</v>
+        <v>414.46840225476495</v>
       </c>
       <c r="B90">
-        <v>70.021780908958803</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>479.11558008297135</v>
+        <v>414.27099870758207</v>
       </c>
       <c r="B91">
-        <v>70.2935940612807</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>481.36287753442355</v>
+        <v>414.17179883278908</v>
       </c>
       <c r="B92">
-        <v>70.614423087409662</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>483.65420633938703</v>
+        <v>413.98239618862902</v>
       </c>
       <c r="B93">
-        <v>71.00566770715615</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>486.05191372844712</v>
+        <v>413.80094147313173</v>
       </c>
       <c r="B94">
-        <v>71.291122569183315</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>488.48133512702731</v>
+        <v>413.64871008390253</v>
       </c>
       <c r="B95">
-        <v>71.386739056183842</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>491.00370575591404</v>
+        <v>413.45993735684817</v>
       </c>
       <c r="B96">
-        <v>71.449303614368347</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>493.61249061990412</v>
+        <v>413.31519280025901</v>
       </c>
       <c r="B97">
-        <v>71.457298557417758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>496.04785126549717</v>
+        <v>413.32670449225407</v>
       </c>
       <c r="B98">
-        <v>71.357675593215589</v>
+        <v>500</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>498.43945397843191</v>
+        <v>413.28656529802305</v>
       </c>
       <c r="B99">
-        <v>71.324270243853377</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>500</v>
+        <v>413.35040487084012</v>
       </c>
       <c r="B100">
-        <v>71.513025275375171</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>500</v>
+        <v>413.33868089985606</v>
       </c>
       <c r="B101">
-        <v>71.619016327279326</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>500</v>
+        <v>413.45605740345377</v>
       </c>
       <c r="B102">
-        <v>71.732596984043241</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>500</v>
+        <v>413.67038498329941</v>
       </c>
       <c r="B103">
-        <v>71.797043524544037</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>500</v>
+        <v>413.81533538417159</v>
       </c>
       <c r="B104">
-        <v>71.90834444895205</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>500</v>
+        <v>413.97799981568744</v>
       </c>
       <c r="B105">
-        <v>72.008341378712529</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>500</v>
+        <v>414.2636047126532</v>
       </c>
       <c r="B106">
-        <v>72.063605964848463</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>500</v>
+        <v>414.51970550924506</v>
       </c>
       <c r="B107">
-        <v>72.070644698177446</v>
+        <v>500</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>500</v>
+        <v>414.67529972686532</v>
       </c>
       <c r="B108">
-        <v>72.10683947523043</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>500</v>
+        <v>414.86963990694477</v>
       </c>
       <c r="B109">
-        <v>72.272602852707237</v>
+        <v>500</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>500</v>
+        <v>415.01442429857246</v>
       </c>
       <c r="B110">
-        <v>72.395331586389858</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>500</v>
+        <v>415.11012396122999</v>
       </c>
       <c r="B111">
-        <v>72.378936185469428</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>500</v>
+        <v>415.1910163642799</v>
       </c>
       <c r="B112">
-        <v>72.285255023431304</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>500</v>
+        <v>415.1221330341574</v>
       </c>
       <c r="B113">
-        <v>72.097256643836587</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>500</v>
+        <v>415.11267876193284</v>
       </c>
       <c r="B114">
-        <v>71.918211460948967</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>500</v>
+        <v>415.08291217953717</v>
       </c>
       <c r="B115">
-        <v>71.83773783351765</v>
+        <v>500</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>500</v>
+        <v>415.05379849423133</v>
       </c>
       <c r="B116">
-        <v>71.831208877266064</v>
+        <v>500</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>500</v>
+        <v>414.97799050631625</v>
       </c>
       <c r="B117">
-        <v>71.90990217023365</v>
+        <v>500</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>500</v>
+        <v>414.86946969094481</v>
       </c>
       <c r="B118">
-        <v>72.067099438297475</v>
+        <v>499.94464895027392</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>500</v>
+        <v>414.72852643041398</v>
       </c>
       <c r="B119">
-        <v>72.348453701875428</v>
+        <v>499.79835572500804</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>500</v>
+        <v>414.41831011486642</v>
       </c>
       <c r="B120">
-        <v>72.515811321186348</v>
+        <v>499.85415777604914</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>500</v>
+        <v>414.12010570909132</v>
       </c>
       <c r="B121">
-        <v>72.638342971088548</v>
+        <v>499.90406583037475</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>500</v>
+        <v>413.61115650668143</v>
       </c>
       <c r="B122">
-        <v>72.76989842917196</v>
+        <v>499.86974639767999</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>500</v>
+        <v>413.16825514947834</v>
       </c>
       <c r="B123">
-        <v>72.845376454300194</v>
+        <v>499.86354426471109</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>500</v>
+        <v>412.87174548630628</v>
       </c>
       <c r="B124">
-        <v>73.09205916664807</v>
+        <v>499.81631246876435</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>500</v>
+        <v>412.66928064240489</v>
       </c>
       <c r="B125">
-        <v>73.536343462270409</v>
+        <v>499.63239606468181</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>500</v>
+        <v>412.53957891720393</v>
       </c>
       <c r="B126">
-        <v>73.971439606392565</v>
+        <v>499.41649115854784</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>500</v>
+        <v>412.36463933582388</v>
       </c>
       <c r="B127">
-        <v>74.3676544817218</v>
+        <v>499.17569944169986</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>500</v>
+        <v>412.18274380772419</v>
       </c>
       <c r="B128">
-        <v>74.561881481076654</v>
+        <v>498.98471061713911</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>500</v>
+        <v>412.05579789067627</v>
       </c>
       <c r="B129">
-        <v>74.899310400132208</v>
+        <v>498.62642481630769</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>500</v>
+        <v>411.93229953125882</v>
       </c>
       <c r="B130">
-        <v>75.310138152503654</v>
+        <v>498.14974490030244</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>500</v>
+        <v>411.73017975064289</v>
       </c>
       <c r="B131">
-        <v>75.712591099112032</v>
+        <v>497.64554057599702</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>500</v>
+        <v>411.51913045494507</v>
       </c>
       <c r="B132">
-        <v>76.12422278172042</v>
+        <v>497.20201419448887</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>500</v>
+        <v>411.3223093090669</v>
       </c>
       <c r="B133">
-        <v>76.653382655130358</v>
+        <v>496.72660842608957</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>500</v>
+        <v>411.24499119777738</v>
       </c>
       <c r="B134">
-        <v>77.212736434012953</v>
+        <v>496.15772755119502</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>500</v>
+        <v>411.21737782959246</v>
       </c>
       <c r="B135">
-        <v>77.711320794930799</v>
+        <v>495.54876958796888</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>500</v>
+        <v>411.17363961392704</v>
       </c>
       <c r="B136">
-        <v>78.251123836145567</v>
+        <v>495.08844732920244</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>500</v>
+        <v>411.3012326516232</v>
       </c>
       <c r="B137">
-        <v>78.825729820005591</v>
+        <v>494.72990616517126</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>500</v>
+        <v>411.54101082214009</v>
       </c>
       <c r="B138">
-        <v>79.550892619744957</v>
+        <v>494.44032791132281</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>500</v>
+        <v>411.8636966470844</v>
       </c>
       <c r="B139">
-        <v>80.35763637246103</v>
+        <v>494.17883633172636</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>500</v>
+        <v>412.12866005105286</v>
       </c>
       <c r="B140">
-        <v>81.192207200500363</v>
+        <v>493.95199390193</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>500</v>
+        <v>412.41772001384402</v>
       </c>
       <c r="B141">
-        <v>82.010917819033779</v>
+        <v>493.80065004601556</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>500</v>
+        <v>412.71888100444318</v>
       </c>
       <c r="B142">
-        <v>82.836666957292948</v>
+        <v>493.62779237377401</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>500</v>
+        <v>413.07646093522072</v>
       </c>
       <c r="B143">
-        <v>83.676571746067026</v>
+        <v>493.48398538367593</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>500</v>
+        <v>413.49857909359099</v>
       </c>
       <c r="B144">
-        <v>84.683641922280458</v>
+        <v>493.39543694541157</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>500</v>
+        <v>413.96338894670697</v>
       </c>
       <c r="B145">
-        <v>85.708690283336821</v>
+        <v>493.37653965478086</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>500</v>
+        <v>414.46793868837563</v>
       </c>
       <c r="B146">
-        <v>86.65307406662231</v>
+        <v>493.42088580489934</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>500</v>
+        <v>414.97461507147233</v>
       </c>
       <c r="B147">
-        <v>87.598888420849875</v>
+        <v>493.40951812855513</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>500</v>
+        <v>415.3691362694334</v>
       </c>
       <c r="B148">
-        <v>88.653477702607304</v>
+        <v>493.2963764022391</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>500</v>
+        <v>415.66126047415923</v>
       </c>
       <c r="B149">
-        <v>89.674076469184286</v>
+        <v>493.24939715197394</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>500</v>
+        <v>415.96458924493015</v>
       </c>
       <c r="B150">
-        <v>90.753054506190381</v>
+        <v>493.3908982581392</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>500</v>
+        <v>416.2982807833846</v>
       </c>
       <c r="B151">
-        <v>91.800420876248253</v>
+        <v>493.51578164059418</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>500</v>
+        <v>416.59181448510094</v>
       </c>
       <c r="B152">
-        <v>92.974228641293777</v>
+        <v>493.48879003615514</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>500</v>
+        <v>416.84852898641753</v>
       </c>
       <c r="B153">
-        <v>94.051538000085401</v>
+        <v>493.40035755078839</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>500</v>
+        <v>417.11693634191488</v>
       </c>
       <c r="B154">
-        <v>95.198146090384867</v>
+        <v>493.30288818369979</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>500</v>
+        <v>417.35846246754039</v>
       </c>
       <c r="B155">
-        <v>96.400436645559225</v>
+        <v>493.21368784709762</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>500</v>
+        <v>417.5233208303182</v>
       </c>
       <c r="B156">
-        <v>97.720025598604806</v>
+        <v>493.08837281080787</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>500</v>
+        <v>417.83280552025468</v>
       </c>
       <c r="B157">
-        <v>99.077464204659009</v>
+        <v>493.03414548702131</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>500</v>
+        <v>418.1870928105871</v>
       </c>
       <c r="B158">
-        <v>100.41652294020176</v>
+        <v>493.08814075177196</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>500</v>
+        <v>418.5182702250703</v>
       </c>
       <c r="B159">
-        <v>101.85000554502457</v>
+        <v>493.11971927894899</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>500</v>
+        <v>418.85072802552696</v>
       </c>
       <c r="B160">
-        <v>103.18619142738198</v>
+        <v>493.17158555211904</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>500</v>
+        <v>419.21757617477749</v>
       </c>
       <c r="B161">
-        <v>104.53482533083044</v>
+        <v>493.10260995723627</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>500</v>
+        <v>419.51515415574096</v>
       </c>
       <c r="B162">
-        <v>105.85748217210153</v>
+        <v>493.02457176115411</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>500</v>
+        <v>419.81472959694435</v>
       </c>
       <c r="B163">
-        <v>107.2287851266111</v>
+        <v>493.04698141287918</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>500</v>
+        <v>420.11083072698847</v>
       </c>
       <c r="B164">
-        <v>108.53404324489968</v>
+        <v>493.12094082508412</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>500</v>
+        <v>420.45747423072339</v>
       </c>
       <c r="B165">
-        <v>109.75513355579768</v>
+        <v>493.19765756746767</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>500</v>
+        <v>420.81443242909279</v>
       </c>
       <c r="B166">
-        <v>111.0867271075771</v>
+        <v>493.27083391781736</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>500</v>
+        <v>421.21461020873664</v>
       </c>
       <c r="B167">
-        <v>112.4329565593</v>
+        <v>493.39986788445816</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>500</v>
+        <v>421.69545421292202</v>
       </c>
       <c r="B168">
-        <v>113.89494201591278</v>
+        <v>493.50456124044655</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>500</v>
+        <v>422.16322983523105</v>
       </c>
       <c r="B169">
-        <v>115.46674616755035</v>
+        <v>493.59389041410606</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>500</v>
+        <v>422.44808955345206</v>
       </c>
       <c r="B170">
-        <v>117.23105395530368</v>
+        <v>493.76912811243272</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>500</v>
+        <v>422.60017699023166</v>
       </c>
       <c r="B171">
-        <v>119.12942338318976</v>
+        <v>493.76518693375516</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>500</v>
+        <v>422.71864443524083</v>
       </c>
       <c r="B172">
-        <v>121.09187819889229</v>
+        <v>493.87662432071704</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>500</v>
+        <v>422.77117204178842</v>
       </c>
       <c r="B173">
-        <v>122.98730291226747</v>
+        <v>494.13227955866142</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>500</v>
+        <v>422.88443261708801</v>
       </c>
       <c r="B174">
-        <v>124.83240877352029</v>
+        <v>494.30694509953116</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>500</v>
+        <v>422.86511968890147</v>
       </c>
       <c r="B175">
-        <v>126.68178936751424</v>
+        <v>494.50976865120464</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>500</v>
+        <v>422.81898085007879</v>
       </c>
       <c r="B176">
-        <v>128.40690425378872</v>
+        <v>494.7134233760533</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>500</v>
+        <v>422.87651979514999</v>
       </c>
       <c r="B177">
-        <v>130.06233433374095</v>
+        <v>494.87484723340776</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>500</v>
+        <v>422.96849641175965</v>
       </c>
       <c r="B178">
-        <v>131.7400701418577</v>
+        <v>494.97834317841949</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>500</v>
+        <v>422.86696489028316</v>
       </c>
       <c r="B179">
-        <v>133.6054167859555</v>
+        <v>495.00321382108081</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>500</v>
+        <v>422.57243966200042</v>
       </c>
       <c r="B180">
-        <v>135.5866488247992</v>
+        <v>495.00884179183919</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>500</v>
+        <v>422.2768053698635</v>
       </c>
       <c r="B181">
-        <v>137.73944415941116</v>
+        <v>494.95406078657277</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>500</v>
+        <v>421.81451762963599</v>
       </c>
       <c r="B182">
-        <v>139.88553420562474</v>
+        <v>494.87435779577766</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>500</v>
+        <v>421.24835125448493</v>
       </c>
       <c r="B183">
-        <v>142.01003074457137</v>
+        <v>494.64783515263753</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>500</v>
+        <v>420.50437218534756</v>
       </c>
       <c r="B184">
-        <v>144.15341483887849</v>
+        <v>494.39961680441166</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>500</v>
+        <v>419.71047398672232</v>
       </c>
       <c r="B185">
-        <v>146.2445185808636</v>
+        <v>494.36975908477893</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>500</v>
+        <v>418.98517827498443</v>
       </c>
       <c r="B186">
-        <v>148.27555852041544</v>
+        <v>494.45769788004804</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>500</v>
+        <v>418.32703183547653</v>
       </c>
       <c r="B187">
-        <v>150.29067524048344</v>
+        <v>494.59792906337668</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>500</v>
+        <v>417.58389652023567</v>
       </c>
       <c r="B188">
-        <v>152.40836276182563</v>
+        <v>494.74734737580843</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>500</v>
+        <v>416.89389303927732</v>
       </c>
       <c r="B189">
-        <v>154.52328018835587</v>
+        <v>495.01106578897947</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>500</v>
+        <v>416.26884698284806</v>
       </c>
       <c r="B190">
-        <v>156.7249618403512</v>
+        <v>495.21639361072982</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>500</v>
+        <v>415.60013460310427</v>
       </c>
       <c r="B191">
-        <v>158.89038982069945</v>
+        <v>495.30643795379615</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>500</v>
+        <v>414.9867981736719</v>
       </c>
       <c r="B192">
-        <v>161.14226800101679</v>
+        <v>495.29995569901359</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>500</v>
+        <v>414.41872856247267</v>
       </c>
       <c r="B193">
-        <v>163.38326601983391</v>
+        <v>495.23053768623589</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>500</v>
+        <v>413.81414093135072</v>
       </c>
       <c r="B194">
-        <v>165.48384095284891</v>
+        <v>495.20373953206177</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>500</v>
+        <v>413.20181750194746</v>
       </c>
       <c r="B195">
-        <v>167.68635577575506</v>
+        <v>495.29431973301337</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>500</v>
+        <v>412.57476727409761</v>
       </c>
       <c r="B196">
-        <v>170.1140011726778</v>
+        <v>495.43170430599133</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>500</v>
+        <v>411.85508500572723</v>
       </c>
       <c r="B197">
-        <v>172.5172533693036</v>
+        <v>495.62029458104263</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>500</v>
+        <v>411.07020920929733</v>
       </c>
       <c r="B198">
-        <v>174.86367039032078</v>
+        <v>495.79150906722111</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>500</v>
+        <v>410.15423594324903</v>
       </c>
       <c r="B199">
-        <v>177.22868574540868</v>
+        <v>495.96428332718148</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>500</v>
+        <v>409.20965724704763</v>
       </c>
       <c r="B200">
-        <v>179.61512736777166</v>
+        <v>496.16099921976587</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>500</v>
+        <v>408.2220236348939</v>
       </c>
       <c r="B201">
-        <v>182.08877181818869</v>
+        <v>496.45238591902921</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>500</v>
+        <v>407.32238170156177</v>
       </c>
       <c r="B202">
-        <v>184.61216660569031</v>
+        <v>496.88910616797557</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>500</v>
+        <v>406.42726073979418</v>
       </c>
       <c r="B203">
-        <v>187.13464006125403</v>
+        <v>497.4228086028736</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>500</v>
+        <v>405.48891103370727</v>
       </c>
       <c r="B204">
-        <v>189.60799770244662</v>
+        <v>497.92228815064885</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>500</v>
+        <v>404.44702088422048</v>
       </c>
       <c r="B205">
-        <v>192.13039649729942</v>
+        <v>498.46413419227235</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>500</v>
+        <v>403.44021295378951</v>
       </c>
       <c r="B206">
-        <v>194.69093977107011</v>
+        <v>499.06256836931408</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>500</v>
+        <v>402.45686406920629</v>
       </c>
       <c r="B207">
-        <v>197.18734126256098</v>
+        <v>499.67404445667995</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>500</v>
+        <v>401.52841757040943</v>
       </c>
       <c r="B208">
-        <v>199.60284034848229</v>
+        <v>500</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>500</v>
+        <v>400.67891060765584</v>
       </c>
       <c r="B209">
-        <v>201.92393143763664</v>
+        <v>500</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>500</v>
+        <v>399.73681921090582</v>
       </c>
       <c r="B210">
-        <v>204.24479934340548</v>
+        <v>500</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>500</v>
+        <v>398.76617847891748</v>
       </c>
       <c r="B211">
-        <v>206.55922452755939</v>
+        <v>500</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>500</v>
+        <v>397.92128016183261</v>
       </c>
       <c r="B212">
-        <v>208.9465336977126</v>
+        <v>500</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>500</v>
+        <v>396.9920020730089</v>
       </c>
       <c r="B213">
-        <v>211.31333594393078</v>
+        <v>500</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>500</v>
+        <v>396.08524525082748</v>
       </c>
       <c r="B214">
-        <v>213.76977226150535</v>
+        <v>500</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>500</v>
+        <v>395.11587431546417</v>
       </c>
       <c r="B215">
-        <v>216.19316296678173</v>
+        <v>500</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>500</v>
+        <v>393.98039077004108</v>
       </c>
       <c r="B216">
-        <v>218.33130787313888</v>
+        <v>500</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217">
-        <v>500</v>
+        <v>392.91791529130649</v>
       </c>
       <c r="B217">
-        <v>220.25850682418087</v>
+        <v>500</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218">
-        <v>500</v>
+        <v>391.96534670525597</v>
       </c>
       <c r="B218">
-        <v>222.20669904932279</v>
+        <v>500</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>500</v>
+        <v>391.0241645447411</v>
       </c>
       <c r="B219">
-        <v>224.06553619891437</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220">
-        <v>500</v>
+        <v>390.22991797695551</v>
       </c>
       <c r="B220">
-        <v>225.92744657874522</v>
+        <v>500</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221">
-        <v>500</v>
+        <v>389.43937612251199</v>
       </c>
       <c r="B221">
-        <v>227.81502727609799</v>
+        <v>500</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222">
-        <v>500</v>
+        <v>388.65853038768313</v>
       </c>
       <c r="B222">
-        <v>229.72435816562833</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223">
-        <v>500</v>
+        <v>387.97660092398473</v>
       </c>
       <c r="B223">
-        <v>231.62967227828261</v>
+        <v>500</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224">
-        <v>500</v>
+        <v>387.30183425378095</v>
       </c>
       <c r="B224">
-        <v>233.48960465813536</v>
+        <v>500</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225">
-        <v>500</v>
+        <v>386.6363739277341</v>
       </c>
       <c r="B225">
-        <v>235.46697744473457</v>
+        <v>500</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>500</v>
+        <v>385.88474484885904</v>
       </c>
       <c r="B226">
-        <v>237.53962583596095</v>
+        <v>500</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>500</v>
+        <v>385.09529380263399</v>
       </c>
       <c r="B227">
-        <v>239.63242060057104</v>
+        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228">
-        <v>500</v>
+        <v>384.19129172073059</v>
       </c>
       <c r="B228">
-        <v>241.71436745447011</v>
+        <v>500</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229">
-        <v>500</v>
+        <v>383.22935619474708</v>
       </c>
       <c r="B229">
-        <v>243.87259839383088</v>
+        <v>500</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230">
-        <v>500</v>
+        <v>382.26917523111564</v>
       </c>
       <c r="B230">
-        <v>246.01139294833985</v>
+        <v>500</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231">
-        <v>500</v>
+        <v>381.30786425212068</v>
       </c>
       <c r="B231">
-        <v>248.04779978012434</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232">
-        <v>500</v>
+        <v>380.28795243302289</v>
       </c>
       <c r="B232">
-        <v>250.18047325780773</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233">
-        <v>500</v>
+        <v>379.31581572618836</v>
       </c>
       <c r="B233">
-        <v>252.29084269393468</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234">
-        <v>500</v>
+        <v>378.34329764186771</v>
       </c>
       <c r="B234">
-        <v>254.36325468447873</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235">
-        <v>500</v>
+        <v>377.24564465226666</v>
       </c>
       <c r="B235">
-        <v>256.43042560775069</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236">
-        <v>500</v>
+        <v>376.14348365947802</v>
       </c>
       <c r="B236">
-        <v>258.51025487077902</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237">
-        <v>500</v>
+        <v>375.04229129782772</v>
       </c>
       <c r="B237">
-        <v>260.63161964898745</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238">
-        <v>500</v>
+        <v>374.01642874228128</v>
       </c>
       <c r="B238">
-        <v>262.96578615174332</v>
+        <v>500</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239">
-        <v>500</v>
+        <v>373.1855999818402</v>
       </c>
       <c r="B239">
-        <v>265.30169890569698</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240">
-        <v>500</v>
+        <v>372.49526078370445</v>
       </c>
       <c r="B240">
-        <v>267.64708286788664</v>
+        <v>500</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241">
-        <v>500</v>
+        <v>371.80471813670187</v>
       </c>
       <c r="B241">
-        <v>270.03208823751885</v>
+        <v>500</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242">
-        <v>500</v>
+        <v>371.14334540710792</v>
       </c>
       <c r="B242">
-        <v>272.33930635042361</v>
+        <v>500</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243">
-        <v>500</v>
+        <v>370.42083397920698</v>
       </c>
       <c r="B243">
-        <v>274.83371118559296</v>
+        <v>500</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244">
-        <v>500</v>
+        <v>369.73839848780352</v>
       </c>
       <c r="B244">
-        <v>277.37669211815466</v>
+        <v>500</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245">
-        <v>500</v>
+        <v>369.11654909095438</v>
       </c>
       <c r="B245">
-        <v>279.86063796948332</v>
+        <v>500</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246">
-        <v>500</v>
+        <v>368.40228227009101</v>
       </c>
       <c r="B246">
-        <v>282.42425027496694</v>
+        <v>500</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247">
-        <v>500</v>
+        <v>367.71709485271458</v>
       </c>
       <c r="B247">
-        <v>284.96114766252487</v>
+        <v>500</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248">
-        <v>500</v>
+        <v>367.1639760942432</v>
       </c>
       <c r="B248">
-        <v>287.55264877626996</v>
+        <v>500</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249">
-        <v>500</v>
+        <v>366.62280208805288</v>
       </c>
       <c r="B249">
-        <v>290.27579812029745</v>
+        <v>500</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250">
-        <v>500</v>
+        <v>366.1124968861867</v>
       </c>
       <c r="B250">
-        <v>293.05828742262418</v>
+        <v>500</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251">
-        <v>500</v>
+        <v>365.50863396886876</v>
       </c>
       <c r="B251">
-        <v>295.9104443239716</v>
+        <v>500</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252">
-        <v>500</v>
+        <v>364.85568677696796</v>
       </c>
       <c r="B252">
-        <v>298.83463621566341</v>
+        <v>500</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253">
-        <v>500</v>
+        <v>364.25072322221604</v>
       </c>
       <c r="B253">
-        <v>301.79363340786364</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254">
-        <v>500</v>
+        <v>363.76209891498053</v>
       </c>
       <c r="B254">
-        <v>304.81056714533457</v>
+        <v>500</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255">
-        <v>500</v>
+        <v>363.29866902974027</v>
       </c>
       <c r="B255">
-        <v>307.99628138039884</v>
+        <v>500</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256">
-        <v>500</v>
+        <v>362.95311178229628</v>
       </c>
       <c r="B256">
-        <v>311.2641199174987</v>
+        <v>500</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257">
-        <v>500</v>
+        <v>362.59138896868899</v>
       </c>
       <c r="B257">
-        <v>314.44051771493469</v>
+        <v>500</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258">
-        <v>500</v>
+        <v>362.15035656609439</v>
       </c>
       <c r="B258">
-        <v>317.542500075389</v>
+        <v>500</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259">
-        <v>500</v>
+        <v>361.71111830126216</v>
       </c>
       <c r="B259">
-        <v>320.65360400808567</v>
+        <v>500</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260">
-        <v>500</v>
+        <v>361.25352527872514</v>
       </c>
       <c r="B260">
-        <v>323.77632816937103</v>
+        <v>500</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261">
-        <v>500</v>
+        <v>360.69210757445961</v>
       </c>
       <c r="B261">
-        <v>326.93910937392963</v>
+        <v>500</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262">
-        <v>500</v>
+        <v>360.09304603678845</v>
       </c>
       <c r="B262">
-        <v>330.14423285579096</v>
+        <v>500</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263">
-        <v>500</v>
+        <v>359.50652947223534</v>
       </c>
       <c r="B263">
-        <v>333.31357065469746</v>
+        <v>500</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264">
-        <v>500</v>
+        <v>358.87428759105563</v>
       </c>
       <c r="B264">
-        <v>336.47076109456589</v>
+        <v>500</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265">
-        <v>500</v>
+        <v>358.30614750061017</v>
       </c>
       <c r="B265">
-        <v>339.73143101318942</v>
+        <v>500</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266">
-        <v>500</v>
+        <v>357.81086519716507</v>
       </c>
       <c r="B266">
-        <v>342.98313162536942</v>
+        <v>500</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267">
-        <v>500</v>
+        <v>357.43952926038662</v>
       </c>
       <c r="B267">
-        <v>346.34001814872755</v>
+        <v>500</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268">
-        <v>500</v>
+        <v>357.11207719434384</v>
       </c>
       <c r="B268">
-        <v>349.79724749010643</v>
+        <v>500</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269">
-        <v>500</v>
+        <v>356.78750647524208</v>
       </c>
       <c r="B269">
-        <v>353.24041005112684</v>
+        <v>500</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270">
-        <v>500</v>
+        <v>356.30932600500961</v>
       </c>
       <c r="B270">
-        <v>356.64724863309345</v>
+        <v>500</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271">
-        <v>500</v>
+        <v>355.85318206427928</v>
       </c>
       <c r="B271">
-        <v>360.05137602466181</v>
+        <v>500</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272">
-        <v>500</v>
+        <v>355.57443815716101</v>
       </c>
       <c r="B272">
-        <v>363.44549314752658</v>
+        <v>500</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273">
-        <v>500</v>
+        <v>355.40333861072776</v>
       </c>
       <c r="B273">
-        <v>366.9861147964383</v>
+        <v>500</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274">
-        <v>500</v>
+        <v>355.22329356835934</v>
       </c>
       <c r="B274">
-        <v>370.63187940143303</v>
+        <v>500</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275">
-        <v>500</v>
+        <v>354.94800668061879</v>
       </c>
       <c r="B275">
-        <v>374.23802161878473</v>
+        <v>500</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276">
-        <v>500</v>
+        <v>354.73342731127775</v>
       </c>
       <c r="B276">
-        <v>377.90388012724844</v>
+        <v>500</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277">
-        <v>500</v>
+        <v>354.59849048771247</v>
       </c>
       <c r="B277">
-        <v>381.66225345675048</v>
+        <v>500</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278">
-        <v>500</v>
+        <v>354.48635852125</v>
       </c>
       <c r="B278">
-        <v>385.39228350662665</v>
+        <v>500</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279">
-        <v>500</v>
+        <v>354.3152815990772</v>
       </c>
       <c r="B279">
-        <v>389.25470088793401</v>
+        <v>500</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280">
-        <v>500</v>
+        <v>354.03831068370903</v>
       </c>
       <c r="B280">
-        <v>393.25509363541011</v>
+        <v>500</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281">
-        <v>500</v>
+        <v>353.83121816739691</v>
       </c>
       <c r="B281">
-        <v>397.22140912430893</v>
+        <v>500</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282">
-        <v>500</v>
+        <v>353.58156445259311</v>
       </c>
       <c r="B282">
-        <v>401.06875785644644</v>
+        <v>500</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283">
-        <v>500</v>
+        <v>353.30217148411464</v>
       </c>
       <c r="B283">
-        <v>404.94101125641618</v>
+        <v>500</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284">
-        <v>500</v>
+        <v>353.07420492506708</v>
       </c>
       <c r="B284">
-        <v>408.85829252028543</v>
+        <v>500</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285">
-        <v>500</v>
+        <v>353.01350427273752</v>
       </c>
       <c r="B285">
-        <v>412.82933956444094</v>
+        <v>500</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286">
-        <v>500</v>
+        <v>352.94910601436868</v>
       </c>
       <c r="B286">
-        <v>416.71893452712544</v>
+        <v>500</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287">
-        <v>500</v>
+        <v>352.89584086069715</v>
       </c>
       <c r="B287">
-        <v>420.65164575393538</v>
+        <v>500</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288">
-        <v>500</v>
+        <v>352.91863051967596</v>
       </c>
       <c r="B288">
-        <v>424.56095196248276</v>
+        <v>500</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289">
-        <v>500</v>
+        <v>352.73754446928069</v>
       </c>
       <c r="B289">
-        <v>428.47383684928769</v>
+        <v>500</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290">
-        <v>500</v>
+        <v>352.55334665846379</v>
       </c>
       <c r="B290">
-        <v>432.37266949483745</v>
+        <v>500</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291">
-        <v>500</v>
+        <v>352.22276955745053</v>
       </c>
       <c r="B291">
-        <v>436.35594152153368</v>
+        <v>500</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292">
-        <v>500</v>
+        <v>351.8009496745828</v>
       </c>
       <c r="B292">
-        <v>440.43396392862235</v>
+        <v>500</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293">
-        <v>500</v>
+        <v>351.48238773304195</v>
       </c>
       <c r="B293">
-        <v>444.52295410422204</v>
+        <v>500</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294">
-        <v>500</v>
+        <v>351.13379344344008</v>
       </c>
       <c r="B294">
-        <v>448.51544207287048</v>
+        <v>500</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295">
-        <v>500</v>
+        <v>350.79870012765434</v>
       </c>
       <c r="B295">
-        <v>452.67934431232402</v>
+        <v>500</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296">
-        <v>500</v>
+        <v>350.47020883451188</v>
       </c>
       <c r="B296">
-        <v>456.9885613775989</v>
+        <v>500</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297">
-        <v>500</v>
+        <v>350.22773929835824</v>
       </c>
       <c r="B297">
-        <v>461.40559569592693</v>
+        <v>500</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298">
-        <v>500</v>
+        <v>349.8537400015735</v>
       </c>
       <c r="B298">
-        <v>465.96218346521857</v>
+        <v>500</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299">
-        <v>500</v>
+        <v>349.43209796349157</v>
       </c>
       <c r="B299">
-        <v>470.60143997184332</v>
+        <v>500</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300">
-        <v>500</v>
+        <v>348.92931498804268</v>
       </c>
       <c r="B300">
-        <v>475.12167933477122</v>
+        <v>500</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301">
-        <v>500</v>
+        <v>348.31861123197257</v>
       </c>
       <c r="B301">
-        <v>479.54007227522675</v>
+        <v>500</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302">
-        <v>500</v>
+        <v>347.61103773393847</v>
       </c>
       <c r="B302">
-        <v>484.03665242493429</v>
+        <v>500</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303">
-        <v>500</v>
+        <v>346.98120746106383</v>
       </c>
       <c r="B303">
-        <v>488.55198212775684</v>
+        <v>500</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304">
-        <v>500</v>
+        <v>346.35338918861351</v>
       </c>
       <c r="B304">
-        <v>493.03885957136902</v>
+        <v>500</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305">
-        <v>500</v>
+        <v>345.66318910391703</v>
       </c>
       <c r="B305">
-        <v>497.53296059984996</v>
+        <v>500</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306">
-        <v>500</v>
+        <v>345.05866734273428</v>
       </c>
       <c r="B306">
         <v>500</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307">
-        <v>500</v>
+        <v>344.50774621896943</v>
       </c>
       <c r="B307">
         <v>500</v>
@@ -2801,7 +2801,7 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308">
-        <v>500</v>
+        <v>343.91142602310214</v>
       </c>
       <c r="B308">
         <v>500</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309">
-        <v>500</v>
+        <v>343.26605660270116</v>
       </c>
       <c r="B309">
         <v>500</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310">
-        <v>500</v>
+        <v>342.57494929565161</v>
       </c>
       <c r="B310">
         <v>500</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311">
-        <v>500</v>
+        <v>342.00497446861004</v>
       </c>
       <c r="B311">
         <v>500</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312">
-        <v>500</v>
+        <v>341.38603972826218</v>
       </c>
       <c r="B312">
         <v>500</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313">
-        <v>500</v>
+        <v>340.66509604769152</v>
       </c>
       <c r="B313">
         <v>500</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314">
-        <v>500</v>
+        <v>339.98129495880949</v>
       </c>
       <c r="B314">
         <v>500</v>
@@ -2857,7 +2857,7 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315">
-        <v>500</v>
+        <v>339.19897154820831</v>
       </c>
       <c r="B315">
         <v>500</v>
@@ -2865,7 +2865,7 @@
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316">
-        <v>500</v>
+        <v>338.34862927916731</v>
       </c>
       <c r="B316">
         <v>500</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317">
-        <v>500</v>
+        <v>337.43408685105362</v>
       </c>
       <c r="B317">
         <v>500</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318">
-        <v>500</v>
+        <v>336.40637275550358</v>
       </c>
       <c r="B318">
         <v>500</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319">
-        <v>500</v>
+        <v>335.22080232543391</v>
       </c>
       <c r="B319">
         <v>500</v>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320">
-        <v>500</v>
+        <v>334.0137999466229</v>
       </c>
       <c r="B320">
         <v>500</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321">
-        <v>500</v>
+        <v>332.86269753780141</v>
       </c>
       <c r="B321">
         <v>500</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322">
-        <v>500</v>
+        <v>331.77183283824894</v>
       </c>
       <c r="B322">
         <v>500</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323">
-        <v>500</v>
+        <v>330.64892623912709</v>
       </c>
       <c r="B323">
         <v>500</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324">
-        <v>500</v>
+        <v>329.418623793584</v>
       </c>
       <c r="B324">
         <v>500</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325">
-        <v>500</v>
+        <v>328.05973192920999</v>
       </c>
       <c r="B325">
         <v>500</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326">
-        <v>500</v>
+        <v>326.78321778947264</v>
       </c>
       <c r="B326">
         <v>500</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327">
-        <v>500</v>
+        <v>325.53540534811242</v>
       </c>
       <c r="B327">
         <v>500</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328">
-        <v>500</v>
+        <v>324.29611722707932</v>
       </c>
       <c r="B328">
         <v>500</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329">
-        <v>500</v>
+        <v>323.03084641887068</v>
       </c>
       <c r="B329">
         <v>500</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330">
-        <v>500</v>
+        <v>321.85836828591897</v>
       </c>
       <c r="B330">
         <v>500</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331">
-        <v>500</v>
+        <v>320.81573923568965</v>
       </c>
       <c r="B331">
         <v>500</v>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332">
-        <v>500</v>
+        <v>319.77334091538705</v>
       </c>
       <c r="B332">
         <v>500</v>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333">
-        <v>500</v>
+        <v>318.77830579630955</v>
       </c>
       <c r="B333">
         <v>500</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334">
-        <v>500</v>
+        <v>317.925010116637</v>
       </c>
       <c r="B334">
         <v>500</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335">
-        <v>500</v>
+        <v>317.10210043329812</v>
       </c>
       <c r="B335">
         <v>500</v>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336">
-        <v>500</v>
+        <v>316.32223632313918</v>
       </c>
       <c r="B336">
         <v>500</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337">
-        <v>500</v>
+        <v>315.77258272284399</v>
       </c>
       <c r="B337">
         <v>500</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338">
-        <v>500</v>
+        <v>315.1357990849923</v>
       </c>
       <c r="B338">
         <v>500</v>
@@ -3049,7 +3049,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339">
-        <v>500</v>
+        <v>314.49598499747475</v>
       </c>
       <c r="B339">
         <v>500</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340">
-        <v>500</v>
+        <v>313.85840810897236</v>
       </c>
       <c r="B340">
         <v>500</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341">
-        <v>500</v>
+        <v>313.27446478349123</v>
       </c>
       <c r="B341">
         <v>500</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342">
-        <v>500</v>
+        <v>312.57170139505047</v>
       </c>
       <c r="B342">
         <v>500</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343">
-        <v>500</v>
+        <v>311.76295860387199</v>
       </c>
       <c r="B343">
         <v>500</v>
@@ -3089,7 +3089,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344">
-        <v>500</v>
+        <v>310.96167048204688</v>
       </c>
       <c r="B344">
         <v>500</v>
@@ -3097,7 +3097,7 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345">
-        <v>500</v>
+        <v>310.11621034928692</v>
       </c>
       <c r="B345">
         <v>500</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346">
-        <v>500</v>
+        <v>309.18456695698075</v>
       </c>
       <c r="B346">
         <v>500</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347">
-        <v>500</v>
+        <v>308.35643205972696</v>
       </c>
       <c r="B347">
         <v>500</v>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348">
-        <v>500</v>
+        <v>307.60077811178019</v>
       </c>
       <c r="B348">
         <v>500</v>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349">
-        <v>500</v>
+        <v>306.85696663400552</v>
       </c>
       <c r="B349">
         <v>500</v>
@@ -3137,7 +3137,7 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350">
-        <v>500</v>
+        <v>306.11092786886968</v>
       </c>
       <c r="B350">
         <v>500</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351">
-        <v>500</v>
+        <v>305.43706002272353</v>
       </c>
       <c r="B351">
         <v>500</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352">
-        <v>500</v>
+        <v>304.72534887473932</v>
       </c>
       <c r="B352">
         <v>500</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353">
-        <v>500</v>
+        <v>304.0446238907727</v>
       </c>
       <c r="B353">
         <v>500</v>
@@ -3169,7 +3169,7 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354">
-        <v>500</v>
+        <v>303.24478226877875</v>
       </c>
       <c r="B354">
         <v>500</v>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355">
-        <v>500</v>
+        <v>302.32730224266834</v>
       </c>
       <c r="B355">
         <v>500</v>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356">
-        <v>500</v>
+        <v>301.29061293644634</v>
       </c>
       <c r="B356">
         <v>500</v>
@@ -3193,7 +3193,7 @@
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357">
-        <v>500</v>
+        <v>300.25523142726195</v>
       </c>
       <c r="B357">
         <v>500</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358">
-        <v>500</v>
+        <v>299.3163701406055</v>
       </c>
       <c r="B358">
         <v>500</v>
@@ -3209,7 +3209,7 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359">
-        <v>500</v>
+        <v>298.46837807032682</v>
       </c>
       <c r="B359">
         <v>500</v>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360">
-        <v>500</v>
+        <v>297.52092558850507</v>
       </c>
       <c r="B360">
         <v>500</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361">
-        <v>500</v>
+        <v>296.52818593399047</v>
       </c>
       <c r="B361">
         <v>500</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362">
-        <v>500</v>
+        <v>295.46291787329818</v>
       </c>
       <c r="B362">
         <v>500</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363">
-        <v>500</v>
+        <v>294.5159742794321</v>
       </c>
       <c r="B363">
         <v>500</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364">
-        <v>500</v>
+        <v>293.50581005136161</v>
       </c>
       <c r="B364">
         <v>500</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365">
-        <v>500</v>
+        <v>292.60123542780934</v>
       </c>
       <c r="B365">
         <v>500</v>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366">
-        <v>500</v>
+        <v>291.79971197844844</v>
       </c>
       <c r="B366">
         <v>500</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367">
-        <v>500</v>
+        <v>291.01922805908202</v>
       </c>
       <c r="B367">
         <v>500</v>
@@ -3281,7 +3281,7 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368">
-        <v>500</v>
+        <v>290.25481624273044</v>
       </c>
       <c r="B368">
         <v>500</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369">
-        <v>500</v>
+        <v>289.35970174345999</v>
       </c>
       <c r="B369">
         <v>500</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370">
-        <v>500</v>
+        <v>288.47117986843932</v>
       </c>
       <c r="B370">
         <v>500</v>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371">
-        <v>500</v>
+        <v>287.56718495901384</v>
       </c>
       <c r="B371">
         <v>500</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372">
-        <v>500</v>
+        <v>286.6910237894752</v>
       </c>
       <c r="B372">
         <v>500</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373">
-        <v>500</v>
+        <v>285.70116233265293</v>
       </c>
       <c r="B373">
         <v>500</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374">
-        <v>500</v>
+        <v>284.76517905695169</v>
       </c>
       <c r="B374">
         <v>500</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375">
-        <v>500</v>
+        <v>283.80327212828075</v>
       </c>
       <c r="B375">
         <v>500</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376">
-        <v>500</v>
+        <v>282.86738249669384</v>
       </c>
       <c r="B376">
         <v>500</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377">
-        <v>500</v>
+        <v>281.94283730718212</v>
       </c>
       <c r="B377">
         <v>500</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378">
-        <v>500</v>
+        <v>281.09640906855617</v>
       </c>
       <c r="B378">
         <v>500</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379">
-        <v>500</v>
+        <v>280.3018731762732</v>
       </c>
       <c r="B379">
         <v>500</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380">
-        <v>500</v>
+        <v>279.42088889995745</v>
       </c>
       <c r="B380">
         <v>500</v>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381">
-        <v>500</v>
+        <v>278.47906171580615</v>
       </c>
       <c r="B381">
         <v>500</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382">
-        <v>500</v>
+        <v>277.21919053592507</v>
       </c>
       <c r="B382">
         <v>500</v>
@@ -3401,7 +3401,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383">
-        <v>500</v>
+        <v>275.855915800866</v>
       </c>
       <c r="B383">
         <v>500</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384">
-        <v>500</v>
+        <v>274.34942387288248</v>
       </c>
       <c r="B384">
         <v>500</v>
@@ -3417,7 +3417,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385">
-        <v>500</v>
+        <v>272.63464598426276</v>
       </c>
       <c r="B385">
         <v>500</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386">
-        <v>500</v>
+        <v>271.02975660727577</v>
       </c>
       <c r="B386">
         <v>500</v>
@@ -3433,7 +3433,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387">
-        <v>500</v>
+        <v>269.40133909090116</v>
       </c>
       <c r="B387">
         <v>500</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388">
-        <v>500</v>
+        <v>267.76702640264438</v>
       </c>
       <c r="B388">
         <v>500</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389">
-        <v>500</v>
+        <v>266.1201507601661</v>
       </c>
       <c r="B389">
         <v>500</v>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390">
-        <v>500</v>
+        <v>264.44006348187639</v>
       </c>
       <c r="B390">
         <v>500</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391">
-        <v>500</v>
+        <v>262.92371551431341</v>
       </c>
       <c r="B391">
         <v>500</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392">
-        <v>500</v>
+        <v>261.50070484134193</v>
       </c>
       <c r="B392">
         <v>500</v>
@@ -3481,7 +3481,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393">
-        <v>500</v>
+        <v>260.09926446855962</v>
       </c>
       <c r="B393">
         <v>500</v>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394">
-        <v>500</v>
+        <v>258.46720644087486</v>
       </c>
       <c r="B394">
         <v>500</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395">
-        <v>500</v>
+        <v>256.75798881381002</v>
       </c>
       <c r="B395">
         <v>500</v>
@@ -3505,2127 +3505,2127 @@
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396">
-        <v>500</v>
+        <v>255.04223930007475</v>
       </c>
       <c r="B396">
-        <v>500</v>
+        <v>499.92406315714277</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397">
-        <v>500</v>
+        <v>253.19624300775757</v>
       </c>
       <c r="B397">
-        <v>500</v>
+        <v>499.76753707187686</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398">
-        <v>500</v>
+        <v>251.44175461994135</v>
       </c>
       <c r="B398">
-        <v>500</v>
+        <v>499.65048880213237</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399">
-        <v>500</v>
+        <v>249.87184053816679</v>
       </c>
       <c r="B399">
-        <v>500</v>
+        <v>499.37828234861632</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400">
-        <v>500</v>
+        <v>248.4305168956264</v>
       </c>
       <c r="B400">
-        <v>500</v>
+        <v>499.21483063520577</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401">
-        <v>500</v>
+        <v>247.06996212789375</v>
       </c>
       <c r="B401">
-        <v>500</v>
+        <v>499.11999284636283</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402">
-        <v>500</v>
+        <v>245.6983746501646</v>
       </c>
       <c r="B402">
-        <v>500</v>
+        <v>498.98835859266683</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403">
-        <v>500</v>
+        <v>244.30922202237738</v>
       </c>
       <c r="B403">
-        <v>500</v>
+        <v>498.89715922843044</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404">
-        <v>500</v>
+        <v>242.77312632066906</v>
       </c>
       <c r="B404">
-        <v>500</v>
+        <v>498.94689372575971</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405">
-        <v>500</v>
+        <v>241.25527039563244</v>
       </c>
       <c r="B405">
-        <v>500</v>
+        <v>498.99228805975622</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406">
-        <v>500</v>
+        <v>239.69134462762617</v>
       </c>
       <c r="B406">
-        <v>500</v>
+        <v>499.13410150581245</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407">
-        <v>500</v>
+        <v>238.20967284744151</v>
       </c>
       <c r="B407">
-        <v>500</v>
+        <v>499.21005490009554</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408">
-        <v>500</v>
+        <v>236.89250667538857</v>
       </c>
       <c r="B408">
-        <v>500</v>
+        <v>499.24514804417453</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409">
-        <v>500</v>
+        <v>235.74830243997599</v>
       </c>
       <c r="B409">
-        <v>500</v>
+        <v>499.31302816141454</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410">
-        <v>500</v>
+        <v>234.62547771160624</v>
       </c>
       <c r="B410">
-        <v>500</v>
+        <v>499.36487930181971</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411">
-        <v>500</v>
+        <v>233.51579394085235</v>
       </c>
       <c r="B411">
-        <v>500</v>
+        <v>499.46027500038997</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412">
-        <v>500</v>
+        <v>232.33672555602752</v>
       </c>
       <c r="B412">
-        <v>500</v>
+        <v>499.46586506208644</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413">
-        <v>500</v>
+        <v>231.07018883818287</v>
       </c>
       <c r="B413">
-        <v>500</v>
+        <v>499.47185216542215</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414">
-        <v>500</v>
+        <v>229.82357355747575</v>
       </c>
       <c r="B414">
-        <v>500</v>
+        <v>499.4473733727894</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415">
-        <v>500</v>
+        <v>228.79756886800141</v>
       </c>
       <c r="B415">
-        <v>500</v>
+        <v>499.38571642700236</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416">
-        <v>500</v>
+        <v>227.94352275501859</v>
       </c>
       <c r="B416">
-        <v>500</v>
+        <v>499.22295573426663</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417">
-        <v>500</v>
+        <v>227.08289311775675</v>
       </c>
       <c r="B417">
-        <v>500</v>
+        <v>498.95382108664677</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418">
-        <v>500</v>
+        <v>226.1431869039597</v>
       </c>
       <c r="B418">
-        <v>500</v>
+        <v>498.60705437712528</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419">
-        <v>500</v>
+        <v>225.27451339323665</v>
       </c>
       <c r="B419">
-        <v>500</v>
+        <v>498.34557393604666</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420">
-        <v>500</v>
+        <v>224.38275004249687</v>
       </c>
       <c r="B420">
-        <v>500</v>
+        <v>498.17663878957103</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421">
-        <v>500</v>
+        <v>223.48846160239921</v>
       </c>
       <c r="B421">
-        <v>500</v>
+        <v>498.00163930242906</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422">
-        <v>500</v>
+        <v>222.56580718359811</v>
       </c>
       <c r="B422">
-        <v>500</v>
+        <v>497.82190533367486</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423">
-        <v>500</v>
+        <v>221.77512765830596</v>
       </c>
       <c r="B423">
-        <v>500</v>
+        <v>497.54929216450944</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424">
-        <v>500</v>
+        <v>220.97838443640779</v>
       </c>
       <c r="B424">
-        <v>500</v>
+        <v>497.19921786544097</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425">
-        <v>500</v>
+        <v>220.32612323784463</v>
       </c>
       <c r="B425">
-        <v>500</v>
+        <v>496.81570786066851</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426">
-        <v>500</v>
+        <v>219.77003580724548</v>
       </c>
       <c r="B426">
-        <v>500</v>
+        <v>496.40558823747659</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427">
-        <v>500</v>
+        <v>219.1903743019864</v>
       </c>
       <c r="B427">
-        <v>500</v>
+        <v>495.84566742799592</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428">
-        <v>500</v>
+        <v>218.60116315170086</v>
       </c>
       <c r="B428">
-        <v>500</v>
+        <v>495.13672093453539</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429">
-        <v>500</v>
+        <v>217.96065927975641</v>
       </c>
       <c r="B429">
-        <v>500</v>
+        <v>494.43762890713958</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430">
-        <v>500</v>
+        <v>217.25457131368341</v>
       </c>
       <c r="B430">
-        <v>500</v>
+        <v>493.76586216730777</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431">
-        <v>500</v>
+        <v>216.49022073137152</v>
       </c>
       <c r="B431">
-        <v>500</v>
+        <v>493.12241634492369</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432">
-        <v>500</v>
+        <v>215.64200888446939</v>
       </c>
       <c r="B432">
-        <v>500</v>
+        <v>492.47961897264361</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433">
-        <v>500</v>
+        <v>214.86234316103736</v>
       </c>
       <c r="B433">
-        <v>500</v>
+        <v>491.87203340814546</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434">
-        <v>500</v>
+        <v>214.14844264682216</v>
       </c>
       <c r="B434">
-        <v>500</v>
+        <v>491.21697970296361</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435">
-        <v>500</v>
+        <v>213.24661663975948</v>
       </c>
       <c r="B435">
-        <v>500</v>
+        <v>490.60668656331586</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436">
-        <v>500</v>
+        <v>212.27549389397836</v>
       </c>
       <c r="B436">
-        <v>500</v>
+        <v>489.87521038261099</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437">
-        <v>500</v>
+        <v>211.36030068517996</v>
       </c>
       <c r="B437">
-        <v>500</v>
+        <v>489.14608662681286</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438">
-        <v>500</v>
+        <v>210.53361109805704</v>
       </c>
       <c r="B438">
-        <v>500</v>
+        <v>488.38807667129078</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439">
-        <v>500</v>
+        <v>209.68895120393367</v>
       </c>
       <c r="B439">
-        <v>500</v>
+        <v>487.56151325658698</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440">
-        <v>500</v>
+        <v>208.8531538818321</v>
       </c>
       <c r="B440">
-        <v>500</v>
+        <v>486.73746359843864</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441">
-        <v>500</v>
+        <v>208.10941807115253</v>
       </c>
       <c r="B441">
-        <v>500</v>
+        <v>485.945649774473</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442">
-        <v>500</v>
+        <v>207.34979220368714</v>
       </c>
       <c r="B442">
-        <v>500</v>
+        <v>485.2255091003326</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443">
-        <v>500</v>
+        <v>206.68238045686198</v>
       </c>
       <c r="B443">
-        <v>500</v>
+        <v>484.66457659518522</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444">
-        <v>500</v>
+        <v>206.16019443984379</v>
       </c>
       <c r="B444">
-        <v>500</v>
+        <v>484.05298520150575</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445">
-        <v>500</v>
+        <v>205.47807467108294</v>
       </c>
       <c r="B445">
-        <v>500</v>
+        <v>483.38537558474559</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446">
-        <v>500</v>
+        <v>204.71071438707102</v>
       </c>
       <c r="B446">
-        <v>500</v>
+        <v>482.7948426935684</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447">
-        <v>500</v>
+        <v>203.88270586762832</v>
       </c>
       <c r="B447">
-        <v>500</v>
+        <v>482.36039377904484</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448">
-        <v>500</v>
+        <v>203.06640644467143</v>
       </c>
       <c r="B448">
-        <v>500</v>
+        <v>481.94044641176674</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449">
-        <v>500</v>
+        <v>202.26898663389551</v>
       </c>
       <c r="B449">
-        <v>500</v>
+        <v>481.46205360674111</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450">
-        <v>500</v>
+        <v>201.52922213330865</v>
       </c>
       <c r="B450">
-        <v>500</v>
+        <v>481.00254213068382</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451">
-        <v>500</v>
+        <v>200.70879087143769</v>
       </c>
       <c r="B451">
-        <v>500</v>
+        <v>480.38596108749965</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452">
-        <v>500</v>
+        <v>199.81735046344258</v>
       </c>
       <c r="B452">
-        <v>500</v>
+        <v>479.6691385494172</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453">
-        <v>500</v>
+        <v>198.70753950790927</v>
       </c>
       <c r="B453">
-        <v>500</v>
+        <v>479.06574040333169</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454">
-        <v>500</v>
+        <v>197.48056321617787</v>
       </c>
       <c r="B454">
-        <v>500</v>
+        <v>478.37141346390564</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455">
-        <v>500</v>
+        <v>196.30370774984468</v>
       </c>
       <c r="B455">
-        <v>500</v>
+        <v>477.69097438560971</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456">
-        <v>500</v>
+        <v>195.08606661136204</v>
       </c>
       <c r="B456">
-        <v>500</v>
+        <v>477.01053976060945</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457">
-        <v>500</v>
+        <v>193.84604653005735</v>
       </c>
       <c r="B457">
-        <v>500</v>
+        <v>476.44780672569874</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458">
-        <v>500</v>
+        <v>192.61841162349347</v>
       </c>
       <c r="B458">
-        <v>500</v>
+        <v>475.92600626470477</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459">
-        <v>500</v>
+        <v>191.42804810650242</v>
       </c>
       <c r="B459">
-        <v>500</v>
+        <v>475.4036172771377</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460">
-        <v>500</v>
+        <v>190.50583508402573</v>
       </c>
       <c r="B460">
-        <v>500</v>
+        <v>474.97461205252893</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461">
-        <v>500</v>
+        <v>189.70844781944115</v>
       </c>
       <c r="B461">
-        <v>500</v>
+        <v>474.35384922951653</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462">
-        <v>500</v>
+        <v>188.98711104052569</v>
       </c>
       <c r="B462">
-        <v>500</v>
+        <v>473.64784910379916</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463">
-        <v>500</v>
+        <v>188.27889021677476</v>
       </c>
       <c r="B463">
-        <v>500</v>
+        <v>473.03890381478504</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464">
-        <v>500</v>
+        <v>187.66727886877237</v>
       </c>
       <c r="B464">
-        <v>500</v>
+        <v>472.6287487450295</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465">
-        <v>500</v>
+        <v>187.12152972355287</v>
       </c>
       <c r="B465">
-        <v>500</v>
+        <v>472.2169186064317</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466">
-        <v>500</v>
+        <v>186.60042277481395</v>
       </c>
       <c r="B466">
-        <v>500</v>
+        <v>471.77920452500422</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467">
-        <v>500</v>
+        <v>186.13854153939818</v>
       </c>
       <c r="B467">
-        <v>500</v>
+        <v>471.36021754683594</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468">
-        <v>500</v>
+        <v>185.68661747690908</v>
       </c>
       <c r="B468">
-        <v>500</v>
+        <v>470.91007077624982</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469">
-        <v>500</v>
+        <v>185.20224532590257</v>
       </c>
       <c r="B469">
-        <v>500</v>
+        <v>470.27471574621114</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470">
-        <v>500</v>
+        <v>184.73310032737055</v>
       </c>
       <c r="B470">
-        <v>500</v>
+        <v>469.6542641778999</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471">
-        <v>500</v>
+        <v>184.10174032552291</v>
       </c>
       <c r="B471">
-        <v>500</v>
+        <v>469.03977082749969</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472">
-        <v>500</v>
+        <v>183.44890320756988</v>
       </c>
       <c r="B472">
-        <v>500</v>
+        <v>468.46053509460501</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473">
-        <v>500</v>
+        <v>182.83834648735998</v>
       </c>
       <c r="B473">
-        <v>500</v>
+        <v>467.91795105359893</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474">
-        <v>500</v>
+        <v>182.21745997844573</v>
       </c>
       <c r="B474">
-        <v>500</v>
+        <v>467.28185547872789</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475">
-        <v>500</v>
+        <v>181.75144092023362</v>
       </c>
       <c r="B475">
-        <v>500</v>
+        <v>466.48347507061391</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476">
-        <v>500</v>
+        <v>181.43096395594534</v>
       </c>
       <c r="B476">
-        <v>500</v>
+        <v>465.62489126294651</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477">
-        <v>500</v>
+        <v>181.16964308682711</v>
       </c>
       <c r="B477">
-        <v>500</v>
+        <v>464.71989713024743</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478">
-        <v>500</v>
+        <v>180.99641530028768</v>
       </c>
       <c r="B478">
-        <v>500</v>
+        <v>463.85763594163768</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479">
-        <v>500</v>
+        <v>180.74827519768348</v>
       </c>
       <c r="B479">
-        <v>500</v>
+        <v>463.05894416243939</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480">
-        <v>500</v>
+        <v>180.41674149779149</v>
       </c>
       <c r="B480">
-        <v>500</v>
+        <v>462.29952723314807</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481">
-        <v>500</v>
+        <v>180.05848899294503</v>
       </c>
       <c r="B481">
-        <v>500</v>
+        <v>461.49873347164856</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482">
-        <v>500</v>
+        <v>179.64321324204093</v>
       </c>
       <c r="B482">
-        <v>500</v>
+        <v>460.71120640133648</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483">
-        <v>500</v>
+        <v>179.35097942016014</v>
       </c>
       <c r="B483">
-        <v>500</v>
+        <v>459.98511865094531</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484">
-        <v>500</v>
+        <v>179.34469533745499</v>
       </c>
       <c r="B484">
-        <v>500</v>
+        <v>459.27144764646522</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485">
-        <v>500</v>
+        <v>179.39984924994494</v>
       </c>
       <c r="B485">
-        <v>500</v>
+        <v>458.65174532396367</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486">
-        <v>500</v>
+        <v>179.5512904774979</v>
       </c>
       <c r="B486">
-        <v>500</v>
+        <v>457.93442647274435</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487">
-        <v>500</v>
+        <v>179.72897825461837</v>
       </c>
       <c r="B487">
-        <v>500</v>
+        <v>457.19499697508621</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488">
-        <v>500</v>
+        <v>179.82495376669709</v>
       </c>
       <c r="B488">
-        <v>500</v>
+        <v>456.4002711222725</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489">
-        <v>500</v>
+        <v>179.91531813704782</v>
       </c>
       <c r="B489">
-        <v>500</v>
+        <v>455.67483562079946</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490">
-        <v>500</v>
+        <v>180.10151559514753</v>
       </c>
       <c r="B490">
-        <v>500</v>
+        <v>454.97478707327423</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491">
-        <v>500</v>
+        <v>180.23531744441541</v>
       </c>
       <c r="B491">
-        <v>500</v>
+        <v>454.27209280794034</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492">
-        <v>500</v>
+        <v>180.3343119571779</v>
       </c>
       <c r="B492">
-        <v>500</v>
+        <v>453.58380024107947</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493">
-        <v>500</v>
+        <v>180.32721201954271</v>
       </c>
       <c r="B493">
-        <v>500</v>
+        <v>452.98383802138301</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494">
-        <v>500</v>
+        <v>180.20447066495407</v>
       </c>
       <c r="B494">
-        <v>500</v>
+        <v>452.32356390020601</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495">
-        <v>500</v>
+        <v>180.03040806560816</v>
       </c>
       <c r="B495">
-        <v>500</v>
+        <v>451.50754800401711</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496">
-        <v>500</v>
+        <v>179.72445088834982</v>
       </c>
       <c r="B496">
-        <v>500</v>
+        <v>450.41888263209552</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497">
-        <v>500</v>
+        <v>179.44954110951812</v>
       </c>
       <c r="B497">
-        <v>500</v>
+        <v>449.31900035985757</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498">
-        <v>500</v>
+        <v>179.11986923950471</v>
       </c>
       <c r="B498">
-        <v>500</v>
+        <v>448.34876107382843</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499">
-        <v>500</v>
+        <v>178.73067984197047</v>
       </c>
       <c r="B499">
-        <v>500</v>
+        <v>447.48399854618975</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500">
-        <v>500</v>
+        <v>178.31996239840356</v>
       </c>
       <c r="B500">
-        <v>500</v>
+        <v>446.6879954191553</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501">
-        <v>500</v>
+        <v>177.95706081520123</v>
       </c>
       <c r="B501">
-        <v>500</v>
+        <v>445.80546707693031</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502">
-        <v>500</v>
+        <v>177.60298610378848</v>
       </c>
       <c r="B502">
-        <v>500</v>
+        <v>444.95310153797942</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503">
-        <v>500</v>
+        <v>177.36257564061171</v>
       </c>
       <c r="B503">
-        <v>500</v>
+        <v>444.13818932116891</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504">
-        <v>500</v>
+        <v>177.23876836812141</v>
       </c>
       <c r="B504">
-        <v>500</v>
+        <v>443.40326573165106</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505">
-        <v>500</v>
+        <v>177.18483267446808</v>
       </c>
       <c r="B505">
-        <v>500</v>
+        <v>442.60077330915868</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506">
-        <v>500</v>
+        <v>177.16455573905165</v>
       </c>
       <c r="B506">
-        <v>500</v>
+        <v>441.6951545609266</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507">
-        <v>500</v>
+        <v>177.36017216971419</v>
       </c>
       <c r="B507">
-        <v>500</v>
+        <v>440.90446795080192</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508">
-        <v>500</v>
+        <v>177.58208662041221</v>
       </c>
       <c r="B508">
-        <v>500</v>
+        <v>440.16421026194092</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509">
-        <v>500</v>
+        <v>178.01510283713338</v>
       </c>
       <c r="B509">
-        <v>500</v>
+        <v>439.44135458403781</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510">
-        <v>500</v>
+        <v>178.57294375683298</v>
       </c>
       <c r="B510">
-        <v>500</v>
+        <v>438.76366466384519</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511">
-        <v>500</v>
+        <v>179.07141365234773</v>
       </c>
       <c r="B511">
-        <v>500</v>
+        <v>438.01107936314509</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512">
-        <v>500</v>
+        <v>179.49541048226695</v>
       </c>
       <c r="B512">
-        <v>500</v>
+        <v>437.14795597927576</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513">
-        <v>500</v>
+        <v>179.79325721602802</v>
       </c>
       <c r="B513">
-        <v>500</v>
+        <v>436.17912521761383</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514">
-        <v>500</v>
+        <v>179.94641433946271</v>
       </c>
       <c r="B514">
-        <v>500</v>
+        <v>435.19758769623871</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515">
-        <v>500</v>
+        <v>180.18587926542668</v>
       </c>
       <c r="B515">
-        <v>500</v>
+        <v>434.1201533715186</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516">
-        <v>500</v>
+        <v>180.50309969250773</v>
       </c>
       <c r="B516">
-        <v>500</v>
+        <v>433.02422140955861</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517">
-        <v>500</v>
+        <v>180.80808165391443</v>
       </c>
       <c r="B517">
-        <v>500</v>
+        <v>432.0107785456504</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518">
-        <v>500</v>
+        <v>181.04559920814589</v>
       </c>
       <c r="B518">
-        <v>500</v>
+        <v>431.09502815142622</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519">
-        <v>500</v>
+        <v>181.29157625263537</v>
       </c>
       <c r="B519">
-        <v>500</v>
+        <v>430.26769492937615</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520">
-        <v>500</v>
+        <v>181.56240933557973</v>
       </c>
       <c r="B520">
-        <v>500</v>
+        <v>429.359999589626</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521">
-        <v>500</v>
+        <v>181.89522561384828</v>
       </c>
       <c r="B521">
-        <v>500</v>
+        <v>428.31186028387003</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522">
-        <v>500</v>
+        <v>182.24854765716236</v>
       </c>
       <c r="B522">
-        <v>500</v>
+        <v>427.19293215643415</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523">
-        <v>500</v>
+        <v>182.65248101487023</v>
       </c>
       <c r="B523">
-        <v>500</v>
+        <v>426.17719902528705</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524">
-        <v>500</v>
+        <v>183.01487316497003</v>
       </c>
       <c r="B524">
-        <v>500</v>
+        <v>425.17953431486353</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525">
-        <v>500</v>
+        <v>183.27965291110073</v>
       </c>
       <c r="B525">
-        <v>500</v>
+        <v>424.18723512136546</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526">
-        <v>500</v>
+        <v>183.57708696131877</v>
       </c>
       <c r="B526">
-        <v>500</v>
+        <v>423.26380422947585</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527">
-        <v>500</v>
+        <v>183.99335967387822</v>
       </c>
       <c r="B527">
-        <v>500</v>
+        <v>422.44756632325931</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528">
-        <v>500</v>
+        <v>184.57273055095328</v>
       </c>
       <c r="B528">
-        <v>500</v>
+        <v>421.68254691562748</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529">
-        <v>500</v>
+        <v>185.14746054470288</v>
       </c>
       <c r="B529">
-        <v>500</v>
+        <v>420.82328191567979</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530">
-        <v>500</v>
+        <v>185.65875239733305</v>
       </c>
       <c r="B530">
-        <v>500</v>
+        <v>419.97230482058075</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531">
-        <v>500</v>
+        <v>186.19681466871043</v>
       </c>
       <c r="B531">
-        <v>500</v>
+        <v>419.29607373070991</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532">
-        <v>500</v>
+        <v>186.72372529126019</v>
       </c>
       <c r="B532">
-        <v>500</v>
+        <v>418.63868676683501</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533">
-        <v>500</v>
+        <v>187.3440253137162</v>
       </c>
       <c r="B533">
-        <v>500</v>
+        <v>417.92760105413799</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534">
-        <v>500</v>
+        <v>187.96510446353508</v>
       </c>
       <c r="B534">
-        <v>500</v>
+        <v>417.26716531747621</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535">
-        <v>500</v>
+        <v>188.70887037606661</v>
       </c>
       <c r="B535">
-        <v>500</v>
+        <v>416.70375913340376</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536">
-        <v>500</v>
+        <v>189.53707105584763</v>
       </c>
       <c r="B536">
-        <v>500</v>
+        <v>416.11669685508451</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537">
-        <v>500</v>
+        <v>190.52326868643715</v>
       </c>
       <c r="B537">
-        <v>500</v>
+        <v>415.63533298667187</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538">
-        <v>500</v>
+        <v>191.67782696040692</v>
       </c>
       <c r="B538">
-        <v>500</v>
+        <v>415.24290930807058</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539">
-        <v>500</v>
+        <v>192.80311430247733</v>
       </c>
       <c r="B539">
-        <v>500</v>
+        <v>414.93937294885575</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540">
-        <v>500</v>
+        <v>194.04067337009309</v>
       </c>
       <c r="B540">
-        <v>500</v>
+        <v>414.56335245741536</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541">
-        <v>500</v>
+        <v>195.24117410660079</v>
       </c>
       <c r="B541">
-        <v>500</v>
+        <v>414.15760686578716</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542">
-        <v>500</v>
+        <v>196.33382296707205</v>
       </c>
       <c r="B542">
-        <v>500</v>
+        <v>413.66378494538372</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543">
-        <v>500</v>
+        <v>197.47106483549479</v>
       </c>
       <c r="B543">
-        <v>500</v>
+        <v>413.223609125515</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544">
-        <v>500</v>
+        <v>198.64435825279108</v>
       </c>
       <c r="B544">
-        <v>500</v>
+        <v>412.96556874161291</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545">
-        <v>500</v>
+        <v>199.65036069071371</v>
       </c>
       <c r="B545">
-        <v>500</v>
+        <v>412.79632780885379</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546">
-        <v>500</v>
+        <v>200.76017070261426</v>
       </c>
       <c r="B546">
-        <v>500</v>
+        <v>412.48746559404702</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A547">
-        <v>500</v>
+        <v>201.83357444525944</v>
       </c>
       <c r="B547">
-        <v>500</v>
+        <v>412.19558043408591</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548">
-        <v>500</v>
+        <v>202.89745356131257</v>
       </c>
       <c r="B548">
-        <v>500</v>
+        <v>412.00258766815671</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549">
-        <v>500</v>
+        <v>203.97948393805868</v>
       </c>
       <c r="B549">
-        <v>500</v>
+        <v>411.92849801175896</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550">
-        <v>500</v>
+        <v>204.8254815662869</v>
       </c>
       <c r="B550">
-        <v>500</v>
+        <v>412.04097315978288</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551">
-        <v>500</v>
+        <v>205.63413456586716</v>
       </c>
       <c r="B551">
-        <v>500</v>
+        <v>412.12574522474961</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552">
-        <v>500</v>
+        <v>206.59383325586407</v>
       </c>
       <c r="B552">
-        <v>500</v>
+        <v>412.17275777847499</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553">
-        <v>500</v>
+        <v>207.43752231368188</v>
       </c>
       <c r="B553">
-        <v>500</v>
+        <v>412.25937800231947</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554">
-        <v>500</v>
+        <v>208.28905268669527</v>
       </c>
       <c r="B554">
-        <v>500</v>
+        <v>412.33062518449589</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555">
-        <v>500</v>
+        <v>209.22973912681195</v>
       </c>
       <c r="B555">
-        <v>500</v>
+        <v>412.42136596921625</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556">
-        <v>500</v>
+        <v>210.28205017637151</v>
       </c>
       <c r="B556">
-        <v>500</v>
+        <v>412.5268343835923</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557">
-        <v>500</v>
+        <v>211.24714174551477</v>
       </c>
       <c r="B557">
-        <v>500</v>
+        <v>412.64932633761379</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558">
-        <v>500</v>
+        <v>212.17496599387241</v>
       </c>
       <c r="B558">
-        <v>500</v>
+        <v>412.67328330134421</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559">
-        <v>500</v>
+        <v>213.16985854955908</v>
       </c>
       <c r="B559">
-        <v>500</v>
+        <v>412.68114007720152</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560">
-        <v>500</v>
+        <v>214.16703514468907</v>
       </c>
       <c r="B560">
-        <v>500</v>
+        <v>412.58234066697878</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561">
-        <v>500</v>
+        <v>215.21493105446476</v>
       </c>
       <c r="B561">
-        <v>500</v>
+        <v>412.47122512890547</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562">
-        <v>500</v>
+        <v>216.17813968212553</v>
       </c>
       <c r="B562">
-        <v>500</v>
+        <v>412.43539113831577</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563">
-        <v>500</v>
+        <v>217.12456513013456</v>
       </c>
       <c r="B563">
-        <v>500</v>
+        <v>412.6064968921097</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564">
-        <v>500</v>
+        <v>218.01693673795756</v>
       </c>
       <c r="B564">
-        <v>500</v>
+        <v>412.79262970497138</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565">
-        <v>500</v>
+        <v>218.93831520033544</v>
       </c>
       <c r="B565">
-        <v>500</v>
+        <v>413.02458298783864</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566">
-        <v>500</v>
+        <v>219.8599933882403</v>
       </c>
       <c r="B566">
-        <v>500</v>
+        <v>413.32923125169719</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567">
-        <v>500</v>
+        <v>220.77787420613578</v>
       </c>
       <c r="B567">
-        <v>500</v>
+        <v>413.63556121295608</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568">
-        <v>500</v>
+        <v>221.64932579954001</v>
       </c>
       <c r="B568">
-        <v>500</v>
+        <v>413.88049112323512</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569">
-        <v>500</v>
+        <v>222.57182102942409</v>
       </c>
       <c r="B569">
-        <v>500</v>
+        <v>414.11596317381378</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570">
-        <v>500</v>
+        <v>223.40012512581103</v>
       </c>
       <c r="B570">
-        <v>500</v>
+        <v>414.53765465469365</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571">
-        <v>500</v>
+        <v>224.25944052275432</v>
       </c>
       <c r="B571">
-        <v>500</v>
+        <v>414.90183806651703</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572">
-        <v>500</v>
+        <v>225.06138282335988</v>
       </c>
       <c r="B572">
-        <v>500</v>
+        <v>415.23958221499817</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573">
-        <v>500</v>
+        <v>225.8977606822192</v>
       </c>
       <c r="B573">
-        <v>500</v>
+        <v>415.58576290700603</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574">
-        <v>500</v>
+        <v>226.71149518131833</v>
       </c>
       <c r="B574">
-        <v>500</v>
+        <v>416.10269862491674</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575">
-        <v>500</v>
+        <v>227.44569773348647</v>
       </c>
       <c r="B575">
-        <v>500</v>
+        <v>416.75698063165578</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576">
-        <v>500</v>
+        <v>228.17522154578882</v>
       </c>
       <c r="B576">
-        <v>500</v>
+        <v>417.43293784622199</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577">
-        <v>500</v>
+        <v>228.93474244494374</v>
       </c>
       <c r="B577">
-        <v>500</v>
+        <v>418.04841216032821</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578">
-        <v>500</v>
+        <v>229.56130208391548</v>
       </c>
       <c r="B578">
-        <v>500</v>
+        <v>418.71797068312225</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579">
-        <v>500</v>
+        <v>230.17794385293999</v>
       </c>
       <c r="B579">
-        <v>500</v>
+        <v>419.43634111547323</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580">
-        <v>500</v>
+        <v>230.76410490347644</v>
       </c>
       <c r="B580">
-        <v>500</v>
+        <v>420.18982188975468</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581">
-        <v>500</v>
+        <v>231.29885624971214</v>
       </c>
       <c r="B581">
-        <v>500</v>
+        <v>421.05373416719567</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582">
-        <v>500</v>
+        <v>231.88022525265851</v>
       </c>
       <c r="B582">
-        <v>500</v>
+        <v>422.01314747748745</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583">
-        <v>500</v>
+        <v>232.4723084025774</v>
       </c>
       <c r="B583">
-        <v>500</v>
+        <v>423.02352775821822</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584">
-        <v>500</v>
+        <v>233.08164529440236</v>
       </c>
       <c r="B584">
-        <v>500</v>
+        <v>424.25146611417733</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585">
-        <v>500</v>
+        <v>233.64458729765244</v>
       </c>
       <c r="B585">
-        <v>500</v>
+        <v>425.5428114929411</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586">
-        <v>500</v>
+        <v>234.35530935193745</v>
       </c>
       <c r="B586">
-        <v>500</v>
+        <v>426.75369895784661</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587">
-        <v>500</v>
+        <v>235.08653508281887</v>
       </c>
       <c r="B587">
-        <v>500</v>
+        <v>427.84853346752476</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588">
-        <v>500</v>
+        <v>235.90526023698334</v>
       </c>
       <c r="B588">
-        <v>500</v>
+        <v>428.86025407749395</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589">
-        <v>500</v>
+        <v>236.75970047201776</v>
       </c>
       <c r="B589">
-        <v>500</v>
+        <v>429.84579474585149</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590">
-        <v>500</v>
+        <v>237.56423956125838</v>
       </c>
       <c r="B590">
-        <v>500</v>
+        <v>430.84292987754344</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591">
-        <v>500</v>
+        <v>238.39268924764281</v>
       </c>
       <c r="B591">
-        <v>500</v>
+        <v>431.71097036060735</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592">
-        <v>500</v>
+        <v>239.19643964551625</v>
       </c>
       <c r="B592">
-        <v>500</v>
+        <v>432.51131764676853</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593">
-        <v>500</v>
+        <v>239.87774658448924</v>
       </c>
       <c r="B593">
-        <v>500</v>
+        <v>433.36235904029701</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594">
-        <v>500</v>
+        <v>240.40850996163465</v>
       </c>
       <c r="B594">
-        <v>500</v>
+        <v>434.14843879082531</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595">
-        <v>500</v>
+        <v>240.85299313617165</v>
       </c>
       <c r="B595">
-        <v>500</v>
+        <v>434.97947999011092</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596">
-        <v>500</v>
+        <v>241.3621968283297</v>
       </c>
       <c r="B596">
-        <v>500</v>
+        <v>435.78490194101943</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597">
-        <v>500</v>
+        <v>242.10038453423155</v>
       </c>
       <c r="B597">
-        <v>500</v>
+        <v>436.77195087971404</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598">
-        <v>500</v>
+        <v>242.93749033633958</v>
       </c>
       <c r="B598">
-        <v>500</v>
+        <v>437.74226157032808</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599">
-        <v>500</v>
+        <v>243.8965959965432</v>
       </c>
       <c r="B599">
-        <v>500</v>
+        <v>438.72939222581959</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600">
-        <v>500</v>
+        <v>244.93541513007006</v>
       </c>
       <c r="B600">
-        <v>500</v>
+        <v>439.5661520236518</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601">
-        <v>500</v>
+        <v>245.93104377654998</v>
       </c>
       <c r="B601">
-        <v>500</v>
+        <v>440.34435007482148</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602">
-        <v>500</v>
+        <v>246.96729049047428</v>
       </c>
       <c r="B602">
-        <v>500</v>
+        <v>441.18233561123009</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603">
-        <v>500</v>
+        <v>248.08451598024664</v>
       </c>
       <c r="B603">
-        <v>500</v>
+        <v>441.9644313287377</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604">
-        <v>500</v>
+        <v>249.25799323728791</v>
       </c>
       <c r="B604">
-        <v>500</v>
+        <v>442.76996021157265</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605">
-        <v>500</v>
+        <v>250.4219109103885</v>
       </c>
       <c r="B605">
-        <v>500</v>
+        <v>443.53698556675323</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606">
-        <v>500</v>
+        <v>251.58452954400582</v>
       </c>
       <c r="B606">
-        <v>500</v>
+        <v>444.38055389245619</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607">
-        <v>500</v>
+        <v>252.67348870229372</v>
       </c>
       <c r="B607">
-        <v>500</v>
+        <v>445.21366088379665</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608">
-        <v>500</v>
+        <v>253.77496028231423</v>
       </c>
       <c r="B608">
-        <v>500</v>
+        <v>445.95066673109238</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609">
-        <v>500</v>
+        <v>254.90348375811922</v>
       </c>
       <c r="B609">
-        <v>500</v>
+        <v>446.71571141697632</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610">
-        <v>500</v>
+        <v>255.92890961018546</v>
       </c>
       <c r="B610">
-        <v>500</v>
+        <v>447.52317869059766</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611">
-        <v>500</v>
+        <v>256.88588535147261</v>
       </c>
       <c r="B611">
-        <v>500</v>
+        <v>448.2691557655163</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612">
-        <v>500</v>
+        <v>257.75255703503115</v>
       </c>
       <c r="B612">
-        <v>500</v>
+        <v>449.01985341316146</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613">
-        <v>500</v>
+        <v>258.74193314647215</v>
       </c>
       <c r="B613">
-        <v>500</v>
+        <v>449.70376076147608</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614">
-        <v>500</v>
+        <v>259.89045940456197</v>
       </c>
       <c r="B614">
-        <v>500</v>
+        <v>450.32099697601279</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615">
-        <v>500</v>
+        <v>261.119271016835</v>
       </c>
       <c r="B615">
-        <v>500</v>
+        <v>450.88196749356706</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616">
-        <v>500</v>
+        <v>262.48388965807476</v>
       </c>
       <c r="B616">
-        <v>500</v>
+        <v>451.36876392486181</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617">
-        <v>500</v>
+        <v>263.90349569021771</v>
       </c>
       <c r="B617">
-        <v>500</v>
+        <v>451.92727055697662</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618">
-        <v>500</v>
+        <v>265.33136816081895</v>
       </c>
       <c r="B618">
-        <v>500</v>
+        <v>452.508238803871</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A619">
-        <v>500</v>
+        <v>266.82337576411356</v>
       </c>
       <c r="B619">
-        <v>500</v>
+        <v>453.15565629312874</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620">
-        <v>500</v>
+        <v>268.21296632470853</v>
       </c>
       <c r="B620">
-        <v>500</v>
+        <v>453.7797715940892</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621">
-        <v>500</v>
+        <v>269.73290123279043</v>
       </c>
       <c r="B621">
-        <v>500</v>
+        <v>454.56032796552211</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A622">
-        <v>500</v>
+        <v>271.18276040432784</v>
       </c>
       <c r="B622">
-        <v>500</v>
+        <v>455.35480220866924</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623">
-        <v>500</v>
+        <v>272.67269757632022</v>
       </c>
       <c r="B623">
-        <v>500</v>
+        <v>456.16969501820773</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624">
-        <v>500</v>
+        <v>274.19561536383696</v>
       </c>
       <c r="B624">
-        <v>500</v>
+        <v>456.96636226037981</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625">
-        <v>500</v>
+        <v>275.7304478806854</v>
       </c>
       <c r="B625">
-        <v>500</v>
+        <v>457.73889869847864</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626">
-        <v>500</v>
+        <v>277.33040091226155</v>
       </c>
       <c r="B626">
-        <v>500</v>
+        <v>458.62088375935139</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627">
-        <v>500</v>
+        <v>279.03883514200948</v>
       </c>
       <c r="B627">
-        <v>500</v>
+        <v>459.56758425155289</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628">
-        <v>500</v>
+        <v>280.87356328367957</v>
       </c>
       <c r="B628">
-        <v>500</v>
+        <v>460.5304442781794</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629">
-        <v>500</v>
+        <v>282.68338623361785</v>
       </c>
       <c r="B629">
-        <v>500</v>
+        <v>461.53023244074683</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630">
-        <v>500</v>
+        <v>284.41495000364131</v>
       </c>
       <c r="B630">
-        <v>500</v>
+        <v>462.58850439655583</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631">
-        <v>500</v>
+        <v>286.21663905053521</v>
       </c>
       <c r="B631">
-        <v>500</v>
+        <v>463.66745316090817</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632">
-        <v>500</v>
+        <v>288.07485142368336</v>
       </c>
       <c r="B632">
-        <v>500</v>
+        <v>464.76048825939665</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633">
-        <v>500</v>
+        <v>289.95104157743719</v>
       </c>
       <c r="B633">
-        <v>500</v>
+        <v>465.95368766783815</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634">
-        <v>500</v>
+        <v>291.89996114717377</v>
       </c>
       <c r="B634">
-        <v>500</v>
+        <v>467.20503120595117</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635">
-        <v>500</v>
+        <v>293.72813504115146</v>
       </c>
       <c r="B635">
-        <v>500</v>
+        <v>468.50970019993707</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636">
-        <v>500</v>
+        <v>295.49946552604928</v>
       </c>
       <c r="B636">
-        <v>500</v>
+        <v>469.95379637514998</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637">
-        <v>500</v>
+        <v>297.33778176047213</v>
       </c>
       <c r="B637">
-        <v>500</v>
+        <v>471.39169626659617</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638">
-        <v>500</v>
+        <v>299.15060339674477</v>
       </c>
       <c r="B638">
-        <v>500</v>
+        <v>472.74843149241764</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639">
-        <v>500</v>
+        <v>300.96925764639667</v>
       </c>
       <c r="B639">
-        <v>500</v>
+        <v>474.06543520879768</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640">
-        <v>500</v>
+        <v>302.94425547819259</v>
       </c>
       <c r="B640">
-        <v>500</v>
+        <v>475.44572466286519</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641">
-        <v>500</v>
+        <v>304.9490054226132</v>
       </c>
       <c r="B641">
-        <v>500</v>
+        <v>476.71881960909406</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642">
-        <v>500</v>
+        <v>306.97017429908914</v>
       </c>
       <c r="B642">
-        <v>500</v>
+        <v>477.88010112294467</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643">
-        <v>500</v>
+        <v>308.94804745680614</v>
       </c>
       <c r="B643">
-        <v>500</v>
+        <v>479.07001216900795</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644">
-        <v>500</v>
+        <v>310.69901593354422</v>
       </c>
       <c r="B644">
-        <v>500</v>
+        <v>480.28373539295455</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645">
-        <v>500</v>
+        <v>312.32325422848811</v>
       </c>
       <c r="B645">
-        <v>500</v>
+        <v>481.49149261490101</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646">
-        <v>500</v>
+        <v>313.86290975641651</v>
       </c>
       <c r="B646">
-        <v>500</v>
+        <v>482.59743430893531</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647">
-        <v>500</v>
+        <v>315.25937822147455</v>
       </c>
       <c r="B647">
-        <v>500</v>
+        <v>483.54802277544826</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648">
-        <v>500</v>
+        <v>316.67884923456791</v>
       </c>
       <c r="B648">
-        <v>500</v>
+        <v>484.55849856083228</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649">
-        <v>500</v>
+        <v>318.19099388295325</v>
       </c>
       <c r="B649">
-        <v>500</v>
+        <v>485.68045591829548</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650">
-        <v>500</v>
+        <v>319.61671940595062</v>
       </c>
       <c r="B650">
-        <v>500</v>
+        <v>486.79320369800161</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651">
-        <v>500</v>
+        <v>320.89774897021044</v>
       </c>
       <c r="B651">
-        <v>500</v>
+        <v>487.95172964984505</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652">
-        <v>500</v>
+        <v>322.03486202294135</v>
       </c>
       <c r="B652">
-        <v>500</v>
+        <v>489.15846010441237</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653">
-        <v>500</v>
+        <v>323.12701930257515</v>
       </c>
       <c r="B653">
-        <v>500</v>
+        <v>490.45606369978719</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654">
-        <v>500</v>
+        <v>324.2893937816836</v>
       </c>
       <c r="B654">
-        <v>500</v>
+        <v>491.70156359519626</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655">
-        <v>500</v>
+        <v>325.38745558925177</v>
       </c>
       <c r="B655">
-        <v>500</v>
+        <v>493.00945017163292</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656">
-        <v>500</v>
+        <v>326.4379014706156</v>
       </c>
       <c r="B656">
-        <v>500</v>
+        <v>494.36488795102542</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657">
-        <v>500</v>
+        <v>327.5424839834044</v>
       </c>
       <c r="B657">
-        <v>500</v>
+        <v>495.69634592861968</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658">
-        <v>500</v>
+        <v>328.60848026240069</v>
       </c>
       <c r="B658">
-        <v>500</v>
+        <v>496.9689869724649</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659">
-        <v>500</v>
+        <v>329.80410954171498</v>
       </c>
       <c r="B659">
-        <v>500</v>
+        <v>498.29062758616902</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660">
-        <v>500</v>
+        <v>331.15993389115408</v>
       </c>
       <c r="B660">
-        <v>500</v>
+        <v>499.7712311899005</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661">
-        <v>500</v>
+        <v>332.46522121293816</v>
       </c>
       <c r="B661">
         <v>500</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662">
-        <v>500</v>
+        <v>333.79066290710807</v>
       </c>
       <c r="B662">
         <v>500</v>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663">
-        <v>500</v>
+        <v>335.21686039216365</v>
       </c>
       <c r="B663">
         <v>500</v>
@@ -5649,7 +5649,7 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664">
-        <v>500</v>
+        <v>336.76321387970989</v>
       </c>
       <c r="B664">
         <v>500</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665">
-        <v>500</v>
+        <v>338.34769448697233</v>
       </c>
       <c r="B665">
         <v>500</v>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666">
-        <v>500</v>
+        <v>339.97381784196961</v>
       </c>
       <c r="B666">
         <v>500</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667">
-        <v>500</v>
+        <v>341.5153376862682</v>
       </c>
       <c r="B667">
         <v>500</v>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668">
-        <v>500</v>
+        <v>343.02562302897155</v>
       </c>
       <c r="B668">
         <v>500</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669">
-        <v>500</v>
+        <v>344.57778618526828</v>
       </c>
       <c r="B669">
         <v>500</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670">
-        <v>500</v>
+        <v>346.14957983092802</v>
       </c>
       <c r="B670">
         <v>500</v>
@@ -5705,7 +5705,7 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671">
-        <v>500</v>
+        <v>347.66771905606618</v>
       </c>
       <c r="B671">
         <v>500</v>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672">
-        <v>500</v>
+        <v>349.26741651041863</v>
       </c>
       <c r="B672">
         <v>500</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673">
-        <v>500</v>
+        <v>350.95156706336024</v>
       </c>
       <c r="B673">
         <v>500</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674">
-        <v>500</v>
+        <v>352.51001080610121</v>
       </c>
       <c r="B674">
         <v>500</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A675">
-        <v>500</v>
+        <v>354.04643607877978</v>
       </c>
       <c r="B675">
         <v>500</v>
@@ -5745,7 +5745,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676">
-        <v>500</v>
+        <v>355.59143329578029</v>
       </c>
       <c r="B676">
         <v>500</v>
@@ -5753,7 +5753,7 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677">
-        <v>500</v>
+        <v>357.12877245885704</v>
       </c>
       <c r="B677">
         <v>500</v>
@@ -5761,7 +5761,7 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678">
-        <v>500</v>
+        <v>358.7897743661913</v>
       </c>
       <c r="B678">
         <v>500</v>
@@ -5769,7 +5769,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679">
-        <v>500</v>
+        <v>360.48201763731686</v>
       </c>
       <c r="B679">
         <v>500</v>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680">
-        <v>500</v>
+        <v>362.13206128596119</v>
       </c>
       <c r="B680">
         <v>500</v>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681">
-        <v>500</v>
+        <v>363.82198710598988</v>
       </c>
       <c r="B681">
         <v>500</v>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682">
-        <v>500</v>
+        <v>365.44394896949615</v>
       </c>
       <c r="B682">
         <v>500</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683">
-        <v>500</v>
+        <v>367.03702079504109</v>
       </c>
       <c r="B683">
         <v>500</v>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684">
-        <v>500</v>
+        <v>368.59929375187153</v>
       </c>
       <c r="B684">
         <v>500</v>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685">
-        <v>500</v>
+        <v>370.18106950714559</v>
       </c>
       <c r="B685">
         <v>500</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686">
-        <v>500</v>
+        <v>371.88805811403307</v>
       </c>
       <c r="B686">
         <v>500</v>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687">
-        <v>500</v>
+        <v>373.73996355966153</v>
       </c>
       <c r="B687">
         <v>500</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688">
-        <v>500</v>
+        <v>375.6775323635564</v>
       </c>
       <c r="B688">
         <v>500</v>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689">
-        <v>500</v>
+        <v>377.50137871816253</v>
       </c>
       <c r="B689">
         <v>500</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690">
-        <v>500</v>
+        <v>379.36363406762001</v>
       </c>
       <c r="B690">
         <v>500</v>
@@ -5865,7 +5865,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691">
-        <v>500</v>
+        <v>381.34758447189427</v>
       </c>
       <c r="B691">
         <v>500</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692">
-        <v>500</v>
+        <v>383.33867951563667</v>
       </c>
       <c r="B692">
         <v>500</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693">
-        <v>500</v>
+        <v>385.3191682971925</v>
       </c>
       <c r="B693">
         <v>500</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694">
-        <v>500</v>
+        <v>387.4324942335615</v>
       </c>
       <c r="B694">
         <v>500</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695">
-        <v>500</v>
+        <v>389.54692672630773</v>
       </c>
       <c r="B695">
         <v>500</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696">
-        <v>500</v>
+        <v>391.59548294987621</v>
       </c>
       <c r="B696">
         <v>500</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697">
-        <v>500</v>
+        <v>393.54720425165686</v>
       </c>
       <c r="B697">
         <v>500</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698">
-        <v>500</v>
+        <v>395.39078241442729</v>
       </c>
       <c r="B698">
         <v>500</v>
@@ -5929,7 +5929,7 @@
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699">
-        <v>500</v>
+        <v>397.30331805385492</v>
       </c>
       <c r="B699">
         <v>500</v>
@@ -5937,7 +5937,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700">
-        <v>500</v>
+        <v>399.13112061536174</v>
       </c>
       <c r="B700">
         <v>500</v>
@@ -5945,7 +5945,7 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701">
-        <v>500</v>
+        <v>400.96297283690899</v>
       </c>
       <c r="B701">
         <v>500</v>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702">
-        <v>500</v>
+        <v>402.65417392222184</v>
       </c>
       <c r="B702">
         <v>500</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703">
-        <v>500</v>
+        <v>404.26353153448423</v>
       </c>
       <c r="B703">
         <v>500</v>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704">
-        <v>500</v>
+        <v>405.90137500286926</v>
       </c>
       <c r="B704">
         <v>500</v>
@@ -5977,7 +5977,7 @@
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705">
-        <v>500</v>
+        <v>407.53484190360172</v>
       </c>
       <c r="B705">
         <v>500</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706">
-        <v>500</v>
+        <v>409.18931753062913</v>
       </c>
       <c r="B706">
         <v>500</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707">
-        <v>500</v>
+        <v>410.81636035704452</v>
       </c>
       <c r="B707">
         <v>500</v>
@@ -6001,7 +6001,7 @@
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A708">
-        <v>500</v>
+        <v>412.52525799400604</v>
       </c>
       <c r="B708">
         <v>500</v>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709">
-        <v>500</v>
+        <v>414.23358752523467</v>
       </c>
       <c r="B709">
         <v>500</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710">
-        <v>500</v>
+        <v>415.90180929496262</v>
       </c>
       <c r="B710">
         <v>500</v>
@@ -6025,7 +6025,7 @@
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A711">
-        <v>500</v>
+        <v>417.60483901561184</v>
       </c>
       <c r="B711">
         <v>500</v>
@@ -6033,7 +6033,7 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A712">
-        <v>500</v>
+        <v>419.36913428098723</v>
       </c>
       <c r="B712">
         <v>500</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713">
-        <v>500</v>
+        <v>421.33325189127135</v>
       </c>
       <c r="B713">
         <v>500</v>
@@ -6049,7 +6049,7 @@
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714">
-        <v>500</v>
+        <v>423.20194079911494</v>
       </c>
       <c r="B714">
         <v>500</v>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715">
-        <v>500</v>
+        <v>425.07597927946659</v>
       </c>
       <c r="B715">
         <v>500</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716">
-        <v>500</v>
+        <v>427.01700905380835</v>
       </c>
       <c r="B716">
         <v>500</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717">
-        <v>500</v>
+        <v>428.91638709146525</v>
       </c>
       <c r="B717">
         <v>500</v>
@@ -6081,7 +6081,7 @@
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718">
-        <v>500</v>
+        <v>430.73489269135433</v>
       </c>
       <c r="B718">
         <v>500</v>
@@ -6089,7 +6089,7 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719">
-        <v>500</v>
+        <v>432.50305223921816</v>
       </c>
       <c r="B719">
         <v>500</v>
@@ -6097,7 +6097,7 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720">
-        <v>500</v>
+        <v>434.3082004876573</v>
       </c>
       <c r="B720">
         <v>500</v>
@@ -6105,7 +6105,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721">
-        <v>500</v>
+        <v>436.16257711226592</v>
       </c>
       <c r="B721">
         <v>500</v>
@@ -6113,7 +6113,7 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722">
-        <v>500</v>
+        <v>437.98461898376115</v>
       </c>
       <c r="B722">
         <v>500</v>
@@ -6121,7 +6121,7 @@
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723">
-        <v>500</v>
+        <v>439.71205655547732</v>
       </c>
       <c r="B723">
         <v>500</v>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A724">
-        <v>500</v>
+        <v>441.52477698648573</v>
       </c>
       <c r="B724">
         <v>500</v>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725">
-        <v>500</v>
+        <v>443.13700677418927</v>
       </c>
       <c r="B725">
         <v>500</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726">
-        <v>500</v>
+        <v>444.83186824270911</v>
       </c>
       <c r="B726">
         <v>500</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727">
-        <v>500</v>
+        <v>446.50942296443526</v>
       </c>
       <c r="B727">
         <v>500</v>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728">
-        <v>500</v>
+        <v>448.17163183464254</v>
       </c>
       <c r="B728">
         <v>500</v>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729">
-        <v>500</v>
+        <v>449.85479155124136</v>
       </c>
       <c r="B729">
         <v>500</v>
@@ -6177,7 +6177,7 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730">
-        <v>500</v>
+        <v>451.53357078261701</v>
       </c>
       <c r="B730">
         <v>500</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731">
-        <v>500</v>
+        <v>453.20631051766742</v>
       </c>
       <c r="B731">
         <v>500</v>
@@ -6193,7 +6193,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732">
-        <v>500</v>
+        <v>455.01718350421061</v>
       </c>
       <c r="B732">
         <v>500</v>
@@ -6201,7 +6201,7 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733">
-        <v>500</v>
+        <v>456.95010886396955</v>
       </c>
       <c r="B733">
         <v>500</v>
@@ -6209,7 +6209,7 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734">
-        <v>500</v>
+        <v>459.00496095613499</v>
       </c>
       <c r="B734">
         <v>500</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A735">
-        <v>500</v>
+        <v>461.11677180538931</v>
       </c>
       <c r="B735">
         <v>500</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736">
-        <v>500</v>
+        <v>463.25509865714957</v>
       </c>
       <c r="B736">
         <v>500</v>
@@ -6233,7 +6233,7 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737">
-        <v>500</v>
+        <v>465.46119914772288</v>
       </c>
       <c r="B737">
         <v>500</v>
@@ -6241,7 +6241,7 @@
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738">
-        <v>500</v>
+        <v>467.53915161544256</v>
       </c>
       <c r="B738">
         <v>500</v>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739">
-        <v>500</v>
+        <v>469.50932294505367</v>
       </c>
       <c r="B739">
         <v>500</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740">
-        <v>500</v>
+        <v>471.48664255181211</v>
       </c>
       <c r="B740">
         <v>500</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741">
-        <v>500</v>
+        <v>473.41978471394538</v>
       </c>
       <c r="B741">
         <v>500</v>
@@ -6273,7 +6273,7 @@
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742">
-        <v>500</v>
+        <v>475.4263163413911</v>
       </c>
       <c r="B742">
         <v>500</v>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743">
-        <v>500</v>
+        <v>477.44638352817668</v>
       </c>
       <c r="B743">
         <v>500</v>
@@ -6289,7 +6289,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744">
-        <v>500</v>
+        <v>479.5884028164337</v>
       </c>
       <c r="B744">
         <v>500</v>
@@ -6297,7 +6297,7 @@
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A745">
-        <v>500</v>
+        <v>481.78743276071719</v>
       </c>
       <c r="B745">
         <v>500</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746">
-        <v>500</v>
+        <v>483.93626217103991</v>
       </c>
       <c r="B746">
         <v>500</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747">
-        <v>500</v>
+        <v>486.20400909637067</v>
       </c>
       <c r="B747">
         <v>500</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748">
-        <v>500</v>
+        <v>488.42186763224134</v>
       </c>
       <c r="B748">
         <v>500</v>
@@ -6329,7 +6329,7 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749">
-        <v>500</v>
+        <v>490.70302987272174</v>
       </c>
       <c r="B749">
         <v>500</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750">
-        <v>500</v>
+        <v>492.95430396278539</v>
       </c>
       <c r="B750">
         <v>500</v>
@@ -6345,7 +6345,7 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751">
-        <v>500</v>
+        <v>495.16249383794548</v>
       </c>
       <c r="B751">
         <v>500</v>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752">
-        <v>500</v>
+        <v>497.42057541088474</v>
       </c>
       <c r="B752">
         <v>500</v>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753">
-        <v>500</v>
+        <v>499.64226747506706</v>
       </c>
       <c r="B753">
         <v>500</v>
@@ -7393,7 +7393,7 @@
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A882">
-        <v>499.98511151192423</v>
+        <v>500</v>
       </c>
       <c r="B882">
         <v>500</v>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A883">
-        <v>499.88251689319378</v>
+        <v>500</v>
       </c>
       <c r="B883">
         <v>500</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A884">
-        <v>499.61883552984199</v>
+        <v>500</v>
       </c>
       <c r="B884">
         <v>500</v>
@@ -7417,7 +7417,7 @@
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A885">
-        <v>499.2937167985462</v>
+        <v>500</v>
       </c>
       <c r="B885">
         <v>500</v>
@@ -7425,7 +7425,7 @@
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A886">
-        <v>498.87747102486082</v>
+        <v>500</v>
       </c>
       <c r="B886">
         <v>500</v>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A887">
-        <v>498.41165961205951</v>
+        <v>500</v>
       </c>
       <c r="B887">
         <v>500</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A888">
-        <v>497.98292257491346</v>
+        <v>500</v>
       </c>
       <c r="B888">
         <v>500</v>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A889">
-        <v>497.51203890676845</v>
+        <v>500</v>
       </c>
       <c r="B889">
         <v>500</v>
@@ -7457,7 +7457,7 @@
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A890">
-        <v>497.20126165763367</v>
+        <v>500</v>
       </c>
       <c r="B890">
         <v>500</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A891">
-        <v>497.09944801874798</v>
+        <v>500</v>
       </c>
       <c r="B891">
         <v>500</v>
@@ -7473,7 +7473,7 @@
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A892">
-        <v>497.11554254460009</v>
+        <v>500</v>
       </c>
       <c r="B892">
         <v>500</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A893">
-        <v>497.09772604024954</v>
+        <v>500</v>
       </c>
       <c r="B893">
         <v>500</v>
@@ -7489,7 +7489,7 @@
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A894">
-        <v>497.02483112834545</v>
+        <v>500</v>
       </c>
       <c r="B894">
         <v>500</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A895">
-        <v>496.9279577905798</v>
+        <v>500</v>
       </c>
       <c r="B895">
         <v>500</v>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A896">
-        <v>496.85310744782055</v>
+        <v>500</v>
       </c>
       <c r="B896">
         <v>500</v>
@@ -7513,7 +7513,7 @@
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A897">
-        <v>496.63392096386519</v>
+        <v>500</v>
       </c>
       <c r="B897">
         <v>500</v>
@@ -7521,7 +7521,7 @@
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A898">
-        <v>496.34448078844349</v>
+        <v>500</v>
       </c>
       <c r="B898">
         <v>500</v>
@@ -7529,7 +7529,7 @@
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A899">
-        <v>495.88361229792679</v>
+        <v>500</v>
       </c>
       <c r="B899">
         <v>500</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A900">
-        <v>495.49350433069327</v>
+        <v>500</v>
       </c>
       <c r="B900">
         <v>500</v>
@@ -7545,7 +7545,7 @@
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A901">
-        <v>495.1412462418748</v>
+        <v>500</v>
       </c>
       <c r="B901">
         <v>500</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A902">
-        <v>494.72141364952205</v>
+        <v>500</v>
       </c>
       <c r="B902">
         <v>500</v>
@@ -7561,7 +7561,7 @@
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A903">
-        <v>494.24808532218941</v>
+        <v>500</v>
       </c>
       <c r="B903">
         <v>500</v>
@@ -7569,7 +7569,7 @@
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A904">
-        <v>493.86115315051211</v>
+        <v>500</v>
       </c>
       <c r="B904">
         <v>500</v>
@@ -7577,7 +7577,7 @@
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A905">
-        <v>493.35840057406665</v>
+        <v>500</v>
       </c>
       <c r="B905">
         <v>500</v>
@@ -7585,7 +7585,7 @@
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A906">
-        <v>492.81055947686576</v>
+        <v>500</v>
       </c>
       <c r="B906">
         <v>500</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A907">
-        <v>492.26887985519318</v>
+        <v>500</v>
       </c>
       <c r="B907">
         <v>500</v>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A908">
-        <v>491.64011324150357</v>
+        <v>500</v>
       </c>
       <c r="B908">
         <v>500</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A909">
-        <v>490.97306196537187</v>
+        <v>500</v>
       </c>
       <c r="B909">
         <v>500</v>
@@ -7617,7 +7617,7 @@
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A910">
-        <v>490.42660217005027</v>
+        <v>500</v>
       </c>
       <c r="B910">
         <v>500</v>
@@ -7625,7 +7625,7 @@
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A911">
-        <v>490.00953414470075</v>
+        <v>500</v>
       </c>
       <c r="B911">
         <v>500</v>
@@ -7633,7 +7633,7 @@
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A912">
-        <v>489.75854736759044</v>
+        <v>500</v>
       </c>
       <c r="B912">
         <v>500</v>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A913">
-        <v>489.59735304309226</v>
+        <v>500</v>
       </c>
       <c r="B913">
         <v>500</v>
@@ -7649,7 +7649,7 @@
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A914">
-        <v>489.41619634756552</v>
+        <v>500</v>
       </c>
       <c r="B914">
         <v>500</v>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A915">
-        <v>489.20821610263511</v>
+        <v>500</v>
       </c>
       <c r="B915">
         <v>500</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A916">
-        <v>488.90915162176884</v>
+        <v>500</v>
       </c>
       <c r="B916">
         <v>500</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A917">
-        <v>488.58199453749404</v>
+        <v>500</v>
       </c>
       <c r="B917">
         <v>500</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A918">
-        <v>488.3288734092452</v>
+        <v>500</v>
       </c>
       <c r="B918">
         <v>500</v>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A919">
-        <v>488.12442437526238</v>
+        <v>500</v>
       </c>
       <c r="B919">
         <v>500</v>
@@ -7697,7 +7697,7 @@
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A920">
-        <v>487.82988402228187</v>
+        <v>500</v>
       </c>
       <c r="B920">
         <v>500</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A921">
-        <v>487.67072620869266</v>
+        <v>500</v>
       </c>
       <c r="B921">
         <v>500</v>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A922">
-        <v>487.46991613247405</v>
+        <v>500</v>
       </c>
       <c r="B922">
         <v>500</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A923">
-        <v>487.15534645158596</v>
+        <v>500</v>
       </c>
       <c r="B923">
         <v>500</v>
@@ -7729,7 +7729,7 @@
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A924">
-        <v>486.78381025668807</v>
+        <v>500</v>
       </c>
       <c r="B924">
         <v>500</v>
@@ -7737,7 +7737,7 @@
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A925">
-        <v>486.27790858413886</v>
+        <v>500</v>
       </c>
       <c r="B925">
         <v>500</v>
@@ -7745,7 +7745,7 @@
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A926">
-        <v>485.72444105264896</v>
+        <v>500</v>
       </c>
       <c r="B926">
         <v>500</v>
@@ -7753,7 +7753,7 @@
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A927">
-        <v>485.20261574955538</v>
+        <v>500</v>
       </c>
       <c r="B927">
         <v>500</v>
@@ -7761,7 +7761,7 @@
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A928">
-        <v>484.73103952482904</v>
+        <v>500</v>
       </c>
       <c r="B928">
         <v>500</v>
@@ -7769,7 +7769,7 @@
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A929">
-        <v>484.17921340366502</v>
+        <v>500</v>
       </c>
       <c r="B929">
         <v>500</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A930">
-        <v>483.67250652555191</v>
+        <v>500</v>
       </c>
       <c r="B930">
         <v>500</v>
@@ -7785,7 +7785,7 @@
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A931">
-        <v>483.11609878551218</v>
+        <v>500</v>
       </c>
       <c r="B931">
         <v>500</v>
@@ -7793,7 +7793,7 @@
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A932">
-        <v>482.53410786251175</v>
+        <v>500</v>
       </c>
       <c r="B932">
         <v>500</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A933">
-        <v>481.92403110733289</v>
+        <v>500</v>
       </c>
       <c r="B933">
         <v>500</v>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A934">
-        <v>481.34192180159334</v>
+        <v>500</v>
       </c>
       <c r="B934">
         <v>500</v>
@@ -7817,7 +7817,7 @@
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A935">
-        <v>480.78930079760431</v>
+        <v>500</v>
       </c>
       <c r="B935">
         <v>500</v>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A936">
-        <v>480.27474376584195</v>
+        <v>500</v>
       </c>
       <c r="B936">
         <v>500</v>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A937">
-        <v>479.77359828708097</v>
+        <v>500</v>
       </c>
       <c r="B937">
         <v>500</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A938">
-        <v>479.39696342594084</v>
+        <v>500</v>
       </c>
       <c r="B938">
         <v>500</v>
@@ -7849,7 +7849,7 @@
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A939">
-        <v>478.97098909630319</v>
+        <v>500</v>
       </c>
       <c r="B939">
         <v>500</v>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A940">
-        <v>478.58681496333134</v>
+        <v>500</v>
       </c>
       <c r="B940">
         <v>500</v>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A941">
-        <v>478.24586030070708</v>
+        <v>500</v>
       </c>
       <c r="B941">
         <v>500</v>
@@ -7873,7 +7873,7 @@
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A942">
-        <v>477.92130385481892</v>
+        <v>500</v>
       </c>
       <c r="B942">
         <v>500</v>
@@ -7881,7 +7881,7 @@
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A943">
-        <v>477.51385913841722</v>
+        <v>500</v>
       </c>
       <c r="B943">
         <v>500</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A944">
-        <v>477.0463383906843</v>
+        <v>500</v>
       </c>
       <c r="B944">
         <v>500</v>
@@ -7897,7 +7897,7 @@
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A945">
-        <v>476.82450911666848</v>
+        <v>500</v>
       </c>
       <c r="B945">
         <v>500</v>
@@ -7905,7 +7905,7 @@
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A946">
-        <v>476.83607368221652</v>
+        <v>500</v>
       </c>
       <c r="B946">
         <v>500</v>
@@ -7913,7 +7913,7 @@
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A947">
-        <v>476.87627890537169</v>
+        <v>500</v>
       </c>
       <c r="B947">
         <v>500</v>
@@ -7921,7 +7921,7 @@
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A948">
-        <v>476.97773967462808</v>
+        <v>500</v>
       </c>
       <c r="B948">
         <v>500</v>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A949">
-        <v>477.1223262504011</v>
+        <v>500</v>
       </c>
       <c r="B949">
         <v>500</v>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A950">
-        <v>477.396956245502</v>
+        <v>500</v>
       </c>
       <c r="B950">
         <v>500</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A951">
-        <v>477.69570906471188</v>
+        <v>500</v>
       </c>
       <c r="B951">
         <v>500</v>
@@ -7953,7 +7953,7 @@
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A952">
-        <v>478.07391254774836</v>
+        <v>500</v>
       </c>
       <c r="B952">
         <v>500</v>
@@ -7961,7 +7961,7 @@
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A953">
-        <v>478.42052207377066</v>
+        <v>500</v>
       </c>
       <c r="B953">
         <v>500</v>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A954">
-        <v>478.61394626987823</v>
+        <v>500</v>
       </c>
       <c r="B954">
         <v>500</v>
@@ -7977,7 +7977,7 @@
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A955">
-        <v>478.89250444604448</v>
+        <v>500</v>
       </c>
       <c r="B955">
         <v>500</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A956">
-        <v>479.23420961349962</v>
+        <v>500</v>
       </c>
       <c r="B956">
         <v>500</v>
@@ -7993,7 +7993,7 @@
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A957">
-        <v>479.63296721322268</v>
+        <v>500</v>
       </c>
       <c r="B957">
         <v>500</v>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A958">
-        <v>480.00668277935381</v>
+        <v>500</v>
       </c>
       <c r="B958">
         <v>500</v>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A959">
-        <v>480.33307662898756</v>
+        <v>500</v>
       </c>
       <c r="B959">
         <v>500</v>
@@ -8017,7 +8017,7 @@
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A960">
-        <v>480.73620071265447</v>
+        <v>500</v>
       </c>
       <c r="B960">
         <v>500</v>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A961">
-        <v>481.23110388513811</v>
+        <v>500</v>
       </c>
       <c r="B961">
         <v>500</v>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A962">
-        <v>481.75921118273141</v>
+        <v>500</v>
       </c>
       <c r="B962">
         <v>500</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A963">
-        <v>482.36689977715167</v>
+        <v>500</v>
       </c>
       <c r="B963">
         <v>500</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A964">
-        <v>482.99845281446125</v>
+        <v>500</v>
       </c>
       <c r="B964">
         <v>500</v>
@@ -8057,7 +8057,7 @@
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A965">
-        <v>483.5485781922124</v>
+        <v>500</v>
       </c>
       <c r="B965">
         <v>500</v>
@@ -8065,7 +8065,7 @@
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A966">
-        <v>484.09967598152093</v>
+        <v>500</v>
       </c>
       <c r="B966">
         <v>500</v>
@@ -8073,7 +8073,7 @@
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A967">
-        <v>484.67825712855182</v>
+        <v>500</v>
       </c>
       <c r="B967">
         <v>500</v>
@@ -8081,7 +8081,7 @@
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A968">
-        <v>485.30572297605818</v>
+        <v>500</v>
       </c>
       <c r="B968">
         <v>500</v>
@@ -8089,7 +8089,7 @@
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A969">
-        <v>486.01210098079389</v>
+        <v>500</v>
       </c>
       <c r="B969">
         <v>500</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A970">
-        <v>486.82904567095483</v>
+        <v>500</v>
       </c>
       <c r="B970">
         <v>500</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A971">
-        <v>487.61710638353202</v>
+        <v>500</v>
       </c>
       <c r="B971">
         <v>500</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A972">
-        <v>488.43899347140547</v>
+        <v>500</v>
       </c>
       <c r="B972">
         <v>500</v>
@@ -8121,7 +8121,7 @@
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A973">
-        <v>489.25290437665353</v>
+        <v>500</v>
       </c>
       <c r="B973">
         <v>500</v>
@@ -8129,7 +8129,7 @@
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A974">
-        <v>490.17514101057498</v>
+        <v>500</v>
       </c>
       <c r="B974">
         <v>500</v>
@@ -8137,7 +8137,7 @@
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A975">
-        <v>490.96730217703811</v>
+        <v>500</v>
       </c>
       <c r="B975">
         <v>500</v>
@@ -8145,7 +8145,7 @@
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A976">
-        <v>491.84101247214329</v>
+        <v>500</v>
       </c>
       <c r="B976">
         <v>500</v>
@@ -8153,7 +8153,7 @@
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A977">
-        <v>492.835315577941</v>
+        <v>500</v>
       </c>
       <c r="B977">
         <v>500</v>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A978">
-        <v>493.79523246747397</v>
+        <v>500</v>
       </c>
       <c r="B978">
         <v>500</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A979">
-        <v>494.67401796004543</v>
+        <v>500</v>
       </c>
       <c r="B979">
         <v>500</v>
@@ -8177,7 +8177,7 @@
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A980">
-        <v>495.60241302562997</v>
+        <v>500</v>
       </c>
       <c r="B980">
         <v>500</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A981">
-        <v>496.58841485602193</v>
+        <v>500</v>
       </c>
       <c r="B981">
         <v>500</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A982">
-        <v>497.76741000695108</v>
+        <v>500</v>
       </c>
       <c r="B982">
         <v>500</v>
@@ -8201,7 +8201,7 @@
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A983">
-        <v>498.97014417165053</v>
+        <v>500</v>
       </c>
       <c r="B983">
         <v>500</v>
